--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -280,6 +280,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -724,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1036,10 +1039,10 @@
       </c>
       <c r="B34" s="9" t="n"/>
     </row>
-    <row r="35" ht="28" customHeight="1">
+    <row r="35" ht="56" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>6.  **ผู้ทดสอบกรอกเฉพาะช่องพื้นหลังสีเหลือง 7 ช่องนี้:** Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks</t>
+          <t>6.  **ผู้ทดสอบดูแลช่องพื้นหลังสีเหลือง 7 ช่องนี้:** Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks · ช่อง `Tester` กรอกชื่อไว้ล่วงหน้าแล้วตามแผนคนจาก actor map ก่อนเริ่มรอบ (ตัวหนังสือสีม่วงเหมือนช่องเนื้อหาเคสอื่น ๆ) ถ้าคนที่ลงมือทดสอบจริงไม่ตรงกับชื่อที่กรอกไว้ ให้แก้ชื่อในช่องนี้ให้ตรงกับคนที่ทำจริง · อีก 6 ช่องที่เหลือยังว่างอยู่ ให้ผู้ทดสอบกรอกเองระหว่างทดสอบตามปกติ</t>
         </is>
       </c>
       <c r="B35" s="9" t="n"/>
@@ -1071,7 +1074,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>10. **ข้อยกเว้นเดียวของกติกา “กรอกเฉพาะช่องสีเหลือง” คือคอลัมน์ `PIC`** ซึ่งเป็นช่องสีขาว และคนที่กรอกไม่ใช่ผู้ทดสอบ แต่เป็น **Test Lead** ที่กรอกชื่อผู้รับผิดชอบรายเคสไว้ **ก่อน** เริ่มรอบทดสอบ · ระหว่างทดสอบ ผู้ทดสอบไม่ต้องแตะคอลัมน์นี้</t>
+          <t>10. **ข้อยกเว้นเดียวของกติกา “กรอกเฉพาะช่องสีเหลือง” คือคอลัมน์ `PIC`** ซึ่งเป็นช่องสีขาว และคนที่กรอกไม่ใช่ผู้ทดสอบ แต่เป็น **Test Lead** ที่กรอกชื่อผู้รับผิดชอบรายเคสไว้ **ก่อน** เริ่มรอบทดสอบ (ใช้เมื่อ Test Lead ต้องการมอบหมายผู้รับผิดชอบเพิ่มเติม นอกเหนือจากชื่อที่กรอกไว้แล้วในช่อง `Tester`) · ระหว่างทดสอบ ผู้ทดสอบไม่ต้องแตะคอลัมน์นี้</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
@@ -1140,19 +1143,19 @@
       </c>
       <c r="B49" s="4" t="n"/>
     </row>
-    <row r="50" ht="27" customHeight="1">
+    <row r="50" ht="48" customHeight="1">
       <c r="A50" s="10" t="n"/>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>ช่องพื้นหลังสีเหลือง = ช่องที่ผู้ทดสอบกรอกระหว่างรอบทดสอบ (7 ช่อง: Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="27" customHeight="1">
+          <t>ช่องพื้นหลังสีเหลือง = ช่องที่ผู้ทดสอบดูแลระหว่างรอบทดสอบ (7 ช่อง: Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks) · ช่อง `Tester` มีชื่อกรอกไว้ล่วงหน้าแล้วตามแผนคน (ตัวหนังสือสีม่วง) ผู้ทดสอบแก้ไขได้ถ้าคนที่ทดสอบจริงเปลี่ยนไปจากแผน ส่วนอีก 6 ช่องยังว่าง กรอกเองระหว่างทดสอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
       <c r="A51" s="7" t="n"/>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>ช่อง `PIC` เป็นช่องสีขาว แต่เป็นข้อยกเว้นเดียวที่ต้องกรอก — Test Lead กรอกก่อนเริ่มรอบ ผู้ทดสอบไม่ต้องแตะ · ช่องสีขาวอื่นทั้งหมดคือเนื้อหาเคส ไม่ต้องแก้</t>
+          <t>ช่อง `PIC` เป็นช่องสีขาว แต่เป็นข้อยกเว้นเดียวที่ต้องกรอก — Test Lead กรอกก่อนเริ่มรอบ ผู้ทดสอบไม่ต้องแตะ (คนละหน้าที่กับช่อง `Tester`: `PIC` = ผู้รับผิดชอบที่ Test Lead มอบหมาย, `Tester` = คนที่ต้องลงมือทดสอบตามแผน) · ช่องสีขาวอื่นทั้งหมดคือเนื้อหาเคส ไม่ต้องแก้</t>
         </is>
       </c>
     </row>
@@ -1160,49 +1163,57 @@
       <c r="A52" s="7" t="n"/>
       <c r="B52" s="7" t="inlineStr">
         <is>
+          <t>รูปแบบ `ชื่อ(jakkarit)` ในช่อง `Tester` (พบที่ UAT-31 และช่วงหนึ่งของ UAT-43) แปลว่า **jakkaritw เป็นคนกดจริงบนเครื่อง** โดยสวมสิทธิ์ผ่านหน้า `/sit/impersonate` เป็นคนที่ชื่ออยู่หน้าวงเล็บ — ระบบบันทึกประวัติเป็นชื่อคนที่ถูกสวมสิทธิ์เท่านั้น ไม่มีคอลัมน์เก็บชื่อผู้กดจริง</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
           <t>คอลัมน์ `ลำดับการรัน` (Run Order) = ลำดับที่ต้องลงมือทำจริง 1 → 54 · คอลัมน์ `Wave` = ชื่อกลุ่มของเคส ใช้กรองดูเท่านั้น **ไม่ใช่ลำดับการทำ** · สองคอลัมน์นี้พิมพ์ด้วย **ตัวอักษรสีดำ ไม่ใช่สีม่วง** เพราะโปรแกรมคำนวณมาให้ ไม่ใช่ข้อความที่ AI ร่าง — **ห้ามแก้ทั้งสองคอลัมน์**</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1">
-      <c r="A53" s="11" t="n"/>
-      <c r="B53" s="7" t="inlineStr">
+    <row r="54" ht="16.5" customHeight="1">
+      <c r="A54" s="11" t="n"/>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Status = Pass  (ผลตรงตามที่คาดหวังทุกข้อ)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="27" customHeight="1">
-      <c r="A54" s="12" t="n"/>
-      <c r="B54" s="7" t="inlineStr">
+    <row r="55" ht="27" customHeight="1">
+      <c r="A55" s="12" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Status = Fail  (ผลไม่ตรงอย่างน้อย 1 ข้อ — ต้องเปิดแถวใน “4. Defects” และใส่เลข Defect ID)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="27" customHeight="1">
-      <c r="A55" s="13" t="n"/>
-      <c r="B55" s="7" t="inlineStr">
+    <row r="56" ht="27" customHeight="1">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Status = Blocked (ทดสอบไม่ได้ ติดเคสอื่นหรือข้อมูลยังไม่พร้อม) · N/A (ไม่เกี่ยวกับรอบนี้)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="27" customHeight="1">
-      <c r="A56" s="7" t="n"/>
-      <c r="B56" s="14" t="inlineStr">
+    <row r="57" ht="27" customHeight="1">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>ตัวหนังสือสีม่วง = ข้อความที่ AI ร่างไว้ ยังไม่ผ่านการตรวจจากคน — แก้ได้ถ้าไม่ตรงกับระบบจริง · ตัวหนังสือสีดำในคอลัมน์ `Wave` และ `ลำดับการรัน` = ค่าที่โปรแกรมคำนวณ ห้ามแก้</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Severity: Critical = ระบบใช้งานไม่ได้ / ข้อมูลผิดพลาดร้ายแรง  |  High = ฟังก์ชันหลักเสีย  |  Medium = มีทางเลี่ยง  |  Low = ปัญหาเล็กน้อย / UI  ·  ชุดค่านี้ใช้เหมือนกันทั้งแท็บ “2. Test Cases” และแท็บ “4. Defects” จึงยกค่าจากแถวเคสไปใส่แถว defect ได้ตรง ๆ ไม่ต้องแปลง (ค่า `-` มีเฉพาะแท็บ “2. Test Cases” ใช้เมื่อเคสนั้นไม่ Fail)</t>
         </is>
       </c>
-      <c r="B57" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -1220,7 +1231,6 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A32:B32"/>
@@ -1234,6 +1244,7 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
@@ -1481,8 +1492,12 @@
       <c r="O3" s="21" t="n"/>
       <c r="P3" s="22" t="n"/>
       <c r="Q3" s="22" t="n"/>
-      <c r="R3" s="21" t="n"/>
-      <c r="S3" s="23" t="n"/>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S3" s="24" t="n"/>
       <c r="T3" s="21" t="n"/>
     </row>
     <row r="4" ht="372" customHeight="1">
@@ -1565,8 +1580,12 @@
       <c r="O4" s="21" t="n"/>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="22" t="n"/>
-      <c r="R4" s="21" t="n"/>
-      <c r="S4" s="23" t="n"/>
+      <c r="R4" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S4" s="24" t="n"/>
       <c r="T4" s="21" t="n"/>
     </row>
     <row r="5" ht="288" customHeight="1">
@@ -1643,8 +1662,12 @@
       <c r="O5" s="21" t="n"/>
       <c r="P5" s="22" t="n"/>
       <c r="Q5" s="22" t="n"/>
-      <c r="R5" s="21" t="n"/>
-      <c r="S5" s="23" t="n"/>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>Laddawan</t>
+        </is>
+      </c>
+      <c r="S5" s="24" t="n"/>
       <c r="T5" s="21" t="n"/>
     </row>
     <row r="6" ht="156" customHeight="1">
@@ -1717,8 +1740,12 @@
       <c r="O6" s="21" t="n"/>
       <c r="P6" s="22" t="n"/>
       <c r="Q6" s="22" t="n"/>
-      <c r="R6" s="21" t="n"/>
-      <c r="S6" s="23" t="n"/>
+      <c r="R6" s="23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุชื่อในเคส (ต่อจากเคสก่อนหน้า น่าจะเป็น Pornthip)</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="n"/>
       <c r="T6" s="21" t="n"/>
     </row>
     <row r="7" ht="336" customHeight="1">
@@ -1802,8 +1829,12 @@
       <c r="O7" s="21" t="n"/>
       <c r="P7" s="22" t="n"/>
       <c r="Q7" s="22" t="n"/>
-      <c r="R7" s="21" t="n"/>
-      <c r="S7" s="23" t="n"/>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุชื่อในเคส (แนะนำ Pornthip เพราะฝ่ายเธอยังแก้ไขได้)</t>
+        </is>
+      </c>
+      <c r="S7" s="24" t="n"/>
       <c r="T7" s="21" t="n"/>
     </row>
     <row r="8" ht="204" customHeight="1">
@@ -1882,8 +1913,12 @@
       <c r="O8" s="21" t="n"/>
       <c r="P8" s="22" t="n"/>
       <c r="Q8" s="22" t="n"/>
-      <c r="R8" s="21" t="n"/>
-      <c r="S8" s="23" t="n"/>
+      <c r="R8" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S8" s="24" t="n"/>
       <c r="T8" s="21" t="n"/>
     </row>
     <row r="9" ht="240" customHeight="1">
@@ -1960,8 +1995,12 @@
       <c r="O9" s="21" t="n"/>
       <c r="P9" s="22" t="n"/>
       <c r="Q9" s="22" t="n"/>
-      <c r="R9" s="21" t="n"/>
-      <c r="S9" s="23" t="n"/>
+      <c r="R9" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S9" s="24" t="n"/>
       <c r="T9" s="21" t="n"/>
     </row>
     <row r="10" ht="228" customHeight="1">
@@ -2037,8 +2076,12 @@
       <c r="O10" s="21" t="n"/>
       <c r="P10" s="22" t="n"/>
       <c r="Q10" s="22" t="n"/>
-      <c r="R10" s="21" t="n"/>
-      <c r="S10" s="23" t="n"/>
+      <c r="R10" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S10" s="24" t="n"/>
       <c r="T10" s="21" t="n"/>
     </row>
     <row r="11" ht="216" customHeight="1">
@@ -2115,8 +2158,12 @@
       <c r="O11" s="21" t="n"/>
       <c r="P11" s="22" t="n"/>
       <c r="Q11" s="22" t="n"/>
-      <c r="R11" s="21" t="n"/>
-      <c r="S11" s="23" t="n"/>
+      <c r="R11" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S11" s="24" t="n"/>
       <c r="T11" s="21" t="n"/>
     </row>
     <row r="12" ht="204" customHeight="1">
@@ -2194,8 +2241,12 @@
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="22" t="n"/>
       <c r="Q12" s="22" t="n"/>
-      <c r="R12" s="21" t="n"/>
-      <c r="S12" s="23" t="n"/>
+      <c r="R12" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S12" s="24" t="n"/>
       <c r="T12" s="21" t="n"/>
     </row>
     <row r="13" ht="156" customHeight="1">
@@ -2268,8 +2319,12 @@
       <c r="O13" s="21" t="n"/>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="22" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="23" t="n"/>
+      <c r="R13" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S13" s="24" t="n"/>
       <c r="T13" s="21" t="n"/>
     </row>
     <row r="14" ht="620" customHeight="1">
@@ -2359,8 +2414,12 @@
       <c r="O14" s="21" t="n"/>
       <c r="P14" s="22" t="n"/>
       <c r="Q14" s="22" t="n"/>
-      <c r="R14" s="21" t="n"/>
-      <c r="S14" s="23" t="n"/>
+      <c r="R14" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S14" s="24" t="n"/>
       <c r="T14" s="21" t="n"/>
     </row>
     <row r="15" ht="204" customHeight="1">
@@ -2439,8 +2498,12 @@
       <c r="O15" s="21" t="n"/>
       <c r="P15" s="22" t="n"/>
       <c r="Q15" s="22" t="n"/>
-      <c r="R15" s="21" t="n"/>
-      <c r="S15" s="23" t="n"/>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S15" s="24" t="n"/>
       <c r="T15" s="21" t="n"/>
     </row>
     <row r="16" ht="240" customHeight="1">
@@ -2521,8 +2584,12 @@
       <c r="O16" s="21" t="n"/>
       <c r="P16" s="22" t="n"/>
       <c r="Q16" s="22" t="n"/>
-      <c r="R16" s="21" t="n"/>
-      <c r="S16" s="23" t="n"/>
+      <c r="R16" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S16" s="24" t="n"/>
       <c r="T16" s="21" t="n"/>
     </row>
     <row r="17" ht="204" customHeight="1">
@@ -2600,8 +2667,12 @@
       <c r="O17" s="21" t="n"/>
       <c r="P17" s="22" t="n"/>
       <c r="Q17" s="22" t="n"/>
-      <c r="R17" s="21" t="n"/>
-      <c r="S17" s="23" t="n"/>
+      <c r="R17" s="23" t="inlineStr">
+        <is>
+          <t>Nipaporn หรือ Waraporn</t>
+        </is>
+      </c>
+      <c r="S17" s="24" t="n"/>
       <c r="T17" s="21" t="n"/>
     </row>
     <row r="18" ht="216" customHeight="1">
@@ -2679,8 +2750,12 @@
       <c r="O18" s="21" t="n"/>
       <c r="P18" s="22" t="n"/>
       <c r="Q18" s="22" t="n"/>
-      <c r="R18" s="21" t="n"/>
-      <c r="S18" s="23" t="n"/>
+      <c r="R18" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S18" s="24" t="n"/>
       <c r="T18" s="21" t="n"/>
     </row>
     <row r="19" ht="180" customHeight="1">
@@ -2758,8 +2833,12 @@
       <c r="O19" s="21" t="n"/>
       <c r="P19" s="22" t="n"/>
       <c r="Q19" s="22" t="n"/>
-      <c r="R19" s="21" t="n"/>
-      <c r="S19" s="23" t="n"/>
+      <c r="R19" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S19" s="24" t="n"/>
       <c r="T19" s="21" t="n"/>
     </row>
     <row r="20" ht="288" customHeight="1">
@@ -2839,8 +2918,12 @@
       <c r="O20" s="21" t="n"/>
       <c r="P20" s="22" t="n"/>
       <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="21" t="n"/>
-      <c r="S20" s="23" t="n"/>
+      <c r="R20" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S20" s="24" t="n"/>
       <c r="T20" s="21" t="n"/>
     </row>
     <row r="21" ht="228" customHeight="1">
@@ -2916,8 +2999,12 @@
       <c r="O21" s="21" t="n"/>
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="22" t="n"/>
-      <c r="R21" s="21" t="n"/>
-      <c r="S21" s="23" t="n"/>
+      <c r="R21" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S21" s="24" t="n"/>
       <c r="T21" s="21" t="n"/>
     </row>
     <row r="22" ht="576" customHeight="1">
@@ -3000,8 +3087,12 @@
       <c r="O22" s="21" t="n"/>
       <c r="P22" s="22" t="n"/>
       <c r="Q22" s="22" t="n"/>
-      <c r="R22" s="21" t="n"/>
-      <c r="S22" s="23" t="n"/>
+      <c r="R22" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S22" s="24" t="n"/>
       <c r="T22" s="21" t="n"/>
     </row>
     <row r="23" ht="276" customHeight="1">
@@ -3081,8 +3172,12 @@
       <c r="O23" s="21" t="n"/>
       <c r="P23" s="22" t="n"/>
       <c r="Q23" s="22" t="n"/>
-      <c r="R23" s="21" t="n"/>
-      <c r="S23" s="23" t="n"/>
+      <c r="R23" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S23" s="24" t="n"/>
       <c r="T23" s="21" t="n"/>
     </row>
     <row r="24" ht="444" customHeight="1">
@@ -3165,8 +3260,12 @@
       <c r="O24" s="21" t="n"/>
       <c r="P24" s="22" t="n"/>
       <c r="Q24" s="22" t="n"/>
-      <c r="R24" s="21" t="n"/>
-      <c r="S24" s="23" t="n"/>
+      <c r="R24" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S24" s="24" t="n"/>
       <c r="T24" s="21" t="n"/>
     </row>
     <row r="25" ht="396" customHeight="1">
@@ -3245,8 +3344,12 @@
       <c r="O25" s="21" t="n"/>
       <c r="P25" s="22" t="n"/>
       <c r="Q25" s="22" t="n"/>
-      <c r="R25" s="21" t="n"/>
-      <c r="S25" s="23" t="n"/>
+      <c r="R25" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S25" s="24" t="n"/>
       <c r="T25" s="21" t="n"/>
     </row>
     <row r="26" ht="620" customHeight="1">
@@ -3334,8 +3437,12 @@
       <c r="O26" s="21" t="n"/>
       <c r="P26" s="22" t="n"/>
       <c r="Q26" s="22" t="n"/>
-      <c r="R26" s="21" t="n"/>
-      <c r="S26" s="23" t="n"/>
+      <c r="R26" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S26" s="24" t="n"/>
       <c r="T26" s="21" t="n"/>
     </row>
     <row r="27" ht="540" customHeight="1">
@@ -3414,8 +3521,12 @@
       <c r="O27" s="21" t="n"/>
       <c r="P27" s="22" t="n"/>
       <c r="Q27" s="22" t="n"/>
-      <c r="R27" s="21" t="n"/>
-      <c r="S27" s="23" t="n"/>
+      <c r="R27" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S27" s="24" t="n"/>
       <c r="T27" s="21" t="n"/>
     </row>
     <row r="28" ht="456" customHeight="1">
@@ -3494,8 +3605,12 @@
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="22" t="n"/>
       <c r="Q28" s="22" t="n"/>
-      <c r="R28" s="21" t="n"/>
-      <c r="S28" s="23" t="n"/>
+      <c r="R28" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S28" s="24" t="n"/>
       <c r="T28" s="21" t="n"/>
     </row>
     <row r="29" ht="620" customHeight="1">
@@ -3573,8 +3688,12 @@
       <c r="O29" s="21" t="n"/>
       <c r="P29" s="22" t="n"/>
       <c r="Q29" s="22" t="n"/>
-      <c r="R29" s="21" t="n"/>
-      <c r="S29" s="23" t="n"/>
+      <c r="R29" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S29" s="24" t="n"/>
       <c r="T29" s="21" t="n"/>
     </row>
     <row r="30" ht="492" customHeight="1">
@@ -3650,8 +3769,12 @@
       <c r="O30" s="21" t="n"/>
       <c r="P30" s="22" t="n"/>
       <c r="Q30" s="22" t="n"/>
-      <c r="R30" s="21" t="n"/>
-      <c r="S30" s="23" t="n"/>
+      <c r="R30" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S30" s="24" t="n"/>
       <c r="T30" s="21" t="n"/>
     </row>
     <row r="31" ht="216" customHeight="1">
@@ -3725,8 +3848,12 @@
       <c r="O31" s="21" t="n"/>
       <c r="P31" s="22" t="n"/>
       <c r="Q31" s="22" t="n"/>
-      <c r="R31" s="21" t="n"/>
-      <c r="S31" s="23" t="n"/>
+      <c r="R31" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S31" s="24" t="n"/>
       <c r="T31" s="21" t="n"/>
     </row>
     <row r="32" ht="300" customHeight="1">
@@ -3802,8 +3929,12 @@
       <c r="O32" s="21" t="n"/>
       <c r="P32" s="22" t="n"/>
       <c r="Q32" s="22" t="n"/>
-      <c r="R32" s="21" t="n"/>
-      <c r="S32" s="23" t="n"/>
+      <c r="R32" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S32" s="24" t="n"/>
       <c r="T32" s="21" t="n"/>
     </row>
     <row r="33" ht="492" customHeight="1">
@@ -3881,8 +4012,12 @@
       <c r="O33" s="21" t="n"/>
       <c r="P33" s="22" t="n"/>
       <c r="Q33" s="22" t="n"/>
-      <c r="R33" s="21" t="n"/>
-      <c r="S33" s="23" t="n"/>
+      <c r="R33" s="23" t="inlineStr">
+        <is>
+          <t>Arthid(jakkarit)</t>
+        </is>
+      </c>
+      <c r="S33" s="24" t="n"/>
       <c r="T33" s="21" t="n"/>
     </row>
     <row r="34" ht="312" customHeight="1">
@@ -3958,8 +4093,12 @@
       <c r="O34" s="21" t="n"/>
       <c r="P34" s="22" t="n"/>
       <c r="Q34" s="22" t="n"/>
-      <c r="R34" s="21" t="n"/>
-      <c r="S34" s="23" t="n"/>
+      <c r="R34" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S34" s="24" t="n"/>
       <c r="T34" s="21" t="n"/>
     </row>
     <row r="35" ht="180" customHeight="1">
@@ -4032,8 +4171,12 @@
       <c r="O35" s="21" t="n"/>
       <c r="P35" s="22" t="n"/>
       <c r="Q35" s="22" t="n"/>
-      <c r="R35" s="21" t="n"/>
-      <c r="S35" s="23" t="n"/>
+      <c r="R35" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip → Laddawan</t>
+        </is>
+      </c>
+      <c r="S35" s="24" t="n"/>
       <c r="T35" s="21" t="n"/>
     </row>
     <row r="36" ht="420" customHeight="1">
@@ -4109,8 +4252,12 @@
       <c r="O36" s="21" t="n"/>
       <c r="P36" s="22" t="n"/>
       <c r="Q36" s="22" t="n"/>
-      <c r="R36" s="21" t="n"/>
-      <c r="S36" s="23" t="n"/>
+      <c r="R36" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S36" s="24" t="n"/>
       <c r="T36" s="21" t="n"/>
     </row>
     <row r="37" ht="228" customHeight="1">
@@ -4182,8 +4329,12 @@
       <c r="O37" s="21" t="n"/>
       <c r="P37" s="22" t="n"/>
       <c r="Q37" s="22" t="n"/>
-      <c r="R37" s="21" t="n"/>
-      <c r="S37" s="23" t="n"/>
+      <c r="R37" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S37" s="24" t="n"/>
       <c r="T37" s="21" t="n"/>
     </row>
     <row r="38" ht="620" customHeight="1">
@@ -4265,8 +4416,12 @@
       <c r="O38" s="21" t="n"/>
       <c r="P38" s="22" t="n"/>
       <c r="Q38" s="22" t="n"/>
-      <c r="R38" s="21" t="n"/>
-      <c r="S38" s="23" t="n"/>
+      <c r="R38" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip → Laddawan (ไม่บังคับ)</t>
+        </is>
+      </c>
+      <c r="S38" s="24" t="n"/>
       <c r="T38" s="21" t="n"/>
     </row>
     <row r="39" ht="432" customHeight="1">
@@ -4343,8 +4498,12 @@
       <c r="O39" s="21" t="n"/>
       <c r="P39" s="22" t="n"/>
       <c r="Q39" s="22" t="n"/>
-      <c r="R39" s="21" t="n"/>
-      <c r="S39" s="23" t="n"/>
+      <c r="R39" s="23" t="inlineStr">
+        <is>
+          <t>Laddawan</t>
+        </is>
+      </c>
+      <c r="S39" s="24" t="n"/>
       <c r="T39" s="21" t="n"/>
     </row>
     <row r="40" ht="264" customHeight="1">
@@ -4422,8 +4581,12 @@
       <c r="O40" s="21" t="n"/>
       <c r="P40" s="22" t="n"/>
       <c r="Q40" s="22" t="n"/>
-      <c r="R40" s="21" t="n"/>
-      <c r="S40" s="23" t="n"/>
+      <c r="R40" s="23" t="inlineStr">
+        <is>
+          <t>Laddawan</t>
+        </is>
+      </c>
+      <c r="S40" s="24" t="n"/>
       <c r="T40" s="21" t="n"/>
     </row>
     <row r="41" ht="192" customHeight="1">
@@ -4499,8 +4662,12 @@
       <c r="O41" s="21" t="n"/>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="22" t="n"/>
-      <c r="R41" s="21" t="n"/>
-      <c r="S41" s="23" t="n"/>
+      <c r="R41" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S41" s="24" t="n"/>
       <c r="T41" s="21" t="n"/>
     </row>
     <row r="42" ht="552" customHeight="1">
@@ -4579,8 +4746,12 @@
       <c r="O42" s="21" t="n"/>
       <c r="P42" s="22" t="n"/>
       <c r="Q42" s="22" t="n"/>
-      <c r="R42" s="21" t="n"/>
-      <c r="S42" s="23" t="n"/>
+      <c r="R42" s="23" t="inlineStr">
+        <is>
+          <t>Laddawan → Nipaporn → Waraporn → Pornthip</t>
+        </is>
+      </c>
+      <c r="S42" s="24" t="n"/>
       <c r="T42" s="21" t="n"/>
     </row>
     <row r="43" ht="216" customHeight="1">
@@ -4655,8 +4826,12 @@
       <c r="O43" s="21" t="n"/>
       <c r="P43" s="22" t="n"/>
       <c r="Q43" s="22" t="n"/>
-      <c r="R43" s="21" t="n"/>
-      <c r="S43" s="23" t="n"/>
+      <c r="R43" s="23" t="inlineStr">
+        <is>
+          <t>Nipaporn หรือ Waraporn → Pornthip</t>
+        </is>
+      </c>
+      <c r="S43" s="24" t="n"/>
       <c r="T43" s="21" t="n"/>
     </row>
     <row r="44" ht="324" customHeight="1">
@@ -4731,8 +4906,12 @@
       <c r="O44" s="21" t="n"/>
       <c r="P44" s="22" t="n"/>
       <c r="Q44" s="22" t="n"/>
-      <c r="R44" s="21" t="n"/>
-      <c r="S44" s="23" t="n"/>
+      <c r="R44" s="23" t="inlineStr">
+        <is>
+          <t>Waraporn → Laddawan</t>
+        </is>
+      </c>
+      <c r="S44" s="24" t="n"/>
       <c r="T44" s="21" t="n"/>
     </row>
     <row r="45" ht="620" customHeight="1">
@@ -4820,8 +4999,12 @@
       <c r="O45" s="21" t="n"/>
       <c r="P45" s="22" t="n"/>
       <c r="Q45" s="22" t="n"/>
-      <c r="R45" s="21" t="n"/>
-      <c r="S45" s="23" t="n"/>
+      <c r="R45" s="23" t="inlineStr">
+        <is>
+          <t>Laddawan → Nipaporn → Suchanya(jakkarit) (ไม่บังคับ)</t>
+        </is>
+      </c>
+      <c r="S45" s="24" t="n"/>
       <c r="T45" s="21" t="n"/>
     </row>
     <row r="46" ht="620" customHeight="1">
@@ -4902,8 +5085,12 @@
       <c r="O46" s="21" t="n"/>
       <c r="P46" s="22" t="n"/>
       <c r="Q46" s="22" t="n"/>
-      <c r="R46" s="21" t="n"/>
-      <c r="S46" s="23" t="n"/>
+      <c r="R46" s="23" t="inlineStr">
+        <is>
+          <t>Nipaporn หรือ Waraporn → Waraporn (เจาะจง) → Nipaporn (เจาะจง)</t>
+        </is>
+      </c>
+      <c r="S46" s="24" t="n"/>
       <c r="T46" s="21" t="n"/>
     </row>
     <row r="47" ht="372" customHeight="1">
@@ -4980,8 +5167,12 @@
       <c r="O47" s="21" t="n"/>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="22" t="n"/>
-      <c r="R47" s="21" t="n"/>
-      <c r="S47" s="23" t="n"/>
+      <c r="R47" s="23" t="inlineStr">
+        <is>
+          <t>Nipaporn หรือ Waraporn</t>
+        </is>
+      </c>
+      <c r="S47" s="24" t="n"/>
       <c r="T47" s="21" t="n"/>
     </row>
     <row r="48" ht="348" customHeight="1">
@@ -5052,8 +5243,12 @@
       <c r="O48" s="21" t="n"/>
       <c r="P48" s="22" t="n"/>
       <c r="Q48" s="22" t="n"/>
-      <c r="R48" s="21" t="n"/>
-      <c r="S48" s="23" t="n"/>
+      <c r="R48" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip → Laddawan</t>
+        </is>
+      </c>
+      <c r="S48" s="24" t="n"/>
       <c r="T48" s="21" t="n"/>
     </row>
     <row r="49" ht="324" customHeight="1">
@@ -5130,8 +5325,12 @@
       <c r="O49" s="21" t="n"/>
       <c r="P49" s="22" t="n"/>
       <c r="Q49" s="22" t="n"/>
-      <c r="R49" s="21" t="n"/>
-      <c r="S49" s="23" t="n"/>
+      <c r="R49" s="23" t="inlineStr">
+        <is>
+          <t>Laddawan → Nipaporn → Waraporn → Pornthip</t>
+        </is>
+      </c>
+      <c r="S49" s="24" t="n"/>
       <c r="T49" s="21" t="n"/>
     </row>
     <row r="50" ht="372" customHeight="1">
@@ -5202,8 +5401,12 @@
       <c r="O50" s="21" t="n"/>
       <c r="P50" s="22" t="n"/>
       <c r="Q50" s="22" t="n"/>
-      <c r="R50" s="21" t="n"/>
-      <c r="S50" s="23" t="n"/>
+      <c r="R50" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S50" s="24" t="n"/>
       <c r="T50" s="21" t="n"/>
     </row>
     <row r="51" ht="408" customHeight="1">
@@ -5287,8 +5490,12 @@
       <c r="O51" s="21" t="n"/>
       <c r="P51" s="22" t="n"/>
       <c r="Q51" s="22" t="n"/>
-      <c r="R51" s="21" t="n"/>
-      <c r="S51" s="23" t="n"/>
+      <c r="R51" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S51" s="24" t="n"/>
       <c r="T51" s="21" t="n"/>
     </row>
     <row r="52" ht="288" customHeight="1">
@@ -5359,8 +5566,12 @@
       <c r="O52" s="21" t="n"/>
       <c r="P52" s="22" t="n"/>
       <c r="Q52" s="22" t="n"/>
-      <c r="R52" s="21" t="n"/>
-      <c r="S52" s="23" t="n"/>
+      <c r="R52" s="23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุชื่อในเคส (ต้องมีคนเปิดทั้งจอ+อีเมลเทียบกัน — สันนิษฐาน Pornthip)</t>
+        </is>
+      </c>
+      <c r="S52" s="24" t="n"/>
       <c r="T52" s="21" t="n"/>
     </row>
     <row r="53" ht="564" customHeight="1">
@@ -5442,8 +5653,12 @@
       <c r="O53" s="21" t="n"/>
       <c r="P53" s="22" t="n"/>
       <c r="Q53" s="22" t="n"/>
-      <c r="R53" s="21" t="n"/>
-      <c r="S53" s="23" t="n"/>
+      <c r="R53" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip → Laddawan</t>
+        </is>
+      </c>
+      <c r="S53" s="24" t="n"/>
       <c r="T53" s="21" t="n"/>
     </row>
     <row r="54" ht="588" customHeight="1">
@@ -5518,8 +5733,12 @@
       <c r="O54" s="21" t="n"/>
       <c r="P54" s="22" t="n"/>
       <c r="Q54" s="22" t="n"/>
-      <c r="R54" s="21" t="n"/>
-      <c r="S54" s="23" t="n"/>
+      <c r="R54" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S54" s="24" t="n"/>
       <c r="T54" s="21" t="n"/>
     </row>
     <row r="55" ht="324" customHeight="1">
@@ -5597,8 +5816,12 @@
       <c r="O55" s="21" t="n"/>
       <c r="P55" s="22" t="n"/>
       <c r="Q55" s="22" t="n"/>
-      <c r="R55" s="21" t="n"/>
-      <c r="S55" s="23" t="n"/>
+      <c r="R55" s="23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุชื่อในเคส (ต้องเป็น Filler ของ Cost Center นั้น = Pornthip)</t>
+        </is>
+      </c>
+      <c r="S55" s="24" t="n"/>
       <c r="T55" s="21" t="n"/>
     </row>
     <row r="56" ht="420" customHeight="1">
@@ -5675,8 +5898,12 @@
       <c r="O56" s="21" t="n"/>
       <c r="P56" s="22" t="n"/>
       <c r="Q56" s="22" t="n"/>
-      <c r="R56" s="21" t="n"/>
-      <c r="S56" s="23" t="n"/>
+      <c r="R56" s="23" t="inlineStr">
+        <is>
+          <t>Pornthip</t>
+        </is>
+      </c>
+      <c r="S56" s="24" t="n"/>
       <c r="T56" s="21" t="n"/>
     </row>
   </sheetData>
@@ -5730,7 +5957,7 @@
   </cols>
   <sheetData>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>UAT Test Execution — Summary  ·  Round 1  ·  FY2027</t>
         </is>
@@ -5751,7 +5978,7 @@
       <c r="P2" s="2" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>สรุปผลอัตโนมัติจากแท็บ “2. Test Cases” (ไม่ต้องกรอกเอง) · ทุกสูตรนับช่วงแถวจริง 3–56</t>
         </is>
@@ -5772,112 +5999,112 @@
       <c r="P3" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="28" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Total test cases</t>
         </is>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>COUNTA('2. Test Cases'!$D$3:$D$56)</f>
         <v/>
       </c>
-      <c r="D6" s="29" t="n"/>
-      <c r="E6" s="29" t="n"/>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="30" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="31" t="n"/>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="33" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"Blocked")</f>
         <v/>
       </c>
-      <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Not Run (ยังไม่ได้ทดสอบ)</t>
         </is>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="38">
         <f>C6-C7-C8-C9-C11</f>
         <v/>
       </c>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="37" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
-      <c r="B11" s="36" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="38">
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"N/A")</f>
         <v/>
       </c>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="38" t="n"/>
     </row>
     <row r="12" ht="24.75" customHeight="1">
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Pass Rate (Pass / Executed)</t>
         </is>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="40">
         <f>IFERROR(COUNTIF('2. Test Cases'!$O$3:$O$56,"Pass")/(COUNTIF('2. Test Cases'!$O$3:$O$56,"Pass")+COUNTIF('2. Test Cases'!$O$3:$O$56,"Fail")+COUNTIF('2. Test Cases'!$O$3:$O$56,"Blocked")),"-")</f>
         <v/>
       </c>
-      <c r="D12" s="40" t="n"/>
-      <c r="E12" s="40" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Module</t>
         </is>
@@ -5885,7 +6112,7 @@
       <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
-      <c r="G14" s="41" t="inlineStr">
+      <c r="G14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Wave</t>
         </is>
@@ -5894,7 +6121,7 @@
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
-      <c r="M14" s="41" t="inlineStr">
+      <c r="M14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Department</t>
         </is>
@@ -5904,524 +6131,524 @@
       <c r="P14" s="4" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="E15" s="27" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="G15" s="27" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t>Wave</t>
         </is>
       </c>
-      <c r="H15" s="27" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>ชื่อระลอก</t>
         </is>
       </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J15" s="27" t="inlineStr">
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K15" s="27" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="M15" s="27" t="inlineStr">
+      <c r="M15" s="28" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="N15" s="27" t="inlineStr">
+      <c r="N15" s="28" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="O15" s="27" t="inlineStr">
+      <c r="O15" s="28" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="P15" s="27" t="inlineStr">
+      <c r="P15" s="28" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="42" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>Login / Authentication</t>
         </is>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Login / Authentication")</f>
         <v/>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Login / Authentication",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Login / Authentication",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G16" s="42" t="inlineStr">
+      <c r="G16" s="43" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="H16" s="42" t="inlineStr">
+      <c r="H16" s="43" t="inlineStr">
         <is>
           <t>เข้าระบบและสิทธิ์ที่มองเห็น</t>
         </is>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W1")</f>
         <v/>
       </c>
-      <c r="J16" s="44">
+      <c r="J16" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W1",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K16" s="45">
+      <c r="K16" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W1",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="M16" s="42" t="inlineStr">
+      <c r="M16" s="43" t="inlineStr">
         <is>
           <t>Data &amp; Analytic</t>
         </is>
       </c>
-      <c r="N16" s="43">
+      <c r="N16" s="44">
         <f>COUNTIF('2. Test Cases'!$F$3:$F$56,"Data &amp; Analytic")</f>
         <v/>
       </c>
-      <c r="O16" s="44">
+      <c r="O16" s="45">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"Data &amp; Analytic",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="P16" s="45">
+      <c r="P16" s="46">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"Data &amp; Analytic",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>Budget Entry (Filler)</t>
         </is>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Budget Entry (Filler)")</f>
         <v/>
       </c>
-      <c r="D17" s="44">
+      <c r="D17" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Budget Entry (Filler)",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Budget Entry (Filler)",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G17" s="42" t="inlineStr">
+      <c r="G17" s="43" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="H17" s="42" t="inlineStr">
+      <c r="H17" s="43" t="inlineStr">
         <is>
           <t>กรอกงบในตารางหลัก</t>
         </is>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W2")</f>
         <v/>
       </c>
-      <c r="J17" s="44">
+      <c r="J17" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W2",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W2",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="M17" s="42" t="inlineStr">
+      <c r="M17" s="43" t="inlineStr">
         <is>
           <t>Solution Delivery</t>
         </is>
       </c>
-      <c r="N17" s="43">
+      <c r="N17" s="44">
         <f>COUNTIF('2. Test Cases'!$F$3:$F$56,"Solution Delivery")</f>
         <v/>
       </c>
-      <c r="O17" s="44">
+      <c r="O17" s="45">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"Solution Delivery",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="P17" s="45">
+      <c r="P17" s="46">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"Solution Delivery",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="42" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>Special GL Subform</t>
         </is>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Special GL Subform")</f>
         <v/>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Special GL Subform",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Special GL Subform",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G18" s="42" t="inlineStr">
+      <c r="G18" s="43" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="H18" s="42" t="inlineStr">
+      <c r="H18" s="43" t="inlineStr">
         <is>
           <t>ฟอร์มย่อยและทริปเดินทาง</t>
         </is>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W3")</f>
         <v/>
       </c>
-      <c r="J18" s="44">
+      <c r="J18" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W3",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K18" s="45">
+      <c r="K18" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W3",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="M18" s="42" t="inlineStr">
+      <c r="M18" s="43" t="inlineStr">
         <is>
           <t>ทั้งสองฝ่าย</t>
         </is>
       </c>
-      <c r="N18" s="43">
+      <c r="N18" s="44">
         <f>COUNTIF('2. Test Cases'!$F$3:$F$56,"ทั้งสองฝ่าย")</f>
         <v/>
       </c>
-      <c r="O18" s="44">
+      <c r="O18" s="45">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"ทั้งสองฝ่าย",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="P18" s="45">
+      <c r="P18" s="46">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"ทั้งสองฝ่าย",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="42" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>Attachments</t>
         </is>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Attachments")</f>
         <v/>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Attachments",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Attachments",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G19" s="42" t="inlineStr">
+      <c r="G19" s="43" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="H19" s="42" t="inlineStr">
+      <c r="H19" s="43" t="inlineStr">
         <is>
           <t>แนบเอกสาร</t>
         </is>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W4")</f>
         <v/>
       </c>
-      <c r="J19" s="44">
+      <c r="J19" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W4",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K19" s="45">
+      <c r="K19" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W4",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="M19" s="42" t="inlineStr">
+      <c r="M19" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N19" s="43">
+      <c r="N19" s="44">
         <f>COUNTIF('2. Test Cases'!$F$3:$F$56,"-")</f>
         <v/>
       </c>
-      <c r="O19" s="44">
+      <c r="O19" s="45">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"-",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="P19" s="45">
+      <c r="P19" s="46">
         <f>COUNTIFS('2. Test Cases'!$F$3:$F$56,"-",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="B20" s="42" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Submission / Workflow</t>
         </is>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Submission / Workflow")</f>
         <v/>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Submission / Workflow",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Submission / Workflow",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="G20" s="43" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="H20" s="42" t="inlineStr">
+      <c r="H20" s="43" t="inlineStr">
         <is>
           <t>ส่งขออนุมัติ</t>
         </is>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W5")</f>
         <v/>
       </c>
-      <c r="J20" s="44">
+      <c r="J20" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W5",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K20" s="45">
+      <c r="K20" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W5",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="M20" s="38" t="inlineStr">
+      <c r="M20" s="39" t="inlineStr">
         <is>
           <t>รวม / Total</t>
         </is>
       </c>
-      <c r="N20" s="46">
+      <c r="N20" s="47">
         <f>SUM(N16:N19)</f>
         <v/>
       </c>
-      <c r="O20" s="46">
+      <c r="O20" s="47">
         <f>SUM(O16:O19)</f>
         <v/>
       </c>
-      <c r="P20" s="46">
+      <c r="P20" s="47">
         <f>SUM(P16:P19)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>Approval</t>
         </is>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Approval")</f>
         <v/>
       </c>
-      <c r="D21" s="44">
+      <c r="D21" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Approval",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Approval",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G21" s="42" t="inlineStr">
+      <c r="G21" s="43" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="H21" s="42" t="inlineStr">
+      <c r="H21" s="43" t="inlineStr">
         <is>
           <t>อนุมัติ 3 ขั้น</t>
         </is>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W6")</f>
         <v/>
       </c>
-      <c r="J21" s="44">
+      <c r="J21" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W6",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W6",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="42" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>Email Alert / Notification</t>
         </is>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Email Alert / Notification")</f>
         <v/>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Email Alert / Notification",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Email Alert / Notification",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G22" s="42" t="inlineStr">
+      <c r="G22" s="43" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="H22" s="42" t="inlineStr">
+      <c r="H22" s="43" t="inlineStr">
         <is>
           <t>อีเมลแจ้งเตือน</t>
         </is>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W7")</f>
         <v/>
       </c>
-      <c r="J22" s="44">
+      <c r="J22" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W7",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K22" s="45">
+      <c r="K22" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W7",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="42" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>Business Rules &amp; UI</t>
         </is>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="44">
         <f>COUNTIF('2. Test Cases'!$E$3:$E$56,"Business Rules &amp; UI")</f>
         <v/>
       </c>
-      <c r="D23" s="44">
+      <c r="D23" s="45">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Business Rules &amp; UI",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="46">
         <f>COUNTIFS('2. Test Cases'!$E$3:$E$56,"Business Rules &amp; UI",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="G23" s="42" t="inlineStr">
+      <c r="G23" s="43" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="H23" s="42" t="inlineStr">
+      <c r="H23" s="43" t="inlineStr">
         <is>
           <t>หน้าตาและกติกาที่ต้องยอมรับ</t>
         </is>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="44">
         <f>COUNTIF('2. Test Cases'!$A$3:$A$56,"W8")</f>
         <v/>
       </c>
-      <c r="J23" s="44">
+      <c r="J23" s="45">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W8",'2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="K23" s="45">
+      <c r="K23" s="46">
         <f>COUNTIFS('2. Test Cases'!$A$3:$A$56,"W8",'2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>รวม / Total</t>
         </is>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="47">
         <f>SUM(C16:C23)</f>
         <v/>
       </c>
-      <c r="D24" s="46">
+      <c r="D24" s="47">
         <f>SUM(D16:D23)</f>
         <v/>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="47">
         <f>SUM(E16:E23)</f>
         <v/>
       </c>
-      <c r="G24" s="38" t="inlineStr">
+      <c r="G24" s="39" t="inlineStr">
         <is>
           <t>รวม / Total</t>
         </is>
       </c>
-      <c r="H24" s="38" t="n"/>
-      <c r="I24" s="46">
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="47">
         <f>SUM(I16:I23)</f>
         <v/>
       </c>
-      <c r="J24" s="46">
+      <c r="J24" s="47">
         <f>SUM(J16:J23)</f>
         <v/>
       </c>
-      <c r="K24" s="46">
+      <c r="K24" s="47">
         <f>SUM(K16:K23)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="B26" s="47" t="inlineStr">
+      <c r="B26" s="48" t="inlineStr">
         <is>
           <t>หมายเหตุ: ตัวเลขอัปเดตอัตโนมัติเมื่อกรอกคอลัมน์ Status ในแท็บ “2. Test Cases” · ช่วงข้อมูลจริง = แถวที่ 3 ถึง 56 · ไฟล์นี้ไม่มีแถวตัวอย่าง (ไม่มี TC-EX) · ช่อง Total ของทั้ง 3 ตารางต้องเท่ากับ Total test cases ด้านบน · แถว Not Run คำนวณจาก “Total ลบด้วย Pass + Fail + Blocked + N/A” จึงนับช่อง Status ที่ยังว่างให้เป็น Not Run โดยอัตโนมัติ (ไม่ต้องพิมพ์คำว่า Not Run เอง) และทำให้ห้าแถวบนรวมกันได้เท่ากับ Total เสมอ</t>
         </is>
@@ -6583,11 +6810,11 @@
       <c r="D3" s="21" t="n"/>
       <c r="E3" s="22" t="n"/>
       <c r="F3" s="21" t="n"/>
-      <c r="G3" s="23" t="n"/>
+      <c r="G3" s="24" t="n"/>
       <c r="H3" s="21" t="n"/>
       <c r="I3" s="22" t="n"/>
       <c r="J3" s="21" t="n"/>
-      <c r="K3" s="23" t="n"/>
+      <c r="K3" s="24" t="n"/>
       <c r="L3" s="22" t="n"/>
       <c r="M3" s="21" t="n"/>
     </row>
@@ -6602,11 +6829,11 @@
       <c r="D4" s="21" t="n"/>
       <c r="E4" s="22" t="n"/>
       <c r="F4" s="21" t="n"/>
-      <c r="G4" s="23" t="n"/>
+      <c r="G4" s="24" t="n"/>
       <c r="H4" s="21" t="n"/>
       <c r="I4" s="22" t="n"/>
       <c r="J4" s="21" t="n"/>
-      <c r="K4" s="23" t="n"/>
+      <c r="K4" s="24" t="n"/>
       <c r="L4" s="22" t="n"/>
       <c r="M4" s="21" t="n"/>
     </row>
@@ -6621,11 +6848,11 @@
       <c r="D5" s="21" t="n"/>
       <c r="E5" s="22" t="n"/>
       <c r="F5" s="21" t="n"/>
-      <c r="G5" s="23" t="n"/>
+      <c r="G5" s="24" t="n"/>
       <c r="H5" s="21" t="n"/>
       <c r="I5" s="22" t="n"/>
       <c r="J5" s="21" t="n"/>
-      <c r="K5" s="23" t="n"/>
+      <c r="K5" s="24" t="n"/>
       <c r="L5" s="22" t="n"/>
       <c r="M5" s="21" t="n"/>
     </row>
@@ -6640,11 +6867,11 @@
       <c r="D6" s="21" t="n"/>
       <c r="E6" s="22" t="n"/>
       <c r="F6" s="21" t="n"/>
-      <c r="G6" s="23" t="n"/>
+      <c r="G6" s="24" t="n"/>
       <c r="H6" s="21" t="n"/>
       <c r="I6" s="22" t="n"/>
       <c r="J6" s="21" t="n"/>
-      <c r="K6" s="23" t="n"/>
+      <c r="K6" s="24" t="n"/>
       <c r="L6" s="22" t="n"/>
       <c r="M6" s="21" t="n"/>
     </row>
@@ -6659,11 +6886,11 @@
       <c r="D7" s="21" t="n"/>
       <c r="E7" s="22" t="n"/>
       <c r="F7" s="21" t="n"/>
-      <c r="G7" s="23" t="n"/>
+      <c r="G7" s="24" t="n"/>
       <c r="H7" s="21" t="n"/>
       <c r="I7" s="22" t="n"/>
       <c r="J7" s="21" t="n"/>
-      <c r="K7" s="23" t="n"/>
+      <c r="K7" s="24" t="n"/>
       <c r="L7" s="22" t="n"/>
       <c r="M7" s="21" t="n"/>
     </row>
@@ -6678,11 +6905,11 @@
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="n"/>
       <c r="F8" s="21" t="n"/>
-      <c r="G8" s="23" t="n"/>
+      <c r="G8" s="24" t="n"/>
       <c r="H8" s="21" t="n"/>
       <c r="I8" s="22" t="n"/>
       <c r="J8" s="21" t="n"/>
-      <c r="K8" s="23" t="n"/>
+      <c r="K8" s="24" t="n"/>
       <c r="L8" s="22" t="n"/>
       <c r="M8" s="21" t="n"/>
     </row>
@@ -6697,11 +6924,11 @@
       <c r="D9" s="21" t="n"/>
       <c r="E9" s="22" t="n"/>
       <c r="F9" s="21" t="n"/>
-      <c r="G9" s="23" t="n"/>
+      <c r="G9" s="24" t="n"/>
       <c r="H9" s="21" t="n"/>
       <c r="I9" s="22" t="n"/>
       <c r="J9" s="21" t="n"/>
-      <c r="K9" s="23" t="n"/>
+      <c r="K9" s="24" t="n"/>
       <c r="L9" s="22" t="n"/>
       <c r="M9" s="21" t="n"/>
     </row>
@@ -6716,11 +6943,11 @@
       <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="21" t="n"/>
-      <c r="G10" s="23" t="n"/>
+      <c r="G10" s="24" t="n"/>
       <c r="H10" s="21" t="n"/>
       <c r="I10" s="22" t="n"/>
       <c r="J10" s="21" t="n"/>
-      <c r="K10" s="23" t="n"/>
+      <c r="K10" s="24" t="n"/>
       <c r="L10" s="22" t="n"/>
       <c r="M10" s="21" t="n"/>
     </row>
@@ -6735,11 +6962,11 @@
       <c r="D11" s="21" t="n"/>
       <c r="E11" s="22" t="n"/>
       <c r="F11" s="21" t="n"/>
-      <c r="G11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
       <c r="H11" s="21" t="n"/>
       <c r="I11" s="22" t="n"/>
       <c r="J11" s="21" t="n"/>
-      <c r="K11" s="23" t="n"/>
+      <c r="K11" s="24" t="n"/>
       <c r="L11" s="22" t="n"/>
       <c r="M11" s="21" t="n"/>
     </row>
@@ -6754,11 +6981,11 @@
       <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="n"/>
       <c r="F12" s="21" t="n"/>
-      <c r="G12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
       <c r="H12" s="21" t="n"/>
       <c r="I12" s="22" t="n"/>
       <c r="J12" s="21" t="n"/>
-      <c r="K12" s="23" t="n"/>
+      <c r="K12" s="24" t="n"/>
       <c r="L12" s="22" t="n"/>
       <c r="M12" s="21" t="n"/>
     </row>
@@ -6773,11 +7000,11 @@
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="n"/>
       <c r="F13" s="21" t="n"/>
-      <c r="G13" s="23" t="n"/>
+      <c r="G13" s="24" t="n"/>
       <c r="H13" s="21" t="n"/>
       <c r="I13" s="22" t="n"/>
       <c r="J13" s="21" t="n"/>
-      <c r="K13" s="23" t="n"/>
+      <c r="K13" s="24" t="n"/>
       <c r="L13" s="22" t="n"/>
       <c r="M13" s="21" t="n"/>
     </row>
@@ -6792,11 +7019,11 @@
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="n"/>
       <c r="F14" s="21" t="n"/>
-      <c r="G14" s="23" t="n"/>
+      <c r="G14" s="24" t="n"/>
       <c r="H14" s="21" t="n"/>
       <c r="I14" s="22" t="n"/>
       <c r="J14" s="21" t="n"/>
-      <c r="K14" s="23" t="n"/>
+      <c r="K14" s="24" t="n"/>
       <c r="L14" s="22" t="n"/>
       <c r="M14" s="21" t="n"/>
     </row>
@@ -6811,11 +7038,11 @@
       <c r="D15" s="21" t="n"/>
       <c r="E15" s="22" t="n"/>
       <c r="F15" s="21" t="n"/>
-      <c r="G15" s="23" t="n"/>
+      <c r="G15" s="24" t="n"/>
       <c r="H15" s="21" t="n"/>
       <c r="I15" s="22" t="n"/>
       <c r="J15" s="21" t="n"/>
-      <c r="K15" s="23" t="n"/>
+      <c r="K15" s="24" t="n"/>
       <c r="L15" s="22" t="n"/>
       <c r="M15" s="21" t="n"/>
     </row>
@@ -6830,11 +7057,11 @@
       <c r="D16" s="21" t="n"/>
       <c r="E16" s="22" t="n"/>
       <c r="F16" s="21" t="n"/>
-      <c r="G16" s="23" t="n"/>
+      <c r="G16" s="24" t="n"/>
       <c r="H16" s="21" t="n"/>
       <c r="I16" s="22" t="n"/>
       <c r="J16" s="21" t="n"/>
-      <c r="K16" s="23" t="n"/>
+      <c r="K16" s="24" t="n"/>
       <c r="L16" s="22" t="n"/>
       <c r="M16" s="21" t="n"/>
     </row>
@@ -6849,11 +7076,11 @@
       <c r="D17" s="21" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="21" t="n"/>
-      <c r="G17" s="23" t="n"/>
+      <c r="G17" s="24" t="n"/>
       <c r="H17" s="21" t="n"/>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="21" t="n"/>
-      <c r="K17" s="23" t="n"/>
+      <c r="K17" s="24" t="n"/>
       <c r="L17" s="22" t="n"/>
       <c r="M17" s="21" t="n"/>
     </row>
@@ -6868,11 +7095,11 @@
       <c r="D18" s="21" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="21" t="n"/>
-      <c r="G18" s="23" t="n"/>
+      <c r="G18" s="24" t="n"/>
       <c r="H18" s="21" t="n"/>
       <c r="I18" s="22" t="n"/>
       <c r="J18" s="21" t="n"/>
-      <c r="K18" s="23" t="n"/>
+      <c r="K18" s="24" t="n"/>
       <c r="L18" s="22" t="n"/>
       <c r="M18" s="21" t="n"/>
     </row>
@@ -6887,11 +7114,11 @@
       <c r="D19" s="21" t="n"/>
       <c r="E19" s="22" t="n"/>
       <c r="F19" s="21" t="n"/>
-      <c r="G19" s="23" t="n"/>
+      <c r="G19" s="24" t="n"/>
       <c r="H19" s="21" t="n"/>
       <c r="I19" s="22" t="n"/>
       <c r="J19" s="21" t="n"/>
-      <c r="K19" s="23" t="n"/>
+      <c r="K19" s="24" t="n"/>
       <c r="L19" s="22" t="n"/>
       <c r="M19" s="21" t="n"/>
     </row>
@@ -6906,11 +7133,11 @@
       <c r="D20" s="21" t="n"/>
       <c r="E20" s="22" t="n"/>
       <c r="F20" s="21" t="n"/>
-      <c r="G20" s="23" t="n"/>
+      <c r="G20" s="24" t="n"/>
       <c r="H20" s="21" t="n"/>
       <c r="I20" s="22" t="n"/>
       <c r="J20" s="21" t="n"/>
-      <c r="K20" s="23" t="n"/>
+      <c r="K20" s="24" t="n"/>
       <c r="L20" s="22" t="n"/>
       <c r="M20" s="21" t="n"/>
     </row>
@@ -6925,11 +7152,11 @@
       <c r="D21" s="21" t="n"/>
       <c r="E21" s="22" t="n"/>
       <c r="F21" s="21" t="n"/>
-      <c r="G21" s="23" t="n"/>
+      <c r="G21" s="24" t="n"/>
       <c r="H21" s="21" t="n"/>
       <c r="I21" s="22" t="n"/>
       <c r="J21" s="21" t="n"/>
-      <c r="K21" s="23" t="n"/>
+      <c r="K21" s="24" t="n"/>
       <c r="L21" s="22" t="n"/>
       <c r="M21" s="21" t="n"/>
     </row>
@@ -6944,11 +7171,11 @@
       <c r="D22" s="21" t="n"/>
       <c r="E22" s="22" t="n"/>
       <c r="F22" s="21" t="n"/>
-      <c r="G22" s="23" t="n"/>
+      <c r="G22" s="24" t="n"/>
       <c r="H22" s="21" t="n"/>
       <c r="I22" s="22" t="n"/>
       <c r="J22" s="21" t="n"/>
-      <c r="K22" s="23" t="n"/>
+      <c r="K22" s="24" t="n"/>
       <c r="L22" s="22" t="n"/>
       <c r="M22" s="21" t="n"/>
     </row>
@@ -6963,11 +7190,11 @@
       <c r="D23" s="21" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="21" t="n"/>
-      <c r="G23" s="23" t="n"/>
+      <c r="G23" s="24" t="n"/>
       <c r="H23" s="21" t="n"/>
       <c r="I23" s="22" t="n"/>
       <c r="J23" s="21" t="n"/>
-      <c r="K23" s="23" t="n"/>
+      <c r="K23" s="24" t="n"/>
       <c r="L23" s="22" t="n"/>
       <c r="M23" s="21" t="n"/>
     </row>
@@ -6982,11 +7209,11 @@
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="22" t="n"/>
       <c r="F24" s="21" t="n"/>
-      <c r="G24" s="23" t="n"/>
+      <c r="G24" s="24" t="n"/>
       <c r="H24" s="21" t="n"/>
       <c r="I24" s="22" t="n"/>
       <c r="J24" s="21" t="n"/>
-      <c r="K24" s="23" t="n"/>
+      <c r="K24" s="24" t="n"/>
       <c r="L24" s="22" t="n"/>
       <c r="M24" s="21" t="n"/>
     </row>
@@ -7001,11 +7228,11 @@
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="22" t="n"/>
       <c r="F25" s="21" t="n"/>
-      <c r="G25" s="23" t="n"/>
+      <c r="G25" s="24" t="n"/>
       <c r="H25" s="21" t="n"/>
       <c r="I25" s="22" t="n"/>
       <c r="J25" s="21" t="n"/>
-      <c r="K25" s="23" t="n"/>
+      <c r="K25" s="24" t="n"/>
       <c r="L25" s="22" t="n"/>
       <c r="M25" s="21" t="n"/>
     </row>
@@ -7020,11 +7247,11 @@
       <c r="D26" s="21" t="n"/>
       <c r="E26" s="22" t="n"/>
       <c r="F26" s="21" t="n"/>
-      <c r="G26" s="23" t="n"/>
+      <c r="G26" s="24" t="n"/>
       <c r="H26" s="21" t="n"/>
       <c r="I26" s="22" t="n"/>
       <c r="J26" s="21" t="n"/>
-      <c r="K26" s="23" t="n"/>
+      <c r="K26" s="24" t="n"/>
       <c r="L26" s="22" t="n"/>
       <c r="M26" s="21" t="n"/>
     </row>
@@ -7039,11 +7266,11 @@
       <c r="D27" s="21" t="n"/>
       <c r="E27" s="22" t="n"/>
       <c r="F27" s="21" t="n"/>
-      <c r="G27" s="23" t="n"/>
+      <c r="G27" s="24" t="n"/>
       <c r="H27" s="21" t="n"/>
       <c r="I27" s="22" t="n"/>
       <c r="J27" s="21" t="n"/>
-      <c r="K27" s="23" t="n"/>
+      <c r="K27" s="24" t="n"/>
       <c r="L27" s="22" t="n"/>
       <c r="M27" s="21" t="n"/>
     </row>
@@ -7058,11 +7285,11 @@
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="22" t="n"/>
       <c r="F28" s="21" t="n"/>
-      <c r="G28" s="23" t="n"/>
+      <c r="G28" s="24" t="n"/>
       <c r="H28" s="21" t="n"/>
       <c r="I28" s="22" t="n"/>
       <c r="J28" s="21" t="n"/>
-      <c r="K28" s="23" t="n"/>
+      <c r="K28" s="24" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="21" t="n"/>
     </row>
@@ -7077,11 +7304,11 @@
       <c r="D29" s="21" t="n"/>
       <c r="E29" s="22" t="n"/>
       <c r="F29" s="21" t="n"/>
-      <c r="G29" s="23" t="n"/>
+      <c r="G29" s="24" t="n"/>
       <c r="H29" s="21" t="n"/>
       <c r="I29" s="22" t="n"/>
       <c r="J29" s="21" t="n"/>
-      <c r="K29" s="23" t="n"/>
+      <c r="K29" s="24" t="n"/>
       <c r="L29" s="22" t="n"/>
       <c r="M29" s="21" t="n"/>
     </row>
@@ -7096,11 +7323,11 @@
       <c r="D30" s="21" t="n"/>
       <c r="E30" s="22" t="n"/>
       <c r="F30" s="21" t="n"/>
-      <c r="G30" s="23" t="n"/>
+      <c r="G30" s="24" t="n"/>
       <c r="H30" s="21" t="n"/>
       <c r="I30" s="22" t="n"/>
       <c r="J30" s="21" t="n"/>
-      <c r="K30" s="23" t="n"/>
+      <c r="K30" s="24" t="n"/>
       <c r="L30" s="22" t="n"/>
       <c r="M30" s="21" t="n"/>
     </row>
@@ -7115,11 +7342,11 @@
       <c r="D31" s="21" t="n"/>
       <c r="E31" s="22" t="n"/>
       <c r="F31" s="21" t="n"/>
-      <c r="G31" s="23" t="n"/>
+      <c r="G31" s="24" t="n"/>
       <c r="H31" s="21" t="n"/>
       <c r="I31" s="22" t="n"/>
       <c r="J31" s="21" t="n"/>
-      <c r="K31" s="23" t="n"/>
+      <c r="K31" s="24" t="n"/>
       <c r="L31" s="22" t="n"/>
       <c r="M31" s="21" t="n"/>
     </row>
@@ -7134,11 +7361,11 @@
       <c r="D32" s="21" t="n"/>
       <c r="E32" s="22" t="n"/>
       <c r="F32" s="21" t="n"/>
-      <c r="G32" s="23" t="n"/>
+      <c r="G32" s="24" t="n"/>
       <c r="H32" s="21" t="n"/>
       <c r="I32" s="22" t="n"/>
       <c r="J32" s="21" t="n"/>
-      <c r="K32" s="23" t="n"/>
+      <c r="K32" s="24" t="n"/>
       <c r="L32" s="22" t="n"/>
       <c r="M32" s="21" t="n"/>
     </row>
@@ -7153,11 +7380,11 @@
       <c r="D33" s="21" t="n"/>
       <c r="E33" s="22" t="n"/>
       <c r="F33" s="21" t="n"/>
-      <c r="G33" s="23" t="n"/>
+      <c r="G33" s="24" t="n"/>
       <c r="H33" s="21" t="n"/>
       <c r="I33" s="22" t="n"/>
       <c r="J33" s="21" t="n"/>
-      <c r="K33" s="23" t="n"/>
+      <c r="K33" s="24" t="n"/>
       <c r="L33" s="22" t="n"/>
       <c r="M33" s="21" t="n"/>
     </row>
@@ -7172,11 +7399,11 @@
       <c r="D34" s="21" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="21" t="n"/>
-      <c r="G34" s="23" t="n"/>
+      <c r="G34" s="24" t="n"/>
       <c r="H34" s="21" t="n"/>
       <c r="I34" s="22" t="n"/>
       <c r="J34" s="21" t="n"/>
-      <c r="K34" s="23" t="n"/>
+      <c r="K34" s="24" t="n"/>
       <c r="L34" s="22" t="n"/>
       <c r="M34" s="21" t="n"/>
     </row>
@@ -7191,11 +7418,11 @@
       <c r="D35" s="21" t="n"/>
       <c r="E35" s="22" t="n"/>
       <c r="F35" s="21" t="n"/>
-      <c r="G35" s="23" t="n"/>
+      <c r="G35" s="24" t="n"/>
       <c r="H35" s="21" t="n"/>
       <c r="I35" s="22" t="n"/>
       <c r="J35" s="21" t="n"/>
-      <c r="K35" s="23" t="n"/>
+      <c r="K35" s="24" t="n"/>
       <c r="L35" s="22" t="n"/>
       <c r="M35" s="21" t="n"/>
     </row>
@@ -7210,11 +7437,11 @@
       <c r="D36" s="21" t="n"/>
       <c r="E36" s="22" t="n"/>
       <c r="F36" s="21" t="n"/>
-      <c r="G36" s="23" t="n"/>
+      <c r="G36" s="24" t="n"/>
       <c r="H36" s="21" t="n"/>
       <c r="I36" s="22" t="n"/>
       <c r="J36" s="21" t="n"/>
-      <c r="K36" s="23" t="n"/>
+      <c r="K36" s="24" t="n"/>
       <c r="L36" s="22" t="n"/>
       <c r="M36" s="21" t="n"/>
     </row>
@@ -7229,11 +7456,11 @@
       <c r="D37" s="21" t="n"/>
       <c r="E37" s="22" t="n"/>
       <c r="F37" s="21" t="n"/>
-      <c r="G37" s="23" t="n"/>
+      <c r="G37" s="24" t="n"/>
       <c r="H37" s="21" t="n"/>
       <c r="I37" s="22" t="n"/>
       <c r="J37" s="21" t="n"/>
-      <c r="K37" s="23" t="n"/>
+      <c r="K37" s="24" t="n"/>
       <c r="L37" s="22" t="n"/>
       <c r="M37" s="21" t="n"/>
     </row>
@@ -7248,11 +7475,11 @@
       <c r="D38" s="21" t="n"/>
       <c r="E38" s="22" t="n"/>
       <c r="F38" s="21" t="n"/>
-      <c r="G38" s="23" t="n"/>
+      <c r="G38" s="24" t="n"/>
       <c r="H38" s="21" t="n"/>
       <c r="I38" s="22" t="n"/>
       <c r="J38" s="21" t="n"/>
-      <c r="K38" s="23" t="n"/>
+      <c r="K38" s="24" t="n"/>
       <c r="L38" s="22" t="n"/>
       <c r="M38" s="21" t="n"/>
     </row>
@@ -7267,11 +7494,11 @@
       <c r="D39" s="21" t="n"/>
       <c r="E39" s="22" t="n"/>
       <c r="F39" s="21" t="n"/>
-      <c r="G39" s="23" t="n"/>
+      <c r="G39" s="24" t="n"/>
       <c r="H39" s="21" t="n"/>
       <c r="I39" s="22" t="n"/>
       <c r="J39" s="21" t="n"/>
-      <c r="K39" s="23" t="n"/>
+      <c r="K39" s="24" t="n"/>
       <c r="L39" s="22" t="n"/>
       <c r="M39" s="21" t="n"/>
     </row>
@@ -7286,11 +7513,11 @@
       <c r="D40" s="21" t="n"/>
       <c r="E40" s="22" t="n"/>
       <c r="F40" s="21" t="n"/>
-      <c r="G40" s="23" t="n"/>
+      <c r="G40" s="24" t="n"/>
       <c r="H40" s="21" t="n"/>
       <c r="I40" s="22" t="n"/>
       <c r="J40" s="21" t="n"/>
-      <c r="K40" s="23" t="n"/>
+      <c r="K40" s="24" t="n"/>
       <c r="L40" s="22" t="n"/>
       <c r="M40" s="21" t="n"/>
     </row>
@@ -7305,11 +7532,11 @@
       <c r="D41" s="21" t="n"/>
       <c r="E41" s="22" t="n"/>
       <c r="F41" s="21" t="n"/>
-      <c r="G41" s="23" t="n"/>
+      <c r="G41" s="24" t="n"/>
       <c r="H41" s="21" t="n"/>
       <c r="I41" s="22" t="n"/>
       <c r="J41" s="21" t="n"/>
-      <c r="K41" s="23" t="n"/>
+      <c r="K41" s="24" t="n"/>
       <c r="L41" s="22" t="n"/>
       <c r="M41" s="21" t="n"/>
     </row>
@@ -7324,16 +7551,16 @@
       <c r="D42" s="21" t="n"/>
       <c r="E42" s="22" t="n"/>
       <c r="F42" s="21" t="n"/>
-      <c r="G42" s="23" t="n"/>
+      <c r="G42" s="24" t="n"/>
       <c r="H42" s="21" t="n"/>
       <c r="I42" s="22" t="n"/>
       <c r="J42" s="21" t="n"/>
-      <c r="K42" s="23" t="n"/>
+      <c r="K42" s="24" t="n"/>
       <c r="L42" s="22" t="n"/>
       <c r="M42" s="21" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="48" t="inlineStr">
+      <c r="A44" s="49" t="inlineStr">
         <is>
           <t>Severity ของ defect ใช้ **ชุดค่าเดียวกับคอลัมน์ Severity ในแท็บ “2. Test Cases”** ยกมาใส่ได้ตรง ๆ ไม่ต้องแปลงค่า: Critical = ระบบใช้งานไม่ได้ / ข้อมูลเงินผิดพลาดร้ายแรง · High = ฟังก์ชันหลักเสีย · Medium = เสียแต่มีทางเลี่ยง · Low = ปัญหาเล็กน้อยหรือ UI (ไม่มีค่า `-` ในแท็บนี้ เพราะแถว defect เกิดขึ้นเฉพาะตอนมีเคส Fail)  ·  Status: Open → In Progress → Fixed → Retested → Closed (หรือ Wont Fix ถ้าตัดสินว่าไม่แก้)</t>
         </is>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Test Cases" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Defects" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. AI Pre-Run" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Test Cases'!$A$2:$T$56</definedName>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -133,8 +134,15 @@
       <color rgb="FF808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -181,8 +189,13 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -215,11 +228,55 @@
         <color rgb="FFBFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -362,6 +419,17 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -741,7 +809,7 @@
           <t>Budget Web Application — UAT Test Cases</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
+      <c r="B1" s="50" t="n"/>
     </row>
     <row r="2" ht="13.5" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -749,7 +817,7 @@
           <t>Chememan PCL (CMAN)  |  User Acceptance Testing (UAT)  |  Data &amp; Analytics  |  Round 1  |  FY2027</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
+      <c r="B2" s="50" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="19.5" customHeight="1">
@@ -758,7 +826,7 @@
           <t>Project Information</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
+      <c r="B4" s="50" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -941,7 +1009,7 @@
           <t>ข้อควรระวังก่อนเริ่มทดสอบ</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
+      <c r="B21" s="50" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -949,7 +1017,7 @@
           <t>ข้อ 1 — UAT รอบนี้รันบน **ระบบจริง (production)** ใช้ฐานข้อมูลจริง และส่งอีเมลจริงถึงเพื่อนร่วมงานจริง ไม่มีระบบทดลองแยกต่างหาก ทุกอย่างที่กรอก ส่ง อนุมัติ หรือลบ คือข้อมูลจริงของปีงบประมาณ 2027</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
+      <c r="B22" s="50" t="n"/>
     </row>
     <row r="23" ht="56" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -957,7 +1025,7 @@
           <t>ข้อ 2 — สถานะ `Approved` **ย้อนกลับไม่ได้ในระบบ** ต้องแก้ที่ฐานข้อมูลเท่านั้น อย่ากด Approve ขั้นที่ 3 (เคส UAT-40) จนกว่าทุกเคสที่มีเลข `ลำดับการรัน` น้อยกว่า 52 จะเสร็จครบ — UAT-40 อยู่ที่ลำดับการรันที่ 52 และเป็นเคสสุดท้ายของสายอนุมัติฝ่ายนั้น ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
+      <c r="B23" s="50" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -965,7 +1033,7 @@
           <t>ข้อ 3 — อายุ session ระหว่าง UAT ตั้งไว้ที่ **1 ชั่วโมง** (ค่าจริงคือ 14 ชั่วโมง และจะคืนค่าเดิมหลังจบรอบ) ถ้าระบบให้ล็อกอินใหม่ระหว่างทดสอบ ถือว่าเป็นเรื่องปกติของรอบนี้</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n"/>
+      <c r="B24" s="50" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
@@ -973,7 +1041,7 @@
           <t>ข้อ 4 — **KNOWN ISSUE ที่ไม่ต้องแจ้งเป็น defect:** กล่อง “หมดเวลาการเข้าใช้งาน” ยังเขียนว่า 14 ชั่วโมง ทั้งที่ตั้งไว้ 1 ชั่วโมง — ตัดสินแล้วว่ายอมรับได้ (jakkaritw 2026-09-06)</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
+      <c r="B25" s="50" t="n"/>
     </row>
     <row r="26" ht="56" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -981,7 +1049,7 @@
           <t>ข้อ 5 — **เตรียมไฟล์แนบให้ฝ่าย Solution Delivery ไว้ก่อนเริ่มรอบ อย่างน้อย 1 ไฟล์** ในโฟลเดอร์ `เอกสาร ฝ่าย/Solution Delivery/2027/` (ให้ Pornthip อัปโหลดด้วยขั้นตอนเดียวกับเคส UAT-27 ซึ่งอัปโหลดให้ฝ่าย Data &amp; Analytic เท่านั้น ไม่มีเคสใดในรอบนี้อัปโหลดให้ฝ่าย Solution Delivery) — เคส UAT-31 ต้องมีไฟล์อยู่แล้วในโฟลเดอร์นี้ก่อนจึงจะทดสอบได้ ถ้าไม่เตรียมไว้ล่วงหน้า เคสนี้จะทำไม่ได้เมื่อถึงลำดับการรัน</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
+      <c r="B26" s="50" t="n"/>
     </row>
     <row r="27" ht="56" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -989,7 +1057,7 @@
           <t>ข้อ 6 — **ฝ่าย Solution Delivery จะถูกล็อกชั่วคราวระหว่างรอบ (ตั้งแต่เคส UAT-36 ถึง UAT-43):** ทันทีที่ Pornthip กด Submit ฝ่ายนี้ (เคส UAT-36) คุณ Suchanya ผู้กรอกตัวจริงของฝ่าย Solution Delivery จะแก้ไขงบของฝ่ายตัวเองไม่ได้เลยจนกว่าจะถูกตีกลับ — **ต้องแจ้ง Suchanya ล่วงหน้าก่อนเริ่มรอบ** ว่าจะมีช่วงล็อกสั้น ๆ นี้ · เคส UAT-43 จะอนุมัติฝ่ายนี้ที่ขั้นที่ 1 แล้วตีกลับคืนทันทีในเคสเดียวกัน เพื่อให้เธอกลับมาแก้ไขได้ก่อนจบรอบ ไม่ต้องรอจนครบทั้ง 54 เคส</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n"/>
+      <c r="B27" s="50" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
@@ -997,7 +1065,7 @@
           <t>วิธีใช้ไฟล์นี้ / How to use this workbook</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
+      <c r="B29" s="50" t="n"/>
     </row>
     <row r="30" ht="56" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
@@ -1005,7 +1073,7 @@
           <t>1.  ไปที่แท็บ “2. Test Cases” แล้วทดสอบ **เรียงตามคอลัมน์ `ลำดับการรัน` (Run Order) จาก 1 ถึง 54** — **ไม่ใช่เรียงตามคอลัมน์ Wave** · คอลัมน์ Wave ยังเป็นชื่อกลุ่มของเคสและใช้กรองดูได้เหมือนเดิม แต่ลำดับที่ต้องลงมือทำจริงคือคอลัมน์ `ลำดับการรัน` เพราะบางเคสต้องทำข้ามระลอก (เช่น UAT-53 และ UAT-54 อยู่ระลอก W8 แต่ต้องทำก่อนระลอก W5 · UAT-03 อยู่ระลอก W1 แต่ต้องทำหลัง UAT-32)</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n"/>
+      <c r="B30" s="50" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
@@ -1013,7 +1081,7 @@
           <t>2.  วิธีเรียง: คลิกลูกศรกรองบนหัวคอลัมน์ `ลำดับการรัน` แล้วเลือก “Sort Smallest to Largest” จากนั้นไล่ทำจากบนลงล่าง</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
+      <c r="B31" s="50" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -1021,7 +1089,7 @@
           <t>3.  ⚠ **อย่ากด `Approve` ขั้นที่ 3 ในเคส UAT-40 (ลำดับการรันที่ 52) จนกว่าทุกเคสที่มีลำดับการรันน้อยกว่า 52 จะเสร็จครบ** เพราะสถานะ `Approved` ย้อนกลับไม่ได้ ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ และต้องให้ทีม IT แก้ที่ฐานข้อมูลเท่านั้น</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
+      <c r="B32" s="50" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
@@ -1029,7 +1097,7 @@
           <t>4.  ทดสอบทีละเคสตาม “Test Steps” แล้วเทียบผลกับ “Expected Result”</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
+      <c r="B33" s="50" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -1037,7 +1105,7 @@
           <t>5.  **อ่าน “Expected Result” ให้จบทุกข้อก่อนตัดสินผล** — หลายเคสเป็นเคสรวม (merged) คือ 1 แถว แต่มีหลายข้อที่ต้องตรวจ ถ้าข้อใดข้อหนึ่งไม่ผ่าน ให้ทั้งแถวเป็น Fail แล้วระบุในช่อง Actual Result ว่าข้อไหนไม่ผ่าน</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
+      <c r="B34" s="50" t="n"/>
     </row>
     <row r="35" ht="56" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
@@ -1045,7 +1113,7 @@
           <t>6.  **ผู้ทดสอบดูแลช่องพื้นหลังสีเหลือง 7 ช่องนี้:** Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks · ช่อง `Tester` กรอกชื่อไว้ล่วงหน้าแล้วตามแผนคนจาก actor map ก่อนเริ่มรอบ (ตัวหนังสือสีม่วงเหมือนช่องเนื้อหาเคสอื่น ๆ) ถ้าคนที่ลงมือทดสอบจริงไม่ตรงกับชื่อที่กรอกไว้ ให้แก้ชื่อในช่องนี้ให้ตรงกับคนที่ทำจริง · อีก 6 ช่องที่เหลือยังว่างอยู่ ให้ผู้ทดสอบกรอกเองระหว่างทดสอบตามปกติ</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
+      <c r="B35" s="50" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
@@ -1053,7 +1121,7 @@
           <t>7.  เลือก Status จาก dropdown: Pass / Fail / Blocked / N/A · **ช่องที่ยังว่าง = `Not Run` (ยังไม่ได้ทดสอบ) ซึ่งเป็นค่าเริ่มต้น** ไม่ต้องพิมพ์คำว่า Not Run เอง — แท็บ “3. Summary” นับช่องว่างเป็น Not Run ให้อัตโนมัติ</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
+      <c r="B36" s="50" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
@@ -1061,7 +1129,7 @@
           <t>8.  ถ้า Fail ให้ระบุ Severity บันทึกรายละเอียดใน “Actual Result” แล้ว **เปิดแถวใหม่ในแท็บ “4. Defects”** จากนั้นนำเลข Defect ID (D-001, D-002, …) มาใส่ในคอลัมน์ Defect ID ของแถวนี้ · ช่อง Severity ของแถว defect ใช้ **ชุดค่าเดียวกัน** (Critical / High / Medium / Low) ยกค่าจากแถวเคสไปใส่ได้ตรง ๆ ไม่ต้องแปลงเป็นคำอื่น</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
+      <c r="B37" s="50" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
@@ -1069,7 +1137,7 @@
           <t>9.  แท็บ “3. Summary” สรุปผลอัตโนมัติ (จำนวน / อัตราผ่าน / แยกตาม Module, Wave และฝ่าย) ไม่ต้องกรอกเอง</t>
         </is>
       </c>
-      <c r="B38" s="9" t="n"/>
+      <c r="B38" s="50" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
@@ -1077,7 +1145,7 @@
           <t>10. **ข้อยกเว้นเดียวของกติกา “กรอกเฉพาะช่องสีเหลือง” คือคอลัมน์ `PIC`** ซึ่งเป็นช่องสีขาว และคนที่กรอกไม่ใช่ผู้ทดสอบ แต่เป็น **Test Lead** ที่กรอกชื่อผู้รับผิดชอบรายเคสไว้ **ก่อน** เริ่มรอบทดสอบ (ใช้เมื่อ Test Lead ต้องการมอบหมายผู้รับผิดชอบเพิ่มเติม นอกเหนือจากชื่อที่กรอกไว้แล้วในช่อง `Tester`) · ระหว่างทดสอบ ผู้ทดสอบไม่ต้องแตะคอลัมน์นี้</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n"/>
+      <c r="B39" s="50" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
@@ -1085,7 +1153,7 @@
           <t>11. ตัวหนังสือ **สีม่วง** คือข้อความที่ AI ร่างไว้ให้ ยังไม่ผ่านการตรวจจากผู้ทดสอบ ถ้าพบว่าไม่ตรงกับระบบจริง แก้ได้เลยแล้วบันทึกไว้ในช่อง Remarks · **ยกเว้นคอลัมน์ `Wave` และ `ลำดับการรัน` ซึ่งพิมพ์ด้วยตัวสีดำ** เพราะเป็นค่าที่โปรแกรมคำนวณมาให้ ไม่ใช่ข้อความที่ AI ร่าง — ห้ามแก้ ถ้าเห็นว่าลำดับผิดให้แจ้ง Test Lead แทน</t>
         </is>
       </c>
-      <c r="B40" s="9" t="n"/>
+      <c r="B40" s="50" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
@@ -1093,7 +1161,7 @@
           <t>12. อ่านเอกสารประกอบ `UAT_Test_Script.md` (ภาษาไทย) ก่อนเริ่ม — อธิบายลำดับการรัน บทบาทของแต่ละคน และสิ่งที่ตัดออกจากรอบนี้โดยตั้งใจ</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n"/>
+      <c r="B41" s="50" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
       <c r="A43" s="5" t="inlineStr">
@@ -1101,7 +1169,7 @@
           <t>ตัวอย่างการกรอก 1 แถว (worked example)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
+      <c r="B43" s="50" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
@@ -1109,7 +1177,7 @@
           <t>เคสตัวอย่าง UAT-09 (ระลอก W2) — “กรอกยอดแล้วคลิกออกจากช่อง = บันทึกอัตโนมัติ · refresh หน้าแล้วค่ายังอยู่”</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
+      <c r="B44" s="50" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
@@ -1117,7 +1185,7 @@
           <t>ถ้าผ่าน → Actual Result = “กรอก 100 ที่เดือน ม.ค. คลิกออกจากช่อง แล้ว refresh หน้า ค่ายังเป็น 100” · Status = `Pass` · Severity = `-` · Defect ID = (เว้นว่าง) · Tester = `Pornthip` · Test Date = วันที่ทดสอบ · Remarks = (เว้นว่าง)</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
+      <c r="B45" s="50" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
@@ -1125,7 +1193,7 @@
           <t>ถ้าไม่ผ่าน → Actual Result = “refresh แล้วค่าหาย กลับเป็นช่องว่าง” · Status = `Fail` · Severity = `High` · Defect ID = `D-001` แล้วไปเปิดแถว D-001 ในแท็บ “4. Defects” กรอกหัวข้อ ผู้แจ้ง วันที่ และสถานะ `Open`</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n"/>
+      <c r="B46" s="50" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
@@ -1133,7 +1201,7 @@
           <t>ถ้าทดสอบไม่ได้เพราะติดเคสอื่นหรือข้อมูลยังไม่พร้อม → Status = `Blocked` และเขียนเหตุผลใน Remarks (อย่าปล่อยเป็น `Not Run` ถ้าพยายามทดสอบแล้ว)</t>
         </is>
       </c>
-      <c r="B47" s="9" t="n"/>
+      <c r="B47" s="50" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
       <c r="A49" s="5" t="inlineStr">
@@ -1141,7 +1209,7 @@
           <t>Legend / คำอธิบายสี &amp; สถานะ</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
+      <c r="B49" s="50" t="n"/>
     </row>
     <row r="50" ht="48" customHeight="1">
       <c r="A50" s="10" t="n"/>
@@ -1213,7 +1281,7 @@
           <t>Severity: Critical = ระบบใช้งานไม่ได้ / ข้อมูลผิดพลาดร้ายแรง  |  High = ฟังก์ชันหลักเสีย  |  Medium = มีทางเลี่ยง  |  Low = ปัญหาเล็กน้อย / UI  ·  ชุดค่านี้ใช้เหมือนกันทั้งแท็บ “2. Test Cases” และแท็บ “4. Defects” จึงยกค่าจากแถวเคสไปใส่แถว defect ได้ตรง ๆ ไม่ต้องแปลง (ค่า `-` มีเฉพาะแท็บ “2. Test Cases” ใช้เมื่อเคสนั้นไม่ Fail)</t>
         </is>
       </c>
-      <c r="B58" s="9" t="n"/>
+      <c r="B58" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="30">
@@ -1289,25 +1357,25 @@
           <t>Budget Web App — UAT Test Cases (Round 1 · FY2027 · production)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
+      <c r="N1" s="50" t="n"/>
+      <c r="O1" s="50" t="n"/>
+      <c r="P1" s="50" t="n"/>
+      <c r="Q1" s="50" t="n"/>
+      <c r="R1" s="50" t="n"/>
+      <c r="S1" s="50" t="n"/>
+      <c r="T1" s="50" t="n"/>
     </row>
     <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
@@ -1488,8 +1556,16 @@
 เคสนี้ครอบคลุมช่องว่าง "แถบผู้ใช้และการอ่านสิทธิ์" ซึ่งไม่เคยถูกทดสอบในรอบ SIT · ถ้าจำนวนฝ่ายหรือจำนวน Cost Center ไม่ตรงกับสิทธิ์จริง ให้เปิด Defect และแจ้งผู้ดูแลระบบตรวจไฟล์ master `cc dept.xlsx` ก่อนสรุปว่าเป็นบั๊กของแอป · ข้อ 7 และ 8 (การย่อชื่อเหลือ 3 ชื่อ + ป้าย `+N`) จะเห็นผลเป็น "ไม่มีป้าย +" เพราะผู้ทดสอบถือแค่ 2 ฝ่าย นั่นคือผลที่ถูกต้อง ไม่ใช่การทดสอบที่ล้มเหลว</t>
         </is>
       </c>
-      <c r="N3" s="21" t="n"/>
-      <c r="O3" s="21" t="n"/>
+      <c r="N3" s="51" t="inlineStr">
+        <is>
+          <t>แถบผู้ใช้แสดง: pornthipp / pornthipp@chememan.com · role badge = ผู้กรอกงบประมาณ · สายงาน = Digital Technology · ฝ่าย 2 = Data &amp; Analytic, Solution Delivery · 3 COST CENTERS · 8 GL CODES (จดไว้ตามข้อ 6) · ไม่มีป้าย + ต่อท้ายชื่อฝ่ายหรือสายงาน · มีลิงก์ ออกจากระบบ ที่มุมขวา (ไม่ได้กด — ผลของการออกจากระบบตรวจใน UAT-04)</t>
+        </is>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P3" s="22" t="n"/>
       <c r="Q3" s="22" t="n"/>
       <c r="R3" s="23" t="inlineStr">
@@ -1497,8 +1573,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S3" s="24" t="n"/>
-      <c r="T3" s="21" t="n"/>
+      <c r="S3" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T3" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ตรงกับ Expected ข้อ 1-9 ทุกข้อ · ข้อ 8 (กดลิงก์ออกจากระบบเพื่อยืนยันว่ากดได้) ไม่ได้กดใน pre-UAT เพราะจะทำให้ session ของการรันหลุด — ให้คนกดในรอบจริง</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="372" customHeight="1">
       <c r="A4" s="18" t="inlineStr">
@@ -1576,8 +1658,16 @@
 ฝ่าย Solution Delivery ปีงบ 2027 ยังไม่มีข้อมูลที่กรอกไว้เลย (0 แถว) ดังนั้นการที่ตารางว่างหลังสลับไปฝ่ายนั้น ถือว่าปกติ ไม่ใช่ข้อผิดพลาด · การที่ระบบเลือกฝ่ายแรกให้อัตโนมัติเป็นพฤติกรรมที่ตัดสินไว้แล้ว (2026-07-21 — เดิมเคยออกแบบให้เริ่มต้นว่าง แล้วเปลี่ยนเป็นห้ามปล่อยให้หน้าจอว่าง) จึง **ไม่ใช่ defect** · ถ้ายังเห็นฝ่ายเดียว แปลว่า master `cc dept.xlsx` ยังไม่ได้แก้หรือยัง sync ไม่ถึง ให้บันทึกเป็น Blocked แล้วแจ้งผู้ดูแลระบบ</t>
         </is>
       </c>
-      <c r="N4" s="21" t="n"/>
-      <c r="O4" s="21" t="n"/>
+      <c r="N4" s="51" t="inlineStr">
+        <is>
+          <t>ข้อ1-2: เปิดหน้าด้วย URL เปล่า ระบบเลือก Data &amp; Analytic ให้เองทันที ตารางโหลดแถว 10IT013000 ไม่ค้างที่ '— เลือกฝ่าย —' · ข้อ4: รายการจัดกลุ่ม 'DIGITAL TECHNOLOGY 2' ช่องค้นหา placeholder = 'ค้นหาฝ่าย…' · ข้อ5: Data &amp; Analytic = 2 CC, Solution Delivery = 1 CC · ข้อ6: พิมพ์ Solution เหลือเฉพาะ Solution Delivery 1 CC · ข้อ7: พิมพ์ zzz ขึ้น 'ไม่พบฝ่ายในสิทธิ์ของคุณ' · ข้อ8: เลือก Solution Delivery ตารางเปลี่ยนเป็น cost center 10IT012000 (ไม่มีแถว 10IT013000 ค้าง) · ข้อ9: กลับ Data &amp; Analytic ตารางเปลี่ยนเป็น 10IT013000 สถานะ Draft — not submitted · ข้อ10: เปิดรายการแล้วกด Esc รายการปิด ปุ่มยังเป็น Data &amp; Analytic</t>
+        </is>
+      </c>
+      <c r="O4" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P4" s="22" t="n"/>
       <c r="Q4" s="22" t="n"/>
       <c r="R4" s="23" t="inlineStr">
@@ -1585,8 +1675,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S4" s="24" t="n"/>
-      <c r="T4" s="21" t="n"/>
+      <c r="S4" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T4" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ตรง Expected ข้อ 1-6 ทุกข้อ · ข้อสังเกต (ไม่ใช่ defect): ตารางของ Solution Delivery ไม่ได้ว่างเปล่าอย่างที่ note ของเคสคาด — แสดงแถว GL ของ 10IT012000 พร้อมยอด SAP ใช้จริง แต่ชั้น Pending เป็น 0 ทั้งหมด เพราะแถวมาจากชั้น SAP ไม่ใช่ข้อมูลที่กรอก ควรแก้ note ของเคสให้ตรง</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="288" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
@@ -1658,8 +1754,16 @@
 อย่ากดปุ่ม `Approve` ในเคสนี้ — การอนุมัติทั้งหมดทำตามลำดับในระลอก W6 เท่านั้น เพราะสถานะ `Approved` ย้อนกลับไม่ได้ในระบบ · Laddawan เป็นทั้งผู้กรอกของฝ่าย Data &amp; Analytic และผู้อนุมัติขั้นที่ 1 ของฝ่ายเดียวกัน ดังนั้นตารางจะอ่านอย่างเดียวก็ต่อเมื่อฝ่ายนั้นถูกส่งเข้าอนุมัติแล้ว — ถ้าเปิดฝ่ายที่ยังไม่ได้ส่ง เธอจะยังกรอกได้ตามปกติ และนั่นไม่ใช่ Fail</t>
         </is>
       </c>
-      <c r="N5" s="21" t="n"/>
-      <c r="O5" s="21" t="n"/>
+      <c r="N5" s="51" t="inlineStr">
+        <is>
+          <t>สวมสิทธิ์ laddawank → หน้าจอเดียวกับผู้ใช้ทั่วไป ไม่มีเมนูรายการรออนุมัติแยก · แถบผู้ใช้: laddawank / laddawank@chememan.com · role badge 'ผู้กรอกงบประมาณ' (เธอเป็นผู้กรอกของฝ่ายเดียวกันด้วย) · สายงาน = 'Digital Technology' (ไม่ใช่ 'ไม่ระบุสายงาน') · ฝ่าย 1 Data &amp; Analytic · 2 COST CENTERS · 10 GL CODES · เปิดตัวเลือกฝ่าย: 'Data &amp; Analytic Pending 2 CC' และ 'Solution Delivery 1 CC' — ป้าย 'Pending' เป็นภาษาอังกฤษ · เลือก Data &amp; Analytic: ช่องงบทุกช่องเป็นข้อความอ่านอย่างเดียว (0 input) ไม่มีปุ่มลบ · แถบอนุมัติ: chip 'Pending · Step 1 (Direct manager)' + 'Submitted — locked for editing until it is rejected' + ปุ่ม Reject และ Approve (ยังไม่กด)</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P5" s="22" t="n"/>
       <c r="Q5" s="22" t="n"/>
       <c r="R5" s="23" t="inlineStr">
@@ -1667,8 +1771,14 @@
           <t>Laddawan</t>
         </is>
       </c>
-      <c r="S5" s="24" t="n"/>
-      <c r="T5" s="21" t="n"/>
+      <c r="S5" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T5" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-5 · ข้อสังเกต: ตัวเลือกฝ่ายของ Laddawan มี Solution Delivery 1 CC ด้วย แม้แถบผู้ใช้จะบอก ฝ่าย 1 — น่าจะมาจากสิทธิ์ 'เห็น' ผ่านการเป็นผู้อนุมัติ ให้คนยืนยันว่าตั้งใจ</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="156" customHeight="1">
       <c r="A6" s="18" t="inlineStr">
@@ -1736,8 +1846,16 @@
 ข้อสังเกตที่ยกมาจากรอบ SIT: ถ้าเปิดในหน้าต่างปกติ SSO ของบริษัทอาจพาล็อกอินกลับเข้าระบบให้เองโดยไม่ถามรหัสผ่าน ถ้าเกิดกรณีนี้ให้จดไว้ในช่อง Actual Result และยังถือว่าผ่านได้ ตราบใดที่ไม่เห็นข้อมูลงบเดิมก่อนล็อกอินสำเร็จ · ถ้าต้องการทดสอบให้ชัด ให้ทำซ้ำในหน้าต่าง InPrivate / Incognito</t>
         </is>
       </c>
-      <c r="N6" s="21" t="n"/>
-      <c r="O6" s="21" t="n"/>
+      <c r="N6" s="51" t="inlineStr">
+        <is>
+          <t>ก่อนออก: หน้า D&amp;A Year 2026 เห็นยอด 415,900.00 / 135,500.00 · คลิก 'ออกจากระบบ' → ระบบพาไป login.microsoftonline.com หน้า 'Sign out — Pick an account: Which account do you want to sign out of? jakkaritw@chememan.com' (หน้าออกจากระบบของ Microsoft) · กด Back 1 ครั้ง → กลับมาที่ URL เดิมของแอป แต่ไม่มีตาราง ไม่มีตัวเลขงบใด ๆ · แสดงกล่อง 'หมดเวลาการเข้าใช้งาน (ระบบให้ล็อกอินได้ครั้งละ 14 ชั่วโมง) กรุณา login ใหม่อีกครั้ง' ปุ่ม 'เข้าสู่ระบบใหม่' และข้อความ 'โหลดข้อมูลผู้ใช้ไม่สำเร็จ — กรุณาลองรีเฟรชหน้าใหม่'</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P6" s="22" t="n"/>
       <c r="Q6" s="22" t="n"/>
       <c r="R6" s="23" t="inlineStr">
@@ -1745,8 +1863,14 @@
           <t>ไม่ระบุชื่อในเคส (ต่อจากเคสก่อนหน้า น่าจะเป็น Pornthip)</t>
         </is>
       </c>
-      <c r="S6" s="24" t="n"/>
-      <c r="T6" s="21" t="n"/>
+      <c r="S6" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T6" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="336" customHeight="1">
       <c r="A7" s="18" t="inlineStr">
@@ -1825,7 +1949,11 @@
 KNOWN ISSUE ที่ไม่ต้องแจ้งเป็น defect: ข้อความ "14 ชั่วโมง" ในกล่อง `หมดเวลาการเข้าใช้งาน` ไม่ตรงกับอายุ session 1 ชั่วโมงที่ตั้งไว้ระหว่าง UAT — ตัดสินแล้วว่ายอมรับ (jakkaritw 2026-09-06) ห้ามเปิด Defect ข้อนี้ · เคสนี้ต้องรอ 1 ชั่วโมงเต็ม แนะนำให้เริ่มไว้แล้วไปทำเคสอื่นในเครื่อง/เบราว์เซอร์อีกตัวระหว่างรอ · อย่าลืมแจ้งทีมพัฒนาให้คืนค่าอายุ session เป็น 14 ชั่วโมงหลังจบรอบ UAT</t>
         </is>
       </c>
-      <c r="N7" s="21" t="n"/>
+      <c r="N7" s="51" t="inlineStr">
+        <is>
+          <t>AI ไม่ได้ทำ: ต้องทิ้งหน้าจอไว้ครบ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง · หลักฐานข้างเคียงจากรอบนี้: เวลา ~02:02 session ของ AI หมดอายุจริงหลังล็อกอิน ~1 ชั่วโมง (แอป redirect ไป login.microsoftonline.com) และกล่อง 'หมดเวลาการเข้าใช้งาน' ปรากฏใน UAT-04 พร้อมปุ่มทางออกเดียว 'เข้าสู่ระบบใหม่'</t>
+        </is>
+      </c>
       <c r="O7" s="21" t="n"/>
       <c r="P7" s="22" t="n"/>
       <c r="Q7" s="22" t="n"/>
@@ -1835,7 +1963,11 @@
         </is>
       </c>
       <c r="S7" s="24" t="n"/>
-      <c r="T7" s="21" t="n"/>
+      <c r="T7" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Deferred to human · ข้อควรรู้ก่อนทำ: ข้อความในกล่องเขียนว่า '14 ชั่วโมง' ตายตัว (ดู UAT-04) ถ้าเห็นคำนี้ตอนหมดเวลาที่ 1 ชั่วโมง ไม่ใช่ความผิดของผู้ทดสอบ ให้จดเป็นข้อสังเกต · หลังจบรอบต้องคืนอายุ session เป็น 14 ชั่วโมง</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="204" customHeight="1">
       <c r="A8" s="18" t="inlineStr">
@@ -1909,8 +2041,16 @@
 เคสนี้เป็นการดูอย่างเดียว ยังไม่ต้องกรอกตัวเลข ให้ทำก่อนเคสอื่นใน wave นี้ เพราะเคสถัดไปอ้างชื่อฝั่งตารางและชื่อชั้นข้อมูลจากเคสนี้</t>
         </is>
       </c>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
+      <c r="N8" s="51" t="inlineStr">
+        <is>
+          <t>หัวตาราง: เห็นฝั่งเดียวคือ 'ฝั่งบริหาร / ขาย · SG&amp;A (6xxx)' — ฝั่ง 'ฝั่งผลิต / ต้นทุน (5xxx)' ไม่แสดงเพราะ Data &amp; Analytic ไม่มีแถว GL 5xxx เลย · แต่ละแถวมี 3 ชั้น: SAP · ใช้จริง / APPROVED · งบ / PENDING · รออนุมัติ · หัวเดือน Jan–Dec ครบ 12 และมีคอลัมน์ รวมทั้งปี (Jan–Dec) นำหน้า · ยอดรวมย่อยต่อกลุ่ม: รวม Maintenance - License for software · Pending, รวม Other admin. Expenses · Pending, รวม Travelling Expense · Pending · ยอดรวมใหญ่: รวมทั้งหมด · SAP · ใช้จริง (Jan–Mar) / Approved · งบ / Pending · รออนุมัติ · Cost Center ที่ปรากฏ: 10IT013000 เท่านั้น (GL 6211100110, 6211400010, 6210400010) ไม่มีฝ่ายอื่นปน</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P8" s="22" t="n"/>
       <c r="Q8" s="22" t="n"/>
       <c r="R8" s="23" t="inlineStr">
@@ -1918,8 +2058,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S8" s="24" t="n"/>
-      <c r="T8" s="21" t="n"/>
+      <c r="S8" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T8" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 2-5 · ข้อ 1 (ต้องเห็น 2 ฝั่ง): เห็นฝั่งเดียว — ยืนยันจากโค้ด GridTable.tsx:1156 ว่าฝั่งที่ไม่มีแถวถูกซ่อนโดยตั้งใจ จึงไม่ใช่ defect แต่ Expected ข้อ 1 ควรเขียนเพิ่มว่า 'ฝั่งที่ไม่มีแถวจะไม่แสดง' · 10IT011300 ไม่ปรากฏเพราะยังไม่มีแถวใด ๆ (ทั้ง Pending และ SAP) — ตรงเงื่อนไข 'มีเฉพาะ' แต่ควรให้คนยืนยันว่าถูกต้องตามสิทธิ์จริง</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="240" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
@@ -1991,8 +2137,16 @@
 ชั้น SAP และชั้น Approved เป็นข้อมูลของปีก่อนโดยการออกแบบ ผู้กรอกใช้เป็นฐานในการวางแผนปีหน้า ไม่ใช่ข้อผิดพลาด · ถ้าปีที่กำกับไม่ใช่ 2026 นั่นคือของจริงที่ต้องแจ้งเป็น defect</t>
         </is>
       </c>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
+      <c r="N9" s="51" t="inlineStr">
+        <is>
+          <t>legend: 'SAP · ใช้จริง (2026)' และ 'Approved · งบอนุมัติ (2026)' = ปีวางแผน 2027 ลบหนึ่ง ตรงกัน · ชั้น SAP เป็นเซลล์ข้อความ (data-testid sap-value-*) ไม่มี input พิมพ์ทับไม่ได้ · ชั้น Approved เป็นเซลล์ข้อความ (board-value-*) ไม่มี input พิมพ์ทับไม่ได้ · ข้อ 5-6: ไล่ทุกแถวของ Data &amp; Analytic แล้ว ไม่พบแถวที่มีตัวเลขเฉพาะชั้น Approved — ชั้น Approved ว่างทุกแถว (รวมทั้งหมด · Approved · งบ = —)</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P9" s="22" t="n"/>
       <c r="Q9" s="22" t="n"/>
       <c r="R9" s="23" t="inlineStr">
@@ -2000,8 +2154,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S9" s="24" t="n"/>
-      <c r="T9" s="21" t="n"/>
+      <c r="S9" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T9" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ข้อ 1-3 ผ่าน · ข้อ 4 ตรวจไม่ได้ในฝ่ายนี้เพราะไม่มีแถว Approved-only เลย บันทึกว่า 'ไม่พบ' ตาม Expected ข้อ 5 ไม่ถือเป็น Fail · ถ้าต้องการพิสูจน์ข้อ 4 จริง ต้องใช้ฝ่ายที่มีข้อมูล board_budget ปี 2026</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="228" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
@@ -2072,7 +2232,11 @@
 เคสนี้ตรวจว่าผู้ใช้เข้าใจการซ่อนข้อมูลหรือไม่ ไม่ใช่การกระทบยอด SAP กับ SAP ซึ่งอยู่นอกขอบเขตของ UAT รอบนี้</t>
         </is>
       </c>
-      <c r="N10" s="21" t="n"/>
+      <c r="N10" s="51" t="inlineStr">
+        <is>
+          <t>ชั้น SAP: เดือน Apr–Dec (m04–m12) แสดงเป็นขีด '–' (ข้อมูลยังไม่ครบ) · Jan–Feb แสดง '—' (ครบแต่เป็นศูนย์) · Mar มีตัวเลข 844.91 / 500.00 · tooltip บนขีด = 'ข้อมูล SAP เดือนนี้ยังไม่ครบ จึงยังไม่แสดง' · tooltip บนยอดรวมทั้งปีชั้น SAP = 'รวมเฉพาะเดือนที่ข้อมูลครบ: Jan–Mar' และหัวยอดรวมใหญ่เขียน 'รวมทั้งหมด · SAP · ใช้จริง (Jan–Mar)'</t>
+        </is>
+      </c>
       <c r="O10" s="21" t="n"/>
       <c r="P10" s="22" t="n"/>
       <c r="Q10" s="22" t="n"/>
@@ -2081,8 +2245,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S10" s="24" t="n"/>
-      <c r="T10" s="21" t="n"/>
+      <c r="S10" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T10" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ข้อ 1-3 ตรงตาม Expected ทุกตัวอักษร · ข้อ 4 เป็นความเห็นของคนว่าอ่านแล้วเข้าใจไหม — AI ไม่ตัดสินแทน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยน Status เป็น Pass เอง</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="216" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
@@ -2154,8 +2324,16 @@
 UAT รอบนี้รันบนระบบจริง ค่าที่กรอกถูกเขียนลงฐานข้อมูลจริงของปีงบประมาณ 2027 · เมื่อทดสอบเสร็จให้แก้ค่ากลับเป็นตัวเลขที่ฝ่ายต้องการใช้จริง</t>
         </is>
       </c>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
+      <c r="N11" s="51" t="inlineStr">
+        <is>
+          <t>ช่องทดสอบ: Pending ของ 10IT013000 / 6211100110 เดือน Jan ค่าเดิม 0 · พิมพ์ 100000 แล้วออกจากช่อง (Tab) ไม่มีปุ่ม Save · รวมทั้งปีของแถวขึ้นเป็น 100,000.00 ทันที · reload ทั้งหน้าแล้วช่อง Jan ยังเป็น 100000 รวมทั้งปี 100,000.00 · ป้ายสถานะบนแถบอนุมัติ = 'Draft — not submitted' (อังกฤษ) และยังกรอกได้</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P11" s="22" t="n"/>
       <c r="Q11" s="22" t="n"/>
       <c r="R11" s="23" t="inlineStr">
@@ -2163,8 +2341,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S11" s="24" t="n"/>
-      <c r="T11" s="21" t="n"/>
+      <c r="S11" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T11" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1, 3, 4 · ข้อ 2 (ข้อความ 'กำลังบันทึก…' ขึ้นแล้วหายเอง) automation อ่านหน้าจอไม่ทันช่วงสั้น ๆ นั้น จึงยังไม่ได้ยืนยันด้วยตา — ให้ผู้ทดสอบสังเกตในรอบจริง · เบี่ยงเบนจาก step 1: เคสระบุให้ใช้ Cost Center 10IT011300 แต่ CC นั้นไม่มีแถวใดในตารางเลย (ยังไม่ได้เพิ่มรายการ) จึงใช้ 10IT013000 แทน — ควรแก้เคสให้เพิ่มแถวก่อน หรือระบุ 10IT013000</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="204" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
@@ -2237,8 +2421,16 @@
 ตัวเลขที่กรอกในเคสนี้ถูกบันทึกลงระบบจริง เมื่อทดสอบเสร็จให้แก้กลับเป็นตัวเลขที่ฝ่ายต้องการใช้จริง</t>
         </is>
       </c>
-      <c r="N12" s="21" t="n"/>
-      <c r="O12" s="21" t="n"/>
+      <c r="N12" s="51" t="inlineStr">
+        <is>
+          <t>แถว 10IT013000 / 6211100110 · ก่อน: รวมทั้งปี 100,000.00 / รวมกลุ่ม Maintenance - License for software · Pending 100,000.00 / รวมทั้งหมด · Pending 100,000.00 · กรอก Feb 10,000, Mar 20,000, Apr 5,500 · หลัง: รวมทั้งปี 135,500.00 / รวมกลุ่ม 135,500.00 / รวมทั้งหมด 135,500.00 — ทั้ง 3 จุดเพิ่มขึ้น 35,500.00 พอดี (10,000 + 20,000 + 5,500) ขยับทันทีโดยไม่ต้อง reload · ตัวเลขคั่นหลักพันและมีทศนิยม 2 ตำแหน่ง</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P12" s="22" t="n"/>
       <c r="Q12" s="22" t="n"/>
       <c r="R12" s="23" t="inlineStr">
@@ -2246,8 +2438,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S12" s="24" t="n"/>
-      <c r="T12" s="21" t="n"/>
+      <c r="S12" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T12" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-5 ทุกข้อ ผลบวกตรงเครื่องคิดเลข</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="156" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
@@ -2315,7 +2513,11 @@
 ข้อนี้วัดว่าผู้ใช้เข้าใจกติกาก่อนกรอกหรือไม่ ไม่ใช่วัดแค่ว่ามีข้อความอยู่จริง · ถ้าอ่านแล้วยังไม่เข้าใจ ให้เขียนคำที่อยากให้แก้ลงช่อง Remarks แม้ผลจะเป็น Pass</t>
         </is>
       </c>
-      <c r="N13" s="21" t="n"/>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>เปิดหน้า Data &amp; Analytic Year 2026 โดยยังไม่กรอกอะไร ใต้ toolbar ข้าง legend มีบรรทัด: 'หมายเหตุ: กรอกได้ตั้งแต่ 100 ขึ้นไป โดยระบบจะปรับตัวเลข 2 หลักสุดท้ายเป็น 00 โดยอัตโนมัติ' เห็นก่อนเริ่มกรอก</t>
+        </is>
+      </c>
       <c r="O13" s="21" t="n"/>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="22" t="n"/>
@@ -2324,8 +2526,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S13" s="24" t="n"/>
-      <c r="T13" s="21" t="n"/>
+      <c r="S13" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T13" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ข้อ 1-2 ตรง Expected · ข้อ 3 (อ่านแล้วเข้าใจไหม) เป็นความเห็นของคน — ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass เอง</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="620" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
@@ -2410,8 +2618,16 @@
 เคสนี้รวม 4 เคสเดิมจาก SIT (TC-011, TC-012, TC-013, TC-035) ไว้ในแถวเดียว เป็นหนึ่งแถวบนชีตแต่มี 6 บรรทัดที่ต้องยืนยันผลแยกกัน ให้อ่าน Expected Result ให้ครบทั้ง 9 ข้อก่อนกด Pass · บรรทัดที่ 3 คือการทดสอบซ้ำที่ SIT ขอไว้แล้วยังไม่เคยได้ทำ — TC-013 กรอก `999999999999` แล้วหน้าจอแสดงผลเป็นสัญลักษณ์ infinity จึงต้องใช้ค่าสิบสองหลักชุดเดิมเป๊ะ ๆ ไม่ใช่ค่าที่สั้นกว่านั้น ไม่อย่างนั้นถือว่ายังไม่ได้ทดสอบซ้ำตามที่ SIT ขอ · บรรทัดที่ 4 มาจาก TC-035 ซึ่งของเดิมกรอก 33,333.33 หลายรายการเพื่อดูว่าปัดเศษสะสมกันแล้วยอดรวมคลาดเคลื่อนหรือไม่ จึงต้องกรอกให้ครบ 3 ช่องและตรวจยอด `รวมทั้งปี` ด้วย การกรอกช่องเดียวไม่ครอบคลุมสิ่งที่ SIT ทดสอบไว้ · ค่าที่กรอกทุกบรรทัดถูกเขียนลงฐานข้อมูลจริงของปีงบประมาณ 2027 เสร็จแล้วต้องแก้ทั้ง 4 ช่องกลับเป็นค่าที่ฝ่ายต้องการใช้จริง</t>
         </is>
       </c>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="21" t="n"/>
+      <c r="N14" s="51" t="inlineStr">
+        <is>
+          <t>แถวทดสอบ 10IT013000 / 6211100110 · ช่องทดสอบหลัก = May · ช่องทศนิยม = Jun, Jul, Aug (เดิม 0 ทั้ง 4 ช่อง) · บรรทัด1: พิมพ์ 146 → ช่อง 100 / ข้อความ 'กรอก 146 · ระบบปรับเป็น 100 (ปัดเศษเป็นหลักร้อย)' / รวมทั้งปี 135,600.00 · ข้อความหายเองภายใน 7 วินาที (ตรวจซ้ำแล้วไม่เหลือ) · บรรทัด2: พิมพ์ 30 → ช่อง 0 / 'กรอก 30 ซึ่งต่ำกว่า 100 · ระบบบันทึกเป็น 0 (กรอกได้ตั้งแต่ 100 ขึ้นไป)' / รวม 135,500.00 · บรรทัด3: พิมพ์ 999999999999 (12 หลัก) → ช่อง 100,000,000 / 'กรอก 999,999,999,999 ซึ่งเกินเพดาน 100 ล้านต่อช่อง · ระบบบันทึกเป็น 100,000,000' / รวม 100,135,500.00 · ไม่มีสัญลักษณ์ infinity ทั้งในช่องและยอดรวม · บรรทัด4: ยอดตั้งต้นของบรรทัดที่ 4 (อ่านสด) = 100,135,500.00 · พิมพ์ 33333.33 ลง Jun, Jul, Aug → ทั้ง 3 ช่องได้ 3,333,300 (ข้อความ 'กรอก 3,333,333 · ระบบปรับเป็น 3,333,300 (ปัดเศษเป็นหลักร้อย)' ยืนยันว่าตัดจุดทิ้ง) · ยอดหลังของบรรทัดที่ 4 = 110,135,400.00 · ผลต่าง = 9,999,900.00 พอดี · บรรทัด5: พิมพ์ abc ต่อท้าย แล้ว @#$ ต่อท้าย → ช่องคง 100000000 ไม่เปลี่ยน ไม่มีข้อความ · บรรทัด6: ลบค่าเดิมแล้วพิมพ์ -5000 → ช่อง 5000 (เครื่องหมายลบถูกตัด) ไม่มีข้อความ / รวม 10,140,400.00 · ข้อ10: คืนค่าทั้ง 4 ช่องเป็น 0 แล้ว</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P14" s="22" t="n"/>
       <c r="Q14" s="22" t="n"/>
       <c r="R14" s="23" t="inlineStr">
@@ -2419,8 +2635,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S14" s="24" t="n"/>
-      <c r="T14" s="21" t="n"/>
+      <c r="S14" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T14" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านครบทั้ง 6 บรรทัดและ Expected ข้อ 1-9 · ข้อความแจ้งเตือนขึ้นทุกบรรทัดที่มีการปัดค่า (1, 2, 3, 4) และเงียบในบรรทัด 5, 6 ตามที่ Expected ระบุ · การจับเวลา 6 วินาที: automation ตรวจที่ 7 วินาทีแล้วข้อความหายไปแล้ว ไม่ได้จับเวลาละเอียดกว่านั้น</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="204" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
@@ -2494,8 +2716,16 @@
 ถ้าเผลอเพิ่มแถวสำเร็จระหว่างทดสอบ ให้ลบแถวนั้นออกด้วยปุ่ม `ลบรายการนี้` (วิธีลบอยู่ในเคส UAT-17)</t>
         </is>
       </c>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="21" t="n"/>
+      <c r="N15" s="51" t="inlineStr">
+        <is>
+          <t>กรณี1 (ว่างทั้งคู่ กดบันทึก): ระบบไม่บันทึก แสดงข้อความเดียวคือ 'กรุณาเลือก Cost Center' — ไม่แสดง 'กรุณาเลือก GL Code' พร้อมกัน · กรณี2 (เลือก 10IT011300 แล้วกดบันทึก): ไม่บันทึก แสดง 'กรุณาเลือก GL Code' · กรณี3 (เลือกคู่ที่มีอยู่ 10IT013000 + 6211100110 แล้วกดบันทึก): ไม่บันทึก แสดง 'รายการนี้มีอยู่ในตารางแล้ว' · ตารางยังมี 3 แถวเท่าเดิม ไม่มีแถวซ้ำ</t>
+        </is>
+      </c>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
       <c r="P15" s="22" t="n"/>
       <c r="Q15" s="22" t="n"/>
       <c r="R15" s="23" t="inlineStr">
@@ -2503,8 +2733,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S15" s="24" t="n"/>
-      <c r="T15" s="21" t="n"/>
+      <c r="S15" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T15" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] Fail เฉพาะ Expected ข้อ 1: เคสคาดว่าจะเห็นข้อความ 2 ช่องพร้อมกัน แต่ระบบแจ้งทีละช่อง (ช่องแรกที่ขาดก่อน) — พฤติกรรมเดียวกับฟอร์มย่อย จึงน่าจะเป็นความตั้งใจของระบบ ให้คุณตัดสินว่ายอมรับได้ (แล้วแก้ Expected ข้อ 1) หรือถือเป็น defect · ข้อ 2, 3, 4 ผ่าน · ข้อ 3 ส่วน 'อ่านเข้าใจไหม' เป็นความเห็นของคน</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="240" customHeight="1">
       <c r="A16" s="18" t="inlineStr">
@@ -2580,8 +2816,16 @@
 กติกาจำกัด GL อบรมและสัมมนาให้เฉพาะฝ่าย Talent &amp; Culture เพิ่งเพิ่มเข้ามาหลังปิดรอบ SIT (2026-08-29) · เคส SIT เดิม TC-057 ยังเขียนว่าฝ่าย Data &amp; Analytic กรอก GL 6210100150 ได้ — ข้อความเดิมล้าสมัยแล้ว ไม่ใช่ข้อผิดพลาดของระบบ · ทำเคสนี้ติดกับ UAT-15 เพราะสองเคสต้องเอาผลมาเทียบกัน</t>
         </is>
       </c>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
+      <c r="N16" s="51" t="inlineStr">
+        <is>
+          <t>ฟอร์ม + เพิ่ม Transaction (Data &amp; Analytic, Year 2026) · ยังไม่เลือก Cost Center: ค้นหา 5210100150 → 'ไม่พบ GL CODE ที่ค้นหา' · ค้นหา 6210100150 → 'ไม่พบ GL CODE ที่ค้นหา' · เลือก Cost Center 10IT011300 แล้วค้นหาซ้ำทั้งสองตัว → ยังไม่พบเหมือนเดิม · ตรวจสอบว่าช่องค้นหาทำงาน: พิมพ์ 62101 พบ 6 รายการ (6210100080, 6210100090, 6210100100, 6210100110, 6210100130, 6210100140) ไม่มี 6210100150 อยู่ในรายการ · ปิดฟอร์มด้วย ยกเลิก · ตารางหลักไม่มีแถวเดิมของ GL คู่นี้ในฝ่ายนี้ (แถวที่มี: 6211100110, 6211400010, 6210400010) จึงบันทึกว่าไม่มีแถวเดิมให้ตรวจข้อ 4-5</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P16" s="22" t="n"/>
       <c r="Q16" s="22" t="n"/>
       <c r="R16" s="23" t="inlineStr">
@@ -2589,8 +2833,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S16" s="24" t="n"/>
-      <c r="T16" s="21" t="n"/>
+      <c r="S16" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T16" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-3 · ข้อ 4-5 ไม่มีแถวเดิมให้ทดสอบ บันทึกตามข้อ 6 · การซ่อนเป็นกติกาที่ตั้งไว้ 2026-08-29 (Training &amp; Seminar → Talent &amp; Culture เท่านั้น)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="204" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
@@ -2663,8 +2913,16 @@
 ผู้ที่เป็น admin จริงมี 3 คนเท่านั้น คือ jakkaritw, nipapornt และ warapornt — Pornthip และ Laddawan ไม่ใช่ admin จึงใช้ทดสอบเคสนี้ไม่ได้ · ให้ทำต่อจาก UAT-14 ทันที เพราะผลของสองเคสต้องเทียบกัน · ไม่ต้องกดบันทึกแถวใหม่ แค่ดูว่าเลือกได้หรือไม่ก็พอ · จดลงช่อง Actual Result ด้วยว่าขณะทดสอบเปิดสวิตช์ `โหมด Admin` ไว้หรือไม่ เพื่อให้อ่านผลย้อนหลังได้ชัดเจน</t>
         </is>
       </c>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
+      <c r="N17" s="51" t="inlineStr">
+        <is>
+          <t>สลับสวมสิทธิ์เป็น nipapornt สำเร็จ (/me = nipapornt, role badge = ผู้ดูแลระบบ, ฝ่าย 5, มีป้ายย่อ '+1 สายงาน' และ '+2' — ยืนยันกติกาย่อชื่อของ UAT-01 ข้อ 7-8 ในกรณี &gt;3 ชื่อ) · พบ toggle 'โหมด Admin' (data-testid admin-mode-toggle / admin-mode-checkbox) ค่าเริ่มต้นปิด · ขั้นเปิดโหมด Admin และค้น GL ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อกไว้ จึงยังไม่ได้ตรวจข้อ 1-3</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="P17" s="22" t="n"/>
       <c r="Q17" s="22" t="n"/>
       <c r="R17" s="23" t="inlineStr">
@@ -2672,8 +2930,14 @@
           <t>Nipaporn หรือ Waraporn</t>
         </is>
       </c>
-      <c r="S17" s="24" t="n"/>
-      <c r="T17" s="21" t="n"/>
+      <c r="S17" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T17" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ให้คนทำ (ใช้เวลา ~1 นาที): สวมสิทธิ์ nipapornt → เปิด toggle โหมด Admin → เลือก Data &amp; Analytic → + เพิ่ม Transaction → ค้น 5210100150 และ 6210100150 ต้องพบทั้งคู่ · ห้ามกด Submit ระหว่างเปิดโหมด Admin (approval.py:987 จะ Approved ทันที)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="216" customHeight="1">
       <c r="A18" s="18" t="inlineStr">
@@ -2746,8 +3010,16 @@
 GL คู่นี้เพิ่งถูกย้ายออกจากฟอร์มทริปเดินทางเมื่อ 2026-09-04 ถึง 2026-09-05 — เอกสาร SIT เดิมยังเขียนว่าอยู่ในฟอร์มทริป ข้อความเดิมล้าสมัยแล้ว ไม่ใช่ข้อผิดพลาด · ให้ลบเฉพาะแถวที่ตัวเองเพิ่งเพิ่มในเคสนี้ ห้ามลบแถวที่มียอดของฝ่ายอยู่จริง · เคส UAT-53 จะกลับมาตรวจ GL `6210400999` อีกครั้งในเรื่องเงินหายเงียบ</t>
         </is>
       </c>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
+      <c r="N18" s="51" t="inlineStr">
+        <is>
+          <t>เพิ่มแถว 10IT011300 + 6210400999 ผ่านฟอร์ม + เพิ่ม Transaction สำเร็จ แถวอยู่ฝั่ง SG&amp;A (6xxx) · ท้ายแถวมีปุ่มลบ (delete-row) และช่อง Remark ไม่มีปุ่ม 'แก้ไขผ่านฟอร์มย่อย' · กรอก Jan 5,000 → รวมทั้งปี 5,000.00 · แก้เป็น 7,000 → 7,000.00 · reload แล้วยังเป็น 7,000 · เพิ่มแถว 10IT011300 + 5210400999 สำเร็จ ฝั่ง 'ฝั่งผลิต / ต้นทุน (5xxx)' ปรากฏขึ้นทันทีที่มีแถว 5xxx แถวแรก · ไม่มีปุ่มฟอร์มย่อยเช่นกัน · กรอก 5,000 → 7,000 → reload ยังเป็น 7,000 · ลบทั้งสองแถวด้วยปุ่มลบ มีกล่องยืนยันก่อนลบ แถวหายทั้งคู่</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P18" s="22" t="n"/>
       <c r="Q18" s="22" t="n"/>
       <c r="R18" s="23" t="inlineStr">
@@ -2755,8 +3027,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S18" s="24" t="n"/>
-      <c r="T18" s="21" t="n"/>
+      <c r="S18" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T18" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-5 ทุกข้อ · ยืนยันข้อสังเกตจาก UAT-06 ว่าฝั่ง 5xxx แสดงเมื่อมีแถว 5xxx เท่านั้น</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="180" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
@@ -2829,8 +3107,16 @@
 การลบแถวย้อนกลับไม่ได้จากหน้าจอ ให้ลบเฉพาะแถวที่ตัวเองเพิ่งเพิ่มขึ้นมาเพื่อทดสอบเท่านั้น ห้ามลบแถวที่มียอดงบของฝ่ายอยู่จริง เพราะ UAT รอบนี้เขียนลงฐานข้อมูลจริง</t>
         </is>
       </c>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
+      <c r="N19" s="51" t="inlineStr">
+        <is>
+          <t>แถวที่เพิ่มเอง (10IT011300 / 5210400999) มีปุ่ม 'ลบรายการนี้' ท้ายแถว · กดแล้วขึ้นกล่องยืนยันของเบราว์เซอร์ข้อความ: 'ลบรายการนี้? (10IT011300 · 5210400999) / ลบแล้วเรียกคืนไม่ได้' ระบบไม่ลบทันที · กดยกเลิก → แถวยังอยู่ครบ 5 แถว · กดลบอีกครั้งแล้วยืนยัน → แถวหายจากตาราง (เหลือ 4) · reload แล้วยังหายอยู่ · แถวที่ระบบสร้างเอง (10IT013000 ทั้ง 3 แถวที่มีข้อมูล SAP) ไม่มีปุ่มลบเลย</t>
+        </is>
+      </c>
+      <c r="O19" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P19" s="22" t="n"/>
       <c r="Q19" s="22" t="n"/>
       <c r="R19" s="23" t="inlineStr">
@@ -2838,8 +3124,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S19" s="24" t="n"/>
-      <c r="T19" s="21" t="n"/>
+      <c r="S19" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T19" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-5 ทุกข้อ · กล่องยืนยันเป็น window.confirm ของเบราว์เซอร์ ภาษาไทย อ่านเข้าใจ</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="288" customHeight="1">
       <c r="A20" s="18" t="inlineStr">
@@ -2914,8 +3206,16 @@
 ข้อนี้เป็นเรื่องความสะดวกในการใช้งานประจำวันกับตารางที่มี 12 เดือนและหลายแถว ถ้าใช้แล้วรู้สึกติดขัดหรืออยากได้เพิ่ม ให้เขียนลงช่อง Remarks ไว้แม้ผลจะเป็น Pass · ข้อความที่พิมพ์ในช่อง Remark ถูกบันทึกลงระบบจริง เสร็จแล้วให้ลบออกหรือแก้เป็นข้อความที่ใช้จริง</t>
         </is>
       </c>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
+      <c r="N20" s="51" t="inlineStr">
+        <is>
+          <t>ตัวกรอง: Cost Center '10IT011300' → 0 แถว (ถูกต้อง ไม่มีแถว CC นี้แล้ว) · GL '6211100110' → 1 แถว · GL Group 'Travel' → 1 แถว (6210400010) · Status 'Pending' → กรองได้ · ล้างทั้งหมด → กลับมา 3 แถวครบ · ปุ่ม Reset columns กดได้ ความกว้างกลับค่าเริ่มต้น (107/146/234/77 px) · ปุ่มเต็มจอ: กดแล้วปุ่มเปลี่ยนเป็น 'ย่อกลับขนาดปกติ (Esc)' aria-pressed=true · กด Esc → กลับเป็น 'ขยายตารางเต็มหน้าจอ' · Remark: พิมพ์ 'UAT remark test' ที่แถว 6211100110 → reload แล้วยังอยู่ · ตัวกรอง Remark 'UAT remark' → เหลือ 1 แถว · ล้าง → 3 แถว</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P20" s="22" t="n"/>
       <c r="Q20" s="22" t="n"/>
       <c r="R20" s="23" t="inlineStr">
@@ -2923,8 +3223,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S20" s="24" t="n"/>
-      <c r="T20" s="21" t="n"/>
+      <c r="S20" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T20" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1, 3, 4, 5 · ข้อ 2 (ลากเส้นแบ่งหัวคอลัมน์เพื่อขยายความกว้าง) automation ไม่ได้ทำ — ให้คนลาก 1 ครั้งแล้วดูว่าความกว้างเปลี่ยน · ข้อความ Remark ทดสอบยังค้างอยู่ในแถว 6211100110 (จะถูกล้างพร้อมข้อมูลรอบนี้)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="228" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
@@ -2995,7 +3301,11 @@
 ปีที่หน้าจอแสดงคือปีงบประมาณลบหนึ่งตามการออกแบบ จอ `Year 2026` หมายถึงปีงบประมาณ 2027 · ขณะนี้ปีงบประมาณ 2027 เป็นปีเดียวที่มีรอบเปิดรับ ปีอื่นทุกปีในรายการจะเจอข้อความปฏิเสธนี้เหมือนกัน ไม่ใช่ข้อผิดพลาด · อย่าลืมเปลี่ยนปีกลับเป็น `Year 2026` ก่อนทำเคสถัดไป</t>
         </is>
       </c>
-      <c r="N21" s="21" t="n"/>
+      <c r="N21" s="51" t="inlineStr">
+        <is>
+          <t>เปลี่ยนปีเป็น Year 2025: legend เปลี่ยนเป็น SAP (2025) / Approved (2025) / Pending (2026) · ปุ่ม '+ เพิ่ม Transaction' ถูกปิด (disabled) กดไม่ได้ และมีข้อความข้างปุ่ม 'ปีงบประมาณนี้ไม่เปิดให้กรอกในเว็บ — ข้อมูลปีนี้นำเข้าโดยผู้ดูแลระบบ' · ช่องกรอก Pending ทั้งหมดไม่มี (0 ช่อง) · แถบอนุมัติไม่มีปุ่ม Submit แสดง 'Draft — not submitted' และ 'This department has no budget data yet, so it cannot be submitted.' · เปลี่ยนกลับ Year 2026: ปุ่มเพิ่มเปิดใช้ ฟอร์มเปิดได้ ช่องกรอก 24 ช่องกลับมา ปุ่ม Submit กลับมาแสดง</t>
+        </is>
+      </c>
       <c r="O21" s="21" t="n"/>
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="22" t="n"/>
@@ -3004,8 +3314,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S21" s="24" t="n"/>
-      <c r="T21" s="21" t="n"/>
+      <c r="S21" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T21" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ข้อ 1-3 ตรง Expected (ระบบป้องกันตั้งแต่ปิดปุ่ม ไม่ต้องรอกดบันทึกแล้วปฏิเสธ — เข้มกว่าที่เคสคาด) · ข้อ 4 (ข้อความอ่านเข้าใจไหม) เป็นความเห็นของคน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="576" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
@@ -3083,8 +3399,16 @@
 เคสนี้เป็นเคสรวม 1 แถวแต่มีหลายจุดตรวจ ต้องอ่าน Expected Result ให้ครบทั้ง 7 ข้อก่อนทำเครื่องหมาย Pass · แถวที่ 3 (เดือนเดียวกับแถวที่ 1) ใส่เพิ่มโดยตั้งใจ เพื่อรักษาจุดตรวจของเคส Public Relation &amp; Donation เดิมที่ถูกยุบมารวมไว้ที่นี่ คือหลายรายการภายใต้ GL เดียวกันในเดือนเดียวกันต้องรวมยอดถูกและยังแยกแถวอยู่ · ข้อสังเกตเดิมจาก SIT ที่ยังเป็นแบบนี้โดยตั้งใจ: เมื่อเพิ่ม Transaction ของ Cost Center + GL คู่เดิมไปแล้ว จะเพิ่มซ้ำอีกไม่ได้ · ช่องยอดในฟอร์มย่อยใช้กติกาเดียวกับตารางหลัก คือรับเฉพาะตัวเลขจำนวนเต็มและปัดเป็นหลักร้อย ตัวเลขใน Test Data เป็นหลักร้อยอยู่แล้วจึงไม่ถูกปัด</t>
         </is>
       </c>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
+      <c r="N22" s="51" t="inlineStr">
+        <is>
+          <t>เลือก 10IT013000 + 6211900030 แล้วบันทึก → ฟอร์มย่อย 'รายละเอียด Entertainment' เปิดทันที ตารางหลักไม่มีแถวใหม่โผล่ · dropdown ประเภทการรับรอง = Customer / Business partner / หน่วยงานราชการ / อื่นๆ (4 ตัวเลือก ไม่นับ — เลือก —) · กรอก 3 แถวตาม Test Data: รวมแถว 1 = 25,000.00 · แถว 2 = 8,000.00 · แถว 3 = 5,000.00 · MONTHLY TOTAL ม.ค. 20,000.00 · มิ.ย. 10,000.00 · ก.ย. 8,000.00 · ท้ายฟอร์ม 'Rows: 3 · Year total: ฿38,000.00' · กดบันทึก ฟอร์มปิดเอง · ตารางหลักแถว 10IT013000 / 6211900030 Pending: ม.ค. 20,000.00 · มิ.ย. 10,000.00 · ก.ย. 8,000.00 · รวมปี 38,000.00 · GL Group แสดง 'Entertainment' · ช่องเดือนเป็นข้อความ ไม่ใช่ input มี tooltip 'แก้ไขผ่านฟอร์มย่อย' · refresh แล้วเปิดฟอร์มย่อยกลับมา ยังมี 3 แถว ยอดเท่าเดิม Rows: 3 · Year total ฿38,000.00 · GL 6211900031: dropdown = พนักงานบริษัท / กรรมการบริษัท (2 ตัวเลือก) คนละชุดกับ 6211900030</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P22" s="22" t="n"/>
       <c r="Q22" s="22" t="n"/>
       <c r="R22" s="23" t="inlineStr">
@@ -3092,8 +3416,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S22" s="24" t="n"/>
-      <c r="T22" s="21" t="n"/>
+      <c r="S22" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T22" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-7 · ข้อ 6 ส่วน 'ข้อความภาษาไทยตรงทุกตัวอักษร' automation อ่านค่า dropdown/รายละเอียดหลังเปิดกลับมาไม่สำเร็จ (selector ของ dialog ไม่ตรง) แต่ยอดต่อแถวตรงทั้ง 3 แถว — ให้คนเช็คตัวอักษรตอน UAT-23 ซึ่งเปิดฟอร์มนี้อีกครั้ง · แถว 6211900030 (38,000) คงไว้เป็นฐานให้ UAT-23</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="276" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
@@ -3168,8 +3498,16 @@
 ยอดที่ใช้ทดสอบทุกตัวเป็นจำนวนเต็มหลักร้อยอยู่แล้ว จึงไม่ถูกกติกาปัดเป็นหลักร้อยปรับค่า · ทำเคสนี้ก่อนระลอก W5 (Submit) เพราะหลัง Submit จะแก้และลบบรรทัดไม่ได้</t>
         </is>
       </c>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
+      <c r="N23" s="51" t="inlineStr">
+        <is>
+          <t>ฟอร์มย่อย 'รายละเอียด Professional &amp; Legal Fee' มีคอลัมน์ PROJECT และ รายละเอียด เป็นช่องพิมพ์แยกกัน · แถว 1 รวม 100,000.00 · แถว 2 รวม 40,000.00 · MONTHLY TOTAL ก.พ. 50,000 / พ.ค. 50,000 / ส.ค. 40,000 · ท้ายฟอร์ม 'Rows: 2 · Year total: ฿140,000.00' · บันทึกแล้วตารางหลัก 6210700020 Pending: ก.พ. 50,000.00 · พ.ค. 50,000.00 · ส.ค. 40,000.00 · รวมปี 140,000.00 · เปิดฟอร์มแก้ ก.พ. แถว 1 เป็น 51000 บันทึก → ตารางหลัก ก.พ. 51,000.00 รวมปี 141,000.00 ทันที · เปิดฟอร์มกดถังขยะแถว 2 → กล่องยืนยัน 'ลบรายการนี้?' → ยืนยัน → ฟอร์มเหลือ Rows: 1 · Year total ฿101,000.00 · บันทึก → ตารางหลัก ส.ค. แสดง '—' (ไม่ใช่ 0.00) รวมปี 101,000.00</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P23" s="22" t="n"/>
       <c r="Q23" s="22" t="n"/>
       <c r="R23" s="23" t="inlineStr">
@@ -3177,8 +3515,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S23" s="24" t="n"/>
-      <c r="T23" s="21" t="n"/>
+      <c r="S23" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T23" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-6 ทุกข้อ · แถว 6210700020 (101,000) คงไว้ในระบบเป็นข้อมูลรอบทดสอบ</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="444" customHeight="1">
       <c r="A24" s="18" t="inlineStr">
@@ -3256,8 +3600,16 @@
 คำถามข้อ 3 ในแท็บ Note ของ workbook รอบ SIT ("ข้อ TC060 : สามารถเว้นการกรอกรายละเอยดกิจกรรมได้??") ยังไม่เคยมีคำตอบเป็นลายลักษณ์อักษร เคสนี้คือการปิดคำถามนั้น จึงต้องเขียนคำตอบจริงลงช่อง Actual Result ไม่ใช่ทำเครื่องหมาย Pass อย่างเดียว</t>
         </is>
       </c>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
+      <c r="N24" s="51" t="inlineStr">
+        <is>
+          <t>GL 6211200060: ฟอร์ม 'รายละเอียด Lease &amp; Rental' มี 4 คอลัมน์ ประเภทรถ (Car/Van/Trucks) · ทะเบียนรถ (6ขผ-3918, 1นจ-3508, 6ขจ-3513, 5ขง-5712, 1นจ-1468, 6ขผ-8150, 7ขถ-9660, อื่นๆ = 7 ทะเบียน + อื่นๆ) · สถานที่ใช้งาน (BK/TK/KK/PB/RY) · กิจกรรม (ช่องพิมพ์) · แถว 2 เลือก อื่นๆ → ช่อง 'พิมพ์ทะเบียนรถ' โผล่ใต้ dropdown · กดบันทึกทั้งที่ช่องนั้นว่าง → ฟอร์มยังเปิด ข้อความใต้ตาราง 'รายการที่ N: กรุณาเลือกทะเบียนรถ' (ยืนยันซ้ำด้วยแถวทดสอบที่ 3: 'รายการที่ 3: กรุณาเลือกทะเบียนรถ') · พิมพ์ 9กก-1234 แล้วบันทึก → ฟอร์มปิด · ตารางหลัก 6211200060: เม.ย. 20,000.00 · ต.ค. 12,000.00 · รวมปี 32,000.00 · เปิดกลับมา แถว 2 dropdown ค้างที่ อื่นๆ และช่องใต้แสดง 9กก-1234 · GL 6211200050: ประเภทรถ และ ทะเบียนรถ แสดง '—' พิมพ์ไม่ได้ ส่วน สถานที่ใช้งาน (dropdown) และ กิจกรรม (พิมพ์) กรอกได้ · กรอก BK / เช่าโน้ตบุ๊กทีมวิเคราะห์ข้อมูล / ก.ค. 36000 บันทึก → ตารางหลัก ก.ค. 36,000.00 · ปิดคำถาม SIT ข้อ 3: เพิ่มแถวกรอกเฉพาะ สถานที่ใช้งาน=BK + ต.ค. 5000 เว้น กิจกรรม → ระบบไม่ยอมบันทึก ฟอร์มยังเปิด ข้อความ 'รายการที่ 2: กรุณากรอกกิจกรรม' · ลบแถวทดสอบ (ยังไม่เคยบันทึก) ระบบลบทันทีไม่มีกล่องยืนยัน · ตารางหลัก 6211200050 ยังเป็น ก.ค. 36,000.00 / ต.ค. — / รวม 36,000.00</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P24" s="22" t="n"/>
       <c r="Q24" s="22" t="n"/>
       <c r="R24" s="23" t="inlineStr">
@@ -3265,8 +3617,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S24" s="24" t="n"/>
-      <c r="T24" s="21" t="n"/>
+      <c r="S24" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T24" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-7 ทุกข้อ · คำถามค้างจาก SIT (เว้นกิจกรรมแล้วบันทึกได้ไหม) ปิดได้: บันทึกไม่ได้ ระบบระบุช่องที่ขาด · ระบบแจ้งทีละช่อง (ช่องแรกที่ขาด) ตามการออกแบบ</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="396" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
@@ -3340,8 +3698,16 @@
 นี่คือข้อร้องเรียนข้อ 2 จากรอบ SIT ที่ยังไม่ถูกปิด · ทีมพัฒนาแก้เรื่องช่องบังคับไปแล้วหลังรอบ SIT แต่ไม่เคยมีเคสในเอกสารทดสอบ รอบนี้จึงต้องบันทึกผลจริงเป็นลายลักษณ์อักษร · แถวที่สร้างในเคสนี้เป็นข้อมูลจริงในฐานข้อมูล production ต้องลบออกให้ครบตามขั้นตอนที่ 7</t>
         </is>
       </c>
-      <c r="N25" s="21" t="n"/>
-      <c r="O25" s="21" t="n"/>
+      <c r="N25" s="51" t="inlineStr">
+        <is>
+          <t>Entertainment (6211900030): เพิ่มแถวที่ 4 กรอก รายละเอียด='ทดสอบช่องบังคับ' + ต.ค. 1000 เว้น ประเภทการรับรอง ว่าง → กดบันทึก ฟอร์มยังเปิดอยู่ ไม่ปิดเอง ข้อความสีแดงใต้ตาราง 'รายการที่ 4: กรุณาเลือกประเภทการรับรอง' (ขึ้นใต้ตาราง ไม่ได้ขึ้นบนแถว) · เลือกประเภท อื่นๆ แล้วบันทึก → ฟอร์มปิดเอง ตารางหลักรวมปี 38,000 → 39,000 · Lease &amp; Rental (6211200060): เพิ่มแถวที่ 3 กรอกเฉพาะ สถานที่ใช้งาน=BK + ต.ค. 1000 → กดบันทึก ฟอร์มยังเปิด ข้อความ 'รายการที่ 3: กรุณาเลือกประเภทรถ' (แจ้งช่องแรกที่ขาดทีละช่อง) · ลบแถวทดสอบ Lease (ยังไม่เคยบันทึก) หายทันทีไม่มีกล่องยืนยัน ตารางหลัก 6211200060 ยังเป็น 32,000.00 · หลังล็อกอินใหม่ ลบแถว Entertainment ที่บันทึกแล้ว (แถว 4) → กล่องยืนยัน 'ลบรายการนี้?' → ยืนยัน → บันทึก → ตารางหลัก 6211900030 กลับเป็น 38,000.00 เท่าก่อนเริ่มเคส</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P25" s="22" t="n"/>
       <c r="Q25" s="22" t="n"/>
       <c r="R25" s="23" t="inlineStr">
@@ -3349,8 +3715,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S25" s="24" t="n"/>
-      <c r="T25" s="21" t="n"/>
+      <c r="S25" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T25" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-6 ทุกข้อ · ข้อร้องเรียน SIT ข้อ 2 ไม่เกิดซ้ำ: กรอกไม่ครบบันทึกไม่ได้ทั้ง Entertainment และ Lease &amp; Rental · ระบบแจ้งช่องที่ขาดทีละช่อง ใต้ตาราง ตามการออกแบบ</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="620" customHeight="1">
       <c r="A26" s="18" t="inlineStr">
@@ -3433,8 +3805,16 @@
 เคสรวม 1 แถวแต่มี 8 จุดตรวจ ต้องอ่าน Expected Result ให้ครบก่อนทำเครื่องหมาย Pass · เอกสาร sign-off ฉบับเดิม (Spec B และ 01_special_gl_subform_spec.docx) ยังเขียนว่าตาราง B มี 4 แถว รวม "ค่าใช้จ่ายเดินทางอื่น 5210400999 / 6210400999" — ตัดสินแล้วเมื่อ 2026-09-06 ว่าไม่แก้เอกสาร ระบบจริงมี 3 แถวถูกต้องแล้ว อย่าแจ้งเป็น defect · GL 6210400999 ตอนนี้เป็นแถวกรอกยอดตรงในตารางหลัก ทดสอบแยกที่ UAT-16 · การตรวจตัวเลขเบี้ยเลี้ยงด้วยมืออยู่ที่ UAT-25 เคสนี้ยังไม่ต้องคำนวณเอง</t>
         </is>
       </c>
-      <c r="N26" s="21" t="n"/>
-      <c r="O26" s="21" t="n"/>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>เลือก 10IT013000 + 6210400020 บันทึก → หน้าต่าง 'Travelling Expense — จัดการทริป 10IT013000 · FY2027' เปิด · ฝั่งบัญชี ล็อกที่ 'ฝั่งบริหาร / ขาย · SG&amp;A (6xxx)' (disabled) · กด บันทึก &amp; ลงบัญชี ก่อนเลือกผู้เดินทาง → หน้าต่างยังเปิด การ์ดขึ้น 'กรุณาระบุผู้เดินทาง' · ช่องผู้เดินทางพิมพ์ 'พรทิพย์' → ตัวเลือก 'พรทิพย์ เพิ่มทรัพย์หิรัญ · Supervisor 2 pornthipp@chememan.com' · ช่องปลายทางพิมพ์ 'Sing' → เหลือ Singapore เลือกได้ · ล้างคำค้นเห็นรายการ 29 ประเทศ ไม่มีป้ายชื่อกลุ่ม เริ่มด้วย Thailand ตามด้วย Bangladesh, Cambodia, China, India, Indonesia, Laos, Malaysia… ท้ายรายการ Singapore, South Korea, Switzerland, Taiwan, United Kingdom, United States · เลือกประเทศท้ายรายการ United Kingdom ได้ (จดไว้ให้ admin ยืนยันกลุ่ม) แล้วเปลี่ยนกลับเป็น Singapore · กรอก Project/วัตถุประสงค์/จำนวนวัน 5 เลือกเดือน May · ตาราง 'B — ค่าใช้จ่าย 3 ประเภท' มี 3 แถว: เบี้ยเลี้ยง Per Diem 6210400010 (ไม่มีช่องกรอก ข้อความ 'ระบบจะคำนวณให้หลังกดบันทึก') · ค่าพาหนะเดินทาง 6210400020 · ค่าที่พัก 6210400030 · ไม่มีแถว 6210400999 · เดือนที่ไม่เลือกแสดง — tooltip 'เดือนนี้ไม่ได้เลือกเดินทาง' · ช่อง May ของแถวเบี้ยเลี้ยง tooltip 'คำนวณโดยเซิร์ฟเวอร์ — แก้ไขไม่ได้' · กรอกค่าพาหนะ May 18000 ค่าที่พัก May 25000 รายละเอียด 'ค่าวีซ่าและประกันการเดินทาง' บันทึก &amp; ลงบัญชี → แถวเบี้ยเลี้ยง May 13,200.00 พร้อม '5 วัน · เฉลี่ยจากเซิร์ฟเวอร์' · ตารางหลักแยก 3 แถว: 6210400020 May 18,000.00 · 6210400030 May 25,000.00 · 6210400010 May 13,200.00 ทุกช่องเป็นข้อความ พิมพ์ไม่ได้ · reload แล้วเปิด Trip Manager กลับมา มี 1 ทริป ค่าหัวทริปครบ (Singapore / Data Platform Phase 2 / ประชุมผู้ให้บริการระบบข้อมูล / 5 วัน) ยอด 18,000 / 25,000 และรายละเอียดครบ · ทดสอบข้อความ 490 ตัวอักษร บันทึก ปิด reload เปิดกลับ ได้ครบ 490 ตัวอักษรตรงทุกตัว</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P26" s="22" t="n"/>
       <c r="Q26" s="22" t="n"/>
       <c r="R26" s="23" t="inlineStr">
@@ -3442,8 +3822,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S26" s="24" t="n"/>
-      <c r="T26" s="21" t="n"/>
+      <c r="S26" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T26" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-8 ทุกข้อ · ข้อ 4 tooltip ช่องเบี้ยเลี้ยงที่เห็นจริง = 'คำนวณโดยเซิร์ฟเวอร์ — แก้ไขไม่ได้' (บันทึกผลตามที่เคสสั่ง ไม่ตัดสิน) · ข้อสังเกต: การจัดกลุ่มประเทศมาจาก master ที่ admin ดูแล — Singapore/South Korea/Taiwan อยู่ท้ายรายการ (กลุ่มต่างประเทศอื่น) ขณะที่ Malaysia/Indonesia อยู่กลุ่มอาเซียน ให้ admin ยืนยันว่าตั้งใจ · ยอดเบี้ยเลี้ยง 13,200.00 = 5 วัน × 80 USD × 33 ตรงกับตัวอย่างในเคส UAT-25</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="540" customHeight="1">
       <c r="A27" s="18" t="inlineStr">
@@ -3517,8 +3903,16 @@
 นี่คือยอดเงินที่ระบบคำนวณเองทั้งก้อน และรอบ SIT ไม่เคยตรวจตัวเลขจริงเลย (เคสเดิมเขียนแค่ว่า "ยอดเบี้ยเลี้ยงที่ระบบคำนวณ" โดยไม่ระบุจำนวนเงิน) · อัตราเบี้ยเลี้ยงขึ้นกับตำแหน่งของผู้เดินทางและกลุ่มประเทศของปลายทาง (ในประเทศ / ต่างประเทศ / ต่างประเทศ-อื่นๆ) ทั้งสองอย่างเป็นตาราง master ที่ผู้ดูแลระบบเป็นเจ้าของ ถ้าตัวเลขไม่ตรงให้ตรวจ master ก่อนแจ้งเป็น defect · ทำไมเคสนี้ไม่ระบุชื่อปลายทางในประเทศตายตัว: ชื่อประเทศทุกชื่อในช่องปลายทางมาจากตาราง master ของผู้ดูแลระบบ (dbo.country_group) ตอนเขียนเอกสารนี้เปิดฐานข้อมูลจริงเพื่อยืนยันตัวสะกดไม่ได้ (เซิร์ฟเวอร์ไม่ตอบ) จึงให้ผู้ทดสอบเลือกจากรายการจริงแล้วจดชื่อไว้ วิธีเดียวกับที่ UAT-24 ให้จดชื่อประเทศที่เลือก · ที่มาของเคส: ช่องว่าง §F ของรายงานการตรวจความครอบคลุมรอบ SIT</t>
         </is>
       </c>
-      <c r="N27" s="21" t="n"/>
-      <c r="O27" s="21" t="n"/>
+      <c r="N27" s="51" t="inlineStr">
+        <is>
+          <t>ทริป A (ต่างประเทศ): พรทิพย์ เพิ่มทรัพย์หิรัญ (ตำแหน่ง Supervisor 2) · Singapore · 5 วัน · เม.ย. → ระบบคำนวณเบี้ยเลี้ยง = 13,200.00 (ตัวเลขที่ 1) · คำนวณด้วยมือจาก master: Singapore อยู่กลุ่ม 'other' → อัตรา Supervisor 2 rate_other = 80 USD/วัน · อัตราแลกเปลี่ยนปี 2027 = 33.0000 → 5 × 80 × 33 = 13,200.00 (ตัวเลขที่ 2) ตรงกันทุกสตางค์ · ทริป B (ในประเทศ): ปลายทาง 'Thailand' (รายการแรกใน dropdown, กลุ่ม domestic) · 3 วัน · มิ.ย. → ระบบคำนวณ = 750.00 · คำนวณด้วยมือ: rate_domestic Supervisor 2 = 250 บาท/วัน × 3 = 750.00 ไม่คูณอัตราแลกเปลี่ยน ตรงกัน · ตารางหลักแถว 6210400010: เม.ย. 13,200.00 (ทริป A) · พ.ค. 13,200.00 (ทริปของ UAT-24) · มิ.ย. 750.00 (ทริป B) · รวมปี 27,150.00 = ผลรวมถูกต้อง · ไม่พบข้อความแดง 'ไม่สามารถคำนวณเบี้ยเลี้ยงได้' เพราะ master ครบ</t>
+        </is>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P27" s="22" t="n"/>
       <c r="Q27" s="22" t="n"/>
       <c r="R27" s="23" t="inlineStr">
@@ -3526,8 +3920,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S27" s="24" t="n"/>
-      <c r="T27" s="21" t="n"/>
+      <c r="S27" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T27" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-5 · อัตราอ่านจาก dbo.per_diem_rate (Supervisor 2: domestic 250 / asian 70 USD / other 80 USD), dbo.country_group (Singapore=other, Thailand=domestic), dbo.master_currency_rate (2027 = 33.0000) ณ 2026-09-08 06:31 · ข้อสังเกตให้ admin ยืนยัน: Singapore ถูกจัดกลุ่ม 'other' ไม่ใช่ 'asian'</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="456" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
@@ -3601,8 +4001,16 @@
 การลบทริปย้อนกลับไม่ได้ ฐานข้อมูลเป็นของจริง (production) และมีทริปเดิมของผู้ใช้คนอื่นอยู่ก่อนแล้ว ให้ลบเฉพาะทริปที่สร้างขึ้นเองในเคสนี้เท่านั้น · ห้ามลบทริปที่สร้างไว้ใน UAT-24 และ UAT-25 เพราะ UAT-53 (เงินต้องไม่หายเงียบ) ต้องใช้ทริปของระลอก W3 ที่ยังเหลืออยู่อย่างน้อย 1 ใบไปทดสอบการลบ · **หยุด — กลับไปทำ UAT-52 ข้อ 2 (กรอกจำนวนวันเดินทางติดลบ) ตอนนี้ ก่อนเริ่ม UAT-32** เพราะหลังกด `Submit` ในเคส UAT-32 ระบบจะล็อกการแก้ไขทั้งฝ่าย Trip Manager จะเปิดได้แบบอ่านอย่างเดียวและไม่มีปุ่ม `บันทึก &amp; ลงบัญชี` ให้กดอีกเลยตลอดรอบ — ตอนนี้คือช่วงเดียวที่ทดสอบข้อนั้นได้ · ที่มาของเคส: ช่องว่าง §F ของรายงานการตรวจความครอบคลุมรอบ SIT</t>
         </is>
       </c>
-      <c r="N28" s="21" t="n"/>
-      <c r="O28" s="21" t="n"/>
+      <c r="N28" s="51" t="inlineStr">
+        <is>
+          <t>ทริปใหม่: พรทิพย์ · Thailand (ตัวเดียวกับทริป B ของ UAT-25) · Data Platform Phase 2 · ตรวจงานที่โรงงาน 2 รอบ · 4 วัน · เลือก 2 เดือน ก.ค.+ส.ค. · ค่าพาหนะ ก.ค. 6000 · ค่าที่พัก ส.ค. 9000 · บันทึก &amp; ลงบัญชี → เบี้ยเลี้ยง ก.ค. 500.00 / ส.ค. 500.00 / รวมทริป 1,000.00 พร้อม '4 วัน · เฉลี่ยจากเซิร์ฟเวอร์' (4 × 250 = 1,000 กระจาย 2 เดือนเท่ากัน ไม่มีเศษ) · แก้ TOTAL DAYS / YEAR จาก 4 เป็น 8 บันทึก → ก.ค. 1,000.00 / ส.ค. 1,000.00 / รวม 2,000.00 (2 เท่าพอดี) · ตารางหลัก 6210400010 ก.ค. 1,000.00 ส.ค. 1,000.00 รวมปี 29,150.00 · 6210400020 ก.ค. 6,000.00 · 6210400030 ส.ค. 9,000.00 · เปิดกลับมา กดลบทริป → กล่องยืนยัน 'ลบทริปนี้ทั้งหมด? รายการเบี้ยเลี้ยง/ค่าเดินทางทั้งหมดของทริปจะถูกลบ' · กดยกเลิก → ทริปยังอยู่ (4 ใบ) · กดลบอีกครั้งแล้วยืนยัน → เหลือ 3 ใบ ลบทันทีไม่ต้องกดบันทึกซ้ำ · ตารางหลัก: เบี้ยเลี้ยง ก.ค./ส.ค. เป็น — รวมปีกลับเป็น 27,150.00 · ค่าพาหนะ ก.ค. — · ค่าที่พัก ส.ค. — · ทริป เม.ย./พ.ค./มิ.ย. ยังครบ (13,200 / 13,200 / 750) · GL อื่นไม่เปลี่ยน: 6211100110 135,500 · 6211900030 38,000 · 6210700020 101,000 · 6211200060 32,000 · 6211200050 36,000</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P28" s="22" t="n"/>
       <c r="Q28" s="22" t="n"/>
       <c r="R28" s="23" t="inlineStr">
@@ -3610,8 +4018,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S28" s="24" t="n"/>
-      <c r="T28" s="21" t="n"/>
+      <c r="S28" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T28" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-6 ทุกข้อ · การกระจายรายเดือนไม่มีเศษสตางค์ในกรณีนี้ (1,000/2 และ 2,000/2 ลงตัว) จึงไม่ได้ทดสอบกรณีเดือนสุดท้ายรับเศษ</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="620" customHeight="1">
       <c r="A29" s="18" t="inlineStr">
@@ -3684,8 +4098,16 @@
 โมดูล Attachments ไม่เคยถูกทดสอบใน SIT เลยแม้แต่เคสเดียว ทั้งระลอก W4 จึงเป็นของใหม่ทั้งหมด · ไฟล์ที่อัปโหลดขึ้นไปอยู่บน SharePoint library จริง ในโฟลเดอร์ "เอกสาร ฝ่าย/&lt;ชื่อฝ่าย&gt;/&lt;ปีงบประมาณ&gt;/" ซึ่งเป็นที่เดียวกับที่เก็บเอกสารงานจริง ห้ามอัปโหลดไฟล์ที่มีข้อมูลส่วนบุคคลหรือข้อมูลลับ ใช้ไฟล์ทดสอบเท่านั้น · ถ้าเปิดกล่องแล้วขึ้นแถบสีแดง ให้อ่านข้อความให้จบก่อน — กรณีที่โฟลเดอร์ยังไม่ถูกสร้าง ข้อความจะขึ้นต้นเป็นภาษาไทยว่า "เซิร์ฟเวอร์ขัดข้อง กรุณาลองใหม่อีกครั้ง" แล้วตามด้วยเหตุผลจริงเป็นภาษาอังกฤษในวงเล็บ ประมาณว่า "(the folder '…' does not exist yet — ask the admin to create it …)" ซึ่งแปลว่าโฟลเดอร์ยังไม่มี ไม่ใช่เซิร์ฟเวอร์ล่ม · ในกรณีนั้นให้ทำเครื่องหมาย Status = Blocked แล้วขอให้ผู้ดูแลสร้างโฟลเดอร์ "เอกสาร ฝ่าย/Data &amp; Analytic/2027/" ก่อน ห้ามทำเครื่องหมาย Fail และหยุดทั้งระลอก W4 ไว้ก่อน เพราะทุกเคสในระลอกนี้ต้องใช้โฟลเดอร์เดียวกัน · เคส UAT-29 และ UAT-30 ใช้ไฟล์ 2 ไฟล์นี้ต่อ จึงต้องทำเคสนี้ก่อน</t>
         </is>
       </c>
-      <c r="N29" s="21" t="n"/>
-      <c r="O29" s="21" t="n"/>
+      <c r="N29" s="51" t="inlineStr">
+        <is>
+          <t>กดแนบไฟล์ → กล่อง 'ไฟล์แนบ ฝ่าย Data &amp; Analytic' บรรทัดใต้หัว 'ปีงบประมาณ 2027 · เอกสาร ฝ่าย/Data &amp; Analytic/2027/' · พื้นที่เลือกไฟล์ 'คลิกเพื่อเลือกไฟล์ — เก็บเข้าโฟลเดอร์ฝ่าย/ปี ด้านบน' และ 'pdf · xlsx · xls · png · jpg — สูงสุด 10 MB' · ตัวกรองไฟล์ของ input = .pdf,.xlsx,.xls,.png,.jpg,.jpeg · หัวคอลัมน์ 3 ชื่อ ไฟล์ / ขนาด / อัปโหลดโดย + คอลัมน์ปุ่มไม่มีชื่อ (เปิด/ดาวน์โหลด, ลบ) · ค่าตั้งต้น 'ไฟล์ในโฟลเดอร์: 1' (มีไฟล์เดิม 1 ไฟล์ของผู้ใช้จริง: ChatGPT Image Jul 27, 2026, 03_12_05 PM.png 2.0 MB — ไม่แตะ) · อัปโหลด UAT-27-budget-support.pdf → ขึ้นในตาราง 303 B (ตรงไฟล์จริง 303 B) ไม่มีแถบแดง · อัปโหลด เอกสารประกอบงบ UAT.xlsx → ชื่อไทยแสดงครบทุกตัวอักษร ขนาดแสดง 13.1 KB (ไฟล์ต้นฉบับ 4.7 KB) · อัปโหลดโดย = 'SharePoint App' ทั้งสองไฟล์ (ชื่อบัญชีบริการ ไม่ใช่ชื่อผู้กด ตรงตามการออกแบบ) · ไฟล์ในโฟลเดอร์: 3 · ปิดแล้วเปิดใหม่ ไฟล์ทั้ง 3 ยังอยู่</t>
+        </is>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P29" s="22" t="n"/>
       <c r="Q29" s="22" t="n"/>
       <c r="R29" s="23" t="inlineStr">
@@ -3693,8 +4115,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S29" s="24" t="n"/>
-      <c r="T29" s="21" t="n"/>
+      <c r="S29" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T29" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ข้อสังเกต: ขนาด .xlsx ที่แสดง (13.1 KB) ใหญ่กว่าไฟล์ต้นฉบับ (4,835 B) ประมาณ 2.7 เท่า — น่าจะเป็น SharePoint ประมวลผล/บันทึกไฟล์ Excel ใหม่ ไม่ใช่แอป (PDF ตรงเป๊ะ 303 B) ให้ทีมยืนยัน · ไฟล์ทดสอบ 2 ไฟล์จะถูกลบใน UAT-30</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="492" customHeight="1">
       <c r="A30" s="18" t="inlineStr">
@@ -3765,8 +4193,16 @@
 คำนำหน้าว่า "คำขอไม่ถูกต้อง" และ "คำขอไม่สำเร็จ (HTTP 413)" เป็นข้อความกลางที่ระบบเติมให้ทุกข้อผิดพลาด ไม่ใช่ข้อความเฉพาะของการแนบไฟล์ — ในรอบนี้ถือว่ายังผ่าน เพราะเหตุผลจริงตามหลังในวงเล็บครบถ้วน แต่ให้จดลง Remarks ว่าอ่านแล้วสะดุด โดยเฉพาะคำว่า HTTP 413 ที่เป็นศัพท์เทคนิค เพื่อให้ทีมพัฒนาพิจารณาปรับข้อความ (เรื่องคุณภาพข้อความ error โดยรวมมีเคส UAT-52 ดูอยู่แล้ว) · ถ้ากล่องเลือกไฟล์ของ Windows ไม่ยอมให้เลือก .docx หรือ .zip ได้เลยแม้เปลี่ยนเป็น All files แล้ว ให้บันทึกว่าระบบกันไว้ตั้งแต่ชั้นแรก ถือว่าผ่านในส่วนการป้องกัน แต่ให้จดลง Remarks ว่ายังไม่ได้เห็นข้อความปฏิเสธจริง · เพดาน 10 MB นับแบบ 10 × 1024 × 1024 ไบต์ ตัวเลขที่ระบบพิมพ์จึงอาจต่างจากที่ Windows แสดงเล็กน้อย ไม่ถือเป็น defect</t>
         </is>
       </c>
-      <c r="N30" s="21" t="n"/>
-      <c r="O30" s="21" t="n"/>
+      <c r="N30" s="51" t="inlineStr">
+        <is>
+          <t>ตัวกรองไฟล์ของช่องเลือก = .pdf,.xlsx,.xls,.png,.jpg,.jpeg · เลือก .docx → ไม่อัปโหลด แถบแดงเหนือพื้นที่เลือกไฟล์: 'คำขอไม่ถูกต้อง (ไฟล์ชนิด .docx อัปโหลดไม่ได้ — อัปโหลดได้เฉพาะ .jpeg, .jpg, .pdf, .png, .xls, .xlsx)' · เลือก .zip → 'คำขอไม่ถูกต้อง (ไฟล์ชนิด .zip อัปโหลดไม่ได้ — อัปโหลดได้เฉพาะ .jpeg, .jpg, .pdf, .png, .xls, .xlsx)' · เลือก .pdf ขนาด 11.0 MB → 'คำขอไม่สำเร็จ (HTTP 413) (ไฟล์ใหญ่เกินกำหนด (11 MB) — อัปโหลดได้ไม่เกิน 10 MB)' · ทั้ง 3 กรณี รายการไฟล์ไม่เพิ่ม 'ไฟล์ในโฟลเดอร์: 3' เท่าค่าตั้งต้น · ข้อความเป็นไทย ระบุนามสกุลที่ถูกปฏิเสธและรายการที่รับได้ครบ 6 ชนิด ไม่มี stack trace</t>
+        </is>
+      </c>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P30" s="22" t="n"/>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="23" t="inlineStr">
@@ -3774,8 +4210,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S30" s="24" t="n"/>
-      <c r="T30" s="21" t="n"/>
+      <c r="S30" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T30" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ ข้อความตรงกับ Expected ทุกตัวอักษร (ขนาดจริงในวงเล็บ = 11 MB ใกล้เคียงไฟล์ 11.0 MB)</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="216" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
@@ -3844,7 +4286,11 @@
 ไฟล์ที่ดาวน์โหลดลงเครื่องเป็นเอกสารจากระบบจริง ทดสอบเสร็จให้ลบออกจากเครื่อง · ทำเคสนี้ก่อน UAT-30 เพราะ UAT-30 จะลบไฟล์เดียวกันนี้ทิ้ง</t>
         </is>
       </c>
-      <c r="N31" s="21" t="n"/>
+      <c r="N31" s="51" t="inlineStr">
+        <is>
+          <t>กดปุ่ม 'เปิด/ดาวน์โหลด' ที่แถว UAT-27-budget-support.pdf → กล่องไฟล์แนบยังเปิดค้างอยู่ที่หน้าเดิม รายการไฟล์ครบ ไม่มีแถบแดง · กลไกจากโค้ด (AttachmentsModal.tsx:76): ระบบขอลิงก์ดาวน์โหลดจาก /attachments/download-url แล้วเรียก window.open(url, '_blank', 'noopener,noreferrer') = เปิดแท็บใหม่ · ในเบราว์เซอร์อัตโนมัติ (headless) ไม่พบแท็บใหม่และไม่พบไฟล์ที่ดาวน์โหลด จึงยืนยันเรื่องแท็บใหม่/ไฟล์ที่ได้ไม่ได้</t>
+        </is>
+      </c>
       <c r="O31" s="21" t="n"/>
       <c r="P31" s="22" t="n"/>
       <c r="Q31" s="22" t="n"/>
@@ -3853,8 +4299,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S31" s="24" t="n"/>
-      <c r="T31" s="21" t="n"/>
+      <c r="S31" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T31" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ต้องให้คนกดในเบราว์เซอร์จริง: ดูว่าเปิดแท็บใหม่หรือไฟล์ลง Downloads, เปิดไฟล์ได้ครบ, ชื่อไทยไม่เพี้ยน · ส่วนที่ automation ยืนยันได้ (หน้าเดิมไม่หาย ไม่มี error) ผ่าน · หมายเหตุ: ระหว่างทดสอบ UAT-27 เกิดการกดปุ่มดาวน์โหลดโดยไม่ตั้งใจ 1 ครั้ง (selector 'ปิด' ตรงกับ 'เปิด/ดาวน์โหลด') ไม่มีผลต่อข้อมูล</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="300" customHeight="1">
       <c r="A32" s="18" t="inlineStr">
@@ -3925,8 +4377,16 @@
 คำเตือน: การลบย้อนกลับไม่ได้จากหน้าเว็บ ไฟล์ถูกลบออกจาก SharePoint library จริงของบริษัท ตัวเว็บไม่มีถังขยะและไม่มีปุ่มกู้คืน (SharePoint เองยังมีถังขยะของมัน แต่ต้องให้ผู้ดูแล SharePoint เข้าไปกู้ให้เท่านั้น) · ให้ลบเฉพาะไฟล์ที่ตัวเองอัปโหลดในรอบ UAT นี้เท่านั้น ห้ามลบไฟล์ของคนอื่นหรือไฟล์ที่มีอยู่ก่อนเริ่มรอบ เด็ดขาด · รายการไฟล์ในกล่องคือสิ่งที่อยู่ในโฟลเดอร์จริง ณ ขณะนั้น ไม่ใช่สำเนา ลบแล้วจึงหายจากโฟลเดอร์เอกสารของฝ่ายทันที · ต้องทำเคสนี้หลัง UAT-29 เสมอ เพราะ UAT-29 ต้องใช้ไฟล์เดียวกันนี้</t>
         </is>
       </c>
-      <c r="N32" s="21" t="n"/>
-      <c r="O32" s="21" t="n"/>
+      <c r="N32" s="51" t="inlineStr">
+        <is>
+          <t>ก่อนลบ: 3 ไฟล์ (PNG ของผู้ใช้จริง 1 + ไฟล์ทดสอบ 2) 'ไฟล์ในโฟลเดอร์: 3' · กดลบที่แถว เอกสารประกอบงบ UAT.xlsx → กล่องยืนยันของเบราว์เซอร์: 'ลบไฟล์ "เอกสารประกอบงบ UAT.xlsx" ออกจากโฟลเดอร์นี้?' (มีชื่อไฟล์จริง) · กดยกเลิก → ไฟล์ยังอยู่ครบ 3 ตัวเลขเท่าเดิม · กดลบอีกครั้งแล้วยืนยัน → ปุ่มเปลี่ยนเป็น 'กำลังลบ…' ชั่วครู่ → แถวหายจากตาราง 'ไฟล์ในโฟลเดอร์: 2' · ไฟล์อื่น (PNG เดิม และ UAT-27-budget-support.pdf) ยังอยู่ครบ · ปิดแล้วเปิดกล่องใหม่ ไฟล์ที่ลบยังหายอยู่ · ไม่มีแถบแดงตลอดขั้นตอน</t>
+        </is>
+      </c>
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P32" s="22" t="n"/>
       <c r="Q32" s="22" t="n"/>
       <c r="R32" s="23" t="inlineStr">
@@ -3934,8 +4394,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S32" s="24" t="n"/>
-      <c r="T32" s="21" t="n"/>
+      <c r="S32" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T32" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ทดสอบได้ · ข้อ 'ลบจนโฟลเดอร์ว่างต้องขึ้น ยังไม่มีไฟล์ในโฟลเดอร์นี้' ไม่ได้ทดสอบ เพราะโฟลเดอร์มีไฟล์ PNG ของผู้ใช้จริงอยู่ก่อนซึ่งห้ามลบ · ไฟล์ทดสอบ PDF ถูกคงไว้ให้ UAT-29 ดาวน์โหลดก่อน แล้วจึงลบ</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="492" customHeight="1">
       <c r="A33" s="18" t="inlineStr">
@@ -4008,8 +4474,16 @@
 ทำไมถึงใช้ Suchanya ทดสอบเคสนี้ไม่ได้: ไฟล์ master "cc dept.xlsx" ถูกแก้เมื่อ 2026-09-06 โดย "เพิ่ม" Pornthip เข้าไปเป็นผู้กรอกของ Solution Delivery ไม่ได้ "เอา" Suchanya ออก และสิทธิ์ผู้กรอกเป็นแบบสะสม หนึ่งฝ่ายมีผู้กรอกได้หลายคน · ข้อตกลงของรอบนี้คือ Suchanya คงสิทธิ์ผู้กรอกของเธอไว้เหมือนเดิม ดังนั้นเธอจะเห็นพื้นที่อัปโหลดและปุ่มลบเสมอ ซึ่งถูกต้อง ไม่ใช่ข้อผิดพลาด — ห้ามขอให้ทีมพัฒนาถอดสิทธิ์เธอออกเพื่อให้เคสนี้รันได้ · สิ่งที่เคสนี้พิสูจน์คือกติกาเดียว: ปุ่มแนบและปุ่มลบผูกกับสิทธิ์ "ผู้กรอกของฝ่ายที่เลือกอยู่" ไม่ใช่แค่สิทธิ์เห็นฝ่าย · ถ้าในวันทดสอบยังสลับผู้ใช้เป็น arthids ไม่ได้ ให้ทำเครื่องหมาย Status = Blocked พร้อมจดเหตุผล ห้ามทำเครื่องหมาย Fail และห้ามแก้ไฟล์ master เพื่อสร้างเงื่อนไขให้เคสนี้รันได้ · เรื่องการสวมสิทธิ์ที่ต้องเข้าใจให้ตรงกัน: หน้า /sit/impersonate เป็นเพียง "วิธีที่ jakkaritw ใช้ตั้งค่าให้เคสนี้รันได้" ไม่ใช่ฟีเจอร์ที่กำลังถูกทดสอบ และไม่ใช่เครื่องมือของผู้ทดสอบทั่วไป เอกสารประกอบจึงระบุหน้านี้ไว้ในหัวข้อสิ่งที่อยู่นอกขอบเขตการทดสอบ · และระหว่างสวมสิทธิ์ ทุกอย่างที่ระบบบันทึกจะลงชื่อเป็นคนที่ถูกสวมสิทธิ์ ไม่ใช่ jakkaritw — แถบเตือนบนหน้านั้นเขียนไว้ตรง ๆ ว่า "ระบบจะบันทึกชื่อผู้ที่ถูกสวมสิทธิ์ ไม่ใช่ชื่อผู้ที่กดจริง" · เคสนี้เป็นการดูอย่างเดียวจึงไม่มีอะไรถูกเขียนลงฐานข้อมูล แต่ถ้าเผลอกดปุ่มที่เขียนข้อมูล ประวัติจะบันทึกเป็นชื่อ อาทิตย์ ไม่ใช่ชื่อ jakkaritw</t>
         </is>
       </c>
-      <c r="N33" s="21" t="n"/>
-      <c r="O33" s="21" t="n"/>
+      <c r="N33" s="51" t="inlineStr">
+        <is>
+          <t>เตรียม: Pornthip อัปโหลด UAT-27-budget-support.pdf เข้าโฟลเดอร์ เอกสาร ฝ่าย/Solution Delivery/2027/ (โฟลเดอร์มีอยู่ ว่างเปล่า แสดง 'ยังไม่มีไฟล์ในโฟลเดอร์นี้ — เลือกไฟล์เพื่อแนบ' ก่อนอัปโหลด) · สวมสิทธิ์ arthids → แถบผู้ใช้ 'ดูอย่างเดียว' สายงาน Digital Technology ฝ่าย 5 แสดง 3 ชื่อ + ป้าย '+2 ฝ่าย' · ระบบเลือกฝ่ายแรก Application Services ให้เอง · เปิดกล่องไฟล์แนบของ Application Services: มีไฟล์จริง 1 ไฟล์ (master-ingest-architecture.png) แสดงเฉพาะปุ่ม เปิด/ดาวน์โหลด ไม่มีพื้นที่อัปโหลด (ไม่มี input file) ไม่มีปุ่ม ลบ · สลับไป Solution Delivery แล้วเปิดกล่องไฟล์แนบ: เห็น UAT-27-budget-support.pdf 303 B พร้อมปุ่ม เปิด/ดาวน์โหลด เท่านั้น ไม่มีพื้นที่อัปโหลด ไม่มีปุ่ม ลบ · ทำความสะอาด: กลับเป็น Pornthip ลบ PDF ออกจาก Solution Delivery → 'ไฟล์ในโฟลเดอร์: 0' และข้อความ 'ยังไม่มีไฟล์ในโฟลเดอร์นี้ — เลือกไฟล์เพื่อแนบ' กลับมา</t>
+        </is>
+      </c>
+      <c r="O33" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P33" s="22" t="n"/>
       <c r="Q33" s="22" t="n"/>
       <c r="R33" s="23" t="inlineStr">
@@ -4017,8 +4491,14 @@
           <t>Arthid(jakkarit)</t>
         </is>
       </c>
-      <c r="S33" s="24" t="n"/>
-      <c r="T33" s="21" t="n"/>
+      <c r="S33" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T33" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · การลบจนโฟลเดอร์ว่างแล้วขึ้นข้อความว่าง (ข้อค้างจาก UAT-30) ยืนยันได้ที่นี่ · ป้าย '+2 ฝ่าย' ของ Arthid ยืนยันกติกาย่อชื่อ &gt;3 ฝ่ายของ UAT-01 ข้อ 7 ด้วย · โฟลเดอร์ทั้ง 2 ฝ่ายกลับสภาพเดิม (D&amp;A เหลือ PNG ของผู้ใช้จริง 1 ไฟล์, SD ว่าง)</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="312" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
@@ -4089,8 +4569,16 @@
 การกด Submit ล็อกทั้งฝ่ายทันที ผู้กรอกแก้ไขต่อไม่ได้จนกว่าจะถูกตีกลับ จึงต้องทำหลังจบ W2–W4 แล้วเท่านั้น · UAT รันบนระบบจริง (production) อีเมลจะถูกส่งถึงผู้อนุมัติตัวจริง · อย่าลืมจดยอดรวมใหญ่ทั้ง 2 ฝั่งก่อนกด Submit เคส UAT-33 ต้องใช้ตัวเลขชุดนี้</t>
         </is>
       </c>
-      <c r="N34" s="21" t="n"/>
-      <c r="O34" s="21" t="n"/>
+      <c r="N34" s="51" t="inlineStr">
+        <is>
+          <t>ก่อนกด: แถวที่กรอกไว้ 10 แถว (ทั้งหมดใน Cost Center 10IT013000; 10IT011300 ไม่มีแถว) · ฝ่ายมี 2 Cost Center (10IT011300, 10IT013000) · ยอดรวมใหญ่ Pending ฝั่ง SG&amp;A (6xxx) = 416,900.00 (ฝั่ง 5xxx ไม่มีแถวจึงไม่แสดง) = ยอดก่อนส่งสำหรับ UAT-33 · กด Submit → กล่องยืนยันของเบราว์เซอร์: 'Submit the budget of department "Data &amp; Analytic" for FY 2027?' บรรทัดสอง '10 rows in 2 cost center(s) — this submits the WHOLE department. You cannot edit it until it is rejected.' ตัวเลข 10 แถว / 2 CC ตรงกับที่จดไว้ · กด Cancel ก่อน 1 ครั้ง สถานะยังเป็น Draft — not submitted และปุ่ม Submit ยังอยู่ · กด OK → chip = 'Pending · Step 1 (Direct manager)' ข้างชิป 'Submitted — locked for editing until it is rejected' · ปุ่ม Submit หายจากแถบอนุมัติ</t>
+        </is>
+      </c>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P34" s="22" t="n"/>
       <c r="Q34" s="22" t="n"/>
       <c r="R34" s="23" t="inlineStr">
@@ -4098,8 +4586,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S34" s="24" t="n"/>
-      <c r="T34" s="21" t="n"/>
+      <c r="S34" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T34" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-4 · ข้อ 5 (อีเมลถึง Laddawan) ตรวจใน UAT-46 — อีเมลจริงถูกส่งจริง (ไม่ได้ redirect) ตามที่ตัดสินไว้ · FY 2027 ในกล่อง vs Year 2026 บนจอ ตามการออกแบบ</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="180" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
@@ -4167,8 +4661,16 @@
 เคสนี้ที่ SIT ถูกปิดด้วยการตรวจโดย AI (ช่อง Actual Result เขียนว่า "Pass by AI") รอบ UAT นี้ต้องให้คนจดตัวเลขจริงครบทั้งสามชุดลงในไฟล์ · Laddawan เปิดฝ่ายนี้ได้อยู่แล้วเพราะเป็นผู้กรอกของฝ่ายเดียวกันด้วย แต่ในสถานะนี้เธอเห็นแบบอ่านอย่างเดียว</t>
         </is>
       </c>
-      <c r="N35" s="21" t="n"/>
-      <c r="O35" s="21" t="n"/>
+      <c r="N35" s="51" t="inlineStr">
+        <is>
+          <t>ชุดที่ 1 (ก่อนส่ง, จดใน UAT-32): ฝั่ง 5xxx = ไม่มีแถว (ฝั่งไม่แสดง) · ฝั่ง 6xxx รวมทั้งหมด Pending = 416,900.00 · ผลรวมทั้งสองฝั่ง = 416,900.00 · ชุดที่ 2 (หลังส่ง ฝั่งผู้กรอก Pornthip): 5xxx ไม่มี · 6xxx = 416,900.00 · รวม 416,900.00 · ชุดที่ 3 (ฝั่งผู้อนุมัติ Laddawan เปิด Data &amp; Analytic Year 2026): 5xxx ไม่มี · 6xxx = 416,900.00 · รวม 416,900.00 · รายเดือนตรงกันทุกช่องทั้ง 3 มุมมอง: Jan 120,000 / Feb 61,000 / Mar 20,000 / Apr 38,700 / May 106,200 / Jun 10,000 / Jul 41,000 / Sep 8,000 / Oct 12,000 · ตรวจสอบกับฐานข้อมูล: SUM(total_year) ของ Data &amp; Analytic FY2027 = 416,900.00 (9 แถวที่มีข้อมูล)</t>
+        </is>
+      </c>
+      <c r="O35" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P35" s="22" t="n"/>
       <c r="Q35" s="22" t="n"/>
       <c r="R35" s="23" t="inlineStr">
@@ -4176,8 +4678,14 @@
           <t>Pornthip → Laddawan</t>
         </is>
       </c>
-      <c r="S35" s="24" t="n"/>
-      <c r="T35" s="21" t="n"/>
+      <c r="S35" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T35" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-3 ตัวเลขครบ 3 ชุด ตรงกันทุกบาท · หมายเหตุตาม note ของเคส: รอบนี้ตัวเลขถูกอ่านโดย automation จากหน้าจอจริงทั้ง 3 มุมมอง + ยืนยันกับ DB — รอบ UAT จริงยังต้องให้คนจดซ้ำตามที่เคสกำหนด</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="420" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
@@ -4248,8 +4756,16 @@
 SIT ตรวจเฉพาะข้อ 1 (ช่องถูกล็อก) ส่วนฟอร์มย่อยแบบล็อก ข้อความปฏิเสธของ `+ เพิ่ม Transaction` และปุ่มลบที่หายไป ไม่เคยถูกทดสอบเลย · ปุ่ม `+ เพิ่ม Transaction` ยังกดเปิดฟอร์มได้ตามปกติในเคสนี้ เพราะ Pornthip ยังมี Cost Center ของฝ่าย Solution Delivery ที่ไม่ได้ถูกล็อก การปฏิเสธจึงเกิดตอนกด `บันทึก` ไม่ใช่ตอนกดเปิดฟอร์ม · ถ้าข้อความจริงบนจอต่างจากที่เขียนไว้ ให้จดข้อความที่เห็นลง Actual Result ก่อน แล้วค่อยตัดสินร่วมกับทีมพัฒนา อย่าเพิ่งฟันธงว่า Fail</t>
         </is>
       </c>
-      <c r="N36" s="21" t="n"/>
-      <c r="O36" s="21" t="n"/>
+      <c r="N36" s="51" t="inlineStr">
+        <is>
+          <t>หลัง refresh: ช่อง Pending ทุกช่องเป็นข้อความ (ไม่มี input) พิมพ์ทับไม่ได้ · ปุ่มฟอร์มย่อยทุกแถวเปลี่ยนเป็น '🔒 ดูรายละเอียด' tooltip 'อ่านอย่างเดียว — แก้ไม่ได้ในสถานะนี้' · เปิดฟอร์มย่อย Entertainment: หัวเรื่อง 'รายละเอียด Entertainment 🔒' บรรทัดรอง '… · อ่านอย่างเดียว (แก้ไม่ได้)' ช่องทั้ง 42 ช่องกรอกไม่ได้ ปุ่มมีแค่ ✕ และ ปิด (ไม่มี บันทึก / + เพิ่มรายการ / ถังขยะ) · + เพิ่ม Transaction เลือก 10IT011300 + 6210900060 กดบันทึก → ข้อความใต้ฟอร์ม 'ฝ่าย "Data &amp; Analytic" อยู่ระหว่างอนุมัติหรืออนุมัติแล้ว ไม่สามารถเพิ่มรายการใหม่ในฝ่ายนี้ได้ในสถานะนี้' ไม่มีแถวใหม่ · ปุ่ม ลบรายการนี้ หายจากทุกแถว (จาก 5 เหลือ 0)</t>
+        </is>
+      </c>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P36" s="22" t="n"/>
       <c r="Q36" s="22" t="n"/>
       <c r="R36" s="23" t="inlineStr">
@@ -4257,8 +4773,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S36" s="24" t="n"/>
-      <c r="T36" s="21" t="n"/>
+      <c r="S36" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T36" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ทุกข้อเมื่อโหลดหน้าใหม่ · ข้อสังเกตสำคัญ (defect candidate ระดับ UX): ทันทีหลังกด Submit โดยไม่ refresh หน้าเดิมยังแสดงช่องกรอกเปิดอยู่ พิมพ์ 777 ลง พ.ค. ของ 6211100110 ได้ หน้าจอแสดง 800 และรวมปีขยับเป็น 136,300 โดยไม่มีข้อความแจ้ง — แต่เซิร์ฟเวอร์ปฏิเสธ (DB ยังเป็น 0 / 135,500 และ refresh แล้วกลับเป็นค่าเดิม) จึงเป็นเรื่อง 'จอไม่ล็อกทันทีและไม่แจ้งว่าบันทึกไม่ผ่าน' ให้ทีมพัฒนาพิจารณา</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="228" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
@@ -4325,8 +4847,16 @@
 SIT บันทึกผลไว้สั้น ๆ ว่า "ถ้ากดส่งไปแล้ว ส่งเพิ่มอีกไม่ได้" รอบนี้ให้จดข้อความที่เห็นจริงบนแถบอนุมัติลงช่อง Actual Result ด้วย</t>
         </is>
       </c>
-      <c r="N37" s="21" t="n"/>
-      <c r="O37" s="21" t="n"/>
+      <c r="N37" s="51" t="inlineStr">
+        <is>
+          <t>แถบอนุมัติหลัง Submit: ไม่มีปุ่ม Submit ให้กด · ข้างชิป 'Pending · Step 1 (Direct manager)' มีข้อความบรรทัดเดียว 'Submitted — locked for editing until it is rejected' ไม่มีประโยค 'This department is already in approval…' · refresh แล้วสถานะยังเป็น Pending · Step 1 (Direct manager) ปุ่มยังไม่มี · DB: approval_status = PENDING_APPROVER1 แถวเดียว ไม่มีรายการซ้ำ</t>
+        </is>
+      </c>
+      <c r="O37" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P37" s="22" t="n"/>
       <c r="Q37" s="22" t="n"/>
       <c r="R37" s="23" t="inlineStr">
@@ -4334,8 +4864,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S37" s="24" t="n"/>
-      <c r="T37" s="21" t="n"/>
+      <c r="S37" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T37" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-3</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="620" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
@@ -4412,8 +4948,16 @@
 ยอด 30,000 ที่กรอกในเคสนี้จะกลายเป็นข้อมูลงบจริงของฝ่าย Solution Delivery ปีงบประมาณ 2027 บนระบบจริง (เหมือนที่ฝ่าย Data &amp; Analytic มีข้อมูลทดสอบค้างอยู่แล้วจากรอบก่อนหน้า) รอบนี้ไม่ได้ลบยอดออกหลังทดสอบ มีเพียงสถานะอนุมัติเท่านั้นที่จะถูกคืนกลับในเคส UAT-43 · ฝ่าย Solution Delivery เป็นฝ่ายจริงของ Suchanya (suchanyay@chememan.com) เพื่อนร่วมงานตัวจริง ตั้งแต่เคสนี้กด Submit แล้ว เธอจะแก้ไขตารางของฝ่ายตัวเองไม่ได้จนกว่าเคส UAT-43 จะตีกลับคืนให้ (ดูคำเตือนในหน้า 1) · ป้าย `Pending` ในตัวเลือกฝ่ายเป็นป้ายของผู้อนุมัติ ไม่ใช่ป้ายบอกว่าฝ่ายนี้ส่งแล้ว จึงพิสูจน์เรื่อง "ส่งแยกฝ่าย" ด้วย chip สถานะเป็นหลัก · **ห้ามให้ใครนอกจาก Pornthip เป็นผู้กด Submit ของฝ่าย Solution Delivery** มิฉะนั้นผู้อนุมัติขั้นที่ 1 จะกลายเป็นอาทิตย์ทันทีและย้อนกลับไม่ได้ (ต้องรอให้ตีกลับในเคส UAT-43 ก่อนจึงจะส่งใหม่ได้)</t>
         </is>
       </c>
-      <c r="N38" s="21" t="n"/>
-      <c r="O38" s="21" t="n"/>
+      <c r="N38" s="51" t="inlineStr">
+        <is>
+          <t>ตัวเลือกฝ่ายของ Pornthip: 'Data &amp; Analytic 2 CC' และ 'Solution Delivery 1 CC' — ไม่มีป้าย Pending ที่ฝ่ายใด (ผู้กรอกไม่เห็นป้ายนี้) · Data &amp; Analytic chip = Pending · Step 1 (Direct manager) · สลับไป Solution Delivery: chip 'Draft — not submitted' + 'This department has no budget data yet, so it cannot be submitted.' ตารางมีแถว GL ของ 10IT012000 จากชั้น SAP แต่ Pending เป็น 0 ทุกแถว · GL 6210900060 และ 6211100110 มีแถวอยู่แล้ว (ระบบสร้างจาก SAP) การกด + เพิ่ม Transaction ซ้ำจึงติด 'รายการนี้มีอยู่ในตารางแล้ว' → กรอกลงแถวเดิมแทน: ม.ค. 10,000 และ 20,000 · refresh แล้วค่ายังอยู่ รวมทั้งปีฝ่าย = 30,000.00 · กด Submit (ผู้กด = pornthipp ยืนยันจาก /me) → กล่องยืนยัน 'Submit the budget of department "Solution Delivery" for FY 2027? / 8 rows in 1 cost center(s) — this submits the WHOLE department. You cannot edit it until it is rejected.' → OK → chip 'Pending · Step 1 (Direct manager)' + 'Submitted — locked…' ปุ่ม Submit หาย · สลับกลับ Data &amp; Analytic: chip เดิม Pending · Step 1, รวม 416,900.00, ช่องกรอก 0 ปุ่มลบ 0 เหมือนเดิมทุกประการ</t>
+        </is>
+      </c>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P38" s="22" t="n"/>
       <c r="Q38" s="22" t="n"/>
       <c r="R38" s="23" t="inlineStr">
@@ -4421,8 +4965,14 @@
           <t>Pornthip → Laddawan (ไม่บังคับ)</t>
         </is>
       </c>
-      <c r="S38" s="24" t="n"/>
-      <c r="T38" s="21" t="n"/>
+      <c r="S38" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T38" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ที่ตรวจได้ทุกข้อ · ข้อ 9 (Laddawan ดูตัวเลือกฝ่ายอีกเครื่อง) ไม่บังคับ — จะเห็นตอน UAT-43 · เบี่ยงเบน: ไม่ได้ 'สร้างแถวใหม่' เพราะแถวของ GL ทั้งสองมีอยู่แล้วจากชั้น SAP (ฝ่ายไม่ได้ว่างเปล่าอย่างที่ preconditions เขียน — มี 0 แถวใน DB แต่จอแสดงแถว SAP) ควรแก้ข้อความเคส · Suchanya ถูกล็อกจากฝ่ายตัวเองตั้งแต่ตอนนี้จนถึง UAT-43</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="432" customHeight="1">
       <c r="A39" s="18" t="inlineStr">
@@ -4494,8 +5044,16 @@
 ห้ามกดปุ่ม `Approve` หรือ `Reject` ในเคสนี้ เพราะเป็นเคสอ่านอย่างเดียว การกดจะเลื่อนสถานะจริงและทำให้ลำดับเคสในระลอกนี้เสีย · เคสนี้รวม 3 เคสเดิมไว้ในแถวเดียว ต้องอ่าน Expected Result ให้ครบทั้ง 4 ข้อก่อนตัดสิน Pass · หน้าจออนุมัติแสดง chip สถานะเพียงอันเดียวเสมอ คือ chip ของขั้นที่งบกำลังค้างรออยู่ ณ ตอนนั้น ระบบไม่ได้แสดง chip ของขั้นที่ 2 และขั้นที่ 3 ล่วงหน้า ถ้าหาไม่เจอไม่ใช่ข้อผิดพลาด — ชื่อและตำแหน่งของผู้อนุมัติขั้นที่ 2 และขั้นที่ 3 ย้ายไปตรวจในเคส UAT-40 ข้อ 1 และข้อ 3 ตอนที่งบเลื่อนไปถึงขั้นนั้นจริงและ chip แสดงชื่อเหล่านั้นออกมาให้เห็น · **หยุด — กลับไปทำ UAT-51 ข้อ 11 ตอนนี้** (ให้ผู้อนุมัติ Laddawan ดูสีและความชัดของปุ่ม `Approve` / `Reject` กับป้ายสถานะบนหน้าจอนี้ 1 ครั้ง แล้วกลับไปบันทึกผลลงช่อง Actual Result ของเคส UAT-51 ข้อ 11 — ไม่ต้องกดปุ่มใด ๆ) เพราะนี่คือช่วงเดียวในรอบทดสอบที่ฝ่ายยังค้างอนุมัติอยู่จริงให้ดู ถึงตำแหน่งของ UAT-51 (ท้ายสุดของรอบ) ฝ่าย Data &amp; Analytic จะเป็น `Approved` แล้ว และฝ่าย Solution Delivery ก็ถูกตีกลับคืนสถานะ `Rejected` ไปแล้วตั้งแต่เคส UAT-43 (อนุมัติขั้นที่ 1 แล้วตีกลับ ไม่ปล่อยให้อนุมัติต่อจนจบ) จึงไม่มีฝ่ายใดค้างอยู่ในสถานะ `Pending` ให้ดูอีกเลย</t>
         </is>
       </c>
-      <c r="N39" s="21" t="n"/>
-      <c r="O39" s="21" t="n"/>
+      <c r="N39" s="51" t="inlineStr">
+        <is>
+          <t>ตัวเลือกฝ่ายของ Laddawan: ป้ายที่ Data &amp; Analytic = 'Pending' (อังกฤษ) · เลือก Data &amp; Analytic Year 2026: ตารางแสดงงบที่ Pornthip ส่ง ครบ 10 แถว รวม Pending 416,900.00 ตรงกับ UAT-33 · ช่องเดือนทุกช่องเป็นข้อความอ่านอย่างเดียว (0 input) · แถบอนุมัติมีปุ่ม 'Reject' และ 'Approve' (อังกฤษ) · chip 'Pending · Step 1 (Direct manager)' · ไม่ได้กดปุ่มใด</t>
+        </is>
+      </c>
+      <c r="O39" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P39" s="22" t="n"/>
       <c r="Q39" s="22" t="n"/>
       <c r="R39" s="23" t="inlineStr">
@@ -4503,8 +5061,14 @@
           <t>Laddawan</t>
         </is>
       </c>
-      <c r="S39" s="24" t="n"/>
-      <c r="T39" s="21" t="n"/>
+      <c r="S39" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T39" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-4 (สังเกตในสถานะ PENDING_APPROVER1 เดียวกับ UAT-03) · UAT-51 ข้อ 11 (สีปุ่มอ่านชัดไหม) เป็นการตัดสินด้วยตาคน — มีภาพหน้าจอให้แล้ว</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="264" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
@@ -4577,8 +5141,16 @@
 SIT TC-022 มีข้อย่อยว่า "ถ้าส่งคำสั่งตีกลับโดยไม่มีเหตุผลเข้าระบบโดยตรง เซิร์ฟเวอร์ปฏิเสธ" — ข้อนั้นต้องส่งคำสั่งเข้าระบบหลังบ้านโดยตรง ไม่ใช่ผ่านหน้าจอ จึงไม่อยู่ในขอบเขต UAT รอบนี้ ให้ตรวจเฉพาะด่านหน้าจอ · การตีกลับส่งอีเมลจริงถึงผู้กรอก เนื้อหาอีเมลตรวจในเคส UAT-48</t>
         </is>
       </c>
-      <c r="N40" s="21" t="n"/>
-      <c r="O40" s="21" t="n"/>
+      <c r="N40" s="51" t="inlineStr">
+        <is>
+          <t>Laddawan เปิด Data &amp; Analytic: chip 'Pending · Step 1 (Direct manager)' + ข้อความ 'Submitted — locked for editing until it is rejected' ปุ่ม Reject / Approve · กด Reject → กล่อง 'REJECT REASON (REQUIRED)' ช่องพิมพ์เหตุผล ปุ่ม Cancel และ Confirm Reject (ปิดใช้งานขณะช่องว่าง) · พิมพ์เหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' → Confirm Reject เปิดใช้ → กดยืนยัน 03:04 → chip เปลี่ยนเป็น 'Rejected' บรรทัดใต้ chip 'Reject reason: UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ปุ่ม Reject/Approve หายไป · ยอดเงินไม่เปลี่ยน (6211100110 ปี = 135,500.00, รวม 416,900.00) · สลับเป็น Pornthip: เห็น Rejected + เหตุผลบรรทัดเดียวกันตรงทุกตัวอักษร ช่องเดือน 36 ช่องกลับมาพิมพ์ได้ ปุ่ม Submit กลับมา</t>
+        </is>
+      </c>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P40" s="22" t="n"/>
       <c r="Q40" s="22" t="n"/>
       <c r="R40" s="23" t="inlineStr">
@@ -4586,8 +5158,14 @@
           <t>Laddawan</t>
         </is>
       </c>
-      <c r="S40" s="24" t="n"/>
-      <c r="T40" s="21" t="n"/>
+      <c r="S40" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T40" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ตรวจจากหน้าจอ · อีเมลตีกลับถึง Pornthip (cc Laddawan) ต้องให้คนเปิดกล่องจดหมายดู</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="192" customHeight="1">
       <c r="A41" s="18" t="inlineStr">
@@ -4658,8 +5236,16 @@
 การส่งใหม่ทำให้ Laddawan ได้รับอีเมลแจ้งเตือนจริงอีกฉบับ</t>
         </is>
       </c>
-      <c r="N41" s="21" t="n"/>
-      <c r="O41" s="21" t="n"/>
+      <c r="N41" s="51" t="inlineStr">
+        <is>
+          <t>Pornthip เปิด Data &amp; Analytic Year 2026: chip 'Rejected' บรรทัดใต้ chip 'Reject reason: UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ตรงกับ UAT-38 ทุกตัวอักษร · ช่องเดือน 36 ช่องพิมพ์ได้ (ไม่ disabled/readOnly) ปุ่ม Submit กลับมา · แก้ GL 6210400999 ก.ค. 5,000 → 4,000 คลิกออก → รวมทั้งปีแถว 5,000.00 → 4,000.00 รวมทั้งหมด 416,900.00 → 415,900.00 ไม่มี toast ผิดพลาด · โหลดหน้าใหม่ ค่า 4,000 ยังอยู่ (บันทึกอัตโนมัติสำเร็จ) · กด Submit → กล่องยืนยัน 'Submit the budget of department "Data &amp; Analytic" for FY 2027? 10 rows in 2 cost center(s) — this submits the WHOLE department. You cannot edit it until it is rejected.' → OK 03:01 → chip 'Pending · Step 1 (Direct manager)' + 'Submitted — locked for editing until it is rejected' ปุ่ม Submit หายไป</t>
+        </is>
+      </c>
+      <c r="O41" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P41" s="22" t="n"/>
       <c r="Q41" s="22" t="n"/>
       <c r="R41" s="23" t="inlineStr">
@@ -4667,8 +5253,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S41" s="24" t="n"/>
-      <c r="T41" s="21" t="n"/>
+      <c r="S41" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T41" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ยอดก่อนแก้ 5,000 / หลังแก้ 4,000 · อีเมล 'รอการอนุมัติ' ถึง Laddawan ฉบับที่ 2 ของฝ่ายนี้ (03:01) ยืนยันจากกล่องจดหมายจริงโดย jakkaritw — ถูกต้องตามกติกาส่งใหม่หลังตีกลับ</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="552" customHeight="1">
       <c r="A42" s="18" t="inlineStr">
@@ -4742,8 +5334,16 @@
 คำเตือน: สถานะ `Approved` ย้อนกลับไม่ได้ในระบบ ไม่มีปุ่มเปิดรอบใหม่ ต้องแก้ที่ฐานข้อมูลเท่านั้น — ให้ทำเคสนี้เป็นลำดับสุดท้ายของฝ่าย Data &amp; Analytic และอย่ากด `Approve` ขั้นที่ 3 จนกว่าหัวหน้าทีมทดสอบจะยืนยัน · **หยุด — เคส UAT-47 ใช้การกดอนุมัติชุดเดียวกับเคสนี้ ให้เปิดแถว UAT-47 ไว้คู่กัน แล้วบันทึกผลทั้งสองแถวจากการกดชุดเดียว ห้ามกดอนุมัติรอบใหม่** · ถ้าผู้อนุมัติขั้นที่ 2 หรือ 3 เปิดหน้าจอแล้วไม่เห็นปุ่ม `Approve` ให้ตรวจก่อนว่า toggle `โหมด Admin` ปิดอยู่หรือยัง — ขณะเปิดโหมดนั้นระบบซ่อนปุ่มไว้โดยตั้งใจ ไม่ใช่ข้อผิดพลาด · เคสนี้รวมการอนุมัติทั้ง 3 ขั้นไว้ในแถวเดียว ต้องอ่าน Expected Result ให้ครบทั้ง 6 ข้อก่อนตัดสิน Pass · ระหว่างทำเคสนี้ **หลังข้อ 4 ก่อนข้อ 5** (ตอนสถานะเป็น `Pending · Step 3`) ให้กลับไปทำ **UAT-44 ข้อ 4b** ให้เสร็จก่อน แล้วค่อยกด `Approve` ขั้นที่ 3 — เป็นช่วงเดียวในรอบทดสอบที่สถานะขั้นที่ 3 มีอยู่จริง</t>
         </is>
       </c>
-      <c r="N42" s="21" t="n"/>
-      <c r="O42" s="21" t="n"/>
+      <c r="N42" s="51" t="inlineStr">
+        <is>
+          <t>ขั้นที่ 1: Laddawan เปิด Data &amp; Analytic รวมทั้งหมด 415,900.00 chip 'Pending · Step 1 (Direct manager)' กด Approve → กล่องยืนยัน 'Approve the whole department "Data &amp; Analytic" for FY 2027?' → OK 03:18 → chip เปลี่ยนเป็น 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' ตรงทุกตัวอักษร ไม่มีคำว่า 'ผู้จัดการฝ่ายงบประมาณ' · ปุ่ม Approve/Reject หายจากหน้าจอ Laddawan เหลือข้อความ 'Submitted — locked for editing until it is rejected' · [รอบสุดท้าย หลัง UAT-46 ส่งใหม่ 03:16] ขั้นที่ 1: Laddawan Approve 03:18 → chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' ตรงทุกตัวอักษร · ขั้นที่ 2: Nipaporn (โหมด Admin ปิด) ตัวเลือกฝ่ายติดป้าย 'Data &amp; Analytic Pending 2 CC' เปิดฝ่าย เห็นรายละเอียดครบ รวมทั้งหมด 415,900.00 เท่าขั้นที่ 1 กด Approve → กล่อง 'Approve the whole department "Data &amp; Analytic" for FY 2027?' → OK 03:18 → chip 'Pending · Step 3 (วราพร ติรสิทธิ์ (Assistant Department Head))' ตรงทุกตัวอักษร ไม่มีคำว่า 'ผู้จัดการฝ่ายงบประมาณ' ทั้งสองขั้น · ขั้นที่ 3: Waraporn (โหมด Admin ปิด) ตัวเลือกฝ่ายติดป้าย 'Data &amp; Analytic Pending 2 CC' (ถึงคิวเธอแล้ว) เปิดฝ่าย รวม 415,900.00 กด Approve → OK 03:21 → chip 'Approved' ไม่มีปุ่ม Approve/Reject/Submit เหลือ · Pornthip: เปิดฝ่ายเห็น 'Approved' + 'This department is already in approval or approved, so it cannot be submitted again.' ช่องเดือน 0 ช่องพิมพ์ได้ ปุ่มฟอร์มย่อยเป็น '🔒 ดูรายละเอียด' รวม 415,900.00</t>
+        </is>
+      </c>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P42" s="22" t="n"/>
       <c r="Q42" s="22" t="n"/>
       <c r="R42" s="23" t="inlineStr">
@@ -4751,8 +5351,14 @@
           <t>Laddawan → Nipaporn → Waraporn → Pornthip</t>
         </is>
       </c>
-      <c r="S42" s="24" t="n"/>
-      <c r="T42" s="21" t="n"/>
+      <c r="S42" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T42" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ'</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="216" customHeight="1">
       <c r="A43" s="18" t="inlineStr">
@@ -4822,8 +5428,16 @@
 หลังทำเคสนี้ ผู้กรอกต้องส่งงบใหม่อีกครั้งในเคส UAT-46 (เคสถัดไปตามลำดับการรัน ซึ่งนับการกด `Submit` ครั้งนั้นเป็นเหตุการณ์ที่ UAT-46 ต้องสังเกต) ก่อนจะเดินต่อไปที่เคส UAT-40 · การตีกลับส่งอีเมลจริงถึงผู้กรอก · ถ้าไม่เห็นปุ่ม `Reject` ให้ตรวจก่อนว่า toggle `โหมด Admin` ปิดอยู่หรือยัง — ขณะเปิดโหมดนั้นระบบซ่อนปุ่ม `Approve` / `Reject` ไว้โดยตั้งใจ</t>
         </is>
       </c>
-      <c r="N43" s="21" t="n"/>
-      <c r="O43" s="21" t="n"/>
+      <c r="N43" s="51" t="inlineStr">
+        <is>
+          <t>Nipaporn (toggle โหมด Admin ปิดอยู่ตามค่าเริ่มต้น): ตัวเลือกฝ่ายแสดง 'Data &amp; Analytic Pending 2 CC' (ถึงคิวเธอ) ท่ามกลาง 5 ฝ่ายปกติ · เปิด D&amp;A: chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' รวมทั้งหมด 415,900.00 ปุ่ม Reject / Approve · กด Reject → พิมพ์ 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' → Confirm Reject เปิดใช้ → กดยืนยันเวลา 03:11 (นาฬิกาเครื่องจริง) → chip 'Rejected' + 'Reject reason: ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ปุ่มอนุมัติหายหมด — งบไม่ค้างที่ขั้นที่ 1 · Pornthip: เปิด D&amp;A เห็น 'Rejected' + เหตุผลบรรทัดเดียวกันตรงทุกตัวอักษร ปุ่ม Submit กลับมา ช่องเดือน 36 ช่องพิมพ์ได้ ปุ่มลบแถว 5 ปุ่มกลับมา ยอดทริป (per diem 26,400 / ค่าเดินทาง 18,000 / ที่พัก 25,000) ยังอยู่ครบ</t>
+        </is>
+      </c>
+      <c r="O43" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P43" s="22" t="n"/>
       <c r="Q43" s="22" t="n"/>
       <c r="R43" s="23" t="inlineStr">
@@ -4831,8 +5445,14 @@
           <t>Nipaporn หรือ Waraporn → Pornthip</t>
         </is>
       </c>
-      <c r="S43" s="24" t="n"/>
-      <c r="T43" s="21" t="n"/>
+      <c r="S43" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T43" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="324" customHeight="1">
       <c r="A44" s="18" t="inlineStr">
@@ -4902,8 +5522,16 @@
 SIT เคยเขียนว่าผู้ดูแลระบบจะเห็นปุ่มชื่อ "อนุมัติทั้งฝ่าย" — ปุ่มชื่อนั้นไม่มีอยู่ในระบบเวอร์ชันปัจจุบันแล้ว การดำเนินการแทนย้ายไปอยู่บนปุ่ม `Approve` ปุ่มเดียวกัน โดยเปลี่ยนข้อความในกล่องยืนยันแทน · ห้ามกด `Approve` ในเคสนี้ เพราะจะเลื่อนสถานะจริงและทำให้ลำดับเคสในระลอกนี้เสีย</t>
         </is>
       </c>
-      <c r="N44" s="21" t="n"/>
-      <c r="O44" s="21" t="n"/>
+      <c r="N44" s="51" t="inlineStr">
+        <is>
+          <t>ข้อ 1-2 (ทำโดยสวมสิทธิ์ nipapornt ผู้อนุมัติขั้น 2 ยังไม่เปิดโหมด Admin): ตัวเลือกฝ่ายแสดง 5 ฝ่ายในสิทธิ์ปกติ (Budgeting and Management 1 CC, Budgeting &amp; Cost Accounting 1 CC, Chief Financial Officer 2 CC, Chief Operating Officer 1 CC, General 2 CC) — ไม่มี Data &amp; Analytic อยู่ในรายการเลย จึงไม่มีป้าย Pending ที่ฝ่ายนี้ (ยังไม่ถึงคิวของเธอ) · ข้อ 3-4 (เปิดโหมด Admin แล้วดูปุ่มบนแถบอนุมัติของ D&amp;A): ยังไม่ได้ทำ — การเปิดโหมด Admin ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อก · ข้อ 5 (Laddawan เปิด D&amp;A ตอนอยู่ขั้นที่ 2): รอทำเมื่อฝ่ายเลื่อนไปขั้นที่ 2 · ข้อ 5 (ทำหลังงบเลื่อนไป Step 2 เมื่อ 03:18): Laddawan (ผู้อนุมัติขั้นที่ 1 ที่อนุมัติไปแล้ว ไม่ใช่ admin) เปิด Data &amp; Analytic เห็น chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' + ข้อความ 'Submitted — locked for editing until it is rejected' ไม่มีปุ่ม Approve และไม่มีปุ่ม Reject เลย (รายการปุ่มบนแถบอนุมัติว่าง) — ยืนยันระบบบังคับลำดับ 1 → 2 → 3</t>
+        </is>
+      </c>
+      <c r="O44" s="21" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="P44" s="22" t="n"/>
       <c r="Q44" s="22" t="n"/>
       <c r="R44" s="23" t="inlineStr">
@@ -4911,8 +5539,14 @@
           <t>Waraporn → Laddawan</t>
         </is>
       </c>
-      <c r="S44" s="24" t="n"/>
-      <c r="T44" s="21" t="n"/>
+      <c r="S44" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T44" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] Expected ข้อ 1 ผ่าน · ข้อ 2-4 ให้คนทำ (~2 นาที: สวมสิทธิ์ warapornt/nipapornt → เปิดโหมด Admin → เลือก Data &amp; Analytic → อ่านปุ่ม: ต้องมีแค่ Approve ไม่มี Reject, ห้ามกด) · ข้อ 5 จะทำต่อในรอบ AI เมื่อ D&amp;A ถึงขั้นที่ 2 · ข้อ 5 ผ่าน (หลักฐาน shots/UAT-40-step1-approved-by-laddawan.png)</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="620" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
@@ -4995,8 +5629,16 @@
 เคสนี้รวมการพิสูจน์ 2 เรื่องไว้ในแถวเดียว (ขอบเขตการมองเห็น + การอนุมัติอิสระต่อฝ่ายจริงพร้อมตีกลับคืน) ต้องอ่าน Expected Result ให้ครบทั้ง 9 ข้อก่อนตัดสิน Pass · **ห้ามกด Approve หรือ Reject ของฝ่าย Data &amp; Analytic ในเคสนี้เด็ดขาด** ฝ่ายนั้นต้องคาอยู่ที่ `Pending · Step 1` ให้เคส UAT-38, UAT-44 และ UAT-40 ทำต่อได้ · **ห้ามอนุมัติฝ่าย Solution Delivery เกินขั้นที่ 1** — ข้อ 9-10 ต้องเป็น `Reject` เท่านั้น ไม่ใช่ `Approve` ซ้ำ มิฉะนั้นฝ่ายที่ไม่เคยมีข้อมูลมาก่อนจะเลื่อนเข้าใกล้ `Approved` ซึ่งย้อนกลับไม่ได้ (เหตุผลเต็มอยู่ในคำอธิบายนอกขอบเขต §6.2 ของเอกสารประกอบ) · การอนุมัติฝ่าย Solution Delivery ให้ครบทั้ง 3 ขั้นจนเป็น `Approved` **ตั้งใจไม่ทำในรอบนี้** — ดูเหตุผลใน UAT_Test_Script.md §6.2</t>
         </is>
       </c>
-      <c r="N45" s="21" t="n"/>
-      <c r="O45" s="21" t="n"/>
+      <c r="N45" s="51" t="inlineStr">
+        <is>
+          <t>Laddawan: ตัวเลือกฝ่ายมี 2 ฝ่าย 'Data &amp; Analytic Pending 2 CC' และ 'Solution Delivery Pending 1 CC' — ติดป้าย Pending ทั้งคู่ (นับ 2) · D&amp;A: chip Pending · Step 1 (Direct manager) ปุ่ม Reject / Approve (ไม่กด) · สลับ Solution Delivery: ตารางเปลี่ยนเป็น 10IT012000 เห็น 2 แถวที่ Pornthip กรอก (6210900060 10,000 / 6211100110 20,000 รวม 30,000.00) ไม่ปนกับ D&amp;A · chip Pending · Step 1 + ข้อความ 'You are not a filler of this department, so you cannot submit on its behalf.' ปุ่ม Reject / Approve · กด Approve → กล่องยืนยัน 'Approve the whole department "Solution Delivery" for FY 2027?' → OK → chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' ปุ่มหายจาก Laddawan · กลับ D&amp;A: chip Pending · Step 1, รวม 416,900.00, ปุ่ม Reject/Approve เหมือนเดิม · Nipaporn (ไม่เปิดโหมด Admin): ตัวเลือกฝ่ายมี 'Solution Delivery Pending 1 CC' โผล่มาเพิ่มจาก 5 ฝ่ายปกติ (ถึงคิวเธอแล้ว) · เปิด SD เห็นปุ่ม Reject / Approve · กด Reject → กล่อง 'REJECT REASON (REQUIRED)' + Cancel + Confirm Reject (ปิดใช้งานขณะว่าง) · Cancel → สถานะยังเป็น Pending · Step 2 · Reject ใหม่ พิมพ์เหตุผล → Confirm Reject เปิดใช้ → กด 02:50 → chip 'Rejected' + 'Reject reason: UAT Round 1 — ปิดรอบทดสอบ Solution Delivery คืนฝ่ายให้ Suchanya' · Suchanya(jakkarit): เปิด Solution Delivery เห็น Rejected + เหตุผล ช่องกรอก 48 ช่องเปิดให้แก้ ปุ่ม Submit กลับมา ข้อมูล 30,000 ยังอยู่ครบ</t>
+        </is>
+      </c>
+      <c r="O45" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P45" s="22" t="n"/>
       <c r="Q45" s="22" t="n"/>
       <c r="R45" s="23" t="inlineStr">
@@ -5004,8 +5646,14 @@
           <t>Laddawan → Nipaporn → Suchanya(jakkarit) (ไม่บังคับ)</t>
         </is>
       </c>
-      <c r="S45" s="24" t="n"/>
-      <c r="T45" s="21" t="n"/>
+      <c r="S45" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T45" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ตรวจจากหน้าจอ · ข้อ 8 และ 12 (กล่องจดหมายของ Nipaporn / Pornthip / อาทิตย์) ต้องให้คนเปิดอีเมลดู — คาดจากโค้ดว่าอาทิตย์ไม่ได้รับเลย เพราะผู้ส่งคือ Pornthip · ข้อสังเกต: ในมุมมองของ Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบายเรื่อง admin submit ยาว 1 บรรทัดปนอยู่ด้วย อ่านแล้วอาจสับสนสำหรับผู้อนุมัติ · SD จบที่สถานะ Rejected ตามที่ตั้งใจ (ไม่ใช่ Draft) ยอด 30,000 ค้างอยู่ในฝ่ายจริงของ Suchanya</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="620" customHeight="1">
       <c r="A46" s="18" t="inlineStr">
@@ -5163,8 +5811,16 @@
 ห้ามกด Submit ขณะเปิดโหมด Admin — การส่งงบด้วยสิทธิ์ผู้ดูแลระบบทำให้สถานะกลายเป็น `Approved` ทันที ซึ่งย้อนกลับไม่ได้ · ขณะเปิดโหมด Admin ระบบจะซ่อนปุ่ม `Approve` / `Reject` ของขั้นที่ตัวเองเป็นผู้อนุมัติไว้โดยตั้งใจ (ทำหน้าที่ผู้ดูแลระบบ ไม่ใช่ผู้อนุมัติ) — ถ้าต้องกลับไปอนุมัติงานของตัวเอง ให้ปิดโหมดก่อน · เคสนี้เป็นการดูอย่างเดียว ไม่ต้องกดอนุมัติหรือส่งงบของฝ่ายอื่น</t>
         </is>
       </c>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
+      <c r="N47" s="51" t="inlineStr">
+        <is>
+          <t>ยังไม่ได้ทดสอบ: การเปิด toggle 'โหมด Admin' ขณะสวมสิทธิ์ admin ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อก (เหตุเดียวกับ UAT-15) · ที่ยืนยันได้จาก UAT-15: สวมสิทธิ์ nipapornt สำเร็จ badge 'ผู้ดูแลระบบ' toggle มีอยู่ (admin-mode-toggle) ค่าเริ่มต้นปิด</t>
+        </is>
+      </c>
+      <c r="O47" s="21" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
       <c r="P47" s="22" t="n"/>
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="23" t="inlineStr">
@@ -5172,8 +5828,14 @@
           <t>Nipaporn หรือ Waraporn</t>
         </is>
       </c>
-      <c r="S47" s="24" t="n"/>
-      <c r="T47" s="21" t="n"/>
+      <c r="S47" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T47" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ให้คนทำ (~2 นาที): สวมสิทธิ์ nipapornt → เปิด toggle → ฝ่ายที่เลือกถูกรีเซ็ตและเห็นฝ่ายทั้งบริษัท → เช็คแถบ admin-zone และ tooltip → ปิด toggle · ห้ามกด Submit ขณะเปิดโหมด Admin</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="348" customHeight="1">
       <c r="A48" s="18" t="inlineStr">
@@ -5239,7 +5901,11 @@
 UAT รันบนระบบจริง (production) อีเมลออกจากระบบจริงถึงกล่องจดหมายของเพื่อนร่วมงานจริง ไม่มีระบบทดลองแยก · เคสนี้เป็นการส่งงบใหม่หลังถูกตีกลับในเคส UAT-41 ซึ่งเป็นการกด `Submit` ที่ต้องเกิดขึ้นจริงตามลำดับการรัน ไม่ใช่การกดซ้ำ · ข้อห้ามกดซ้ำใช้เฉพาะตอนที่สถานะเป็น `Pending` อยู่แล้วเท่านั้น กรณีนั้นให้ใช้อีเมลฉบับล่าสุดที่ยังอยู่ในกล่องจดหมาย แล้วเทียบเวลาบนอีเมลกับเวลาที่บันทึกไว้ตอนกด `Submit` แทน · ถ้าไม่กด `Submit` ในเคสนี้ ฝ่ายจะค้างอยู่ที่ `Rejected` และเคส UAT-47 กับ UAT-40 จะทำต่อไม่ได้</t>
         </is>
       </c>
-      <c r="N48" s="21" t="n"/>
+      <c r="N48" s="51" t="inlineStr">
+        <is>
+          <t>ก่อนกด: D&amp;A สถานะ 'Rejected' + 'Reject reason: ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ปุ่ม Submit แสดง · Pornthip กด Submit → กล่องยืนยันส่งทั้งฝ่าย → OK เวลา 03:16 (นาฬิกาเครื่องจริง) → chip 'Pending · Step 1 (Direct manager)' + 'Submitted — locked for editing until it is rejected' ปุ่ม Submit หาย · ฝ่ายกลับไปอยู่ Pending · Step 1 พร้อมให้ UAT-47/UAT-40 เดินต่อ</t>
+        </is>
+      </c>
       <c r="O48" s="21" t="n"/>
       <c r="P48" s="22" t="n"/>
       <c r="Q48" s="22" t="n"/>
@@ -5248,8 +5914,14 @@
           <t>Pornthip → Laddawan</t>
         </is>
       </c>
-      <c r="S48" s="24" t="n"/>
-      <c r="T48" s="21" t="n"/>
+      <c r="S48" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T48" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง · เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="324" customHeight="1">
       <c r="A49" s="18" t="inlineStr">
@@ -5321,7 +5993,11 @@
 เคสเดียวแต่มี 3 ข้อที่ต้องตรวจแยกกัน อ่านช่อง Expected Result ให้ครบทั้ง 3 ข้อก่อน mark Pass · **ข้อ 3 ทำให้สถานะเป็น `Approved` ซึ่งย้อนกลับไม่ได้ในระบบ ต้องแก้ที่ฐานข้อมูลเท่านั้น** ให้รันเคสนี้พร้อมกับ UAT-40 เป็นลำดับสุดท้ายของฝ่าย Data &amp; Analytic และห้ามกดอนุมัติชุดใหม่เพื่อทำเคสซ้ำ · ห้ามให้ผู้ดูแลระบบ (admin) กดอนุมัติแทนผู้อนุมัติตัวจริง เพราะจะได้อีเมลคนละแบบ (ดูเคส UAT-44) · อีเมลออกจากระบบจริงถึงเพื่อนร่วมงานจริง</t>
         </is>
       </c>
-      <c r="N49" s="21" t="n"/>
+      <c r="N49" s="51" t="inlineStr">
+        <is>
+          <t>ลำดับการกดจริง (นาฬิกาเครื่อง): Laddawan Approve 03:18 → สถานะ Step 2 · Nipaporn Approve 03:18 → สถานะ Step 3 · Waraporn Approve 03:21 → Approved · ก่อนขั้นที่ 2 กด ตัวเลือกฝ่ายของ Waraporn ไม่ติดป้าย Pending ที่ D&amp;A (ตรวจใน UAT-42 ตอนสถานะ Step 1) และติดป้ายเมื่อถึง Step 3 เท่านั้น — สอดคล้องกับกติกา 'ส่งเมลเมื่อถึงคิว'</t>
+        </is>
+      </c>
       <c r="O49" s="21" t="n"/>
       <c r="P49" s="22" t="n"/>
       <c r="Q49" s="22" t="n"/>
@@ -5330,8 +6006,14 @@
           <t>Laddawan → Nipaporn → Waraporn → Pornthip</t>
         </is>
       </c>
-      <c r="S49" s="24" t="n"/>
-      <c r="T49" s="21" t="n"/>
+      <c r="S49" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T49" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน · คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="372" customHeight="1">
       <c r="A50" s="18" t="inlineStr">
@@ -5486,7 +6168,11 @@
 เคสเดียวแต่มี 8 ข้อที่ต้องตรวจแยกกัน (ยุบมาจาก SIT 8 เคส) อ่านช่อง Expected Result ให้ครบทั้ง 8 ข้อก่อน mark Pass · SIT ตรวจข้อ 6 เฉพาะบนคอมพิวเตอร์และค้างการเปิดบนมือถือไว้ รอบนี้ต้องเปิดบนมือถืออย่างน้อย 1 ครั้ง · ถ้าจำเป็นต้องใช้อีเมลฉบับอื่นที่ไม่ใช่ "ได้รับการอนุมัติ" ให้จดหัวข้อฉบับที่ใช้จริงลงช่อง Actual Result แล้วเทียบ To/CC และหัวข้อตามฉบับนั้น เพราะข้อ 2 กับข้อ 3 เขียนตามฉบับ "ได้รับการอนุมัติ"</t>
         </is>
       </c>
-      <c r="N51" s="21" t="n"/>
+      <c r="N51" s="51" t="inlineStr">
+        <is>
+          <t>ข้อ 5 (ลิงก์ในอีเมล): ระบบสร้างลิงก์รูปแบบ /?dept=Data%20%26%20Analytic&amp;year=2026 (ปีบนลิงก์ = ปีหน้าจอ) · เปิดลิงก์นี้ในนาม Pornthip → หน้าเปิดที่ฝ่าย 'Data &amp; Analytic' ปี 'Year 2026' ถูกเลือกทันที ตาราง 10 แถวโหลดครบ สถานะ 'Approved' ไม่มีข้อความผิดพลาด ไม่ใช่หน้าเปล่า · ข้อ 8: อีเมลระบุ 'ปีงบประมาณ 2027 (หน้าจอ: Year 2026)' ตามภาพกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู — จับคู่ปีถูกต้อง · จากภาพเดียวกัน: ผู้ส่ง CMAN_PowerBI, To ผู้อนุมัติ, Cc CMAN_PowerBI, หัวข้อ 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027', ตัวอักษรไทยครบ ไม่มี ??? (บนคอมพิวเตอร์)</t>
+        </is>
+      </c>
       <c r="O51" s="21" t="n"/>
       <c r="P51" s="22" t="n"/>
       <c r="Q51" s="22" t="n"/>
@@ -5495,8 +6181,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S51" s="24" t="n"/>
-      <c r="T51" s="21" t="n"/>
+      <c r="S51" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T51" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 5, 8 ผ่าน; ข้อ 1-4, 6, 7 รอคนตรวจกล่องจดหมาย · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT)</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="288" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
@@ -5649,7 +6341,11 @@
 เคสนี้เป็น 1 แถวแต่มี 4 ข้อที่ต้องตรวจ ต้องอ่าน Expected Result ให้ครบทั้ง 4 ข้อก่อนกด Pass · การตรวจบน Microsoft Edge เป็นข้อค้างจาก SIT (ผู้ทดสอบเดิมบันทึกไว้ว่า "ยังต้องให้คนตรวจบน Edge") รอบนี้ต้องมีคนเปิดบน Edge จริง ไม่ใช่เดาว่าเหมือนกัน · ชุดสีของบริษัทเพิ่งเปลี่ยนหลังปิดรอบ SIT ผู้ทดสอบเดิมจึงเห็นสีเขียวคนละเฉดกับที่เห็นตอนนี้ อย่าใช้ภาพหน้าจอเก่าเป็นเกณฑ์เทียบ · ถ้าพบจุดที่อ่านยากหรือตัวเลขทับกัน ให้เปิดแถวใหม่ในชีต `4. Defects` แล้วแนบภาพหน้าจอไปด้วย · เคสนี้ทำหลังระลอก W6 ฝ่ายที่ใช้ดูอาจอยู่ในสถานะ `Approved` แล้ว ปุ่ม `Submit` จะไม่ปรากฏ ซึ่งถูกต้องตามสถานะ ไม่ใช่ข้อผิดพลาด ให้ตรวจเฉพาะปุ่มที่มีจริงในสถานะนั้น</t>
         </is>
       </c>
-      <c r="N53" s="21" t="n"/>
+      <c r="N53" s="51" t="inlineStr">
+        <is>
+          <t>บันทึกภาพหน้าจอ 3 ภาพในสถานะ Approved: ตารางทั้งหน้า (full page), ฟอร์มย่อย Entertainment แบบอ่านอย่างเดียว, กล่องแนบไฟล์ · ตัวเลขยาวสุดในฝ่ายนี้ = 415,900.00 (ยังไม่ถึงหลักล้าน) · ชื่อฝ่ายไทย/ชื่อ GL ยาวแสดงครบหลังโหลดใหม่หลายครั้งตลอดรอบ · ข้อ 11 (มุมมองผู้อนุมัติขณะ Pending) ดูได้จากภาพ UAT-38/40/41 ที่ถ่ายไว้ตอนสถานะ Pending</t>
+        </is>
+      </c>
       <c r="O53" s="21" t="n"/>
       <c r="P53" s="22" t="n"/>
       <c r="Q53" s="22" t="n"/>
@@ -5658,8 +6354,14 @@
           <t>Pornthip → Laddawan</t>
         </is>
       </c>
-      <c r="S53" s="24" t="n"/>
-      <c r="T53" s="21" t="n"/>
+      <c r="S53" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T53" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge · AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="588" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
@@ -5729,7 +6431,11 @@
 กรณี "เปิด 2 แท็บแล้วแก้แถวเดียวกันพร้อมกัน" ที่ SIT เคยมีอยู่ ถูกตัดออกจากรอบนี้แล้ว — jakkaritw ตัดสินเมื่อ 2026-08-20 ว่าผ่าน เพราะตัวเลขอัปเดตให้ทันทีอยู่แล้ว โอกาสพลาดน้อยมาก จึงไม่ต้องทดสอบซ้ำ · ตามลำดับการรัน เคสนี้ถูกวางไว้ **ก่อนเคส UAT-40 โดยตั้งใจ** เพราะขั้นตอนที่ 1 ต้องใช้ฝ่ายที่ส่งขออนุมัติแล้วแต่ยัง **ไม่** เป็น `Approved` — ห้ามเลื่อนเคสนี้ไปทำหลัง UAT-40 · แต่ **ขั้นตอนที่ 2 (จำนวนวันเดินทางติดลบ) ทำตรงตำแหน่งนี้ไม่ได้** เพราะระบบล็อกการแก้ไขทั้งฝ่ายตั้งแต่ตอนกด `Submit` ไม่ใช่ตอน `Approved` — สถานะ `Pending` ทั้ง 3 ขั้นล็อกเท่ากับ `Approved` ทุกประการ ทำให้ Trip Manager เปิดเป็นแบบอ่านอย่างเดียวและไม่มีปุ่ม `บันทึก &amp; ลงบัญชี` ให้กด · **หยุด — ต้องย้อนกลับไปทำขั้นตอนที่ 2 ทำทันทีหลัง UAT-26 ก่อนเริ่ม UAT-32** ซึ่งเป็นช่วงเดียวในรอบทดสอบที่ทริปยังแก้ไขได้ ถ้าไม่ทำตามป้ายนี้ การทดสอบจำนวนวันเดินทางติดลบจะหายไปจากรอบนี้ทั้งรอบ · ถ้าถึงตอนนั้นแล้วไม่มีทริปที่แก้ไขได้เหลืออยู่จริง ห้ามข้ามเงียบ ๆ ให้บันทึกเป็น Blocked พร้อมเหตุผลลงช่อง Remarks แล้วแจ้งหัวหน้าทีมทดสอบทันที (ฝ่าย Solution Delivery ไม่มีแถวงบให้ใช้แทน และปีอื่นนอกจากปีงบประมาณ 2027 ยังไม่เปิดให้กรอก) · ขั้นตอนที่ 3 ให้ปิด Wi-Fi ของเครื่องตัวเองเท่านั้น อย่าไปแตะอุปกรณ์เครือข่ายของสำนักงาน</t>
         </is>
       </c>
-      <c r="N54" s="21" t="n"/>
+      <c r="N54" s="51" t="inlineStr">
+        <is>
+          <t>ข้อ 1 (ฝ่าย Data &amp; Analytic สถานะ Pending · Step 1): โหลดหน้าใหม่แล้วช่องเดือนทั้งหมดเป็นตัวหนังสืออ่านอย่างเดียว ไม่มีช่องพิมพ์เลย (0 ช่อง) ปุ่มฟอร์มย่อยเปลี่ยนเป็น '🔒 ดูรายละเอียด' tooltip 'อ่านอย่างเดียว — แก้ไม่ได้ในสถานะนี้' ปุ่มลบแถวหายทั้งหมด · ปุ่ม '+ เพิ่ม Transaction' ยังกดได้ → ฟอร์มเลือก Cost Center / GL เปิดขึ้น เลือก 10IT013000 + 6210900060 — ค่าไปรษณีย์ กด บันทึก → ข้อความสีแดงในฟอร์ม (คำต่อคำ): 'ฝ่าย "Data &amp; Analytic" อยู่ระหว่างอนุมัติหรืออนุมัติแล้ว ไม่สามารถเพิ่มรายการใหม่ในฝ่ายนี้ได้ในสถานะนี้' แถวไม่ถูกเพิ่ม (ยังคง 10 แถว) กด ยกเลิก ปิดฟอร์มได้ · ข้อ 4 สำหรับข้อความนี้: (ก) บอกสาเหตุ = ใช่ (ข) บอกสิ่งที่ต้องทำต่อ = ไม่ชัด (ไม่บอกว่าต้องรอตีกลับหรือรอรอบถัดไป) · ไม่มี stack trace / .py / SQL · ข้อ 2 (ทำตอนฝ่ายกลับเป็น Rejected หลัง UAT-41 ทริปแก้ได้อีกครั้ง): เปิด Trip Manager ผ่านปุ่มฟอร์มย่อย GL 6210400020 เห็นทริป 52 และ 53 (วันเดินทาง 5 / 5) · พิมพ์ -3 ลงช่องวันเดินทางของทริป 52 → ช่องรับค่าเป็น 3 ทันที (เครื่องหมายลบถูกตัดทิ้ง) ไม่มีข้อความแจ้งใด ๆ · กด บันทึก &amp; ลงบัญชี → บันทึกสำเร็จเงียบ ๆ ด้วยค่า 3 วัน (AI แก้กลับเป็น 5 และบันทึกซ้ำแล้ว ยอด per diem กลับเป็น 13,200 / 13,200 รวม 26,400 และรวมทั้งหมด 415,900.00 เท่าเดิม ตรวจหลังโหลดหน้าใหม่) · ข้อ 3 (จำลองตัดเครือข่ายเฉพาะ browser ทดสอบ ไม่แตะ Wi-Fi เครื่อง): พิมพ์ 4,100 ลงช่อง ก.ค. ของ GL 6210400999 (เดิม 4,000) คลิกออก → แถบข้อความ 'เชื่อมต่อเซิร์ฟเวอร์ไม่ได้ กรุณาตรวจสอบอินเทอร์เน็ต' ค่าที่พิมพ์ยังค้างบนจอ · คืนเครือข่ายแล้วโหลดหน้าใหม่ → ค่ากลับเป็น 4,000 (ไม่ถูกบันทึกระหว่างไม่มีเน็ต) · ข้อ 4: ข้อความข้อ 3 บอกสาเหตุ = ใช่ บอกสิ่งที่ต้องทำ = ใช่ (ตรวจอินเทอร์เน็ต) · ทุกข้อความไม่มี stack trace / .py / SQL · ข้อ 5: ตลอด W1-W7 ไม่พบข้อความแจ้งข้อผิดพลาดที่อ่านไม่รู้เรื่อง</t>
+        </is>
+      </c>
       <c r="O54" s="21" t="n"/>
       <c r="P54" s="22" t="n"/>
       <c r="Q54" s="22" t="n"/>
@@ -5738,8 +6444,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S54" s="24" t="n"/>
-      <c r="T54" s="21" t="n"/>
+      <c r="S54" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T54" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — ข้อ 1, 3, 4 ผ่าน; ข้อ 2 ให้คนตัดสิน (ระบบกันค่าติดลบแบบเงียบ ไม่มีข้อความ) · ข้อ 1, 3, 4, 5 ผ่าน · ข้อ 2 ไม่ตรง Expected ตรงตัว: ระบบ 'กัน' ค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) แทนที่จะปฏิเสธพร้อมข้อความ — ผลข้างเคียงคือถ้าผู้ใช้พิมพ์ผิดเป็น -3 จะได้ทริป 3 วันโดยไม่รู้ตัว ขอให้หัวหน้าทีมทดสอบตัดสินว่ารับได้หรือเปิดเป็น defect (ข้อเสนอ: แจ้งเตือนสั้น ๆ ว่า 'จำนวนวันต้องเป็น 1 ขึ้นไป') · ข้อสังเกตเดิม: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อกการเรียก API ใน browser ทดสอบแทนการปิด Wi-Fi จริง — ผลจากมุมของแอปเหมือนกัน (Failed to fetch) แต่รอบคนทดสอบควรปิด Wi-Fi จริงซ้ำ 1 ครั้ง</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="324" customHeight="1">
       <c r="A55" s="18" t="inlineStr">
@@ -5812,8 +6524,16 @@
 เคสนี้คือการยืนยันการแก้บั๊ก "เงินหายเงียบ ๆ" — ตอนที่ยังเป็นบั๊ก เงินหายโดยไม่มีข้อความแจ้ง ไม่มี log และไม่มีอีเมล ผู้ใช้จึงไม่มีทางรู้ตัว ถ้าตัวเลขในขั้นตอนที่ 8 ไม่เท่ากับขั้นตอนที่ 4 ให้เปิด Defect ระดับ Blocker ทันที · การลบทริปย้อนกลับไม่ได้ ให้ลบเฉพาะทริปที่สร้างขึ้นเองในรอบ UAT นี้เท่านั้น ห้ามลบทริปของคนอื่น · ต้องทำเคสนี้ตอนที่ฝ่ายยังแก้ไขได้ ถ้าฝ่ายถูกล็อกจากการ Submit ไปแล้ว ให้เลื่อนไปทำหลังจากถูกตีกลับ หรือทำก่อนเริ่มระลอก W5</t>
         </is>
       </c>
-      <c r="N55" s="21" t="n"/>
-      <c r="O55" s="21" t="n"/>
+      <c r="N55" s="51" t="inlineStr">
+        <is>
+          <t>ใช้ Cost Center 10IT013000 (ที่มีทริปของระลอก W3) · เพิ่มแถว 6210400999 ผ่านฟอร์ม + เพิ่ม Transaction · กรอก ก.ค. 5000 → ช่องแสดง 5000 รวมทั้งปี 5,000.00 (ค่าตั้งต้น) · เปิด Trip Manager จากแถวค่าพาหนะ ลบทริป existing-54 (Thailand มิ.ย. 3 วัน ที่สร้างใน UAT-25) ยืนยันที่กล่อง 'ลบทริปนี้ทั้งหมด?' · ปิดหน้าต่าง refresh → แถว 6210400999 ยังอยู่ ก.ค. = 5000 รวมทั้งปี 5,000.00 เท่าเดิมทุกบาท · ยอดที่เปลี่ยนมีเฉพาะ GL ของทริป: เบี้ยเลี้ยง มิ.ย. 750.00 → — (รวมปี 27,150 → 26,400) · ค่าพาหนะ/ค่าที่พักไม่เปลี่ยน (ทริปที่ลบไม่มียอด 2 แถวนี้) · GL อื่นทั้งหมดเท่าเดิม (135,500 / 38,000 / 101,000 / 32,000 / 36,000)</t>
+        </is>
+      </c>
+      <c r="O55" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P55" s="22" t="n"/>
       <c r="Q55" s="22" t="n"/>
       <c r="R55" s="23" t="inlineStr">
@@ -5821,8 +6541,14 @@
           <t>ไม่ระบุชื่อในเคส (ต้องเป็น Filler ของ Cost Center นั้น = Pornthip)</t>
         </is>
       </c>
-      <c r="S55" s="24" t="n"/>
-      <c r="T55" s="21" t="n"/>
+      <c r="S55" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T55" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ข้อ 1-5 ทุกข้อ · บั๊ก 'เงินหายเงียบ' ไม่เกิดซ้ำ · เบี่ยงเบนจาก Test Data: ใช้ CC 10IT013000 แทน 10IT011300 เพราะทริปทั้งหมดอยู่ที่ 10IT013000 และเคสบังคับว่าต้องเป็น CC เดียวกับทริป (10IT011300 ไม่มีทริป) · ทริปที่เหลือ: existing-52 (พ.ค.) และ existing-53 (เม.ย.)</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="420" customHeight="1">
       <c r="A56" s="18" t="inlineStr">
@@ -5894,7 +6620,11 @@
 พฤติกรรมนี้ตัดสินไปแล้วเมื่อ 2026-08-21 ว่าจะไม่แก้ (jakkaritw) — **ห้ามแจ้งเป็น defect** จุดประสงค์ของเคสนี้คือให้ผู้ใช้รับรู้และเซ็นรับทราบก่อนใช้งานจริง ไม่ใช่การหาข้อบกพร่อง · การแก้อัตราแลกเปลี่ยนคือการแก้ข้อมูล master จริงบนระบบจริง ให้ผู้ดูแลระบบเป็นคนทำเท่านั้น จดค่าเดิมไว้ก่อน และคืนค่าเดิมทันทีที่ทดสอบเสร็จ · ถ้าทีมตัดสินว่าไม่ควรแตะ master จริงในรอบนี้ ให้ข้ามขั้นตอนที่ 2 ถึง 6 แล้วทำเฉพาะขั้นตอนที่ 7 (อธิบายพฤติกรรมให้ผู้ใช้ฟังแล้วบันทึกคำตอบ) พร้อมระบุใน Actual Result ว่าเลือกใช้ทางเลือกใด · ต้องทำเคสนี้ก่อนที่ฝ่ายจะถูกอนุมัติครบ 3 ขั้น เพราะต้องกด `บันทึก &amp; ลงบัญชี` ซ้ำได้</t>
         </is>
       </c>
-      <c r="N56" s="21" t="n"/>
+      <c r="N56" s="51" t="inlineStr">
+        <is>
+          <t>ค่าตั้งต้น (ขั้นตอนที่ 1) จดไว้แล้ว: ทริปต่างประเทศ Singapore 5 วัน (ทริป existing-53 เดือน เม.ย. และ existing-52 เดือน พ.ค.) เบี้ยเลี้ยงในฟอร์มย่อย = 13,200.00 ต่อทริป · ตารางหลัก 6210400010 เม.ย. 13,200.00 / พ.ค. 13,200.00 · 6210400020 พ.ค. 18,000.00 · 6210400030 พ.ค. 25,000.00 · อัตราแลกเปลี่ยนใน master ปี 2027 = 33.0000 USD/THB (dbo.master_currency_rate) · ขั้นตอนที่ 2-6 (ให้ admin แก้อัตราแลกเปลี่ยนในไฟล์ master จริงแล้วคืนค่า) AI ไม่ทำ เพราะเป็นการแก้ master ของทั้งบริษัทบนระบบจริง</t>
+        </is>
+      </c>
       <c r="O56" s="21" t="n"/>
       <c r="P56" s="22" t="n"/>
       <c r="Q56" s="22" t="n"/>
@@ -5903,8 +6633,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S56" s="24" t="n"/>
-      <c r="T56" s="21" t="n"/>
+      <c r="S56" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T56" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ทางเลือกตาม note ของเคส: ข้ามขั้นตอน 2-6 ทำเฉพาะขั้นตอนที่ 7 · ต้องให้คนอธิบายพฤติกรรม (ฟอร์มย่อยคำนวณใหม่ทันที แต่ตารางหลักคงยอดเดิมจนกดบันทึกซ้ำ — ตัดสินแล้ว 2026-08-21 ว่าไม่แก้) แล้วให้ผู้ใช้เขียนใน Remarks ว่ารับทราบหรือไม่ · ถ้าทีมตัดสินใจทดสอบจริง admin ต้องแก้ค่า 33.0000 แล้วคืนค่าทันที</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:T56"/>
@@ -5962,20 +6698,20 @@
           <t>UAT Test Execution — Summary  ·  Round 1  ·  FY2027</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="C2" s="50" t="n"/>
+      <c r="D2" s="50" t="n"/>
+      <c r="E2" s="50" t="n"/>
+      <c r="F2" s="50" t="n"/>
+      <c r="G2" s="50" t="n"/>
+      <c r="H2" s="50" t="n"/>
+      <c r="I2" s="50" t="n"/>
+      <c r="J2" s="50" t="n"/>
+      <c r="K2" s="50" t="n"/>
+      <c r="L2" s="50" t="n"/>
+      <c r="M2" s="50" t="n"/>
+      <c r="N2" s="50" t="n"/>
+      <c r="O2" s="50" t="n"/>
+      <c r="P2" s="50" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="B3" s="26" t="inlineStr">
@@ -5983,20 +6719,20 @@
           <t>สรุปผลอัตโนมัติจากแท็บ “2. Test Cases” (ไม่ต้องกรอกเอง) · ทุกสูตรนับช่วงแถวจริง 3–56</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="50" t="n"/>
+      <c r="E3" s="50" t="n"/>
+      <c r="F3" s="50" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="50" t="n"/>
+      <c r="L3" s="50" t="n"/>
+      <c r="M3" s="50" t="n"/>
+      <c r="N3" s="50" t="n"/>
+      <c r="O3" s="50" t="n"/>
+      <c r="P3" s="50" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="27" t="inlineStr">
@@ -6009,8 +6745,8 @@
           <t>Count</t>
         </is>
       </c>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
+      <c r="D5" s="50" t="n"/>
+      <c r="E5" s="52" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="B6" s="29" t="inlineStr">
@@ -6022,8 +6758,8 @@
         <f>COUNTA('2. Test Cases'!$D$3:$D$56)</f>
         <v/>
       </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
+      <c r="D6" s="50" t="n"/>
+      <c r="E6" s="52" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="B7" s="31" t="inlineStr">
@@ -6035,8 +6771,8 @@
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"Pass")</f>
         <v/>
       </c>
-      <c r="D7" s="32" t="n"/>
-      <c r="E7" s="32" t="n"/>
+      <c r="D7" s="50" t="n"/>
+      <c r="E7" s="52" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
@@ -6048,8 +6784,8 @@
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"Fail")</f>
         <v/>
       </c>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n"/>
+      <c r="D8" s="50" t="n"/>
+      <c r="E8" s="52" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="B9" s="35" t="inlineStr">
@@ -6061,8 +6797,8 @@
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"Blocked")</f>
         <v/>
       </c>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
+      <c r="D9" s="50" t="n"/>
+      <c r="E9" s="52" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="B10" s="37" t="inlineStr">
@@ -6074,8 +6810,8 @@
         <f>C6-C7-C8-C9-C11</f>
         <v/>
       </c>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
+      <c r="D10" s="50" t="n"/>
+      <c r="E10" s="52" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="B11" s="37" t="inlineStr">
@@ -6087,8 +6823,8 @@
         <f>COUNTIF('2. Test Cases'!$O$3:$O$56,"N/A")</f>
         <v/>
       </c>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="38" t="n"/>
+      <c r="D11" s="50" t="n"/>
+      <c r="E11" s="52" t="n"/>
     </row>
     <row r="12" ht="24.75" customHeight="1">
       <c r="B12" s="39" t="inlineStr">
@@ -6100,8 +6836,8 @@
         <f>IFERROR(COUNTIF('2. Test Cases'!$O$3:$O$56,"Pass")/(COUNTIF('2. Test Cases'!$O$3:$O$56,"Pass")+COUNTIF('2. Test Cases'!$O$3:$O$56,"Fail")+COUNTIF('2. Test Cases'!$O$3:$O$56,"Blocked")),"-")</f>
         <v/>
       </c>
-      <c r="D12" s="41" t="n"/>
-      <c r="E12" s="41" t="n"/>
+      <c r="D12" s="50" t="n"/>
+      <c r="E12" s="52" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="42" t="inlineStr">
@@ -6109,26 +6845,26 @@
           <t>Breakdown by Module</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="n"/>
+      <c r="E14" s="50" t="n"/>
       <c r="G14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Wave</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
+      <c r="H14" s="50" t="n"/>
+      <c r="I14" s="50" t="n"/>
+      <c r="J14" s="50" t="n"/>
+      <c r="K14" s="50" t="n"/>
       <c r="M14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Department</t>
         </is>
       </c>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
+      <c r="N14" s="50" t="n"/>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="50" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="28" t="inlineStr">
@@ -6653,20 +7389,20 @@
           <t>หมายเหตุ: ตัวเลขอัปเดตอัตโนมัติเมื่อกรอกคอลัมน์ Status ในแท็บ “2. Test Cases” · ช่วงข้อมูลจริง = แถวที่ 3 ถึง 56 · ไฟล์นี้ไม่มีแถวตัวอย่าง (ไม่มี TC-EX) · ช่อง Total ของทั้ง 3 ตารางต้องเท่ากับ Total test cases ด้านบน · แถว Not Run คำนวณจาก “Total ลบด้วย Pass + Fail + Blocked + N/A” จึงนับช่อง Status ที่ยังว่างให้เป็น Not Run โดยอัตโนมัติ (ไม่ต้องพิมพ์คำว่า Not Run เอง) และทำให้ห้าแถวบนรวมกันได้เท่ากับ Total เสมอ</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
-      <c r="O26" s="9" t="n"/>
-      <c r="P26" s="9" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+      <c r="E26" s="50" t="n"/>
+      <c r="F26" s="50" t="n"/>
+      <c r="G26" s="50" t="n"/>
+      <c r="H26" s="50" t="n"/>
+      <c r="I26" s="50" t="n"/>
+      <c r="J26" s="50" t="n"/>
+      <c r="K26" s="50" t="n"/>
+      <c r="L26" s="50" t="n"/>
+      <c r="M26" s="50" t="n"/>
+      <c r="N26" s="50" t="n"/>
+      <c r="O26" s="50" t="n"/>
+      <c r="P26" s="50" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -6674,13 +7410,13 @@
     <mergeCell ref="B2:P2"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="B26:P26"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B3:P3"/>
-    <mergeCell ref="M14:P14"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="G14:K14"/>
     <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="M14:P14"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C10:E10"/>
@@ -6719,18 +7455,18 @@
           <t>Budget Web App — UAT Defect Log  ·  เปิดแถวใหม่ทุกครั้งที่มีเคส Status = Fail แล้วนำเลข Defect ID ไปใส่ในคอลัมน์ Defect ID ของแท็บ “2. Test Cases”</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
+      <c r="B1" s="50" t="n"/>
+      <c r="C1" s="50" t="n"/>
+      <c r="D1" s="50" t="n"/>
+      <c r="E1" s="50" t="n"/>
+      <c r="F1" s="50" t="n"/>
+      <c r="G1" s="50" t="n"/>
+      <c r="H1" s="50" t="n"/>
+      <c r="I1" s="50" t="n"/>
+      <c r="J1" s="50" t="n"/>
+      <c r="K1" s="50" t="n"/>
+      <c r="L1" s="50" t="n"/>
+      <c r="M1" s="50" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
@@ -7565,18 +8301,18 @@
           <t>Severity ของ defect ใช้ **ชุดค่าเดียวกับคอลัมน์ Severity ในแท็บ “2. Test Cases”** ยกมาใส่ได้ตรง ๆ ไม่ต้องแปลงค่า: Critical = ระบบใช้งานไม่ได้ / ข้อมูลเงินผิดพลาดร้ายแรง · High = ฟังก์ชันหลักเสีย · Medium = เสียแต่มีทางเลี่ยง · Low = ปัญหาเล็กน้อยหรือ UI (ไม่มีค่า `-` ในแท็บนี้ เพราะแถว defect เกิดขึ้นเฉพาะตอนมีเคส Fail)  ·  Status: Open → In Progress → Fixed → Retested → Closed (หรือ Wont Fix ถ้าตัดสินว่าไม่แก้)</t>
         </is>
       </c>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="9" t="n"/>
+      <c r="B44" s="50" t="n"/>
+      <c r="C44" s="50" t="n"/>
+      <c r="D44" s="50" t="n"/>
+      <c r="E44" s="50" t="n"/>
+      <c r="F44" s="50" t="n"/>
+      <c r="G44" s="50" t="n"/>
+      <c r="H44" s="50" t="n"/>
+      <c r="I44" s="50" t="n"/>
+      <c r="J44" s="50" t="n"/>
+      <c r="K44" s="50" t="n"/>
+      <c r="L44" s="50" t="n"/>
+      <c r="M44" s="50" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:M42"/>
@@ -7597,4 +8333,1750 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>AI pre-run บน production ผ่าน /sit/impersonate — 09/09/2026 00:54–03:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI สวมสิทธิ์เป็นผู้ทดสอบตามคอลัมน์ Tester แล้วรันตาม Run Order · ผลอยู่ในช่องสีเหลืองของแท็บ 2 · Status ใส่เฉพาะ Pass/Fail/Blocked ที่ AI มั่นใจ ช่องว่าง = ให้คนตัดสินหรือทำเอง · ภาพหลักฐาน: .scratch/uat-prep/runner/shots/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>Run Order</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>Tester (impersonated)</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>AI Status</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>UAT-01</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E5" s="55" t="inlineStr">
+        <is>
+          <t>ตรงกับ Expected ข้อ 1-9 ทุกข้อ · ข้อ 8 (กดลิงก์ออกจากระบบเพื่อยืนยันว่ากดได้) ไม่ได้กดใน pre-UAT เพราะจะทำให้ session ของการรันหลุด — ให้คนกดในรอบจริง</t>
+        </is>
+      </c>
+      <c r="F5" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-01_userbar.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="55" t="inlineStr">
+        <is>
+          <t>UAT-02</t>
+        </is>
+      </c>
+      <c r="C6" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E6" s="55" t="inlineStr">
+        <is>
+          <t>ตรง Expected ข้อ 1-6 ทุกข้อ · ข้อสังเกต (ไม่ใช่ defect): ตารางของ Solution Delivery ไม่ได้ว่างเปล่าอย่างที่ note ของเคสคาด — แสดงแถว GL ของ 10IT012000 พร้อมยอด SAP ใช้จริง แต่ชั้น Pending เป็น 0 ทั้งหมด เพราะแถวมาจากชั้น SAP ไม่ใช่ข้อมูลที่กรอก ควรแก้ note ของเคสให้ตรง</t>
+        </is>
+      </c>
+      <c r="F6" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-02_picker_open.png, shots/UAT-02_solution_delivery_selected.png, shots/UAT-02_back_to_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="55" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="55" t="inlineStr">
+        <is>
+          <t>UAT-06</t>
+        </is>
+      </c>
+      <c r="C7" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 2-5 · ข้อ 1 (ต้องเห็น 2 ฝั่ง): เห็นฝั่งเดียว — ยืนยันจากโค้ด GridTable.tsx:1156 ว่าฝั่งที่ไม่มีแถวถูกซ่อนโดยตั้งใจ จึงไม่ใช่ defect แต่ Expected ข้อ 1 ควรเขียนเพิ่มว่า 'ฝั่งที่ไม่มีแถวจะไม่แสดง' · 10IT011300 ไม่ปรากฏเพราะยังไม่มีแถวใด ๆ (ทั้ง Pending และ SAP) — ตรงเงื่อนไข 'มีเฉพาะ' แต่ควรให้คนยืนยันว่าถูกต้องตามสิทธิ์จริง</t>
+        </is>
+      </c>
+      <c r="F7" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-06-08_grid_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="55" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="55" t="inlineStr">
+        <is>
+          <t>UAT-07</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>ข้อ 1-3 ผ่าน · ข้อ 4 ตรวจไม่ได้ในฝ่ายนี้เพราะไม่มีแถว Approved-only เลย บันทึกว่า 'ไม่พบ' ตาม Expected ข้อ 5 ไม่ถือเป็น Fail · ถ้าต้องการพิสูจน์ข้อ 4 จริง ต้องใช้ฝ่ายที่มีข้อมูล board_budget ปี 2026</t>
+        </is>
+      </c>
+      <c r="F8" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-06-08_grid_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="55" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="55" t="inlineStr">
+        <is>
+          <t>UAT-08</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only</t>
+        </is>
+      </c>
+      <c r="E9" s="55" t="inlineStr">
+        <is>
+          <t>ข้อ 1-3 ตรงตาม Expected ทุกตัวอักษร · ข้อ 4 เป็นความเห็นของคนว่าอ่านแล้วเข้าใจไหม — AI ไม่ตัดสินแทน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยน Status เป็น Pass เอง</t>
+        </is>
+      </c>
+      <c r="F9" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-06-08_grid_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="55" t="inlineStr">
+        <is>
+          <t>UAT-09</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E10" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1, 3, 4 · ข้อ 2 (ข้อความ 'กำลังบันทึก…' ขึ้นแล้วหายเอง) automation อ่านหน้าจอไม่ทันช่วงสั้น ๆ นั้น จึงยังไม่ได้ยืนยันด้วยตา — ให้ผู้ทดสอบสังเกตในรอบจริง · เบี่ยงเบนจาก step 1: เคสระบุให้ใช้ Cost Center 10IT011300 แต่ CC นั้นไม่มีแถวใดในตารางเลย (ยังไม่ได้เพิ่มรายการ) จึงใช้ 10IT013000 แทน — ควรแก้เคสให้เพิ่มแถวก่อน หรือระบุ 10IT013000</t>
+        </is>
+      </c>
+      <c r="F10" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-09_after_reload.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="55" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>UAT-10</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E11" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1-5 ทุกข้อ ผลบวกตรงเครื่องคิดเลข</t>
+        </is>
+      </c>
+      <c r="F11" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-10_totals.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="55" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="55" t="inlineStr">
+        <is>
+          <t>UAT-11</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only</t>
+        </is>
+      </c>
+      <c r="E12" s="55" t="inlineStr">
+        <is>
+          <t>ข้อ 1-2 ตรง Expected · ข้อ 3 (อ่านแล้วเข้าใจไหม) เป็นความเห็นของคน — ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass เอง</t>
+        </is>
+      </c>
+      <c r="F12" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-06-08_grid_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>UAT-12</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E13" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านครบทั้ง 6 บรรทัดและ Expected ข้อ 1-9 · ข้อความแจ้งเตือนขึ้นทุกบรรทัดที่มีการปัดค่า (1, 2, 3, 4) และเงียบในบรรทัด 5, 6 ตามที่ Expected ระบุ · การจับเวลา 6 วินาที: automation ตรวจที่ 7 วินาทีแล้วข้อความหายไปแล้ว ไม่ได้จับเวลาละเอียดกว่านั้น</t>
+        </is>
+      </c>
+      <c r="F13" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-12_line1_toast.png, shots/UAT-12_line3_cap.png, shots/UAT-12_line4_drift.png, shots/UAT-12_line6_negative.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="55" t="inlineStr">
+        <is>
+          <t>UAT-13</t>
+        </is>
+      </c>
+      <c r="C14" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="E14" s="55" t="inlineStr">
+        <is>
+          <t>Fail เฉพาะ Expected ข้อ 1: เคสคาดว่าจะเห็นข้อความ 2 ช่องพร้อมกัน แต่ระบบแจ้งทีละช่อง (ช่องแรกที่ขาดก่อน) — พฤติกรรมเดียวกับฟอร์มย่อย จึงน่าจะเป็นความตั้งใจของระบบ ให้คุณตัดสินว่ายอมรับได้ (แล้วแก้ Expected ข้อ 1) หรือถือเป็น defect · ข้อ 2, 3, 4 ผ่าน · ข้อ 3 ส่วน 'อ่านเข้าใจไหม' เป็นความเห็นของคน</t>
+        </is>
+      </c>
+      <c r="F14" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-13_case1_empty.png, shots/UAT-13_case2_cc_only.png, shots/UAT-13_case3_duplicate.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="55" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="55" t="inlineStr">
+        <is>
+          <t>UAT-14</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D15" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E15" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-3 · ข้อ 4-5 ไม่มีแถวเดิมให้ทดสอบ บันทึกตามข้อ 6 · การซ่อนเป็นกติกาที่ตั้งไว้ 2026-08-29 (Training &amp; Seminar → Talent &amp; Culture เท่านั้น)</t>
+        </is>
+      </c>
+      <c r="F15" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-14_gl_search_noCC.png, shots/UAT-14_gl_search_withCC.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>UAT-15</t>
+        </is>
+      </c>
+      <c r="C16" s="55" t="inlineStr">
+        <is>
+          <t>Nipaporn (impersonated) — สลับสำเร็จ แต่ AI ไม่ได้เปิดโหมด Admin</t>
+        </is>
+      </c>
+      <c r="D16" s="55" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>ให้คนทำ (ใช้เวลา ~1 นาที): สวมสิทธิ์ nipapornt → เปิด toggle โหมด Admin → เลือก Data &amp; Analytic → + เพิ่ม Transaction → ค้น 5210100150 และ 6210100150 ต้องพบทั้งคู่ · ห้ามกด Submit ระหว่างเปิดโหมด Admin (approval.py:987 จะ Approved ทันที)</t>
+        </is>
+      </c>
+      <c r="F16" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-15_nipaporn_landing.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="55" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t>UAT-16</t>
+        </is>
+      </c>
+      <c r="C17" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D17" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E17" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-5 ทุกข้อ · ยืนยันข้อสังเกตจาก UAT-06 ว่าฝั่ง 5xxx แสดงเมื่อมีแถว 5xxx เท่านั้น</t>
+        </is>
+      </c>
+      <c r="F17" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-16_row_added_6210400999.png, shots/UAT-16_6210400999_after_reload.png, shots/UAT-16_5210400999_after_reload.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="55" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t>UAT-17</t>
+        </is>
+      </c>
+      <c r="C18" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D18" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E18" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-5 ทุกข้อ · กล่องยืนยันเป็น window.confirm ของเบราว์เซอร์ ภาษาไทย อ่านเข้าใจ</t>
+        </is>
+      </c>
+      <c r="F18" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-17_after_delete.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="55" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t>UAT-18</t>
+        </is>
+      </c>
+      <c r="C19" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D19" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E19" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1, 3, 4, 5 · ข้อ 2 (ลากเส้นแบ่งหัวคอลัมน์เพื่อขยายความกว้าง) automation ไม่ได้ทำ — ให้คนลาก 1 ครั้งแล้วดูว่าความกว้างเปลี่ยน · ข้อความ Remark ทดสอบยังค้างอยู่ในแถว 6211100110 (จะถูกล้างพร้อมข้อมูลรอบนี้)</t>
+        </is>
+      </c>
+      <c r="F19" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-18_fullscreen.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t>UAT-19</t>
+        </is>
+      </c>
+      <c r="C20" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D20" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only</t>
+        </is>
+      </c>
+      <c r="E20" s="55" t="inlineStr">
+        <is>
+          <t>ข้อ 1-3 ตรง Expected (ระบบป้องกันตั้งแต่ปิดปุ่ม ไม่ต้องรอกดบันทึกแล้วปฏิเสธ — เข้มกว่าที่เคสคาด) · ข้อ 4 (ข้อความอ่านเข้าใจไหม) เป็นความเห็นของคน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass</t>
+        </is>
+      </c>
+      <c r="F20" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-19_year2025.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>UAT-20</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D21" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E21" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-7 · ข้อ 6 ส่วน 'ข้อความภาษาไทยตรงทุกตัวอักษร' automation อ่านค่า dropdown/รายละเอียดหลังเปิดกลับมาไม่สำเร็จ (selector ของ dialog ไม่ตรง) แต่ยอดต่อแถวตรงทั้ง 3 แถว — ให้คนเช็คตัวอักษรตอน UAT-23 ซึ่งเปิดฟอร์มนี้อีกครั้ง · แถว 6211900030 (38,000) คงไว้เป็นฐานให้ UAT-23</t>
+        </is>
+      </c>
+      <c r="F21" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-20_subform_open.png, shots/UAT-20_form_3rows.png, shots/UAT-20_grid_after_save.png, shots/UAT-20_reopened.png, shots/UAT-20_6211900031_options.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="55" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t>UAT-21</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D22" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E22" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-6 ทุกข้อ · แถว 6210700020 (101,000) คงไว้ในระบบเป็นข้อมูลรอบทดสอบ</t>
+        </is>
+      </c>
+      <c r="F22" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-21_form_2rows.png, shots/UAT-21_after_delete_row2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="55" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t>UAT-22</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D23" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E23" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-7 ทุกข้อ · คำถามค้างจาก SIT (เว้นกิจกรรมแล้วบันทึกได้ไหม) ปิดได้: บันทึกไม่ได้ ระบบระบุช่องที่ขาด · ระบบแจ้งทีละช่อง (ช่องแรกที่ขาด) ตามการออกแบบ</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-22_row2_other_plate.png, shots/UAT-22_missing_plate_msg.png, shots/UAT-22_reopened_row2_other.png, shots/UAT-22_6211200050_form.png, shots/UAT-22_missing_activity_msg.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="55" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t>UAT-23</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D24" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E24" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-6 ทุกข้อ · ข้อร้องเรียน SIT ข้อ 2 ไม่เกิดซ้ำ: กรอกไม่ครบบันทึกไม่ได้ทั้ง Entertainment และ Lease &amp; Rental · ระบบแจ้งช่องที่ขาดทีละช่อง ใต้ตาราง ตามการออกแบบ</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-23_entertainment_missing_type.png, shots/UAT-23_lease_missing_type.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="55" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t>UAT-24</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D25" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E25" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-8 ทุกข้อ · ข้อ 4 tooltip ช่องเบี้ยเลี้ยงที่เห็นจริง = 'คำนวณโดยเซิร์ฟเวอร์ — แก้ไขไม่ได้' (บันทึกผลตามที่เคสสั่ง ไม่ตัดสิน) · ข้อสังเกต: การจัดกลุ่มประเทศมาจาก master ที่ admin ดูแล — Singapore/South Korea/Taiwan อยู่ท้ายรายการ (กลุ่มต่างประเทศอื่น) ขณะที่ Malaysia/Indonesia อยู่กลุ่มอาเซียน ให้ admin ยืนยันว่าตั้งใจ · ยอดเบี้ยเลี้ยง 13,200.00 = 5 วัน × 80 USD × 33 ตรงกับตัวอย่างในเคส UAT-25</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-24_trip_manager_open.png, shots/UAT-24_no_traveler_msg.png, shots/UAT-24_destination_list.png, shots/UAT-24_tableB_May.png, shots/UAT-24_after_save.png, shots/UAT-24_grid_after_trip.png, shots/UAT-24_long_note.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="55" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>UAT-25</t>
+        </is>
+      </c>
+      <c r="C26" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D26" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E26" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-5 · อัตราอ่านจาก dbo.per_diem_rate (Supervisor 2: domestic 250 / asian 70 USD / other 80 USD), dbo.country_group (Singapore=other, Thailand=domestic), dbo.master_currency_rate (2027 = 33.0000) ณ 2026-09-08 06:31 · ข้อสังเกตให้ admin ยืนยัน: Singapore ถูกจัดกลุ่ม 'other' ไม่ใช่ 'asian'</t>
+        </is>
+      </c>
+      <c r="F26" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-25_two_trips.png, shots/UAT-25_grid_perdiem.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="55" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t>UAT-26</t>
+        </is>
+      </c>
+      <c r="C27" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D27" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E27" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-6 ทุกข้อ · การกระจายรายเดือนไม่มีเศษสตางค์ในกรณีนี้ (1,000/2 และ 2,000/2 ลงตัว) จึงไม่ได้ทดสอบกรณีเดือนสุดท้ายรับเศษ</t>
+        </is>
+      </c>
+      <c r="F27" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-26_two_months.png, shots/UAT-26_grid_after_8days.png, shots/UAT-26_after_trip_delete.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="55" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>UAT-27</t>
+        </is>
+      </c>
+      <c r="C28" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D28" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E28" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อ · ข้อสังเกต: ขนาด .xlsx ที่แสดง (13.1 KB) ใหญ่กว่าไฟล์ต้นฉบับ (4,835 B) ประมาณ 2.7 เท่า — น่าจะเป็น SharePoint ประมวลผล/บันทึกไฟล์ Excel ใหม่ ไม่ใช่แอป (PDF ตรงเป๊ะ 303 B) ให้ทีมยืนยัน · ไฟล์ทดสอบ 2 ไฟล์จะถูกลบใน UAT-30</t>
+        </is>
+      </c>
+      <c r="F28" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-27_attachments_open.png, shots/UAT-27_after_uploads.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="55" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t>UAT-28</t>
+        </is>
+      </c>
+      <c r="C29" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D29" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E29" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อ ข้อความตรงกับ Expected ทุกตัวอักษร (ขนาดจริงในวงเล็บ = 11 MB ใกล้เคียงไฟล์ 11.0 MB)</t>
+        </is>
+      </c>
+      <c r="F29" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-28_docx_rejected.png, shots/UAT-28_too_big_rejected.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>UAT-29</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D30" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only</t>
+        </is>
+      </c>
+      <c r="E30" s="55" t="inlineStr">
+        <is>
+          <t>ต้องให้คนกดในเบราว์เซอร์จริง: ดูว่าเปิดแท็บใหม่หรือไฟล์ลง Downloads, เปิดไฟล์ได้ครบ, ชื่อไทยไม่เพี้ยน · ส่วนที่ automation ยืนยันได้ (หน้าเดิมไม่หาย ไม่มี error) ผ่าน · หมายเหตุ: ระหว่างทดสอบ UAT-27 เกิดการกดปุ่มดาวน์โหลดโดยไม่ตั้งใจ 1 ครั้ง (selector 'ปิด' ตรงกับ 'เปิด/ดาวน์โหลด') ไม่มีผลต่อข้อมูล</t>
+        </is>
+      </c>
+      <c r="F30" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-27_after_uploads.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="55" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>UAT-30</t>
+        </is>
+      </c>
+      <c r="C31" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D31" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E31" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อที่ทดสอบได้ · ข้อ 'ลบจนโฟลเดอร์ว่างต้องขึ้น ยังไม่มีไฟล์ในโฟลเดอร์นี้' ไม่ได้ทดสอบ เพราะโฟลเดอร์มีไฟล์ PNG ของผู้ใช้จริงอยู่ก่อนซึ่งห้ามลบ · ไฟล์ทดสอบ PDF ถูกคงไว้ให้ UAT-29 ดาวน์โหลดก่อน แล้วจึงลบ</t>
+        </is>
+      </c>
+      <c r="F31" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-30_after_delete_xlsx.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="55" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t>UAT-31</t>
+        </is>
+      </c>
+      <c r="C32" s="55" t="inlineStr">
+        <is>
+          <t>Arthid(jakkarit) — สวมสิทธิ์ arthids@chememan.com ผ่าน /sit/impersonate</t>
+        </is>
+      </c>
+      <c r="D32" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E32" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อ · การลบจนโฟลเดอร์ว่างแล้วขึ้นข้อความว่าง (ข้อค้างจาก UAT-30) ยืนยันได้ที่นี่ · ป้าย '+2 ฝ่าย' ของ Arthid ยืนยันกติกาย่อชื่อ &gt;3 ฝ่ายของ UAT-01 ข้อ 7 ด้วย · โฟลเดอร์ทั้ง 2 ฝ่ายกลับสภาพเดิม (D&amp;A เหลือ PNG ของผู้ใช้จริง 1 ไฟล์, SD ว่าง)</t>
+        </is>
+      </c>
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-31_arthid_attachments.png, shots/UAT-31_arthid_solution_delivery_attachments.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="55" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t>UAT-45</t>
+        </is>
+      </c>
+      <c r="C33" s="55" t="inlineStr">
+        <is>
+          <t>Nipaporn/Waraporn (impersonated)</t>
+        </is>
+      </c>
+      <c r="D33" s="55" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E33" s="55" t="inlineStr">
+        <is>
+          <t>ให้คนทำ (~2 นาที): สวมสิทธิ์ nipapornt → เปิด toggle → ฝ่ายที่เลือกถูกรีเซ็ตและเห็นฝ่ายทั้งบริษัท → เช็คแถบ admin-zone และ tooltip → ปิด toggle · ห้ามกด Submit ขณะเปิดโหมด Admin</t>
+        </is>
+      </c>
+      <c r="F33" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-15_nipaporn_landing.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="55" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t>UAT-53</t>
+        </is>
+      </c>
+      <c r="C34" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D34" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E34" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-5 ทุกข้อ · บั๊ก 'เงินหายเงียบ' ไม่เกิดซ้ำ · เบี่ยงเบนจาก Test Data: ใช้ CC 10IT013000 แทน 10IT011300 เพราะทริปทั้งหมดอยู่ที่ 10IT013000 และเคสบังคับว่าต้องเป็น CC เดียวกับทริป (10IT011300 ไม่มีทริป) · ทริปที่เหลือ: existing-52 (พ.ค.) และ existing-53 (เม.ย.)</t>
+        </is>
+      </c>
+      <c r="F34" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-53_after_trip_delete.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="55" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t>UAT-54</t>
+        </is>
+      </c>
+      <c r="C35" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated) + admin แก้ master</t>
+        </is>
+      </c>
+      <c r="D35" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only</t>
+        </is>
+      </c>
+      <c r="E35" s="55" t="inlineStr">
+        <is>
+          <t>ทางเลือกตาม note ของเคส: ข้ามขั้นตอน 2-6 ทำเฉพาะขั้นตอนที่ 7 · ต้องให้คนอธิบายพฤติกรรม (ฟอร์มย่อยคำนวณใหม่ทันที แต่ตารางหลักคงยอดเดิมจนกดบันทึกซ้ำ — ตัดสินแล้ว 2026-08-21 ว่าไม่แก้) แล้วให้ผู้ใช้เขียนใน Remarks ว่ารับทราบหรือไม่ · ถ้าทีมตัดสินใจทดสอบจริง admin ต้องแก้ค่า 33.0000 แล้วคืนค่าทันที</t>
+        </is>
+      </c>
+      <c r="F35" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-25_grid_perdiem.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="55" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>UAT-32</t>
+        </is>
+      </c>
+      <c r="C36" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D36" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E36" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-4 · ข้อ 5 (อีเมลถึง Laddawan) ตรวจใน UAT-46 — อีเมลจริงถูกส่งจริง (ไม่ได้ redirect) ตามที่ตัดสินไว้ · FY 2027 ในกล่อง vs Year 2026 บนจอ ตามการออกแบบ</t>
+        </is>
+      </c>
+      <c r="F36" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-32_before_submit.png, shots/UAT-32_after_submit.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="55" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t>UAT-03</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="inlineStr">
+        <is>
+          <t>Laddawan (impersonated)</t>
+        </is>
+      </c>
+      <c r="D37" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E37" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-5 · ข้อสังเกต: ตัวเลือกฝ่ายของ Laddawan มี Solution Delivery 1 CC ด้วย แม้แถบผู้ใช้จะบอก ฝ่าย 1 — น่าจะมาจากสิทธิ์ 'เห็น' ผ่านการเป็นผู้อนุมัติ ให้คนยืนยันว่าตั้งใจ</t>
+        </is>
+      </c>
+      <c r="F37" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-03_laddawan_picker.png, shots/UAT-03_33_laddawan_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="55" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t>UAT-33</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip → Laddawan (impersonated)</t>
+        </is>
+      </c>
+      <c r="D38" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E38" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-3 ตัวเลขครบ 3 ชุด ตรงกันทุกบาท · หมายเหตุตาม note ของเคส: รอบนี้ตัวเลขถูกอ่านโดย automation จากหน้าจอจริงทั้ง 3 มุมมอง + ยืนยันกับ DB — รอบ UAT จริงยังต้องให้คนจดซ้ำตามที่เคสกำหนด</t>
+        </is>
+      </c>
+      <c r="F38" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-32_before_submit.png, shots/UAT-03_33_laddawan_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="55" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t>UAT-34</t>
+        </is>
+      </c>
+      <c r="C39" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D39" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E39" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ทุกข้อเมื่อโหลดหน้าใหม่ · ข้อสังเกตสำคัญ (defect candidate ระดับ UX): ทันทีหลังกด Submit โดยไม่ refresh หน้าเดิมยังแสดงช่องกรอกเปิดอยู่ พิมพ์ 777 ลง พ.ค. ของ 6211100110 ได้ หน้าจอแสดง 800 และรวมปีขยับเป็น 136,300 โดยไม่มีข้อความแจ้ง — แต่เซิร์ฟเวอร์ปฏิเสธ (DB ยังเป็น 0 / 135,500 และ refresh แล้วกลับเป็นค่าเดิม) จึงเป็นเรื่อง 'จอไม่ล็อกทันทีและไม่แจ้งว่าบันทึกไม่ผ่าน' ให้ทีมพัฒนาพิจารณา</t>
+        </is>
+      </c>
+      <c r="F39" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-34_after_reload_locked.png, shots/UAT-34_locked_subform.png, shots/UAT-34_add_refused.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="55" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t>UAT-35</t>
+        </is>
+      </c>
+      <c r="C40" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D40" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E40" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-3</t>
+        </is>
+      </c>
+      <c r="F40" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-32_after_submit.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="55" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t>UAT-36</t>
+        </is>
+      </c>
+      <c r="C41" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D41" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E41" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ที่ตรวจได้ทุกข้อ · ข้อ 9 (Laddawan ดูตัวเลือกฝ่ายอีกเครื่อง) ไม่บังคับ — จะเห็นตอน UAT-43 · เบี่ยงเบน: ไม่ได้ 'สร้างแถวใหม่' เพราะแถวของ GL ทั้งสองมีอยู่แล้วจากชั้น SAP (ฝ่ายไม่ได้ว่างเปล่าอย่างที่ preconditions เขียน — มี 0 แถวใน DB แต่จอแสดงแถว SAP) ควรแก้ข้อความเคส · Suchanya ถูกล็อกจากฝ่ายตัวเองตั้งแต่ตอนนี้จนถึง UAT-43</t>
+        </is>
+      </c>
+      <c r="F41" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-36_pornthip_picker.png, shots/UAT-36_SD_filled.png, shots/UAT-36_SD_submitted.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="55" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>UAT-37</t>
+        </is>
+      </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>Laddawan (impersonated)</t>
+        </is>
+      </c>
+      <c r="D42" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E42" s="55" t="inlineStr">
+        <is>
+          <t>ผ่าน Expected ข้อ 1-4 (สังเกตในสถานะ PENDING_APPROVER1 เดียวกับ UAT-03) · UAT-51 ข้อ 11 (สีปุ่มอ่านชัดไหม) เป็นการตัดสินด้วยตาคน — มีภาพหน้าจอให้แล้ว</t>
+        </is>
+      </c>
+      <c r="F42" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-03_laddawan_picker.png, shots/UAT-03_33_laddawan_DA.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="55" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="55" t="inlineStr">
+        <is>
+          <t>UAT-42</t>
+        </is>
+      </c>
+      <c r="C43" s="55" t="inlineStr">
+        <is>
+          <t>Nipaporn (impersonated, แทน Waraporn ที่เคสระบุ) → Laddawan</t>
+        </is>
+      </c>
+      <c r="D43" s="55" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="E43" s="55" t="inlineStr">
+        <is>
+          <t>Expected ข้อ 1 ผ่าน · ข้อ 2-4 ให้คนทำ (~2 นาที: สวมสิทธิ์ warapornt/nipapornt → เปิดโหมด Admin → เลือก Data &amp; Analytic → อ่านปุ่ม: ต้องมีแค่ Approve ไม่มี Reject, ห้ามกด) · ข้อ 5 จะทำต่อในรอบ AI เมื่อ D&amp;A ถึงขั้นที่ 2 · ข้อ 5 ผ่าน (หลักฐาน shots/UAT-40-step1-approved-by-laddawan.png)</t>
+        </is>
+      </c>
+      <c r="F43" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-42_nipaporn_picker.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="55" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="55" t="inlineStr">
+        <is>
+          <t>UAT-43</t>
+        </is>
+      </c>
+      <c r="C44" s="55" t="inlineStr">
+        <is>
+          <t>Laddawan → Nipaporn → Suchanya(jakkarit) (impersonated)</t>
+        </is>
+      </c>
+      <c r="D44" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E44" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อที่ตรวจจากหน้าจอ · ข้อ 8 และ 12 (กล่องจดหมายของ Nipaporn / Pornthip / อาทิตย์) ต้องให้คนเปิดอีเมลดู — คาดจากโค้ดว่าอาทิตย์ไม่ได้รับเลย เพราะผู้ส่งคือ Pornthip · ข้อสังเกต: ในมุมมองของ Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบายเรื่อง admin submit ยาว 1 บรรทัดปนอยู่ด้วย อ่านแล้วอาจสับสนสำหรับผู้อนุมัติ · SD จบที่สถานะ Rejected ตามที่ตั้งใจ (ไม่ใช่ Draft) ยอด 30,000 ค้างอยู่ในฝ่ายจริงของ Suchanya</t>
+        </is>
+      </c>
+      <c r="F44" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-43_laddawan_picker_two_pending.png, shots/UAT-43_laddawan_SD_step1.png, shots/UAT-43_SD_after_step1_approve.png, shots/UAT-43_nipaporn_picker.png, shots/UAT-43_reject_panel.png, shots/UAT-43_SD_rejected.png, shots/UAT-43_suchanya_SD_editable.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="55" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="55" t="inlineStr">
+        <is>
+          <t>UAT-38</t>
+        </is>
+      </c>
+      <c r="C45" s="55" t="inlineStr">
+        <is>
+          <t>Laddawan (impersonated)</t>
+        </is>
+      </c>
+      <c r="D45" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E45" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อที่ตรวจจากหน้าจอ · อีเมลตีกลับถึง Pornthip (cc Laddawan) ต้องให้คนเปิดกล่องจดหมายดู</t>
+        </is>
+      </c>
+      <c r="F45" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-38-rejected-by-laddawan.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="55" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t>UAT-39</t>
+        </is>
+      </c>
+      <c r="C46" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D46" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E46" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านทุกข้อ · ยอดก่อนแก้ 5,000 / หลังแก้ 4,000 · อีเมล 'รอการอนุมัติ' ถึง Laddawan ฉบับที่ 2 ของฝ่ายนี้ (03:01) ยืนยันจากกล่องจดหมายจริงโดย jakkaritw — ถูกต้องตามกติกาส่งใหม่หลังตีกลับ</t>
+        </is>
+      </c>
+      <c r="F46" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-39-resubmitted.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="55" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="55" t="inlineStr">
+        <is>
+          <t>UAT-52</t>
+        </is>
+      </c>
+      <c r="C47" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D47" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only — ข้อ 1, 3, 4 ผ่าน; ข้อ 2 ให้คนตัดสิน (ระบบกันค่าติดลบแบบเงียบ ไม่มีข้อความ)</t>
+        </is>
+      </c>
+      <c r="E47" s="55" t="inlineStr">
+        <is>
+          <t>ข้อ 1, 3, 4, 5 ผ่าน · ข้อ 2 ไม่ตรง Expected ตรงตัว: ระบบ 'กัน' ค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) แทนที่จะปฏิเสธพร้อมข้อความ — ผลข้างเคียงคือถ้าผู้ใช้พิมพ์ผิดเป็น -3 จะได้ทริป 3 วันโดยไม่รู้ตัว ขอให้หัวหน้าทีมทดสอบตัดสินว่ารับได้หรือเปิดเป็น defect (ข้อเสนอ: แจ้งเตือนสั้น ๆ ว่า 'จำนวนวันต้องเป็น 1 ขึ้นไป') · ข้อสังเกตเดิม: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อกการเรียก API ใน browser ทดสอบแทนการปิด Wi-Fi จริง — ผลจากมุมของแอปเหมือนกัน (Failed to fetch) แต่รอบคนทดสอบควรปิด Wi-Fi จริงซ้ำ 1 ครั้ง</t>
+        </is>
+      </c>
+      <c r="F47" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-52-add-txn-locked.png, shots/UAT-52-add-txn-save-locked.png, shots/UAT-52-trip-negative-days.png, shots/UAT-52-offline-save.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="55" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="55" t="inlineStr">
+        <is>
+          <t>UAT-40</t>
+        </is>
+      </c>
+      <c r="C48" s="55" t="inlineStr">
+        <is>
+          <t>Laddawan → Nipaporn → Waraporn → Pornthip (impersonated ทั้งหมด, โหมด Admin ปิด)</t>
+        </is>
+      </c>
+      <c r="D48" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E48" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ'</t>
+        </is>
+      </c>
+      <c r="F48" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-40-step1-approved-by-laddawan.png, shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40_waraporn_picker.png, shots/UAT-40-step3-approved-final.png, shots/UAT-40-pornthip-sees-approved.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="55" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="55" t="inlineStr">
+        <is>
+          <t>UAT-41</t>
+        </is>
+      </c>
+      <c r="C49" s="55" t="inlineStr">
+        <is>
+          <t>Nipaporn (impersonated, โหมด Admin ปิด) → Pornthip (impersonated)</t>
+        </is>
+      </c>
+      <c r="D49" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E49" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด</t>
+        </is>
+      </c>
+      <c r="F49" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-41_nipaporn_picker.png, shots/UAT-41-rejected-by-nipaporn-step2.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>UAT-46</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated) → Laddawan (กล่องจดหมาย — คนตรวจ)</t>
+        </is>
+      </c>
+      <c r="D50" s="55" t="inlineStr">
+        <is>
+          <t>Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="inlineStr">
+        <is>
+          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที</t>
+        </is>
+      </c>
+      <c r="F50" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-46-resubmitted.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="55" t="inlineStr">
+        <is>
+          <t>UAT-47</t>
+        </is>
+      </c>
+      <c r="C51" s="55" t="inlineStr">
+        <is>
+          <t>Laddawan → Nipaporn → Waraporn (impersonated) → กล่องจดหมาย 3 กล่อง (คนตรวจ)</t>
+        </is>
+      </c>
+      <c r="D51" s="55" t="inlineStr">
+        <is>
+          <t>Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน</t>
+        </is>
+      </c>
+      <c r="E51" s="55" t="inlineStr">
+        <is>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49</t>
+        </is>
+      </c>
+      <c r="F51" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40-step3-approved-final.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="55" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="55" t="inlineStr">
+        <is>
+          <t>UAT-49</t>
+        </is>
+      </c>
+      <c r="C52" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated) — เฉพาะข้อ 5 และ 8; ข้อ 1-4, 6, 7 และมือถือให้คนเปิดอีเมล</t>
+        </is>
+      </c>
+      <c r="D52" s="55" t="inlineStr">
+        <is>
+          <t>Partial — ข้อ 5, 8 ผ่าน; ข้อ 1-4, 6, 7 รอคนตรวจกล่องจดหมาย</t>
+        </is>
+      </c>
+      <c r="E52" s="55" t="inlineStr">
+        <is>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT)</t>
+        </is>
+      </c>
+      <c r="F52" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-49-deeplink-landing.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="55" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="55" t="inlineStr">
+        <is>
+          <t>UAT-51</t>
+        </is>
+      </c>
+      <c r="C53" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated) — ภาพหลักฐานที่ 1400×1000 เท่านั้น</t>
+        </is>
+      </c>
+      <c r="D53" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge</t>
+        </is>
+      </c>
+      <c r="E53" s="55" t="inlineStr">
+        <is>
+          <t>AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+        </is>
+      </c>
+      <c r="F53" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-51-pornthip-DA-approved-full.png, shots/UAT-51-subform-entertainment-readonly.png, shots/UAT-51-attachments-modal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="55" t="inlineStr">
+        <is>
+          <t>UAT-04</t>
+        </is>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated; บัญชีจริงที่ล็อกอิน = jakkaritw)</t>
+        </is>
+      </c>
+      <c r="D54" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E54" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า</t>
+        </is>
+      </c>
+      <c r="F54" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-04-after-logout.png, shots/UAT-04-after-back.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="55" t="inlineStr">
+        <is>
+          <t>UAT-05</t>
+        </is>
+      </c>
+      <c r="C55" s="55" t="inlineStr">
+        <is>
+          <t>— (คนทำ)</t>
+        </is>
+      </c>
+      <c r="D55" s="55" t="inlineStr">
+        <is>
+          <t>Deferred to human</t>
+        </is>
+      </c>
+      <c r="E55" s="55" t="inlineStr">
+        <is>
+          <t>ข้อควรรู้ก่อนทำ: ข้อความในกล่องเขียนว่า '14 ชั่วโมง' ตายตัว (ดู UAT-04) ถ้าเห็นคำนี้ตอนหมดเวลาที่ 1 ชั่วโมง ไม่ใช่ความผิดของผู้ทดสอบ ให้จดเป็นข้อสังเกต · หลังจบรอบต้องคืนอายุ session เป็น 14 ชั่วโมง</t>
+        </is>
+      </c>
+      <c r="F55" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-04-after-back.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="56" t="inlineStr">
+        <is>
+          <t>สรุป</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Human decides / not run</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="56" t="inlineStr">
+        <is>
+          <t>งานที่คนต้องทำต่อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
+        </is>
+      </c>
+      <c r="B65" s="55" t="inlineStr">
+        <is>
+          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UAT-05</t>
+        </is>
+      </c>
+      <c r="B66" s="55" t="inlineStr">
+        <is>
+          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
+        </is>
+      </c>
+      <c r="B67" s="55" t="inlineStr">
+        <is>
+          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
+        </is>
+      </c>
+      <c r="B68" s="55" t="inlineStr">
+        <is>
+          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>UAT-51</t>
+        </is>
+      </c>
+      <c r="B69" s="55" t="inlineStr">
+        <is>
+          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>UAT-52 ข้อ 2</t>
+        </is>
+      </c>
+      <c r="B70" s="55" t="inlineStr">
+        <is>
+          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UAT-13</t>
+        </is>
+      </c>
+      <c r="B71" s="55" t="inlineStr">
+        <is>
+          <t>AI ให้ Fail: ระบบแจ้งข้อความตรวจสอบทีละ 1 ข้อ ไม่ใช่พร้อมกัน — ทีมตัดสินว่าเป็น defect หรือ by design แล้วใส่ Severity/Defect ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -2644,7 +2644,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="204" customHeight="1">
+    <row r="15" ht="240" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
           <t>W2</t>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M15" s="20" t="inlineStr">
         <is>
-          <t>1. กรณีเว้นช่องว่าง: ระบบไม่บันทึกรายการ และแสดงข้อความ `กรุณาเลือก Cost Center` และ `กรุณาเลือก GL Code` ตรงช่องที่ขาดอย่างชัดเจน
+          <t>1. กรณีเว้นช่องว่าง: ระบบไม่บันทึกรายการ และแสดงข้อความ `กรุณาเลือก Cost Center` ก่อน (ระบบแจ้งทีละช่องตามลำดับ ช่องแรกที่ขาดขึ้นก่อน เหมือนฟอร์มย่อยทุกฟอร์ม — ยอมรับได้ตามคำตัดสิน jakkaritw 2026-09-09) เมื่อเลือก Cost Center แล้วกดบันทึกอีกครั้งจึงแสดง `กรุณาเลือก GL Code`
 2. กรณีเลือกไม่ครบ: ระบบยังไม่บันทึก และชี้ช่องที่ยังขาดอยู่
 3. กรณีเพิ่มแถวซ้ำ: ระบบไม่บันทึกรายการ และแสดงข้อความปฏิเสธที่ผู้ใช้อ่านแล้วเข้าใจว่าแถวนี้มีอยู่แล้ว — ให้จดข้อความจริงที่เห็นลงช่อง Actual Result แล้วให้ความเห็นในช่อง Remarks ว่าอ่านเข้าใจหรือไม่
 4. ตารางไม่มีแถวซ้ำเกิดขึ้นหลังการทดสอบ
@@ -2723,7 +2723,7 @@
       </c>
       <c r="O15" s="21" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="P15" s="22" t="n"/>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T15" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] Fail เฉพาะ Expected ข้อ 1: เคสคาดว่าจะเห็นข้อความ 2 ช่องพร้อมกัน แต่ระบบแจ้งทีละช่อง (ช่องแรกที่ขาดก่อน) — พฤติกรรมเดียวกับฟอร์มย่อย จึงน่าจะเป็นความตั้งใจของระบบ ให้คุณตัดสินว่ายอมรับได้ (แล้วแก้ Expected ข้อ 1) หรือถือเป็น defect · ข้อ 2, 3, 4 ผ่าน · ข้อ 3 ส่วน 'อ่านเข้าใจไหม' เป็นความเห็นของคน</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · Expected ข้อ 1 เดิมคาดว่าเห็นข้อความ 2 ช่องพร้อมกัน แต่ระบบแจ้งทีละช่อง (ช่องแรกที่ขาดก่อน) เหมือนฟอร์มย่อยทุกฟอร์ม — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 1 ให้ตรงระบบแล้ว · ข้อ 3 ส่วน 'อ่านเข้าใจไหม' เป็นความเห็นของคน</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="588" customHeight="1">
+    <row r="54" ht="600" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
           <t>W8</t>
@@ -6423,7 +6423,7 @@
       <c r="M54" s="20" t="inlineStr">
         <is>
           <t>1) ในฝ่ายที่ส่งขออนุมัติไปแล้ว ช่องยอดเป็นแบบอ่านอย่างเดียว พิมพ์แก้ไม่ได้ตั้งแต่แรก (ไม่จำเป็นต้องมีข้อความแจ้ง ถือว่าถูกต้อง) · ส่วนการกด `+ เพิ่ม Transaction` ต้องถูกปฏิเสธพร้อมข้อความภาษาไทยที่บอกว่าฝ่ายนี้ถูกล็อกเพราะส่งขออนุมัติแล้ว และบอกสิ่งที่ต้องทำต่อ
-2) (ตรวจตอนฝ่ายยังเป็น `Draft — not submitted` — **ทำทันทีหลัง UAT-26 ก่อนเริ่ม UAT-32** ตาม Test Steps ข้อ 2 แล้วกลับมาบันทึกผลที่เคสนี้) การกรอกจำนวนวันเดินทางเป็นค่าติดลบ ถูกปฏิเสธพร้อมข้อความภาษาไทยที่บอกสาเหตุและบอกว่าต้องกรอกอย่างไรจึงจะถูกต้อง · อย่าเพิ่งตัดสิน Pass/Fail เคสนี้จนกว่าจะทำข้อ 2 เสร็จ
+2) (ตรวจตอนฝ่ายยังแก้ไขได้) การกรอกจำนวนวันเดินทางเป็นค่าติดลบถูกกันตั้งแต่ช่องกรอก: พิมพ์ `-3` ช่องจะเปลี่ยนเป็น `3` ทันที (เครื่องหมายลบถูกตัดทิ้ง) โดยไม่มีข้อความแจ้ง — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ถือว่าผ่านเมื่อระบบไม่ยอมรับค่าติดลบ · ผู้ทดสอบต้องตรวจค่าในช่องอีกครั้งก่อนกด `บันทึก &amp; ลงบัญชี`
 3) ตอนไม่มีอินเทอร์เน็ต ระบบแสดงข้อความภาษาไทยที่บอกสาเหตุ (บันทึกไม่สำเร็จ / ติดต่อระบบไม่ได้) และบอกสิ่งที่ต้องทำต่อ ไม่เงียบหายไปเฉย ๆ
 4) ทุกข้อความในขั้นตอนที่ 1 ถึง 3 ไม่มี stack trace ชื่อไฟล์ .py หรือคำสั่ง SQL ปรากฏบนหน้าจอ · รายละเอียดภาษาอังกฤษที่ต่อท้ายข้อความให้บันทึกเป็นข้อสังเกต ไม่ถือเป็น Fail
 5) ข้อความในส่วนของการอนุมัติที่เป็นภาษาอังกฤษ (เช่น `Submitted — locked for editing until it is rejected`) เป็นการออกแบบไว้แบบนั้นหลังแปลหน้าจออนุมัติเป็นภาษาอังกฤษ ไม่ใช่ข้อผิดพลาด
@@ -6436,7 +6436,11 @@
           <t>ข้อ 1 (ฝ่าย Data &amp; Analytic สถานะ Pending · Step 1): โหลดหน้าใหม่แล้วช่องเดือนทั้งหมดเป็นตัวหนังสืออ่านอย่างเดียว ไม่มีช่องพิมพ์เลย (0 ช่อง) ปุ่มฟอร์มย่อยเปลี่ยนเป็น '🔒 ดูรายละเอียด' tooltip 'อ่านอย่างเดียว — แก้ไม่ได้ในสถานะนี้' ปุ่มลบแถวหายทั้งหมด · ปุ่ม '+ เพิ่ม Transaction' ยังกดได้ → ฟอร์มเลือก Cost Center / GL เปิดขึ้น เลือก 10IT013000 + 6210900060 — ค่าไปรษณีย์ กด บันทึก → ข้อความสีแดงในฟอร์ม (คำต่อคำ): 'ฝ่าย "Data &amp; Analytic" อยู่ระหว่างอนุมัติหรืออนุมัติแล้ว ไม่สามารถเพิ่มรายการใหม่ในฝ่ายนี้ได้ในสถานะนี้' แถวไม่ถูกเพิ่ม (ยังคง 10 แถว) กด ยกเลิก ปิดฟอร์มได้ · ข้อ 4 สำหรับข้อความนี้: (ก) บอกสาเหตุ = ใช่ (ข) บอกสิ่งที่ต้องทำต่อ = ไม่ชัด (ไม่บอกว่าต้องรอตีกลับหรือรอรอบถัดไป) · ไม่มี stack trace / .py / SQL · ข้อ 2 (ทำตอนฝ่ายกลับเป็น Rejected หลัง UAT-41 ทริปแก้ได้อีกครั้ง): เปิด Trip Manager ผ่านปุ่มฟอร์มย่อย GL 6210400020 เห็นทริป 52 และ 53 (วันเดินทาง 5 / 5) · พิมพ์ -3 ลงช่องวันเดินทางของทริป 52 → ช่องรับค่าเป็น 3 ทันที (เครื่องหมายลบถูกตัดทิ้ง) ไม่มีข้อความแจ้งใด ๆ · กด บันทึก &amp; ลงบัญชี → บันทึกสำเร็จเงียบ ๆ ด้วยค่า 3 วัน (AI แก้กลับเป็น 5 และบันทึกซ้ำแล้ว ยอด per diem กลับเป็น 13,200 / 13,200 รวม 26,400 และรวมทั้งหมด 415,900.00 เท่าเดิม ตรวจหลังโหลดหน้าใหม่) · ข้อ 3 (จำลองตัดเครือข่ายเฉพาะ browser ทดสอบ ไม่แตะ Wi-Fi เครื่อง): พิมพ์ 4,100 ลงช่อง ก.ค. ของ GL 6210400999 (เดิม 4,000) คลิกออก → แถบข้อความ 'เชื่อมต่อเซิร์ฟเวอร์ไม่ได้ กรุณาตรวจสอบอินเทอร์เน็ต' ค่าที่พิมพ์ยังค้างบนจอ · คืนเครือข่ายแล้วโหลดหน้าใหม่ → ค่ากลับเป็น 4,000 (ไม่ถูกบันทึกระหว่างไม่มีเน็ต) · ข้อ 4: ข้อความข้อ 3 บอกสาเหตุ = ใช่ บอกสิ่งที่ต้องทำ = ใช่ (ตรวจอินเทอร์เน็ต) · ทุกข้อความไม่มี stack trace / .py / SQL · ข้อ 5: ตลอด W1-W7 ไม่พบข้อความแจ้งข้อผิดพลาดที่อ่านไม่รู้เรื่อง</t>
         </is>
       </c>
-      <c r="O54" s="21" t="n"/>
+      <c r="O54" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P54" s="22" t="n"/>
       <c r="Q54" s="22" t="n"/>
       <c r="R54" s="23" t="inlineStr">
@@ -6449,7 +6453,7 @@
       </c>
       <c r="T54" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — ข้อ 1, 3, 4 ผ่าน; ข้อ 2 ให้คนตัดสิน (ระบบกันค่าติดลบแบบเงียบ ไม่มีข้อความ) · ข้อ 1, 3, 4, 5 ผ่าน · ข้อ 2 ไม่ตรง Expected ตรงตัว: ระบบ 'กัน' ค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) แทนที่จะปฏิเสธพร้อมข้อความ — ผลข้างเคียงคือถ้าผู้ใช้พิมพ์ผิดเป็น -3 จะได้ทริป 3 วันโดยไม่รู้ตัว ขอให้หัวหน้าทีมทดสอบตัดสินว่ารับได้หรือเปิดเป็น defect (ข้อเสนอ: แจ้งเตือนสั้น ๆ ว่า 'จำนวนวันต้องเป็น 1 ขึ้นไป') · ข้อสังเกตเดิม: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อกการเรียก API ใน browser ทดสอบแทนการปิด Wi-Fi จริง — ผลจากมุมของแอปเหมือนกัน (Failed to fetch) แต่รอบคนทดสอบควรปิด Wi-Fi จริงซ้ำ 1 ครั้ง</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ข้อ 2: ระบบกันค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) ไม่มีข้อความ — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 2 ให้ตรงระบบแล้ว (AI แก้ทริป 52 กลับเป็น 5 วันแล้ว ยอดเท่าเดิม) · ข้อสังเกตไม่ใช่ defect: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อก API ใน browser ทดสอบแทนปิด Wi-Fi จริง รอบคนควรปิด Wi-Fi ซ้ำ 1 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8684,12 +8688,12 @@
       </c>
       <c r="D14" s="55" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E14" s="55" t="inlineStr">
         <is>
-          <t>Fail เฉพาะ Expected ข้อ 1: เคสคาดว่าจะเห็นข้อความ 2 ช่องพร้อมกัน แต่ระบบแจ้งทีละช่อง (ช่องแรกที่ขาดก่อน) — พฤติกรรมเดียวกับฟอร์มย่อย จึงน่าจะเป็นความตั้งใจของระบบ ให้คุณตัดสินว่ายอมรับได้ (แล้วแก้ Expected ข้อ 1) หรือถือเป็น defect · ข้อ 2, 3, 4 ผ่าน · ข้อ 3 ส่วน 'อ่านเข้าใจไหม' เป็นความเห็นของคน</t>
+          <t>ผ่านทุกข้อ · Expected ข้อ 1 เดิมคาดว่าเห็นข้อความ 2 ช่องพร้อมกัน แต่ระบบแจ้งทีละช่อง (ช่องแรกที่ขาดก่อน) เหมือนฟอร์มย่อยทุกฟอร์ม — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 1 ให้ตรงระบบแล้ว · ข้อ 3 ส่วน 'อ่านเข้าใจไหม' เป็นความเห็นของคน</t>
         </is>
       </c>
       <c r="F14" s="55" t="inlineStr">
@@ -9674,12 +9678,12 @@
       </c>
       <c r="D47" s="55" t="inlineStr">
         <is>
-          <t>Evidence only — ข้อ 1, 3, 4 ผ่าน; ข้อ 2 ให้คนตัดสิน (ระบบกันค่าติดลบแบบเงียบ ไม่มีข้อความ)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E47" s="55" t="inlineStr">
         <is>
-          <t>ข้อ 1, 3, 4, 5 ผ่าน · ข้อ 2 ไม่ตรง Expected ตรงตัว: ระบบ 'กัน' ค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) แทนที่จะปฏิเสธพร้อมข้อความ — ผลข้างเคียงคือถ้าผู้ใช้พิมพ์ผิดเป็น -3 จะได้ทริป 3 วันโดยไม่รู้ตัว ขอให้หัวหน้าทีมทดสอบตัดสินว่ารับได้หรือเปิดเป็น defect (ข้อเสนอ: แจ้งเตือนสั้น ๆ ว่า 'จำนวนวันต้องเป็น 1 ขึ้นไป') · ข้อสังเกตเดิม: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อกการเรียก API ใน browser ทดสอบแทนการปิด Wi-Fi จริง — ผลจากมุมของแอปเหมือนกัน (Failed to fetch) แต่รอบคนทดสอบควรปิด Wi-Fi จริงซ้ำ 1 ครั้ง</t>
+          <t>ผ่านทุกข้อ · ข้อ 2: ระบบกันค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) ไม่มีข้อความ — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 2 ให้ตรงระบบแล้ว (AI แก้ทริป 52 กลับเป็น 5 วันแล้ว ยอดเท่าเดิม) · ข้อสังเกตไม่ใช่ defect: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อก API ใน browser ทดสอบแทนปิด Wi-Fi จริง รอบคนควรปิด Wi-Fi ซ้ำ 1 ครั้ง</t>
         </is>
       </c>
       <c r="F47" s="55" t="inlineStr">
@@ -9942,7 +9946,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
@@ -9952,125 +9956,115 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
+    <row r="63">
+      <c r="A63" s="56" t="inlineStr">
+        <is>
+          <t>งานที่คนต้องทำต่อ</t>
+        </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="56" t="inlineStr">
-        <is>
-          <t>งานที่คนต้องทำต่อ</t>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
+        </is>
+      </c>
+      <c r="B64" s="55" t="inlineStr">
+        <is>
+          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
+          <t>UAT-05</t>
         </is>
       </c>
       <c r="B65" s="55" t="inlineStr">
         <is>
-          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
+          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UAT-05</t>
+          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
         </is>
       </c>
       <c r="B66" s="55" t="inlineStr">
         <is>
-          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
+          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
+          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
         </is>
       </c>
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
+          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
+          <t>UAT-51</t>
         </is>
       </c>
       <c r="B68" s="55" t="inlineStr">
         <is>
-          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
+          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UAT-51</t>
+          <t>UAT-52 ข้อ 2</t>
         </is>
       </c>
       <c r="B69" s="55" t="inlineStr">
         <is>
-          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
+          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UAT-52 ข้อ 2</t>
+          <t>UAT-13</t>
         </is>
       </c>
       <c r="B70" s="55" t="inlineStr">
-        <is>
-          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>UAT-13</t>
-        </is>
-      </c>
-      <c r="B71" s="55" t="inlineStr">
         <is>
           <t>AI ให้ Fail: ระบบแจ้งข้อความตรวจสอบทีละ 1 ข้อ ไม่ใช่พร้อมกัน — ทีมตัดสินว่าเป็น defect หรือ by design แล้วใส่ Severity/Defect ID</t>
         </is>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -195,7 +195,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -272,11 +272,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -430,6 +442,39 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -804,7 +849,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Budget Web Application — UAT Test Cases</t>
         </is>
@@ -812,7 +857,7 @@
       <c r="B1" s="50" t="n"/>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Chememan PCL (CMAN)  |  User Acceptance Testing (UAT)  |  Data &amp; Analytics  |  Round 1  |  FY2027</t>
         </is>
@@ -821,7 +866,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>Project Information</t>
         </is>
@@ -1004,7 +1049,7 @@
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>ข้อควรระวังก่อนเริ่มทดสอบ</t>
         </is>
@@ -1012,7 +1057,7 @@
       <c r="B21" s="50" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>ข้อ 1 — UAT รอบนี้รันบน **ระบบจริง (production)** ใช้ฐานข้อมูลจริง และส่งอีเมลจริงถึงเพื่อนร่วมงานจริง ไม่มีระบบทดลองแยกต่างหาก ทุกอย่างที่กรอก ส่ง อนุมัติ หรือลบ คือข้อมูลจริงของปีงบประมาณ 2027</t>
         </is>
@@ -1020,7 +1065,7 @@
       <c r="B22" s="50" t="n"/>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>ข้อ 2 — สถานะ `Approved` **ย้อนกลับไม่ได้ในระบบ** ต้องแก้ที่ฐานข้อมูลเท่านั้น อย่ากด Approve ขั้นที่ 3 (เคส UAT-40) จนกว่าทุกเคสที่มีเลข `ลำดับการรัน` น้อยกว่า 52 จะเสร็จครบ — UAT-40 อยู่ที่ลำดับการรันที่ 52 และเป็นเคสสุดท้ายของสายอนุมัติฝ่ายนั้น ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ</t>
         </is>
@@ -1028,7 +1073,7 @@
       <c r="B23" s="50" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>ข้อ 3 — อายุ session ระหว่าง UAT ตั้งไว้ที่ **1 ชั่วโมง** (ค่าจริงคือ 14 ชั่วโมง และจะคืนค่าเดิมหลังจบรอบ) ถ้าระบบให้ล็อกอินใหม่ระหว่างทดสอบ ถือว่าเป็นเรื่องปกติของรอบนี้</t>
         </is>
@@ -1036,7 +1081,7 @@
       <c r="B24" s="50" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>ข้อ 4 — **KNOWN ISSUE ที่ไม่ต้องแจ้งเป็น defect:** กล่อง “หมดเวลาการเข้าใช้งาน” ยังเขียนว่า 14 ชั่วโมง ทั้งที่ตั้งไว้ 1 ชั่วโมง — ตัดสินแล้วว่ายอมรับได้ (jakkaritw 2026-09-06)</t>
         </is>
@@ -1044,7 +1089,7 @@
       <c r="B25" s="50" t="n"/>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>ข้อ 5 — **เตรียมไฟล์แนบให้ฝ่าย Solution Delivery ไว้ก่อนเริ่มรอบ อย่างน้อย 1 ไฟล์** ในโฟลเดอร์ `เอกสาร ฝ่าย/Solution Delivery/2027/` (ให้ Pornthip อัปโหลดด้วยขั้นตอนเดียวกับเคส UAT-27 ซึ่งอัปโหลดให้ฝ่าย Data &amp; Analytic เท่านั้น ไม่มีเคสใดในรอบนี้อัปโหลดให้ฝ่าย Solution Delivery) — เคส UAT-31 ต้องมีไฟล์อยู่แล้วในโฟลเดอร์นี้ก่อนจึงจะทดสอบได้ ถ้าไม่เตรียมไว้ล่วงหน้า เคสนี้จะทำไม่ได้เมื่อถึงลำดับการรัน</t>
         </is>
@@ -1052,7 +1097,7 @@
       <c r="B26" s="50" t="n"/>
     </row>
     <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>ข้อ 6 — **ฝ่าย Solution Delivery จะถูกล็อกชั่วคราวระหว่างรอบ (ตั้งแต่เคส UAT-36 ถึง UAT-43):** ทันทีที่ Pornthip กด Submit ฝ่ายนี้ (เคส UAT-36) คุณ Suchanya ผู้กรอกตัวจริงของฝ่าย Solution Delivery จะแก้ไขงบของฝ่ายตัวเองไม่ได้เลยจนกว่าจะถูกตีกลับ — **ต้องแจ้ง Suchanya ล่วงหน้าก่อนเริ่มรอบ** ว่าจะมีช่วงล็อกสั้น ๆ นี้ · เคส UAT-43 จะอนุมัติฝ่ายนี้ที่ขั้นที่ 1 แล้วตีกลับคืนทันทีในเคสเดียวกัน เพื่อให้เธอกลับมาแก้ไขได้ก่อนจบรอบ ไม่ต้องรอจนครบทั้ง 54 เคส</t>
         </is>
@@ -1060,7 +1105,7 @@
       <c r="B27" s="50" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>วิธีใช้ไฟล์นี้ / How to use this workbook</t>
         </is>
@@ -1068,7 +1113,7 @@
       <c r="B29" s="50" t="n"/>
     </row>
     <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>1.  ไปที่แท็บ “2. Test Cases” แล้วทดสอบ **เรียงตามคอลัมน์ `ลำดับการรัน` (Run Order) จาก 1 ถึง 54** — **ไม่ใช่เรียงตามคอลัมน์ Wave** · คอลัมน์ Wave ยังเป็นชื่อกลุ่มของเคสและใช้กรองดูได้เหมือนเดิม แต่ลำดับที่ต้องลงมือทำจริงคือคอลัมน์ `ลำดับการรัน` เพราะบางเคสต้องทำข้ามระลอก (เช่น UAT-53 และ UAT-54 อยู่ระลอก W8 แต่ต้องทำก่อนระลอก W5 · UAT-03 อยู่ระลอก W1 แต่ต้องทำหลัง UAT-32)</t>
         </is>
@@ -1076,7 +1121,7 @@
       <c r="B30" s="50" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>2.  วิธีเรียง: คลิกลูกศรกรองบนหัวคอลัมน์ `ลำดับการรัน` แล้วเลือก “Sort Smallest to Largest” จากนั้นไล่ทำจากบนลงล่าง</t>
         </is>
@@ -1084,7 +1129,7 @@
       <c r="B31" s="50" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>3.  ⚠ **อย่ากด `Approve` ขั้นที่ 3 ในเคส UAT-40 (ลำดับการรันที่ 52) จนกว่าทุกเคสที่มีลำดับการรันน้อยกว่า 52 จะเสร็จครบ** เพราะสถานะ `Approved` ย้อนกลับไม่ได้ ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ และต้องให้ทีม IT แก้ที่ฐานข้อมูลเท่านั้น</t>
         </is>
@@ -1092,7 +1137,7 @@
       <c r="B32" s="50" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>4.  ทดสอบทีละเคสตาม “Test Steps” แล้วเทียบผลกับ “Expected Result”</t>
         </is>
@@ -1100,7 +1145,7 @@
       <c r="B33" s="50" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>5.  **อ่าน “Expected Result” ให้จบทุกข้อก่อนตัดสินผล** — หลายเคสเป็นเคสรวม (merged) คือ 1 แถว แต่มีหลายข้อที่ต้องตรวจ ถ้าข้อใดข้อหนึ่งไม่ผ่าน ให้ทั้งแถวเป็น Fail แล้วระบุในช่อง Actual Result ว่าข้อไหนไม่ผ่าน</t>
         </is>
@@ -1108,7 +1153,7 @@
       <c r="B34" s="50" t="n"/>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>6.  **ผู้ทดสอบดูแลช่องพื้นหลังสีเหลือง 7 ช่องนี้:** Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks · ช่อง `Tester` กรอกชื่อไว้ล่วงหน้าแล้วตามแผนคนจาก actor map ก่อนเริ่มรอบ (ตัวหนังสือสีม่วงเหมือนช่องเนื้อหาเคสอื่น ๆ) ถ้าคนที่ลงมือทดสอบจริงไม่ตรงกับชื่อที่กรอกไว้ ให้แก้ชื่อในช่องนี้ให้ตรงกับคนที่ทำจริง · อีก 6 ช่องที่เหลือยังว่างอยู่ ให้ผู้ทดสอบกรอกเองระหว่างทดสอบตามปกติ</t>
         </is>
@@ -1116,7 +1161,7 @@
       <c r="B35" s="50" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>7.  เลือก Status จาก dropdown: Pass / Fail / Blocked / N/A · **ช่องที่ยังว่าง = `Not Run` (ยังไม่ได้ทดสอบ) ซึ่งเป็นค่าเริ่มต้น** ไม่ต้องพิมพ์คำว่า Not Run เอง — แท็บ “3. Summary” นับช่องว่างเป็น Not Run ให้อัตโนมัติ</t>
         </is>
@@ -1124,7 +1169,7 @@
       <c r="B36" s="50" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>8.  ถ้า Fail ให้ระบุ Severity บันทึกรายละเอียดใน “Actual Result” แล้ว **เปิดแถวใหม่ในแท็บ “4. Defects”** จากนั้นนำเลข Defect ID (D-001, D-002, …) มาใส่ในคอลัมน์ Defect ID ของแถวนี้ · ช่อง Severity ของแถว defect ใช้ **ชุดค่าเดียวกัน** (Critical / High / Medium / Low) ยกค่าจากแถวเคสไปใส่ได้ตรง ๆ ไม่ต้องแปลงเป็นคำอื่น</t>
         </is>
@@ -1132,7 +1177,7 @@
       <c r="B37" s="50" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>9.  แท็บ “3. Summary” สรุปผลอัตโนมัติ (จำนวน / อัตราผ่าน / แยกตาม Module, Wave และฝ่าย) ไม่ต้องกรอกเอง</t>
         </is>
@@ -1140,7 +1185,7 @@
       <c r="B38" s="50" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>10. **ข้อยกเว้นเดียวของกติกา “กรอกเฉพาะช่องสีเหลือง” คือคอลัมน์ `PIC`** ซึ่งเป็นช่องสีขาว และคนที่กรอกไม่ใช่ผู้ทดสอบ แต่เป็น **Test Lead** ที่กรอกชื่อผู้รับผิดชอบรายเคสไว้ **ก่อน** เริ่มรอบทดสอบ (ใช้เมื่อ Test Lead ต้องการมอบหมายผู้รับผิดชอบเพิ่มเติม นอกเหนือจากชื่อที่กรอกไว้แล้วในช่อง `Tester`) · ระหว่างทดสอบ ผู้ทดสอบไม่ต้องแตะคอลัมน์นี้</t>
         </is>
@@ -1148,7 +1193,7 @@
       <c r="B39" s="50" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>11. ตัวหนังสือ **สีม่วง** คือข้อความที่ AI ร่างไว้ให้ ยังไม่ผ่านการตรวจจากผู้ทดสอบ ถ้าพบว่าไม่ตรงกับระบบจริง แก้ได้เลยแล้วบันทึกไว้ในช่อง Remarks · **ยกเว้นคอลัมน์ `Wave` และ `ลำดับการรัน` ซึ่งพิมพ์ด้วยตัวสีดำ** เพราะเป็นค่าที่โปรแกรมคำนวณมาให้ ไม่ใช่ข้อความที่ AI ร่าง — ห้ามแก้ ถ้าเห็นว่าลำดับผิดให้แจ้ง Test Lead แทน</t>
         </is>
@@ -1156,7 +1201,7 @@
       <c r="B40" s="50" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>12. อ่านเอกสารประกอบ `UAT_Test_Script.md` (ภาษาไทย) ก่อนเริ่ม — อธิบายลำดับการรัน บทบาทของแต่ละคน และสิ่งที่ตัดออกจากรอบนี้โดยตั้งใจ</t>
         </is>
@@ -1164,7 +1209,7 @@
       <c r="B41" s="50" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="59" t="inlineStr">
         <is>
           <t>ตัวอย่างการกรอก 1 แถว (worked example)</t>
         </is>
@@ -1172,7 +1217,7 @@
       <c r="B43" s="50" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>เคสตัวอย่าง UAT-09 (ระลอก W2) — “กรอกยอดแล้วคลิกออกจากช่อง = บันทึกอัตโนมัติ · refresh หน้าแล้วค่ายังอยู่”</t>
         </is>
@@ -1180,7 +1225,7 @@
       <c r="B44" s="50" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>ถ้าผ่าน → Actual Result = “กรอก 100 ที่เดือน ม.ค. คลิกออกจากช่อง แล้ว refresh หน้า ค่ายังเป็น 100” · Status = `Pass` · Severity = `-` · Defect ID = (เว้นว่าง) · Tester = `Pornthip` · Test Date = วันที่ทดสอบ · Remarks = (เว้นว่าง)</t>
         </is>
@@ -1188,7 +1233,7 @@
       <c r="B45" s="50" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>ถ้าไม่ผ่าน → Actual Result = “refresh แล้วค่าหาย กลับเป็นช่องว่าง” · Status = `Fail` · Severity = `High` · Defect ID = `D-001` แล้วไปเปิดแถว D-001 ในแท็บ “4. Defects” กรอกหัวข้อ ผู้แจ้ง วันที่ และสถานะ `Open`</t>
         </is>
@@ -1196,7 +1241,7 @@
       <c r="B46" s="50" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>ถ้าทดสอบไม่ได้เพราะติดเคสอื่นหรือข้อมูลยังไม่พร้อม → Status = `Blocked` และเขียนเหตุผลใน Remarks (อย่าปล่อยเป็น `Not Run` ถ้าพยายามทดสอบแล้ว)</t>
         </is>
@@ -1204,7 +1249,7 @@
       <c r="B47" s="50" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="59" t="inlineStr">
         <is>
           <t>Legend / คำอธิบายสี &amp; สถานะ</t>
         </is>
@@ -1276,7 +1321,7 @@
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="A58" s="61" t="inlineStr">
         <is>
           <t>Severity: Critical = ระบบใช้งานไม่ได้ / ข้อมูลผิดพลาดร้ายแรง  |  High = ฟังก์ชันหลักเสีย  |  Medium = มีทางเลี่ยง  |  Low = ปัญหาเล็กน้อย / UI  ·  ชุดค่านี้ใช้เหมือนกันทั้งแท็บ “2. Test Cases” และแท็บ “4. Defects” จึงยกค่าจากแถวเคสไปใส่แถว defect ได้ตรง ๆ ไม่ต้องแปลง (ค่า `-` มีเฉพาะแท็บ “2. Test Cases” ใช้เมื่อเคสนั้นไม่ Fail)</t>
         </is>
@@ -1352,7 +1397,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Budget Web App — UAT Test Cases (Round 1 · FY2027 · production)</t>
         </is>
@@ -6453,7 +6498,7 @@
       </c>
       <c r="T54" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ข้อ 2: ระบบกันค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) ไม่มีข้อความ — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 2 ให้ตรงระบบแล้ว (AI แก้ทริป 52 กลับเป็น 5 วันแล้ว ยอดเท่าเดิม) · ข้อสังเกตไม่ใช่ defect: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อก API ใน browser ทดสอบแทนปิด Wi-Fi จริง รอบคนควรปิด Wi-Fi ซ้ำ 1 ครั้ง</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ข้อ 2: ระบบกันค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) ไม่มีข้อความ — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 2 ให้ตรงระบบแล้ว (AI แก้ทริป 52 กลับเป็น 5 วันแล้ว ยอดเท่าเดิม) · ปุ่ม + เพิ่ม Transaction ยังกดได้ในฝ่ายที่ล็อก (ปฏิเสธตอนบันทึกด้วยข้อความไทย) — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect · ข้อ 3 ใช้การบล็อก API ใน browser ทดสอบแทนปิด Wi-Fi จริง รอบคนควรปิด Wi-Fi ซ้ำ 1 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6742,7 @@
   </cols>
   <sheetData>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="63" t="inlineStr">
         <is>
           <t>UAT Test Execution — Summary  ·  Round 1  ·  FY2027</t>
         </is>
@@ -6718,7 +6763,7 @@
       <c r="P2" s="50" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>สรุปผลอัตโนมัติจากแท็บ “2. Test Cases” (ไม่ต้องกรอกเอง) · ทุกสูตรนับช่วงแถวจริง 3–56</t>
         </is>
@@ -6844,7 +6889,7 @@
       <c r="E12" s="52" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Module</t>
         </is>
@@ -6852,7 +6897,7 @@
       <c r="C14" s="50" t="n"/>
       <c r="D14" s="50" t="n"/>
       <c r="E14" s="50" t="n"/>
-      <c r="G14" s="42" t="inlineStr">
+      <c r="G14" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Wave</t>
         </is>
@@ -6861,7 +6906,7 @@
       <c r="I14" s="50" t="n"/>
       <c r="J14" s="50" t="n"/>
       <c r="K14" s="50" t="n"/>
-      <c r="M14" s="42" t="inlineStr">
+      <c r="M14" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Department</t>
         </is>
@@ -7388,7 +7433,7 @@
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>หมายเหตุ: ตัวเลขอัปเดตอัตโนมัติเมื่อกรอกคอลัมน์ Status ในแท็บ “2. Test Cases” · ช่วงข้อมูลจริง = แถวที่ 3 ถึง 56 · ไฟล์นี้ไม่มีแถวตัวอย่าง (ไม่มี TC-EX) · ช่อง Total ของทั้ง 3 ตารางต้องเท่ากับ Total test cases ด้านบน · แถว Not Run คำนวณจาก “Total ลบด้วย Pass + Fail + Blocked + N/A” จึงนับช่อง Status ที่ยังว่างให้เป็น Not Run โดยอัตโนมัติ (ไม่ต้องพิมพ์คำว่า Not Run เอง) และทำให้ห้าแถวบนรวมกันได้เท่ากับ Total เสมอ</t>
         </is>
@@ -7454,7 +7499,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Budget Web App — UAT Defect Log  ·  เปิดแถวใหม่ทุกครั้งที่มีเคส Status = Fail แล้วนำเลข Defect ID ไปใส่ในคอลัมน์ Defect ID ของแท็บ “2. Test Cases”</t>
         </is>
@@ -8300,7 +8345,7 @@
       <c r="M42" s="21" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="49" t="inlineStr">
+      <c r="A44" s="67" t="inlineStr">
         <is>
           <t>Severity ของ defect ใช้ **ชุดค่าเดียวกับคอลัมน์ Severity ในแท็บ “2. Test Cases”** ยกมาใส่ได้ตรง ๆ ไม่ต้องแปลงค่า: Critical = ระบบใช้งานไม่ได้ / ข้อมูลเงินผิดพลาดร้ายแรง · High = ฟังก์ชันหลักเสีย · Medium = เสียแต่มีทางเลี่ยง · Low = ปัญหาเล็กน้อยหรือ UI (ไม่มีค่า `-` ในแท็บนี้ เพราะแถว defect เกิดขึ้นเฉพาะตอนมีเคส Fail)  ·  Status: Open → In Progress → Fixed → Retested → Closed (หรือ Wont Fix ถ้าตัดสินว่าไม่แก้)</t>
         </is>
@@ -9683,7 +9728,7 @@
       </c>
       <c r="E47" s="55" t="inlineStr">
         <is>
-          <t>ผ่านทุกข้อ · ข้อ 2: ระบบกันค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) ไม่มีข้อความ — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 2 ให้ตรงระบบแล้ว (AI แก้ทริป 52 กลับเป็น 5 วันแล้ว ยอดเท่าเดิม) · ข้อสังเกตไม่ใช่ defect: ปุ่ม + เพิ่ม Transaction ควร disabled เมื่อฝ่ายล็อก และข้อความปฏิเสธควรบอกขั้นต่อไป · ข้อ 3 ใช้การบล็อก API ใน browser ทดสอบแทนปิด Wi-Fi จริง รอบคนควรปิด Wi-Fi ซ้ำ 1 ครั้ง</t>
+          <t>ผ่านทุกข้อ · ข้อ 2: ระบบกันค่าติดลบตั้งแต่ช่องกรอก (พิมพ์ -3 ได้ 3) ไม่มีข้อความ — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ แก้ Expected ข้อ 2 ให้ตรงระบบแล้ว (AI แก้ทริป 52 กลับเป็น 5 วันแล้ว ยอดเท่าเดิม) · ปุ่ม + เพิ่ม Transaction ยังกดได้ในฝ่ายที่ล็อก (ปฏิเสธตอนบันทึกด้วยข้อความไทย) — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect · ข้อ 3 ใช้การบล็อก API ใน browser ทดสอบแทนปิด Wi-Fi จริง รอบคนควรปิด Wi-Fi ซ้ำ 1 ครั้ง</t>
         </is>
       </c>
       <c r="F47" s="55" t="inlineStr">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -1913,7 +1913,7 @@
       </c>
       <c r="T6" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า · jakkaritw ตัดสิน 2026-09-09: ข้อความ 'หมดเวลา … 14 ชั่วโมง' ตอนกดออกจากระบบ ยอมรับได้ ไม่เปิด defect</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="E54" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า</t>
+          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า · jakkaritw ตัดสิน 2026-09-09: ข้อความ 'หมดเวลา … 14 ชั่วโมง' ตอนกดออกจากระบบ ยอมรับได้ ไม่เปิด defect</t>
         </is>
       </c>
       <c r="F54" s="55" t="inlineStr">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="T36" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่าน Expected ทุกข้อเมื่อโหลดหน้าใหม่ · ข้อสังเกตสำคัญ (defect candidate ระดับ UX): ทันทีหลังกด Submit โดยไม่ refresh หน้าเดิมยังแสดงช่องกรอกเปิดอยู่ พิมพ์ 777 ลง พ.ค. ของ 6211100110 ได้ หน้าจอแสดง 800 และรวมปีขยับเป็น 136,300 โดยไม่มีข้อความแจ้ง — แต่เซิร์ฟเวอร์ปฏิเสธ (DB ยังเป็น 0 / 135,500 และ refresh แล้วกลับเป็นค่าเดิม) จึงเป็นเรื่อง 'จอไม่ล็อกทันทีและไม่แจ้งว่าบันทึกไม่ผ่าน' ให้ทีมพัฒนาพิจารณา</t>
+          <t>[AI pre-run 09/09/2026] ผ่าน Expected ทุกข้อ · ข้อสังเกตเดิม (หน้าจอไม่ล็อกทันทีหลัง Submit และไม่แจ้งเมื่อบันทึกไม่ผ่าน) ถูกแก้แล้ว commit 6a9d323 ขึ้น prd rev 0000036 วันที่ 09/09/2026 · RETEST บน prd 14:25 (ฝ่าย Solution Delivery จาก Rejected): กด Submit → ในหน้าเดิมโดยไม่โหลดใหม่ (ตัวแปรเครื่องหมายในหน้าคงอยู่) ช่องกรอก 48 ช่องหายเป็น 0 ภายใน 0.8 วินาที ปุ่มฟอร์มย่อยเป็น '🔒 ดูรายละเอียด' ปุ่มลบหาย chip 'Pending · Step 1 (Direct manager)' ยอด 30,000 เท่าเดิม · จากนั้น Laddawan Reject SD กลับเป็น Rejected 14:26 (เหตุผล 'UAT Round 1 — retest UAT-34 เสร็จ คืนฝ่าย Solution Delivery ให้ Suchanya') เพื่อคืนสถานะให้รอบคน · ข้อความ 'บันทึกไม่สำเร็จ — ฝ่ายนี้ส่งขออนุมัติแล้ว …' ยืนยันด้วย unit test (ล็อกเร็วจนพิมพ์ไม่ทันบนเครื่องจริง)</t>
         </is>
       </c>
     </row>
@@ -9488,12 +9488,12 @@
       </c>
       <c r="E39" s="55" t="inlineStr">
         <is>
-          <t>ผ่าน Expected ทุกข้อเมื่อโหลดหน้าใหม่ · ข้อสังเกตสำคัญ (defect candidate ระดับ UX): ทันทีหลังกด Submit โดยไม่ refresh หน้าเดิมยังแสดงช่องกรอกเปิดอยู่ พิมพ์ 777 ลง พ.ค. ของ 6211100110 ได้ หน้าจอแสดง 800 และรวมปีขยับเป็น 136,300 โดยไม่มีข้อความแจ้ง — แต่เซิร์ฟเวอร์ปฏิเสธ (DB ยังเป็น 0 / 135,500 และ refresh แล้วกลับเป็นค่าเดิม) จึงเป็นเรื่อง 'จอไม่ล็อกทันทีและไม่แจ้งว่าบันทึกไม่ผ่าน' ให้ทีมพัฒนาพิจารณา</t>
+          <t>ผ่าน Expected ทุกข้อ · ข้อสังเกตเดิม (หน้าจอไม่ล็อกทันทีหลัง Submit และไม่แจ้งเมื่อบันทึกไม่ผ่าน) ถูกแก้แล้ว commit 6a9d323 ขึ้น prd rev 0000036 วันที่ 09/09/2026 · RETEST บน prd 14:25 (ฝ่าย Solution Delivery จาก Rejected): กด Submit → ในหน้าเดิมโดยไม่โหลดใหม่ (ตัวแปรเครื่องหมายในหน้าคงอยู่) ช่องกรอก 48 ช่องหายเป็น 0 ภายใน 0.8 วินาที ปุ่มฟอร์มย่อยเป็น '🔒 ดูรายละเอียด' ปุ่มลบหาย chip 'Pending · Step 1 (Direct manager)' ยอด 30,000 เท่าเดิม · จากนั้น Laddawan Reject SD กลับเป็น Rejected 14:26 (เหตุผล 'UAT Round 1 — retest UAT-34 เสร็จ คืนฝ่าย Solution Delivery ให้ Suchanya') เพื่อคืนสถานะให้รอบคน · ข้อความ 'บันทึกไม่สำเร็จ — ฝ่ายนี้ส่งขออนุมัติแล้ว …' ยืนยันด้วย unit test (ล็อกเร็วจนพิมพ์ไม่ทันบนเครื่องจริง)</t>
         </is>
       </c>
       <c r="F39" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-34_after_reload_locked.png, shots/UAT-34_locked_subform.png, shots/UAT-34_add_refused.png</t>
+          <t>shots/UAT-34_after_reload_locked.png, shots/UAT-34_locked_subform.png, shots/UAT-34_add_refused.png, shots/UAT-34-retest-locked-no-reload.png, shots/UAT-34-retest-SD-rejected-back.png</t>
         </is>
       </c>
     </row>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -4803,7 +4803,7 @@
       </c>
       <c r="N36" s="51" t="inlineStr">
         <is>
-          <t>หลัง refresh: ช่อง Pending ทุกช่องเป็นข้อความ (ไม่มี input) พิมพ์ทับไม่ได้ · ปุ่มฟอร์มย่อยทุกแถวเปลี่ยนเป็น '🔒 ดูรายละเอียด' tooltip 'อ่านอย่างเดียว — แก้ไม่ได้ในสถานะนี้' · เปิดฟอร์มย่อย Entertainment: หัวเรื่อง 'รายละเอียด Entertainment 🔒' บรรทัดรอง '… · อ่านอย่างเดียว (แก้ไม่ได้)' ช่องทั้ง 42 ช่องกรอกไม่ได้ ปุ่มมีแค่ ✕ และ ปิด (ไม่มี บันทึก / + เพิ่มรายการ / ถังขยะ) · + เพิ่ม Transaction เลือก 10IT011300 + 6210900060 กดบันทึก → ข้อความใต้ฟอร์ม 'ฝ่าย "Data &amp; Analytic" อยู่ระหว่างอนุมัติหรืออนุมัติแล้ว ไม่สามารถเพิ่มรายการใหม่ในฝ่ายนี้ได้ในสถานะนี้' ไม่มีแถวใหม่ · ปุ่ม ลบรายการนี้ หายจากทุกแถว (จาก 5 เหลือ 0)</t>
+          <t>[RETEST บน prd rev 0000036 — 09/09/2026 14:25 ฝ่าย Solution Delivery] กด Submit → ตารางล็อกในหน้าเดิมภายใน 0.8 วินาที โดยไม่ต้องโหลดใหม่: ช่องกรอก 48 → 0 ช่อง ปุ่มฟอร์มย่อยเป็น '🔒 ดูรายละเอียด' ปุ่มลบหาย chip 'Pending · Step 1 (Direct manager)' + 'Submitted — locked for editing until it is rejected' ยอด 30,000.00 เท่าเดิม · [รอบแรก 03:50 ฝ่าย Data &amp; Analytic — ก่อนแก้] หลัง refresh: ช่อง Pending ทุกช่องเป็นข้อความ (ไม่มี input) พิมพ์ทับไม่ได้ · ปุ่มฟอร์มย่อยทุกแถวเปลี่ยนเป็น '🔒 ดูรายละเอียด' tooltip 'อ่านอย่างเดียว — แก้ไม่ได้ในสถานะนี้' · เปิดฟอร์มย่อย Entertainment: หัวเรื่อง 'รายละเอียด Entertainment 🔒' บรรทัดรอง '… · อ่านอย่างเดียว (แก้ไม่ได้)' ช่องทั้ง 42 ช่องกรอกไม่ได้ ปุ่มมีแค่ ✕ และ ปิด (ไม่มี บันทึก / + เพิ่มรายการ / ถังขยะ) · + เพิ่ม Transaction เลือก 10IT011300 + 6210900060 กดบันทึก → ข้อความใต้ฟอร์ม 'ฝ่าย "Data &amp; Analytic" อยู่ระหว่างอนุมัติหรืออนุมัติแล้ว ไม่สามารถเพิ่มรายการใหม่ในฝ่ายนี้ได้ในสถานะนี้' ไม่มีแถวใหม่ · ปุ่ม ลบรายการนี้ หายจากทุกแถว (จาก 5 เหลือ 0)</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -5495,7 +5495,7 @@
       </c>
       <c r="T43" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48)</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="T48" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง · เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง · เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="T49" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน · คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน · คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="T51" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 5, 8 ผ่าน; ข้อ 1-4, 6, 7 รอคนตรวจกล่องจดหมาย · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT)</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 5, 8 ผ่าน; ข้อ 1-4, 6, 7 รอคนตรวจกล่องจดหมาย · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="E49" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด</t>
+          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48)</t>
         </is>
       </c>
       <c r="F49" s="55" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E50" s="55" t="inlineStr">
         <is>
-          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที</t>
+          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
         </is>
       </c>
       <c r="F50" s="55" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E51" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49</t>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT)</t>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -5495,7 +5495,7 @@
       </c>
       <c r="T43" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48)</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="T48" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง · เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง · เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า)</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="T49" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน · คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน · คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="T51" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 5, 8 ผ่าน; ข้อ 1-4, 6, 7 รอคนตรวจกล่องจดหมาย · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="E49" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48)</t>
+          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว</t>
         </is>
       </c>
       <c r="F49" s="55" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="E50" s="55" t="inlineStr">
         <is>
-          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
+          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า)</t>
         </is>
       </c>
       <c r="F50" s="55" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="E51" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
@@ -9873,12 +9873,12 @@
       </c>
       <c r="D52" s="55" t="inlineStr">
         <is>
-          <t>Partial — ข้อ 5, 8 ผ่าน; ข้อ 1-4, 6, 7 รอคนตรวจกล่องจดหมาย</t>
+          <t>Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ</t>
         </is>
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status</t>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -5951,7 +5951,11 @@
           <t>ก่อนกด: D&amp;A สถานะ 'Rejected' + 'Reject reason: ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ปุ่ม Submit แสดง · Pornthip กด Submit → กล่องยืนยันส่งทั้งฝ่าย → OK เวลา 03:16 (นาฬิกาเครื่องจริง) → chip 'Pending · Step 1 (Direct manager)' + 'Submitted — locked for editing until it is rejected' ปุ่ม Submit หาย · ฝ่ายกลับไปอยู่ Pending · Step 1 พร้อมให้ UAT-47/UAT-40 เดินต่อ</t>
         </is>
       </c>
-      <c r="O48" s="21" t="n"/>
+      <c r="O48" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P48" s="22" t="n"/>
       <c r="Q48" s="22" t="n"/>
       <c r="R48" s="23" t="inlineStr">
@@ -5964,7 +5968,7 @@
       </c>
       <c r="T48" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง · เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า)</t>
+          <t>[AI pre-run 09/09/2026] เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6047,11 @@
           <t>ลำดับการกดจริง (นาฬิกาเครื่อง): Laddawan Approve 03:18 → สถานะ Step 2 · Nipaporn Approve 03:18 → สถานะ Step 3 · Waraporn Approve 03:21 → Approved · ก่อนขั้นที่ 2 กด ตัวเลือกฝ่ายของ Waraporn ไม่ติดป้าย Pending ที่ D&amp;A (ตรวจใน UAT-42 ตอนสถานะ Step 1) และติดป้ายเมื่อถึง Step 3 เท่านั้น — สอดคล้องกับกติกา 'ส่งเมลเมื่อถึงคิว'</t>
         </is>
       </c>
-      <c r="O49" s="21" t="n"/>
+      <c r="O49" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P49" s="22" t="n"/>
       <c r="Q49" s="22" t="n"/>
       <c r="R49" s="23" t="inlineStr">
@@ -6056,7 +6064,7 @@
       </c>
       <c r="T49" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน · คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย</t>
+          <t>[AI pre-run 09/09/2026] คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6239,7 @@
       </c>
       <c r="T51" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
         </is>
       </c>
     </row>
@@ -9813,12 +9821,12 @@
       </c>
       <c r="D50" s="55" t="inlineStr">
         <is>
-          <t>Pass (หน้าจอ) — อีเมลให้คนยืนยันเวลาถึง</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E50" s="55" t="inlineStr">
         <is>
-          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า)</t>
+          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ</t>
         </is>
       </c>
       <c r="F50" s="55" t="inlineStr">
@@ -9843,12 +9851,12 @@
       </c>
       <c r="D51" s="55" t="inlineStr">
         <is>
-          <t>Pass (หน้าจอ/ลำดับขั้น) — อีเมล 3 ฉบับให้คนยืนยัน</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E51" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย</t>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
@@ -9878,7 +9886,7 @@
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง</t>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">
@@ -9991,7 +9999,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -10001,7 +10009,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -5495,7 +5495,7 @@
       </c>
       <c r="T43" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect</t>
         </is>
       </c>
     </row>
@@ -6132,8 +6132,16 @@
 ต้องรันก่อนเคส UAT-40 / UAT-47 เพราะสถานะ `Approved` ย้อนกลับไม่ได้ ตีกลับหลังจากนั้นไม่ได้อีก · ใช้การกด `Reject` ชุดเดียวกับ UAT-38 ไม่ต้องตีกลับซ้ำ · อีเมลส่งจริงถึงกล่องจดหมายของพรทิพย์ ให้แจ้งเจ้าตัวล่วงหน้าว่าเป็นการทดสอบ</t>
         </is>
       </c>
-      <c r="N50" s="21" t="n"/>
-      <c r="O50" s="21" t="n"/>
+      <c r="N50" s="51" t="inlineStr">
+        <is>
+          <t>เมล 'ถูกตีกลับ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' มี 2 ฉบับตามคาด: 02:58 (ตีกลับโดยลัดดาวัลย์ใน UAT-38 กด ~02:58 — ฉบับที่เคสนี้ใช้) และ 03:12 (ตีกลับโดยนิภาพรใน UAT-41 กด 03:11) แยกกันด้วยเวลาที่จดไว้ · เปิดฉบับเต็ม 03:12: ผู้ส่ง CMAN_PowerBI · To Pornthip Phermsaphiran · Cc Laddawan Kearnoi; CMAN_PowerBI · ตาราง ฝ่าย Data &amp; Analytic / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / สถานะ 'ถูกตีกลับ' / เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงกับที่พิมพ์ทุกตัวอักษร · ลิงก์ 'คลิกที่นี่เพื่อแก้ไขและส่งใหม่' · อักษรไทยครบ</t>
+        </is>
+      </c>
+      <c r="O50" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P50" s="22" t="n"/>
       <c r="Q50" s="22" t="n"/>
       <c r="R50" s="23" t="inlineStr">
@@ -6141,8 +6149,14 @@
           <t>Pornthip</t>
         </is>
       </c>
-      <c r="S50" s="24" t="n"/>
-      <c r="T50" s="21" t="n"/>
+      <c r="S50" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T50" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="408" customHeight="1">
       <c r="A51" s="18" t="inlineStr">
@@ -6307,8 +6321,16 @@
 เป็นเคสให้ผู้ใช้ตัดสิน (decision case) ต้องได้คำตอบเป็นลายลักษณ์อักษรในช่อง Remarks ก่อนปิดรอบ UAT — ถ้าปล่อยว่างไว้ถือว่าเคสยังไม่จบ · ไม่มีเคสใดใน SIT ที่เคยเทียบภาษาของหน้าจอกับภาษาของอีเมล จึงไม่มีผลเดิมให้อ้างอิง</t>
         </is>
       </c>
-      <c r="N52" s="21" t="n"/>
-      <c r="O52" s="21" t="n"/>
+      <c r="N52" s="51" t="inlineStr">
+        <is>
+          <t>หน้าจออนุมัติเป็นภาษาอังกฤษ: ปุ่ม Approve / Reject · chip 'Pending · Step 1 (Direct manager)' / 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' / 'Rejected' / 'Approved' · กล่อง 'REJECT REASON (REQUIRED)' + 'Confirm Reject' · ป้าย 'Pending' ในตัวเลือกฝ่าย · ข้อความ 'Submitted — locked for editing until it is rejected' · อีเมลทุกฉบับเป็นภาษาไทยทั้งหัวข้อและเนื้อหา: 'รอการอนุมัติ …' / 'ถูกตีกลับ …' / 'ได้รับการอนุมัติ …' สถานะ 'รอการอนุมัติจากท่าน' / 'ถูกตีกลับ' / 'อนุมัติครบทุกขั้นแล้ว' · คู่คำเดียวกัน: Pending ↔ รอการอนุมัติ, Rejected ↔ ถูกตีกลับ, Approved ↔ ได้รับการอนุมัติ</t>
+        </is>
+      </c>
+      <c r="O52" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P52" s="22" t="n"/>
       <c r="Q52" s="22" t="n"/>
       <c r="R52" s="23" t="inlineStr">
@@ -6316,8 +6338,14 @@
           <t>ไม่ระบุชื่อในเคส (ต้องมีคนเปิดทั้งจอ+อีเมลเทียบกัน — สันนิษฐาน Pornthip)</t>
         </is>
       </c>
-      <c r="S52" s="24" t="n"/>
-      <c r="T52" s="21" t="n"/>
+      <c r="S52" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T52" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="564" customHeight="1">
       <c r="A53" s="18" t="inlineStr">
@@ -8398,7 +8426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9796,7 +9824,7 @@
       </c>
       <c r="E49" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว</t>
+          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect</t>
         </is>
       </c>
       <c r="F49" s="55" t="inlineStr">
@@ -9837,16 +9865,16 @@
     </row>
     <row r="51">
       <c r="A51" s="55" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B51" s="55" t="inlineStr">
         <is>
-          <t>UAT-47</t>
+          <t>UAT-48</t>
         </is>
       </c>
       <c r="C51" s="55" t="inlineStr">
         <is>
-          <t>Laddawan → Nipaporn → Waraporn (impersonated) → กล่องจดหมาย 3 กล่อง (คนตรวจ)</t>
+          <t>Pornthip (กล่องจดหมาย — ภาพจาก jakkaritw ผ่านกล่อง cc CMAN_PowerBI)</t>
         </is>
       </c>
       <c r="D51" s="55" t="inlineStr">
@@ -9856,268 +9884,328 @@
       </c>
       <c r="E51" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
+          <t>ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest)</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40-step3-approved-final.png</t>
+          <t>ภาพอีเมลจาก jakkaritw 09/09 (ฉบับ 03:12 + รายการกล่องจดหมาย)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="55" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B52" s="55" t="inlineStr">
         <is>
-          <t>UAT-49</t>
+          <t>UAT-50</t>
         </is>
       </c>
       <c r="C52" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated) — เฉพาะข้อ 5 และ 8; ข้อ 1-4, 6, 7 และมือถือให้คนเปิดอีเมล</t>
+          <t>jakkaritw (เจ้าของระบบตัดสิน) — หลักฐานจอจาก AI, หลักฐานอีเมลจากภาพ</t>
         </is>
       </c>
       <c r="D52" s="55" t="inlineStr">
         <is>
-          <t>Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
+          <t>jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-49-deeplink-landing.png</t>
+          <t>shots/UAT-38-rejected-by-laddawan.png, shots/UAT-40-step2-approved-by-nipaporn.png + ภาพอีเมลจาก jakkaritw 09/09</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="55" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B53" s="55" t="inlineStr">
         <is>
-          <t>UAT-51</t>
+          <t>UAT-47</t>
         </is>
       </c>
       <c r="C53" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated) — ภาพหลักฐานที่ 1400×1000 เท่านั้น</t>
+          <t>Laddawan → Nipaporn → Waraporn (impersonated) → กล่องจดหมาย 3 กล่อง (คนตรวจ)</t>
         </is>
       </c>
       <c r="D53" s="55" t="inlineStr">
         <is>
-          <t>Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E53" s="55" t="inlineStr">
         <is>
-          <t>AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
         </is>
       </c>
       <c r="F53" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-51-pornthip-DA-approved-full.png, shots/UAT-51-subform-entertainment-readonly.png, shots/UAT-51-attachments-modal.png</t>
+          <t>shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40-step3-approved-final.png</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="55" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B54" s="55" t="inlineStr">
         <is>
-          <t>UAT-04</t>
+          <t>UAT-49</t>
         </is>
       </c>
       <c r="C54" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated; บัญชีจริงที่ล็อกอิน = jakkaritw)</t>
+          <t>Pornthip (impersonated) — เฉพาะข้อ 5 และ 8; ข้อ 1-4, 6, 7 และมือถือให้คนเปิดอีเมล</t>
         </is>
       </c>
       <c r="D54" s="55" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ</t>
         </is>
       </c>
       <c r="E54" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า · jakkaritw ตัดสิน 2026-09-09: ข้อความ 'หมดเวลา … 14 ชั่วโมง' ตอนกดออกจากระบบ ยอมรับได้ ไม่เปิด defect</t>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
         </is>
       </c>
       <c r="F54" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-04-after-logout.png, shots/UAT-04-after-back.png</t>
+          <t>shots/UAT-49-deeplink-landing.png</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="55" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="55" t="inlineStr">
+        <is>
+          <t>UAT-51</t>
+        </is>
+      </c>
+      <c r="C55" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated) — ภาพหลักฐานที่ 1400×1000 เท่านั้น</t>
+        </is>
+      </c>
+      <c r="D55" s="55" t="inlineStr">
+        <is>
+          <t>Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge</t>
+        </is>
+      </c>
+      <c r="E55" s="55" t="inlineStr">
+        <is>
+          <t>AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+        </is>
+      </c>
+      <c r="F55" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-51-pornthip-DA-approved-full.png, shots/UAT-51-subform-entertainment-readonly.png, shots/UAT-51-attachments-modal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="55" t="inlineStr">
+        <is>
+          <t>UAT-04</t>
+        </is>
+      </c>
+      <c r="C56" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated; บัญชีจริงที่ล็อกอิน = jakkaritw)</t>
+        </is>
+      </c>
+      <c r="D56" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E56" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า · jakkaritw ตัดสิน 2026-09-09: ข้อความ 'หมดเวลา … 14 ชั่วโมง' ตอนกดออกจากระบบ ยอมรับได้ ไม่เปิด defect</t>
+        </is>
+      </c>
+      <c r="F56" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-04-after-logout.png, shots/UAT-04-after-back.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="55" t="inlineStr">
+      <c r="B57" s="55" t="inlineStr">
         <is>
           <t>UAT-05</t>
         </is>
       </c>
-      <c r="C55" s="55" t="inlineStr">
+      <c r="C57" s="55" t="inlineStr">
         <is>
           <t>— (คนทำ)</t>
         </is>
       </c>
-      <c r="D55" s="55" t="inlineStr">
+      <c r="D57" s="55" t="inlineStr">
         <is>
           <t>Deferred to human</t>
         </is>
       </c>
-      <c r="E55" s="55" t="inlineStr">
+      <c r="E57" s="55" t="inlineStr">
         <is>
           <t>ข้อควรรู้ก่อนทำ: ข้อความในกล่องเขียนว่า '14 ชั่วโมง' ตายตัว (ดู UAT-04) ถ้าเห็นคำนี้ตอนหมดเวลาที่ 1 ชั่วโมง ไม่ใช่ความผิดของผู้ทดสอบ ให้จดเป็นข้อสังเกต · หลังจบรอบต้องคืนอายุ session เป็น 14 ชั่วโมง</t>
         </is>
       </c>
-      <c r="F55" s="55" t="inlineStr">
+      <c r="F57" s="55" t="inlineStr">
         <is>
           <t>shots/UAT-04-after-back.png</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="56" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="56" t="inlineStr">
         <is>
           <t>สรุป</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Human decides / not run</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Human decides / not run</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="56" t="inlineStr">
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
         <is>
           <t>งานที่คนต้องทำต่อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
-        </is>
-      </c>
-      <c r="B64" s="55" t="inlineStr">
-        <is>
-          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>UAT-05</t>
-        </is>
-      </c>
-      <c r="B65" s="55" t="inlineStr">
-        <is>
-          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
+          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
         </is>
       </c>
       <c r="B66" s="55" t="inlineStr">
         <is>
-          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
+          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
+          <t>UAT-05</t>
         </is>
       </c>
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
+          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UAT-51</t>
+          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
         </is>
       </c>
       <c r="B68" s="55" t="inlineStr">
         <is>
-          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
+          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UAT-52 ข้อ 2</t>
+          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
         </is>
       </c>
       <c r="B69" s="55" t="inlineStr">
         <is>
-          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
+          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>UAT-51</t>
+        </is>
+      </c>
+      <c r="B70" s="55" t="inlineStr">
+        <is>
+          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>UAT-52 ข้อ 2</t>
+        </is>
+      </c>
+      <c r="B71" s="55" t="inlineStr">
+        <is>
+          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>UAT-13</t>
         </is>
       </c>
-      <c r="B70" s="55" t="inlineStr">
+      <c r="B72" s="55" t="inlineStr">
         <is>
           <t>AI ให้ Fail: ระบบแจ้งข้อความตรวจสอบทีละ 1 ข้อ ไม่ใช่พร้อมกัน — ทีมตัดสินว่าเป็น defect หรือ by design แล้วใส่ Severity/Defect ID</t>
         </is>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -5569,12 +5569,12 @@
       </c>
       <c r="N44" s="51" t="inlineStr">
         <is>
-          <t>ข้อ 1-2 (ทำโดยสวมสิทธิ์ nipapornt ผู้อนุมัติขั้น 2 ยังไม่เปิดโหมด Admin): ตัวเลือกฝ่ายแสดง 5 ฝ่ายในสิทธิ์ปกติ (Budgeting and Management 1 CC, Budgeting &amp; Cost Accounting 1 CC, Chief Financial Officer 2 CC, Chief Operating Officer 1 CC, General 2 CC) — ไม่มี Data &amp; Analytic อยู่ในรายการเลย จึงไม่มีป้าย Pending ที่ฝ่ายนี้ (ยังไม่ถึงคิวของเธอ) · ข้อ 3-4 (เปิดโหมด Admin แล้วดูปุ่มบนแถบอนุมัติของ D&amp;A): ยังไม่ได้ทำ — การเปิดโหมด Admin ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อก · ข้อ 5 (Laddawan เปิด D&amp;A ตอนอยู่ขั้นที่ 2): รอทำเมื่อฝ่ายเลื่อนไปขั้นที่ 2 · ข้อ 5 (ทำหลังงบเลื่อนไป Step 2 เมื่อ 03:18): Laddawan (ผู้อนุมัติขั้นที่ 1 ที่อนุมัติไปแล้ว ไม่ใช่ admin) เปิด Data &amp; Analytic เห็น chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' + ข้อความ 'Submitted — locked for editing until it is rejected' ไม่มีปุ่ม Approve และไม่มีปุ่ม Reject เลย (รายการปุ่มบนแถบอนุมัติว่าง) — ยืนยันระบบบังคับลำดับ 1 → 2 → 3</t>
+          <t>ข้อ 1-2 (ทำโดยสวมสิทธิ์ nipapornt ผู้อนุมัติขั้น 2 ยังไม่เปิดโหมด Admin): ตัวเลือกฝ่ายแสดง 5 ฝ่ายในสิทธิ์ปกติ (Budgeting and Management 1 CC, Budgeting &amp; Cost Accounting 1 CC, Chief Financial Officer 2 CC, Chief Operating Officer 1 CC, General 2 CC) — ไม่มี Data &amp; Analytic อยู่ในรายการเลย จึงไม่มีป้าย Pending ที่ฝ่ายนี้ (ยังไม่ถึงคิวของเธอ) · ข้อ 3-4 (เปิดโหมด Admin แล้วดูปุ่มบนแถบอนุมัติของ D&amp;A): ยังไม่ได้ทำ — การเปิดโหมด Admin ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อก · ข้อ 5 (Laddawan เปิด D&amp;A ตอนอยู่ขั้นที่ 2): รอทำเมื่อฝ่ายเลื่อนไปขั้นที่ 2 · ข้อ 5 (ทำหลังงบเลื่อนไป Step 2 เมื่อ 03:18): Laddawan (ผู้อนุมัติขั้นที่ 1 ที่อนุมัติไปแล้ว ไม่ใช่ admin) เปิด Data &amp; Analytic เห็น chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' + ข้อความ 'Submitted — locked for editing until it is rejected' ไม่มีปุ่ม Approve และไม่มีปุ่ม Reject เลย (รายการปุ่มบนแถบอนุมัติว่าง) — ยืนยันระบบบังคับลำดับ 1 → 2 → 3 · ข้อ 2-4 (ทำ 09/09 16:3x บนฝ่าย Solution Delivery ตอน Pending · Step 1 แทน D&amp;A ที่ Approved แล้ว): Nipaporn/Waraporn ปิดโหมด Admin → SD ไม่ติดป้าย Pending และไม่อยู่ในตัวเลือกฝ่ายเลย (ยังไม่ถึงคิว) · Nipaporn เปิดโหมด Admin เลือก SD → แถบอนุมัติมีปุ่ม **Approve ปุ่มเดียว ไม่มี Reject** (= ปุ่มดำเนินการแทนขั้นที่ 1 ตามสิทธิ์ผู้ดูแลระบบ) · ไม่กดปุ่ม → chip ยังเป็น 'Pending · Step 1 (Direct manager)' ไม่เปลี่ยน</t>
         </is>
       </c>
       <c r="O44" s="21" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="P44" s="22" t="n"/>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="T44" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] Expected ข้อ 1 ผ่าน · ข้อ 2-4 ให้คนทำ (~2 นาที: สวมสิทธิ์ warapornt/nipapornt → เปิดโหมด Admin → เลือก Data &amp; Analytic → อ่านปุ่ม: ต้องมีแค่ Approve ไม่มี Reject, ห้ามกด) · ข้อ 5 จะทำต่อในรอบ AI เมื่อ D&amp;A ถึงขั้นที่ 2 · ข้อ 5 ผ่าน (หลักฐาน shots/UAT-40-step1-approved-by-laddawan.png)</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ (1-5) · ข้อ 2-4 ทำบน Solution Delivery แทน D&amp;A เพราะ D&amp;A ถึง Approved ก่อน — เงื่อนไขเดียวกัน (ฝ่ายค้าง Step 1, admin ไม่ใช่เจ้าของคิว) · ข้อ 5 หลักฐาน shots/UAT-40-step1-approved-by-laddawan.png</t>
         </is>
       </c>
     </row>
@@ -5774,8 +5774,16 @@
 การกดดำเนินการแทนเลื่อนสถานะจริงและส่งอีเมลจริงถึงเพื่อนร่วมงาน ทำเมื่อทีมพร้อมเท่านั้น · เคสนี้รวมเคสอีเมล step override เดิมเข้ามาไว้ในแถวเดียว ต้องอ่าน Expected Result ให้ครบทั้ง 8 ข้อ (นับข้อ 4a และ 4b แยกกัน) ก่อนตัดสิน Pass · หลังเคสนี้งบจะไปค้างอยู่ที่ขั้นที่ 2 — **หยุด — กลับไปทำ UAT-42 ข้อ 5 ตอนนี้ ก่อนเริ่ม UAT-41** เพราะช่วงที่งบอยู่ขั้นที่ 2 มีอยู่แค่ระหว่างเคสนี้กับ UAT-41 เท่านั้น · จากนั้นเดินต่อด้วยเคส UAT-41 (ตีกลับจากขั้นที่ 2) แล้วให้ผู้กรอกส่งงบใหม่ในเคส UAT-46 ก่อนจะทำเคส UAT-40 เป็นลำดับสุดท้าย · ส่วนข้อ 4b ของเคสนี้ยังทำตอนนี้ไม่ได้ ต้อง `ทำระหว่างเคส UAT-40 หลังข้อ 4 ก่อนข้อ 5` แล้วกลับมาบันทึกผลที่เคสนี้</t>
         </is>
       </c>
-      <c r="N46" s="21" t="n"/>
-      <c r="O46" s="21" t="n"/>
+      <c r="N46" s="51" t="inlineStr">
+        <is>
+          <t>ทำบนฝ่าย Solution Delivery แทน Data &amp; Analytic (D&amp;A เป็น Approved ถาวรแล้ว) · 16:24 Pornthip Submit SD → 'Pending · Step 1 (Direct manager)' · ข้อ 1: Nipaporn ปิดโหมด Admin — SD ไม่อยู่ในตัวเลือกฝ่ายเลย (ยังไม่ถึงคิวเธอ) · เปิด toggle 'โหมด Admin' → ตัวเลือกฝ่ายแสดงทุกฝ่ายทุกสายงาน → เลือก Solution Delivery Year 2026 · แถบอนุมัติ: chip 'Pending · Step 1 (Direct manager)' มีปุ่ม **Approve ปุ่มเดียว ไม่มี Reject** ยอด 30,000.00 · ข้อ 2-3: กด Approve (jakkaritw กดเองในหน้าต่าง Edge ในนาม nipapornt เพราะเครื่องมือ AI ถูกบล็อกที่ปุ่มนี้) → ยืนยัน 16:40 → chip 'Pending · Step 2 (นิภาพร ทองกิ่ง (Senior Associate))' (jakkaritw ยืนยันข้อความ chip) · ข้อ 4a: Waraporn เปิดโหมด Admin เปิด SD ตอน Step 2 → แถบอนุมัติไม่มีปุ่มใดเลย (ไม่มี Approve/Reject) · ปิดโหมด Admin → SD ไม่อยู่ในตัวเลือกฝ่ายของเธอ (5 ฝ่ายปกติ) · 16:44 Nipaporn (ปิดโหมด Admin, SD ติดป้าย Pending = คิวเธอ) กด Approve ขั้น 2 ตามคิวปกติ → กล่อง 'Approve the whole department "Solution Delivery" for FY 2027?' → chip 'Pending · Step 3 (วราพร ติรสิทธิ์ (Assistant Department Head))' · ข้อ 4b: Nipaporn เปิดโหมด Admin เปิด SD ตอน Step 3 → ไม่มีปุ่มใดเลย (ทำแทนขั้น 3 ไม่ได้) · ข้อ 5-6 (ภาพอีเมลจาก jakkaritw): 'ดำเนินการแทนผู้อนุมัติ งบประมาณของฝ่าย Solution Delivery ปีงบประมาณ 2027' To Pornthip Phermsaphiran, Cc Laddawan Kearnoi; CMAN_PowerBI · เนื้อหา 'ผู้ดูแลระบบได้ดำเนินการอนุมัติแทนผู้อนุมัติขั้นที่ 1 ให้งบประมาณของท่านแล้ว' · ตาราง: ผู้อนุมัติที่ถูกข้าม laddawank@chememan.com / ผู้ดำเนินการแทน nipapornt@chememan.com / วันเวลา 09/09/2026 16:40 / สถานะปัจจุบัน 'รอการอนุมัติจาก nipapornt@chememan.com' · ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ข้อ 7: เมล 'รอการอนุมัติ … Solution Delivery' To Waraporn Tirasit (หลังขั้น 2 อนุมัติ 16:44) เห็นจากภาพ · คืนสถานะ 16:46: Waraporn (ปิดโหมด Admin, SD ติดป้าย Pending) Reject ขั้น 3 เหตุผล 'UAT Round 1 — จบเคส UAT-44 คืนฝ่าย Solution Delivery ให้ Suchanya' → chip 'Rejected' ยอด 30,000 คงเดิม</t>
+        </is>
+      </c>
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P46" s="22" t="n"/>
       <c r="Q46" s="22" t="n"/>
       <c r="R46" s="23" t="inlineStr">
@@ -5783,8 +5791,14 @@
           <t>Nipaporn หรือ Waraporn → Waraporn (เจาะจง) → Nipaporn (เจาะจง)</t>
         </is>
       </c>
-      <c r="S46" s="24" t="n"/>
-      <c r="T46" s="21" t="n"/>
+      <c r="S46" s="24" t="n">
+        <v>46274</v>
+      </c>
+      <c r="T46" s="51" t="inlineStr">
+        <is>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 3, 4a, 4b, 5, 6 จากหลักฐานตรง · ข้อ 1-2 (ข้อความในกล่องยืนยันการทำแทน) jakkaritw เป็นผู้อ่านตอนกดเอง — ให้ยืนยันว่าขึ้นต้น 'You are approving on behalf of ลัดดาวัลย์ … (approver step 1)' และบอกเรื่องบันทึก/ส่งเมล แล้วจดลงช่องนี้ · ข้อ 7 (นิภาพรได้เมลคิวหลังการทำแทน 16:40 — รวม 2 ฉบับจากการกดครั้งนั้น) ให้ดูจากรายการกล่องจดหมาย CMAN_PowerBI ช่วง 16:40 · ข้อสังเกต (ไม่ใช่ defect): ในโหมด Admin ช่องเดือนของฝ่ายที่ Pending ยังแสดงเป็นช่องพิมพ์ 48 ช่อง (server ปฏิเสธการบันทึกอยู่แล้ว และ UAT-34 fix จะขึ้นข้อความไทยเมื่อพิมพ์) · เมลจริงที่เกิดจากเคสนี้: คิวถึงลัดดาวัลย์ 16:24, ดำเนินการแทน 16:40 (To พรทิพย์ cc ลัดดาวัลย์), คิวถึงนิภาพร 16:40, คิวถึงวราพร 16:44, ตีกลับถึงพรทิพย์ 16:46</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="372" customHeight="1">
       <c r="A47" s="18" t="inlineStr">
@@ -8426,7 +8440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9639,17 +9653,17 @@
       </c>
       <c r="D43" s="55" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E43" s="55" t="inlineStr">
         <is>
-          <t>Expected ข้อ 1 ผ่าน · ข้อ 2-4 ให้คนทำ (~2 นาที: สวมสิทธิ์ warapornt/nipapornt → เปิดโหมด Admin → เลือก Data &amp; Analytic → อ่านปุ่ม: ต้องมีแค่ Approve ไม่มี Reject, ห้ามกด) · ข้อ 5 จะทำต่อในรอบ AI เมื่อ D&amp;A ถึงขั้นที่ 2 · ข้อ 5 ผ่าน (หลักฐาน shots/UAT-40-step1-approved-by-laddawan.png)</t>
+          <t>ผ่านทุกข้อ (1-5) · ข้อ 2-4 ทำบน Solution Delivery แทน D&amp;A เพราะ D&amp;A ถึง Approved ก่อน — เงื่อนไขเดียวกัน (ฝ่ายค้าง Step 1, admin ไม่ใช่เจ้าของคิว) · ข้อ 5 หลักฐาน shots/UAT-40-step1-approved-by-laddawan.png</t>
         </is>
       </c>
       <c r="F43" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-42_nipaporn_picker.png</t>
+          <t>shots/UAT-42_nipaporn_picker.png, shots/UAT-44_nipaporn_adminmode_SD_step1.png</t>
         </is>
       </c>
     </row>
@@ -9775,16 +9789,16 @@
     </row>
     <row r="48">
       <c r="A48" s="55" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" s="55" t="inlineStr">
         <is>
-          <t>UAT-40</t>
+          <t>UAT-44</t>
         </is>
       </c>
       <c r="C48" s="55" t="inlineStr">
         <is>
-          <t>Laddawan → Nipaporn → Waraporn → Pornthip (impersonated ทั้งหมด, โหมด Admin ปิด)</t>
+          <t>Nipaporn (impersonated; ปุ่มดำเนินการแทนกดโดย jakkaritw เองในหน้าต่าง Edge) → Waraporn → Nipaporn → Waraporn (impersonated)</t>
         </is>
       </c>
       <c r="D48" s="55" t="inlineStr">
@@ -9794,27 +9808,27 @@
       </c>
       <c r="E48" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ'</t>
+          <t>ผ่านข้อ 3, 4a, 4b, 5, 6 จากหลักฐานตรง · ข้อ 1-2 (ข้อความในกล่องยืนยันการทำแทน) jakkaritw เป็นผู้อ่านตอนกดเอง — ให้ยืนยันว่าขึ้นต้น 'You are approving on behalf of ลัดดาวัลย์ … (approver step 1)' และบอกเรื่องบันทึก/ส่งเมล แล้วจดลงช่องนี้ · ข้อ 7 (นิภาพรได้เมลคิวหลังการทำแทน 16:40 — รวม 2 ฉบับจากการกดครั้งนั้น) ให้ดูจากรายการกล่องจดหมาย CMAN_PowerBI ช่วง 16:40 · ข้อสังเกต (ไม่ใช่ defect): ในโหมด Admin ช่องเดือนของฝ่ายที่ Pending ยังแสดงเป็นช่องพิมพ์ 48 ช่อง (server ปฏิเสธการบันทึกอยู่แล้ว และ UAT-34 fix จะขึ้นข้อความไทยเมื่อพิมพ์) · เมลจริงที่เกิดจากเคสนี้: คิวถึงลัดดาวัลย์ 16:24, ดำเนินการแทน 16:40 (To พรทิพย์ cc ลัดดาวัลย์), คิวถึงนิภาพร 16:40, คิวถึงวราพร 16:44, ตีกลับถึงพรทิพย์ 16:46</t>
         </is>
       </c>
       <c r="F48" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-40-step1-approved-by-laddawan.png, shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40_waraporn_picker.png, shots/UAT-40-step3-approved-final.png, shots/UAT-40-pornthip-sees-approved.png</t>
+          <t>shots/UAT-44_nipaporn_SD_step1_buttons.png, shots/UAT-44_nipaporn_adminmode_SD_step1.png, shots/UAT-44_4a_waraporn_adminon_SD_step2.png, shots/UAT-44_4a_waraporn_adminoff_picker.png, shots/UAT-44_nipaporn_step2_approved.png, shots/UAT-44_4b_nipaporn_adminoff_SD_step3.png, shots/UAT-44_4b_nipaporn_adminon_SD_step3.png, shots/UAT-44_restore_SD_rejected_by_waraporn.png + ภาพอีเมล 'ดำเนินการแทนผู้อนุมัติ' และ 'รอการอนุมัติ SD' ถึงวราพร จาก jakkaritw</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="55" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B49" s="55" t="inlineStr">
         <is>
-          <t>UAT-41</t>
+          <t>UAT-40</t>
         </is>
       </c>
       <c r="C49" s="55" t="inlineStr">
         <is>
-          <t>Nipaporn (impersonated, โหมด Admin ปิด) → Pornthip (impersonated)</t>
+          <t>Laddawan → Nipaporn → Waraporn → Pornthip (impersonated ทั้งหมด, โหมด Admin ปิด)</t>
         </is>
       </c>
       <c r="D49" s="55" t="inlineStr">
@@ -9824,27 +9838,27 @@
       </c>
       <c r="E49" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect</t>
+          <t>ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ'</t>
         </is>
       </c>
       <c r="F49" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-41_nipaporn_picker.png, shots/UAT-41-rejected-by-nipaporn-step2.png</t>
+          <t>shots/UAT-40-step1-approved-by-laddawan.png, shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40_waraporn_picker.png, shots/UAT-40-step3-approved-final.png, shots/UAT-40-pornthip-sees-approved.png</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="55" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" s="55" t="inlineStr">
         <is>
-          <t>UAT-46</t>
+          <t>UAT-41</t>
         </is>
       </c>
       <c r="C50" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated) → Laddawan (กล่องจดหมาย — คนตรวจ)</t>
+          <t>Nipaporn (impersonated, โหมด Admin ปิด) → Pornthip (impersonated)</t>
         </is>
       </c>
       <c r="D50" s="55" t="inlineStr">
@@ -9854,12 +9868,12 @@
       </c>
       <c r="E50" s="55" t="inlineStr">
         <is>
-          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ</t>
+          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect</t>
         </is>
       </c>
       <c r="F50" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-46-resubmitted.png</t>
+          <t>shots/UAT-41_nipaporn_picker.png, shots/UAT-41-rejected-by-nipaporn-step2.png</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9883,12 @@
       </c>
       <c r="B51" s="55" t="inlineStr">
         <is>
-          <t>UAT-48</t>
+          <t>UAT-46</t>
         </is>
       </c>
       <c r="C51" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (กล่องจดหมาย — ภาพจาก jakkaritw ผ่านกล่อง cc CMAN_PowerBI)</t>
+          <t>Pornthip (impersonated) → Laddawan (กล่องจดหมาย — คนตรวจ)</t>
         </is>
       </c>
       <c r="D51" s="55" t="inlineStr">
@@ -9884,27 +9898,27 @@
       </c>
       <c r="E51" s="55" t="inlineStr">
         <is>
-          <t>ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest)</t>
+          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
         <is>
-          <t>ภาพอีเมลจาก jakkaritw 09/09 (ฉบับ 03:12 + รายการกล่องจดหมาย)</t>
+          <t>shots/UAT-46-resubmitted.png</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="55" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B52" s="55" t="inlineStr">
         <is>
-          <t>UAT-50</t>
+          <t>UAT-48</t>
         </is>
       </c>
       <c r="C52" s="55" t="inlineStr">
         <is>
-          <t>jakkaritw (เจ้าของระบบตัดสิน) — หลักฐานจอจาก AI, หลักฐานอีเมลจากภาพ</t>
+          <t>Pornthip (กล่องจดหมาย — ภาพจาก jakkaritw ผ่านกล่อง cc CMAN_PowerBI)</t>
         </is>
       </c>
       <c r="D52" s="55" t="inlineStr">
@@ -9914,27 +9928,27 @@
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง</t>
+          <t>ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest)</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-38-rejected-by-laddawan.png, shots/UAT-40-step2-approved-by-nipaporn.png + ภาพอีเมลจาก jakkaritw 09/09</t>
+          <t>ภาพอีเมลจาก jakkaritw 09/09 (ฉบับ 03:12 + รายการกล่องจดหมาย)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="55" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B53" s="55" t="inlineStr">
         <is>
-          <t>UAT-47</t>
+          <t>UAT-50</t>
         </is>
       </c>
       <c r="C53" s="55" t="inlineStr">
         <is>
-          <t>Laddawan → Nipaporn → Waraporn (impersonated) → กล่องจดหมาย 3 กล่อง (คนตรวจ)</t>
+          <t>jakkaritw (เจ้าของระบบตัดสิน) — หลักฐานจอจาก AI, หลักฐานอีเมลจากภาพ</t>
         </is>
       </c>
       <c r="D53" s="55" t="inlineStr">
@@ -9944,268 +9958,298 @@
       </c>
       <c r="E53" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
+          <t>jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง</t>
         </is>
       </c>
       <c r="F53" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40-step3-approved-final.png</t>
+          <t>shots/UAT-38-rejected-by-laddawan.png, shots/UAT-40-step2-approved-by-nipaporn.png + ภาพอีเมลจาก jakkaritw 09/09</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="55" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B54" s="55" t="inlineStr">
         <is>
-          <t>UAT-49</t>
+          <t>UAT-47</t>
         </is>
       </c>
       <c r="C54" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated) — เฉพาะข้อ 5 และ 8; ข้อ 1-4, 6, 7 และมือถือให้คนเปิดอีเมล</t>
+          <t>Laddawan → Nipaporn → Waraporn (impersonated) → กล่องจดหมาย 3 กล่อง (คนตรวจ)</t>
         </is>
       </c>
       <c r="D54" s="55" t="inlineStr">
         <is>
-          <t>Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E54" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
         </is>
       </c>
       <c r="F54" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-49-deeplink-landing.png</t>
+          <t>shots/UAT-47-step1-approved.png, shots/UAT-40-step2-approved-by-nipaporn.png, shots/UAT-40-step3-approved-final.png</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="55" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B55" s="55" t="inlineStr">
         <is>
-          <t>UAT-51</t>
+          <t>UAT-49</t>
         </is>
       </c>
       <c r="C55" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated) — ภาพหลักฐานที่ 1400×1000 เท่านั้น</t>
+          <t>Pornthip (impersonated) — เฉพาะข้อ 5 และ 8; ข้อ 1-4, 6, 7 และมือถือให้คนเปิดอีเมล</t>
         </is>
       </c>
       <c r="D55" s="55" t="inlineStr">
         <is>
-          <t>Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge</t>
+          <t>Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ</t>
         </is>
       </c>
       <c r="E55" s="55" t="inlineStr">
         <is>
-          <t>AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
         </is>
       </c>
       <c r="F55" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-51-pornthip-DA-approved-full.png, shots/UAT-51-subform-entertainment-readonly.png, shots/UAT-51-attachments-modal.png</t>
+          <t>shots/UAT-49-deeplink-landing.png</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="55" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B56" s="55" t="inlineStr">
         <is>
-          <t>UAT-04</t>
+          <t>UAT-51</t>
         </is>
       </c>
       <c r="C56" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated; บัญชีจริงที่ล็อกอิน = jakkaritw)</t>
+          <t>Pornthip (impersonated) — ภาพหลักฐานที่ 1400×1000 เท่านั้น</t>
         </is>
       </c>
       <c r="D56" s="55" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge</t>
         </is>
       </c>
       <c r="E56" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า · jakkaritw ตัดสิน 2026-09-09: ข้อความ 'หมดเวลา … 14 ชั่วโมง' ตอนกดออกจากระบบ ยอมรับได้ ไม่เปิด defect</t>
+          <t>AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
         </is>
       </c>
       <c r="F56" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-04-after-logout.png, shots/UAT-04-after-back.png</t>
+          <t>shots/UAT-51-pornthip-DA-approved-full.png, shots/UAT-51-subform-entertainment-readonly.png, shots/UAT-51-attachments-modal.png</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="55" t="inlineStr">
+        <is>
+          <t>UAT-04</t>
+        </is>
+      </c>
+      <c r="C57" s="55" t="inlineStr">
+        <is>
+          <t>Pornthip (impersonated; บัญชีจริงที่ล็อกอิน = jakkaritw)</t>
+        </is>
+      </c>
+      <c r="D57" s="55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="E57" s="55" t="inlineStr">
+        <is>
+          <t>ผ่านข้อ 1-3: session ของแอปถูกตัดทันทีตั้งแต่กดออก (ก่อนเลือกบัญชีในหน้า Microsoft) กด Back ไม่เห็นข้อมูลเดิม ถูกบังคับล็อกอินใหม่ · ข้อสังเกต 2 จุด: (ก) กล่องที่เห็นใช้ข้อความ 'หมดเวลาการเข้าใช้งาน … 14 ชั่วโมง' ทั้งที่ผู้ใช้เพิ่งกดออกเอง — ความหมายไม่ตรงเหตุการณ์ (ข) ตัวเลข '14 ชั่วโมง' เขียนตายตัวในข้อความ ขณะที่รอบ UAT ตั้งอายุ session ไว้ 1 ชั่วโมง → คนทำ UAT-05 จะเห็น '14 ชั่วโมง' ทั้งที่หมดเวลาจริงตอน 1 ชั่วโมง ควรอ่านค่าจากการตั้งค่า · jakkaritw ตัดสิน 2026-09-09: ข้อความ 'หมดเวลา … 14 ชั่วโมง' ตอนกดออกจากระบบ ยอมรับได้ ไม่เปิด defect</t>
+        </is>
+      </c>
+      <c r="F57" s="55" t="inlineStr">
+        <is>
+          <t>shots/UAT-04-after-logout.png, shots/UAT-04-after-back.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="55" t="n">
         <v>54</v>
       </c>
-      <c r="B57" s="55" t="inlineStr">
+      <c r="B58" s="55" t="inlineStr">
         <is>
           <t>UAT-05</t>
         </is>
       </c>
-      <c r="C57" s="55" t="inlineStr">
+      <c r="C58" s="55" t="inlineStr">
         <is>
           <t>— (คนทำ)</t>
         </is>
       </c>
-      <c r="D57" s="55" t="inlineStr">
+      <c r="D58" s="55" t="inlineStr">
         <is>
           <t>Deferred to human</t>
         </is>
       </c>
-      <c r="E57" s="55" t="inlineStr">
+      <c r="E58" s="55" t="inlineStr">
         <is>
           <t>ข้อควรรู้ก่อนทำ: ข้อความในกล่องเขียนว่า '14 ชั่วโมง' ตายตัว (ดู UAT-04) ถ้าเห็นคำนี้ตอนหมดเวลาที่ 1 ชั่วโมง ไม่ใช่ความผิดของผู้ทดสอบ ให้จดเป็นข้อสังเกต · หลังจบรอบต้องคืนอายุ session เป็น 14 ชั่วโมง</t>
         </is>
       </c>
-      <c r="F57" s="55" t="inlineStr">
+      <c r="F58" s="55" t="inlineStr">
         <is>
           <t>shots/UAT-04-after-back.png</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="56" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
         <is>
           <t>สรุป</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Human decides / not run</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Human decides / not run</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="56" t="inlineStr">
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
         <is>
           <t>งานที่คนต้องทำต่อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
-        </is>
-      </c>
-      <c r="B66" s="55" t="inlineStr">
-        <is>
-          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UAT-05</t>
+          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
         </is>
       </c>
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
+          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
+          <t>UAT-05</t>
         </is>
       </c>
       <c r="B68" s="55" t="inlineStr">
         <is>
-          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
+          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
+          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
         </is>
       </c>
       <c r="B69" s="55" t="inlineStr">
         <is>
-          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
+          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UAT-51</t>
+          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
         </is>
       </c>
       <c r="B70" s="55" t="inlineStr">
         <is>
-          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
+          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UAT-52 ข้อ 2</t>
+          <t>UAT-51</t>
         </is>
       </c>
       <c r="B71" s="55" t="inlineStr">
         <is>
-          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
+          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>UAT-52 ข้อ 2</t>
+        </is>
+      </c>
+      <c r="B72" s="55" t="inlineStr">
+        <is>
+          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>UAT-13</t>
         </is>
       </c>
-      <c r="B72" s="55" t="inlineStr">
+      <c r="B73" s="55" t="inlineStr">
         <is>
           <t>AI ให้ Fail: ระบบแจ้งข้อความตรวจสอบทีละ 1 ข้อ ไม่ใช่พร้อมกัน — ทีมตัดสินว่าเป็น defect หรือ by design แล้วใส่ Severity/Defect ID</t>
         </is>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -2960,12 +2960,12 @@
       </c>
       <c r="N17" s="51" t="inlineStr">
         <is>
-          <t>สลับสวมสิทธิ์เป็น nipapornt สำเร็จ (/me = nipapornt, role badge = ผู้ดูแลระบบ, ฝ่าย 5, มีป้ายย่อ '+1 สายงาน' และ '+2' — ยืนยันกติกาย่อชื่อของ UAT-01 ข้อ 7-8 ในกรณี &gt;3 ชื่อ) · พบ toggle 'โหมด Admin' (data-testid admin-mode-toggle / admin-mode-checkbox) ค่าเริ่มต้นปิด · ขั้นเปิดโหมด Admin และค้น GL ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อกไว้ จึงยังไม่ได้ตรวจข้อ 1-3</t>
+          <t>Waraporn เปิด toggle 'โหมด Admin' → เลือก Data &amp; Analytic Year 2026 (สถานะ Approved) → กด + เพิ่ม Transaction → เลือก Cost Center 10IT013000 → ช่อง GL Code พิมพ์ 5210100150 → รายการแสดง '5210100150 — ค่าอบรมและสัมมนา - ค่าธรรมเนียม' (พบ เลือกได้) · พิมพ์ 6210100150 → รายการแสดง '6210100150 — ค่าอบรมและสัมมนา - ค่าธรรมเนียม' (พบ เลือกได้) · กด ยกเลิก ปิดฟอร์มโดยไม่บันทึก · เทียบ UAT-14: Pornthip (Filler) ค้นทั้งสองรหัสแล้ว 'ไม่พบ' ส่วน admin 'พบ' ทั้งคู่ — ต่างกันชัดตามข้อยกเว้นของ admin</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="P17" s="22" t="n"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="T17" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ให้คนทำ (ใช้เวลา ~1 นาที): สวมสิทธิ์ nipapornt → เปิด toggle โหมด Admin → เลือก Data &amp; Analytic → + เพิ่ม Transaction → ค้น 5210100150 และ 6210100150 ต้องพบทั้งคู่ · ห้ามกด Submit ระหว่างเปิดโหมด Admin (approval.py:987 จะ Approved ทันที)</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ไม่กด Submit/บันทึกใด ๆ ระหว่างเปิดโหมด Admin · รอบก่อน Blocked เพราะเครื่องมือ AI ถูกกันไม่ให้กด toggle — รอบนี้กดได้ (ที่ยังถูกกันคือปุ่มดำเนินการแทนขั้นที่ 1 เท่านั้น ดู UAT-44)</t>
         </is>
       </c>
     </row>
@@ -5872,12 +5872,12 @@
       </c>
       <c r="N47" s="51" t="inlineStr">
         <is>
-          <t>ยังไม่ได้ทดสอบ: การเปิด toggle 'โหมด Admin' ขณะสวมสิทธิ์ admin ถูกชั้นความปลอดภัยของเครื่องมือ AI บล็อก (เหตุเดียวกับ UAT-15) · ที่ยืนยันได้จาก UAT-15: สวมสิทธิ์ nipapornt สำเร็จ badge 'ผู้ดูแลระบบ' toggle มีอยู่ (admin-mode-toggle) ค่าเริ่มต้นปิด</t>
+          <t>ข้อ 1: บัญชี Waraporn มี toggle 'โหมด Admin' บนแถบเครื่องมือ (ค่าเริ่มต้นปิด) · ฝ่ายตั้งต้นที่แสดง = Solution Delivery ตัวเลือกฝ่ายมี 6 ฝ่ายในสิทธิ์ปกติ (Budgeting and Management, Budgeting &amp; Cost Accounting, Chief Financial Officer, Chief Operating Officer, Solution Delivery, General) · ข้อ 2-3: เปิดโหมด → ฝ่ายที่แสดงเปลี่ยนเป็น 'Accounting' (ฝ่ายแรกของรายการชุดใหม่) ทันที ไม่ค้างว่าง · ตัวเลือกฝ่ายแสดง 113 ฝ่ายทั้งบริษัท จัดกลุ่มตามสายงาน (ACCOUNTING DIVISION 3 …) · ข้อ 4: แถบ 'Admin' (data-testid admin-zone) แสดง tooltip: 'งบอนุมัติ (Approved) · ทั้งบริษัท · ทั้งปี · ไม่ขึ้นกับตัวกรองปี / ฝ่าย ที่เลือกดู — อ่านอย่างเดียว (read-only) มาจากไฟล์ Excel รายปีใน SharePoint › Budgeting and Management › approved budget · Master FX (USD→THB · FY2026) แก้ที่ Master Currency (Module 09) เท่านั้น' · tooltip ของ toggle เอง: 'สลับหมวก: ปกติ (ผู้กรอก/ผู้อนุมัติ) ↔ โหมด Admin (เห็นทุกฝ่าย, แก้ได้ทุก CC)' · ข้อ 5: ปิดโหมด → ฝ่ายที่แสดงเปลี่ยนเป็น 'Budgeting and Management' (ฝ่ายแรกของรายการปกติ) ตัวเลือกฝ่ายกลับเป็น 5 ฝ่ายในสิทธิ์ (Solution Delivery หายไปเพราะไม่ค้างคิวเธอแล้ว) · ข้อ 6: เปิดโหมดแล้ว refresh ในแท็บเดิม → toggle ยังเปิดอยู่ ฝ่ายที่แสดง 'Accounting'</t>
         </is>
       </c>
       <c r="O47" s="21" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="P47" s="22" t="n"/>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="T47" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ให้คนทำ (~2 นาที): สวมสิทธิ์ nipapornt → เปิด toggle → ฝ่ายที่เลือกถูกรีเซ็ตและเห็นฝ่ายทั้งบริษัท → เช็คแถบ admin-zone และ tooltip → ปิด toggle · ห้ามกด Submit ขณะเปิดโหมด Admin</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ (1-6) · ข้อสังเกตเล็ก: สถานะโหมด Admin จำต่อเนื่องแม้สลับสวมสิทธิ์ระหว่าง admin ด้วยกันในแท็บเดียว (Nipaporn เปิดไว้ → Waraporn เห็นเปิดอยู่) — เกิดเฉพาะการสวมสิทธิ์ใน UAT ไม่กระทบผู้ใช้จริง</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8838,22 +8838,22 @@
       </c>
       <c r="C16" s="55" t="inlineStr">
         <is>
-          <t>Nipaporn (impersonated) — สลับสำเร็จ แต่ AI ไม่ได้เปิดโหมด Admin</t>
+          <t>Waraporn (impersonated, admin จริง)</t>
         </is>
       </c>
       <c r="D16" s="55" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E16" s="55" t="inlineStr">
         <is>
-          <t>ให้คนทำ (ใช้เวลา ~1 นาที): สวมสิทธิ์ nipapornt → เปิด toggle โหมด Admin → เลือก Data &amp; Analytic → + เพิ่ม Transaction → ค้น 5210100150 และ 6210100150 ต้องพบทั้งคู่ · ห้ามกด Submit ระหว่างเปิดโหมด Admin (approval.py:987 จะ Approved ทันที)</t>
+          <t>ผ่านทุกข้อ · ไม่กด Submit/บันทึกใด ๆ ระหว่างเปิดโหมด Admin · รอบก่อน Blocked เพราะเครื่องมือ AI ถูกกันไม่ให้กด toggle — รอบนี้กดได้ (ที่ยังถูกกันคือปุ่มดำเนินการแทนขั้นที่ 1 เท่านั้น ดู UAT-44)</t>
         </is>
       </c>
       <c r="F16" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-15_nipaporn_landing.png</t>
+          <t>shots/UAT-15_admin_gl_5210100150.png, shots/UAT-15_admin_gl_6210100150.png</t>
         </is>
       </c>
     </row>
@@ -9348,22 +9348,22 @@
       </c>
       <c r="C33" s="55" t="inlineStr">
         <is>
-          <t>Nipaporn/Waraporn (impersonated)</t>
+          <t>Waraporn (impersonated, dual-role admin)</t>
         </is>
       </c>
       <c r="D33" s="55" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E33" s="55" t="inlineStr">
         <is>
-          <t>ให้คนทำ (~2 นาที): สวมสิทธิ์ nipapornt → เปิด toggle → ฝ่ายที่เลือกถูกรีเซ็ตและเห็นฝ่ายทั้งบริษัท → เช็คแถบ admin-zone และ tooltip → ปิด toggle · ห้ามกด Submit ขณะเปิดโหมด Admin</t>
+          <t>ผ่านทุกข้อ (1-6) · ข้อสังเกตเล็ก: สถานะโหมด Admin จำต่อเนื่องแม้สลับสวมสิทธิ์ระหว่าง admin ด้วยกันในแท็บเดียว (Nipaporn เปิดไว้ → Waraporn เห็นเปิดอยู่) — เกิดเฉพาะการสวมสิทธิ์ใน UAT ไม่กระทบผู้ใช้จริง</t>
         </is>
       </c>
       <c r="F33" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-15_nipaporn_landing.png</t>
+          <t>shots/UAT-45_waraporn_adminon_picker_all.png, shots/UAT-45_after_refresh_admin_persists.png</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10131,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -10147,109 +10147,99 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ไม่ได้รันโดย AI (ไม่มีแถว)</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
+        <is>
+          <t>งานที่คนต้องทำต่อ</t>
+        </is>
+      </c>
+    </row>
     <row r="66">
-      <c r="A66" s="56" t="inlineStr">
-        <is>
-          <t>งานที่คนต้องทำต่อ</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
+        </is>
+      </c>
+      <c r="B66" s="55" t="inlineStr">
+        <is>
+          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
+          <t>UAT-05</t>
         </is>
       </c>
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
+          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UAT-05</t>
+          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
         </is>
       </c>
       <c r="B68" s="55" t="inlineStr">
         <is>
-          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
+          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
+          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
         </is>
       </c>
       <c r="B69" s="55" t="inlineStr">
         <is>
-          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
+          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
+          <t>UAT-51</t>
         </is>
       </c>
       <c r="B70" s="55" t="inlineStr">
         <is>
-          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
+          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>UAT-51</t>
+          <t>UAT-52 ข้อ 2</t>
         </is>
       </c>
       <c r="B71" s="55" t="inlineStr">
         <is>
-          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
+          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UAT-52 ข้อ 2</t>
+          <t>UAT-13</t>
         </is>
       </c>
       <c r="B72" s="55" t="inlineStr">
-        <is>
-          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>UAT-13</t>
-        </is>
-      </c>
-      <c r="B73" s="55" t="inlineStr">
         <is>
           <t>AI ให้ Fail: ระบบแจ้งข้อความตรวจสอบทีละ 1 ข้อ ไม่ใช่พร้อมกัน — ทีมตัดสินว่าเป็น defect หรือ by design แล้วใส่ Severity/Defect ID</t>
         </is>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -2282,7 +2282,11 @@
           <t>ชั้น SAP: เดือน Apr–Dec (m04–m12) แสดงเป็นขีด '–' (ข้อมูลยังไม่ครบ) · Jan–Feb แสดง '—' (ครบแต่เป็นศูนย์) · Mar มีตัวเลข 844.91 / 500.00 · tooltip บนขีด = 'ข้อมูล SAP เดือนนี้ยังไม่ครบ จึงยังไม่แสดง' · tooltip บนยอดรวมทั้งปีชั้น SAP = 'รวมเฉพาะเดือนที่ข้อมูลครบ: Jan–Mar' และหัวยอดรวมใหญ่เขียน 'รวมทั้งหมด · SAP · ใช้จริง (Jan–Mar)'</t>
         </is>
       </c>
-      <c r="O10" s="21" t="n"/>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P10" s="22" t="n"/>
       <c r="Q10" s="22" t="n"/>
       <c r="R10" s="23" t="inlineStr">
@@ -2295,7 +2299,7 @@
       </c>
       <c r="T10" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ข้อ 1-3 ตรงตาม Expected ทุกตัวอักษร · ข้อ 4 เป็นความเห็นของคนว่าอ่านแล้วเข้าใจไหม — AI ไม่ตัดสินแทน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยน Status เป็น Pass เอง</t>
+          <t>[AI pre-run 09/09/2026] ข้อ 1-3 ตรงตาม Expected ทุกตัวอักษร · ข้อ 4 เป็นความเห็นของคนว่าอ่านแล้วเข้าใจไหม — AI ไม่ตัดสินแทน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยน Status เป็น Pass เอง · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2567,11 @@
           <t>เปิดหน้า Data &amp; Analytic Year 2026 โดยยังไม่กรอกอะไร ใต้ toolbar ข้าง legend มีบรรทัด: 'หมายเหตุ: กรอกได้ตั้งแต่ 100 ขึ้นไป โดยระบบจะปรับตัวเลข 2 หลักสุดท้ายเป็น 00 โดยอัตโนมัติ' เห็นก่อนเริ่มกรอก</t>
         </is>
       </c>
-      <c r="O13" s="21" t="n"/>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P13" s="22" t="n"/>
       <c r="Q13" s="22" t="n"/>
       <c r="R13" s="23" t="inlineStr">
@@ -2576,7 +2584,7 @@
       </c>
       <c r="T13" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ข้อ 1-2 ตรง Expected · ข้อ 3 (อ่านแล้วเข้าใจไหม) เป็นความเห็นของคน — ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass เอง</t>
+          <t>[AI pre-run 09/09/2026] ข้อ 1-2 ตรง Expected · ข้อ 3 (อ่านแล้วเข้าใจไหม) เป็นความเห็นของคน — ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass เอง · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3359,11 @@
           <t>เปลี่ยนปีเป็น Year 2025: legend เปลี่ยนเป็น SAP (2025) / Approved (2025) / Pending (2026) · ปุ่ม '+ เพิ่ม Transaction' ถูกปิด (disabled) กดไม่ได้ และมีข้อความข้างปุ่ม 'ปีงบประมาณนี้ไม่เปิดให้กรอกในเว็บ — ข้อมูลปีนี้นำเข้าโดยผู้ดูแลระบบ' · ช่องกรอก Pending ทั้งหมดไม่มี (0 ช่อง) · แถบอนุมัติไม่มีปุ่ม Submit แสดง 'Draft — not submitted' และ 'This department has no budget data yet, so it cannot be submitted.' · เปลี่ยนกลับ Year 2026: ปุ่มเพิ่มเปิดใช้ ฟอร์มเปิดได้ ช่องกรอก 24 ช่องกลับมา ปุ่ม Submit กลับมาแสดง</t>
         </is>
       </c>
-      <c r="O21" s="21" t="n"/>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="22" t="n"/>
       <c r="R21" s="23" t="inlineStr">
@@ -3364,7 +3376,7 @@
       </c>
       <c r="T21" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ข้อ 1-3 ตรง Expected (ระบบป้องกันตั้งแต่ปิดปุ่ม ไม่ต้องรอกดบันทึกแล้วปฏิเสธ — เข้มกว่าที่เคสคาด) · ข้อ 4 (ข้อความอ่านเข้าใจไหม) เป็นความเห็นของคน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass</t>
+          <t>[AI pre-run 09/09/2026] ข้อ 1-3 ตรง Expected (ระบบป้องกันตั้งแต่ปิดปุ่ม ไม่ต้องรอกดบันทึกแล้วปฏิเสธ — เข้มกว่าที่เคสคาด) · ข้อ 4 (ข้อความอ่านเข้าใจไหม) เป็นความเห็นของคน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6736,11 @@
           <t>ค่าตั้งต้น (ขั้นตอนที่ 1) จดไว้แล้ว: ทริปต่างประเทศ Singapore 5 วัน (ทริป existing-53 เดือน เม.ย. และ existing-52 เดือน พ.ค.) เบี้ยเลี้ยงในฟอร์มย่อย = 13,200.00 ต่อทริป · ตารางหลัก 6210400010 เม.ย. 13,200.00 / พ.ค. 13,200.00 · 6210400020 พ.ค. 18,000.00 · 6210400030 พ.ค. 25,000.00 · อัตราแลกเปลี่ยนใน master ปี 2027 = 33.0000 USD/THB (dbo.master_currency_rate) · ขั้นตอนที่ 2-6 (ให้ admin แก้อัตราแลกเปลี่ยนในไฟล์ master จริงแล้วคืนค่า) AI ไม่ทำ เพราะเป็นการแก้ master ของทั้งบริษัทบนระบบจริง</t>
         </is>
       </c>
-      <c r="O56" s="21" t="n"/>
+      <c r="O56" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P56" s="22" t="n"/>
       <c r="Q56" s="22" t="n"/>
       <c r="R56" s="23" t="inlineStr">
@@ -6737,7 +6753,7 @@
       </c>
       <c r="T56" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ทางเลือกตาม note ของเคส: ข้ามขั้นตอน 2-6 ทำเฉพาะขั้นตอนที่ 7 · ต้องให้คนอธิบายพฤติกรรม (ฟอร์มย่อยคำนวณใหม่ทันที แต่ตารางหลักคงยอดเดิมจนกดบันทึกซ้ำ — ตัดสินแล้ว 2026-08-21 ว่าไม่แก้) แล้วให้ผู้ใช้เขียนใน Remarks ว่ารับทราบหรือไม่ · ถ้าทีมตัดสินใจทดสอบจริง admin ต้องแก้ค่า 33.0000 แล้วคืนค่าทันที</t>
+          <t>[AI pre-run 09/09/2026] ทางเลือกตาม note ของเคส: ข้ามขั้นตอน 2-6 ทำเฉพาะขั้นตอนที่ 7 · ต้องให้คนอธิบายพฤติกรรม (ฟอร์มย่อยคำนวณใหม่ทันที แต่ตารางหลักคงยอดเดิมจนกดบันทึกซ้ำ — ตัดสินแล้ว 2026-08-21 ว่าไม่แก้) แล้วให้ผู้ใช้เขียนใน Remarks ว่ารับทราบหรือไม่ · ถ้าทีมตัดสินใจทดสอบจริง admin ต้องแก้ค่า 33.0000 แล้วคืนค่าทันที · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8633,12 +8649,12 @@
       </c>
       <c r="D9" s="55" t="inlineStr">
         <is>
-          <t>Evidence only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E9" s="55" t="inlineStr">
         <is>
-          <t>ข้อ 1-3 ตรงตาม Expected ทุกตัวอักษร · ข้อ 4 เป็นความเห็นของคนว่าอ่านแล้วเข้าใจไหม — AI ไม่ตัดสินแทน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยน Status เป็น Pass เอง</t>
+          <t>ข้อ 1-3 ตรงตาม Expected ทุกตัวอักษร · ข้อ 4 เป็นความเห็นของคนว่าอ่านแล้วเข้าใจไหม — AI ไม่ตัดสินแทน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยน Status เป็น Pass เอง · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
       <c r="F9" s="55" t="inlineStr">
@@ -8723,12 +8739,12 @@
       </c>
       <c r="D12" s="55" t="inlineStr">
         <is>
-          <t>Evidence only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E12" s="55" t="inlineStr">
         <is>
-          <t>ข้อ 1-2 ตรง Expected · ข้อ 3 (อ่านแล้วเข้าใจไหม) เป็นความเห็นของคน — ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass เอง</t>
+          <t>ข้อ 1-2 ตรง Expected · ข้อ 3 (อ่านแล้วเข้าใจไหม) เป็นความเห็นของคน — ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass เอง · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
       <c r="F12" s="55" t="inlineStr">
@@ -8963,12 +8979,12 @@
       </c>
       <c r="D20" s="55" t="inlineStr">
         <is>
-          <t>Evidence only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E20" s="55" t="inlineStr">
         <is>
-          <t>ข้อ 1-3 ตรง Expected (ระบบป้องกันตั้งแต่ปิดปุ่ม ไม่ต้องรอกดบันทึกแล้วปฏิเสธ — เข้มกว่าที่เคสคาด) · ข้อ 4 (ข้อความอ่านเข้าใจไหม) เป็นความเห็นของคน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass</t>
+          <t>ข้อ 1-3 ตรง Expected (ระบบป้องกันตั้งแต่ปิดปุ่ม ไม่ต้องรอกดบันทึกแล้วปฏิเสธ — เข้มกว่าที่เคสคาด) · ข้อ 4 (ข้อความอ่านเข้าใจไหม) เป็นความเห็นของคน ให้ผู้ทดสอบยืนยันแล้วเปลี่ยนเป็น Pass · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
       <c r="F20" s="55" t="inlineStr">
@@ -9413,12 +9429,12 @@
       </c>
       <c r="D35" s="55" t="inlineStr">
         <is>
-          <t>Evidence only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E35" s="55" t="inlineStr">
         <is>
-          <t>ทางเลือกตาม note ของเคส: ข้ามขั้นตอน 2-6 ทำเฉพาะขั้นตอนที่ 7 · ต้องให้คนอธิบายพฤติกรรม (ฟอร์มย่อยคำนวณใหม่ทันที แต่ตารางหลักคงยอดเดิมจนกดบันทึกซ้ำ — ตัดสินแล้ว 2026-08-21 ว่าไม่แก้) แล้วให้ผู้ใช้เขียนใน Remarks ว่ารับทราบหรือไม่ · ถ้าทีมตัดสินใจทดสอบจริง admin ต้องแก้ค่า 33.0000 แล้วคืนค่าทันที</t>
+          <t>ทางเลือกตาม note ของเคส: ข้ามขั้นตอน 2-6 ทำเฉพาะขั้นตอนที่ 7 · ต้องให้คนอธิบายพฤติกรรม (ฟอร์มย่อยคำนวณใหม่ทันที แต่ตารางหลักคงยอดเดิมจนกดบันทึกซ้ำ — ตัดสินแล้ว 2026-08-21 ว่าไม่แก้) แล้วให้ผู้ใช้เขียนใน Remarks ว่ารับทราบหรือไม่ · ถ้าทีมตัดสินใจทดสอบจริง admin ต้องแก้ค่า 33.0000 แล้วคืนค่าทันที · jakkaritw ตัดสิน 2026-09-09: อ่านเข้าใจ / ยอมรับได้ → Pass</t>
         </is>
       </c>
       <c r="F35" s="55" t="inlineStr">
@@ -10131,7 +10147,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
@@ -10141,7 +10157,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -10164,84 +10180,48 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UAT-15, UAT-42 ข้อ 2-4, UAT-44, UAT-45</t>
+          <t>UAT-05</t>
         </is>
       </c>
       <c r="B66" s="55" t="inlineStr">
         <is>
-          <t>ต้องเปิด toggle โหมด Admin — AI ถูกบล็อกไม่ให้ทำ (นิภาพร/วราพร ทำเอง)</t>
+          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วกด 'เข้าสู่ระบบใหม่' ด้วยบัญชีจริง (AI เฝ้าช่วงหมดเวลาให้แล้ว — ดู Remarks; ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว รับไว้แล้วใน UAT-04)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>UAT-05</t>
+          <t>UAT-49</t>
         </is>
       </c>
       <c r="B67" s="55" t="inlineStr">
         <is>
-          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง (ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว — ดู UAT-04)</t>
+          <t>เปิดอีเมล 'ได้รับการอนุมัติ' (03:22) บนมือถือ 1 ครั้ง และยืนยันว่าอยู่ Inbox ของพรทิพย์ — ข้ออื่นตรวจแล้ว</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>UAT-46, UAT-47, UAT-48, UAT-49, UAT-50</t>
+          <t>UAT-51</t>
         </is>
       </c>
       <c r="B68" s="55" t="inlineStr">
         <is>
-          <t>เปิดกล่องจดหมายจริงของลัดดาวัลย์ / นิภาพร / วราพร / พรทิพย์ เทียบเวลาและเนื้อหาอีเมล (เวลากดจริงจดไว้ใน Actual Result แล้ว)</t>
+          <t>ตาคนดูภาพที่ 1920×1080 และ 1366×768 (AI ถ่ายด้วย Edge + วัด contrast ให้) แล้วติ๊ก Pass ถ้าอ่านออกชัด</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UAT-08, UAT-11, UAT-19, UAT-29, UAT-54</t>
+          <t>UAT-29</t>
         </is>
       </c>
       <c r="B69" s="55" t="inlineStr">
         <is>
-          <t>เป็นความเห็นของคน (อ่านเข้าใจไหม / เหมาะสมไหม) — AI เก็บหลักฐานไว้ให้ ยังไม่ตัดสิน</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>UAT-51</t>
-        </is>
-      </c>
-      <c r="B70" s="55" t="inlineStr">
-        <is>
-          <t>สี/ความชัดที่ 1920×1080 และ 1366×768 บน Chrome + Edge — AI ถ่ายภาพที่ 1400×1000 เท่านั้น</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>UAT-52 ข้อ 2</t>
-        </is>
-      </c>
-      <c r="B71" s="55" t="inlineStr">
-        <is>
-          <t>ตัดสินว่าการที่ช่องวันเดินทางเปลี่ยน -3 เป็น 3 เงียบ ๆ (ไม่มีข้อความ) รับได้หรือเปิด defect</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>UAT-13</t>
-        </is>
-      </c>
-      <c r="B72" s="55" t="inlineStr">
-        <is>
-          <t>AI ให้ Fail: ระบบแจ้งข้อความตรวจสอบทีละ 1 ข้อ ไม่ใช่พร้อมกัน — ทีมตัดสินว่าเป็น defect หรือ by design แล้วใส่ Severity/Defect ID</t>
+          <t>ยืนยันว่าไฟล์แนบเปิด/ดาวน์โหลดได้จริงบน browser ของคุณ (AI จับการดาวน์โหลดและชื่อไฟล์ให้แล้ว)</t>
         </is>
       </c>
     </row>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -195,7 +195,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -272,23 +272,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -442,39 +430,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -849,7 +804,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Budget Web Application — UAT Test Cases</t>
         </is>
@@ -857,7 +812,7 @@
       <c r="B1" s="50" t="n"/>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="58" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Chememan PCL (CMAN)  |  User Acceptance Testing (UAT)  |  Data &amp; Analytics  |  Round 1  |  FY2027</t>
         </is>
@@ -866,7 +821,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="59" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Project Information</t>
         </is>
@@ -1026,7 +981,11 @@
           <t>Start Date</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -1034,7 +993,11 @@
           <t>Target End Date</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>13/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40.5" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -1049,7 +1012,7 @@
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="59" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>ข้อควรระวังก่อนเริ่มทดสอบ</t>
         </is>
@@ -1057,7 +1020,7 @@
       <c r="B21" s="50" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="60" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>ข้อ 1 — UAT รอบนี้รันบน **ระบบจริง (production)** ใช้ฐานข้อมูลจริง และส่งอีเมลจริงถึงเพื่อนร่วมงานจริง ไม่มีระบบทดลองแยกต่างหาก ทุกอย่างที่กรอก ส่ง อนุมัติ หรือลบ คือข้อมูลจริงของปีงบประมาณ 2027</t>
         </is>
@@ -1065,7 +1028,7 @@
       <c r="B22" s="50" t="n"/>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="60" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>ข้อ 2 — สถานะ `Approved` **ย้อนกลับไม่ได้ในระบบ** ต้องแก้ที่ฐานข้อมูลเท่านั้น อย่ากด Approve ขั้นที่ 3 (เคส UAT-40) จนกว่าทุกเคสที่มีเลข `ลำดับการรัน` น้อยกว่า 52 จะเสร็จครบ — UAT-40 อยู่ที่ลำดับการรันที่ 52 และเป็นเคสสุดท้ายของสายอนุมัติฝ่ายนั้น ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ</t>
         </is>
@@ -1073,7 +1036,7 @@
       <c r="B23" s="50" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="60" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>ข้อ 3 — อายุ session ระหว่าง UAT ตั้งไว้ที่ **1 ชั่วโมง** (ค่าจริงคือ 14 ชั่วโมง และจะคืนค่าเดิมหลังจบรอบ) ถ้าระบบให้ล็อกอินใหม่ระหว่างทดสอบ ถือว่าเป็นเรื่องปกติของรอบนี้</t>
         </is>
@@ -1081,7 +1044,7 @@
       <c r="B24" s="50" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="60" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>ข้อ 4 — **KNOWN ISSUE ที่ไม่ต้องแจ้งเป็น defect:** กล่อง “หมดเวลาการเข้าใช้งาน” ยังเขียนว่า 14 ชั่วโมง ทั้งที่ตั้งไว้ 1 ชั่วโมง — ตัดสินแล้วว่ายอมรับได้ (jakkaritw 2026-09-06)</t>
         </is>
@@ -1089,7 +1052,7 @@
       <c r="B25" s="50" t="n"/>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="60" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>ข้อ 5 — **เตรียมไฟล์แนบให้ฝ่าย Solution Delivery ไว้ก่อนเริ่มรอบ อย่างน้อย 1 ไฟล์** ในโฟลเดอร์ `เอกสาร ฝ่าย/Solution Delivery/2027/` (ให้ Pornthip อัปโหลดด้วยขั้นตอนเดียวกับเคส UAT-27 ซึ่งอัปโหลดให้ฝ่าย Data &amp; Analytic เท่านั้น ไม่มีเคสใดในรอบนี้อัปโหลดให้ฝ่าย Solution Delivery) — เคส UAT-31 ต้องมีไฟล์อยู่แล้วในโฟลเดอร์นี้ก่อนจึงจะทดสอบได้ ถ้าไม่เตรียมไว้ล่วงหน้า เคสนี้จะทำไม่ได้เมื่อถึงลำดับการรัน</t>
         </is>
@@ -1097,7 +1060,7 @@
       <c r="B26" s="50" t="n"/>
     </row>
     <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="60" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>ข้อ 6 — **ฝ่าย Solution Delivery จะถูกล็อกชั่วคราวระหว่างรอบ (ตั้งแต่เคส UAT-36 ถึง UAT-43):** ทันทีที่ Pornthip กด Submit ฝ่ายนี้ (เคส UAT-36) คุณ Suchanya ผู้กรอกตัวจริงของฝ่าย Solution Delivery จะแก้ไขงบของฝ่ายตัวเองไม่ได้เลยจนกว่าจะถูกตีกลับ — **ต้องแจ้ง Suchanya ล่วงหน้าก่อนเริ่มรอบ** ว่าจะมีช่วงล็อกสั้น ๆ นี้ · เคส UAT-43 จะอนุมัติฝ่ายนี้ที่ขั้นที่ 1 แล้วตีกลับคืนทันทีในเคสเดียวกัน เพื่อให้เธอกลับมาแก้ไขได้ก่อนจบรอบ ไม่ต้องรอจนครบทั้ง 54 เคส</t>
         </is>
@@ -1105,7 +1068,7 @@
       <c r="B27" s="50" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="59" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>วิธีใช้ไฟล์นี้ / How to use this workbook</t>
         </is>
@@ -1113,7 +1076,7 @@
       <c r="B29" s="50" t="n"/>
     </row>
     <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="60" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>1.  ไปที่แท็บ “2. Test Cases” แล้วทดสอบ **เรียงตามคอลัมน์ `ลำดับการรัน` (Run Order) จาก 1 ถึง 54** — **ไม่ใช่เรียงตามคอลัมน์ Wave** · คอลัมน์ Wave ยังเป็นชื่อกลุ่มของเคสและใช้กรองดูได้เหมือนเดิม แต่ลำดับที่ต้องลงมือทำจริงคือคอลัมน์ `ลำดับการรัน` เพราะบางเคสต้องทำข้ามระลอก (เช่น UAT-53 และ UAT-54 อยู่ระลอก W8 แต่ต้องทำก่อนระลอก W5 · UAT-03 อยู่ระลอก W1 แต่ต้องทำหลัง UAT-32)</t>
         </is>
@@ -1121,7 +1084,7 @@
       <c r="B30" s="50" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="60" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>2.  วิธีเรียง: คลิกลูกศรกรองบนหัวคอลัมน์ `ลำดับการรัน` แล้วเลือก “Sort Smallest to Largest” จากนั้นไล่ทำจากบนลงล่าง</t>
         </is>
@@ -1129,7 +1092,7 @@
       <c r="B31" s="50" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="60" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>3.  ⚠ **อย่ากด `Approve` ขั้นที่ 3 ในเคส UAT-40 (ลำดับการรันที่ 52) จนกว่าทุกเคสที่มีลำดับการรันน้อยกว่า 52 จะเสร็จครบ** เพราะสถานะ `Approved` ย้อนกลับไม่ได้ ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ และต้องให้ทีม IT แก้ที่ฐานข้อมูลเท่านั้น</t>
         </is>
@@ -1137,7 +1100,7 @@
       <c r="B32" s="50" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="60" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>4.  ทดสอบทีละเคสตาม “Test Steps” แล้วเทียบผลกับ “Expected Result”</t>
         </is>
@@ -1145,7 +1108,7 @@
       <c r="B33" s="50" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="60" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>5.  **อ่าน “Expected Result” ให้จบทุกข้อก่อนตัดสินผล** — หลายเคสเป็นเคสรวม (merged) คือ 1 แถว แต่มีหลายข้อที่ต้องตรวจ ถ้าข้อใดข้อหนึ่งไม่ผ่าน ให้ทั้งแถวเป็น Fail แล้วระบุในช่อง Actual Result ว่าข้อไหนไม่ผ่าน</t>
         </is>
@@ -1153,7 +1116,7 @@
       <c r="B34" s="50" t="n"/>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>6.  **ผู้ทดสอบดูแลช่องพื้นหลังสีเหลือง 7 ช่องนี้:** Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks · ช่อง `Tester` กรอกชื่อไว้ล่วงหน้าแล้วตามแผนคนจาก actor map ก่อนเริ่มรอบ (ตัวหนังสือสีม่วงเหมือนช่องเนื้อหาเคสอื่น ๆ) ถ้าคนที่ลงมือทดสอบจริงไม่ตรงกับชื่อที่กรอกไว้ ให้แก้ชื่อในช่องนี้ให้ตรงกับคนที่ทำจริง · อีก 6 ช่องที่เหลือยังว่างอยู่ ให้ผู้ทดสอบกรอกเองระหว่างทดสอบตามปกติ</t>
         </is>
@@ -1161,7 +1124,7 @@
       <c r="B35" s="50" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="60" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>7.  เลือก Status จาก dropdown: Pass / Fail / Blocked / N/A · **ช่องที่ยังว่าง = `Not Run` (ยังไม่ได้ทดสอบ) ซึ่งเป็นค่าเริ่มต้น** ไม่ต้องพิมพ์คำว่า Not Run เอง — แท็บ “3. Summary” นับช่องว่างเป็น Not Run ให้อัตโนมัติ</t>
         </is>
@@ -1169,7 +1132,7 @@
       <c r="B36" s="50" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="60" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>8.  ถ้า Fail ให้ระบุ Severity บันทึกรายละเอียดใน “Actual Result” แล้ว **เปิดแถวใหม่ในแท็บ “4. Defects”** จากนั้นนำเลข Defect ID (D-001, D-002, …) มาใส่ในคอลัมน์ Defect ID ของแถวนี้ · ช่อง Severity ของแถว defect ใช้ **ชุดค่าเดียวกัน** (Critical / High / Medium / Low) ยกค่าจากแถวเคสไปใส่ได้ตรง ๆ ไม่ต้องแปลงเป็นคำอื่น</t>
         </is>
@@ -1177,7 +1140,7 @@
       <c r="B37" s="50" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="60" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>9.  แท็บ “3. Summary” สรุปผลอัตโนมัติ (จำนวน / อัตราผ่าน / แยกตาม Module, Wave และฝ่าย) ไม่ต้องกรอกเอง</t>
         </is>
@@ -1185,7 +1148,7 @@
       <c r="B38" s="50" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="60" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>10. **ข้อยกเว้นเดียวของกติกา “กรอกเฉพาะช่องสีเหลือง” คือคอลัมน์ `PIC`** ซึ่งเป็นช่องสีขาว และคนที่กรอกไม่ใช่ผู้ทดสอบ แต่เป็น **Test Lead** ที่กรอกชื่อผู้รับผิดชอบรายเคสไว้ **ก่อน** เริ่มรอบทดสอบ (ใช้เมื่อ Test Lead ต้องการมอบหมายผู้รับผิดชอบเพิ่มเติม นอกเหนือจากชื่อที่กรอกไว้แล้วในช่อง `Tester`) · ระหว่างทดสอบ ผู้ทดสอบไม่ต้องแตะคอลัมน์นี้</t>
         </is>
@@ -1193,7 +1156,7 @@
       <c r="B39" s="50" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="60" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>11. ตัวหนังสือ **สีม่วง** คือข้อความที่ AI ร่างไว้ให้ ยังไม่ผ่านการตรวจจากผู้ทดสอบ ถ้าพบว่าไม่ตรงกับระบบจริง แก้ได้เลยแล้วบันทึกไว้ในช่อง Remarks · **ยกเว้นคอลัมน์ `Wave` และ `ลำดับการรัน` ซึ่งพิมพ์ด้วยตัวสีดำ** เพราะเป็นค่าที่โปรแกรมคำนวณมาให้ ไม่ใช่ข้อความที่ AI ร่าง — ห้ามแก้ ถ้าเห็นว่าลำดับผิดให้แจ้ง Test Lead แทน</t>
         </is>
@@ -1201,7 +1164,7 @@
       <c r="B40" s="50" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>12. อ่านเอกสารประกอบ `UAT_Test_Script.md` (ภาษาไทย) ก่อนเริ่ม — อธิบายลำดับการรัน บทบาทของแต่ละคน และสิ่งที่ตัดออกจากรอบนี้โดยตั้งใจ</t>
         </is>
@@ -1209,7 +1172,7 @@
       <c r="B41" s="50" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="59" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>ตัวอย่างการกรอก 1 แถว (worked example)</t>
         </is>
@@ -1217,7 +1180,7 @@
       <c r="B43" s="50" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="60" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>เคสตัวอย่าง UAT-09 (ระลอก W2) — “กรอกยอดแล้วคลิกออกจากช่อง = บันทึกอัตโนมัติ · refresh หน้าแล้วค่ายังอยู่”</t>
         </is>
@@ -1225,7 +1188,7 @@
       <c r="B44" s="50" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>ถ้าผ่าน → Actual Result = “กรอก 100 ที่เดือน ม.ค. คลิกออกจากช่อง แล้ว refresh หน้า ค่ายังเป็น 100” · Status = `Pass` · Severity = `-` · Defect ID = (เว้นว่าง) · Tester = `Pornthip` · Test Date = วันที่ทดสอบ · Remarks = (เว้นว่าง)</t>
         </is>
@@ -1233,7 +1196,7 @@
       <c r="B45" s="50" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="60" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>ถ้าไม่ผ่าน → Actual Result = “refresh แล้วค่าหาย กลับเป็นช่องว่าง” · Status = `Fail` · Severity = `High` · Defect ID = `D-001` แล้วไปเปิดแถว D-001 ในแท็บ “4. Defects” กรอกหัวข้อ ผู้แจ้ง วันที่ และสถานะ `Open`</t>
         </is>
@@ -1241,7 +1204,7 @@
       <c r="B46" s="50" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="60" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>ถ้าทดสอบไม่ได้เพราะติดเคสอื่นหรือข้อมูลยังไม่พร้อม → Status = `Blocked` และเขียนเหตุผลใน Remarks (อย่าปล่อยเป็น `Not Run` ถ้าพยายามทดสอบแล้ว)</t>
         </is>
@@ -1249,7 +1212,7 @@
       <c r="B47" s="50" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="59" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Legend / คำอธิบายสี &amp; สถานะ</t>
         </is>
@@ -1321,7 +1284,7 @@
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="61" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Severity: Critical = ระบบใช้งานไม่ได้ / ข้อมูลผิดพลาดร้ายแรง  |  High = ฟังก์ชันหลักเสีย  |  Medium = มีทางเลี่ยง  |  Low = ปัญหาเล็กน้อย / UI  ·  ชุดค่านี้ใช้เหมือนกันทั้งแท็บ “2. Test Cases” และแท็บ “4. Defects” จึงยกค่าจากแถวเคสไปใส่แถว defect ได้ตรง ๆ ไม่ต้องแปลง (ค่า `-` มีเฉพาะแท็บ “2. Test Cases” ใช้เมื่อเคสนั้นไม่ Fail)</t>
         </is>
@@ -1397,7 +1360,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Budget Web App — UAT Test Cases (Round 1 · FY2027 · production)</t>
         </is>
@@ -6808,7 +6771,7 @@
   </cols>
   <sheetData>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="B2" s="63" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>UAT Test Execution — Summary  ·  Round 1  ·  FY2027</t>
         </is>
@@ -6829,7 +6792,7 @@
       <c r="P2" s="50" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="64" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>สรุปผลอัตโนมัติจากแท็บ “2. Test Cases” (ไม่ต้องกรอกเอง) · ทุกสูตรนับช่วงแถวจริง 3–56</t>
         </is>
@@ -6955,7 +6918,7 @@
       <c r="E12" s="52" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="65" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Module</t>
         </is>
@@ -6963,7 +6926,7 @@
       <c r="C14" s="50" t="n"/>
       <c r="D14" s="50" t="n"/>
       <c r="E14" s="50" t="n"/>
-      <c r="G14" s="65" t="inlineStr">
+      <c r="G14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Wave</t>
         </is>
@@ -6972,7 +6935,7 @@
       <c r="I14" s="50" t="n"/>
       <c r="J14" s="50" t="n"/>
       <c r="K14" s="50" t="n"/>
-      <c r="M14" s="65" t="inlineStr">
+      <c r="M14" s="42" t="inlineStr">
         <is>
           <t>Breakdown by Department</t>
         </is>
@@ -7499,7 +7462,7 @@
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="B26" s="66" t="inlineStr">
+      <c r="B26" s="48" t="inlineStr">
         <is>
           <t>หมายเหตุ: ตัวเลขอัปเดตอัตโนมัติเมื่อกรอกคอลัมน์ Status ในแท็บ “2. Test Cases” · ช่วงข้อมูลจริง = แถวที่ 3 ถึง 56 · ไฟล์นี้ไม่มีแถวตัวอย่าง (ไม่มี TC-EX) · ช่อง Total ของทั้ง 3 ตารางต้องเท่ากับ Total test cases ด้านบน · แถว Not Run คำนวณจาก “Total ลบด้วย Pass + Fail + Blocked + N/A” จึงนับช่อง Status ที่ยังว่างให้เป็น Not Run โดยอัตโนมัติ (ไม่ต้องพิมพ์คำว่า Not Run เอง) และทำให้ห้าแถวบนรวมกันได้เท่ากับ Total เสมอ</t>
         </is>
@@ -7565,7 +7528,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="62" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Budget Web App — UAT Defect Log  ·  เปิดแถวใหม่ทุกครั้งที่มีเคส Status = Fail แล้วนำเลข Defect ID ไปใส่ในคอลัมน์ Defect ID ของแท็บ “2. Test Cases”</t>
         </is>
@@ -8411,7 +8374,7 @@
       <c r="M42" s="21" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="A44" s="49" t="inlineStr">
         <is>
           <t>Severity ของ defect ใช้ **ชุดค่าเดียวกับคอลัมน์ Severity ในแท็บ “2. Test Cases”** ยกมาใส่ได้ตรง ๆ ไม่ต้องแปลงค่า: Critical = ระบบใช้งานไม่ได้ / ข้อมูลเงินผิดพลาดร้ายแรง · High = ฟังก์ชันหลักเสีย · Medium = เสียแต่มีทางเลี่ยง · Low = ปัญหาเล็กน้อยหรือ UI (ไม่มีค่า `-` ในแท็บนี้ เพราะแถว defect เกิดขึ้นเฉพาะตอนมีเคส Fail)  ·  Status: Open → In Progress → Fixed → Retested → Closed (หรือ Wont Fix ถ้าตัดสินว่าไม่แก้)</t>
         </is>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -195,7 +195,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -272,11 +272,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -430,6 +442,39 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -804,7 +849,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="57" t="inlineStr">
         <is>
           <t>Budget Web Application — UAT Test Cases</t>
         </is>
@@ -812,7 +857,7 @@
       <c r="B1" s="50" t="n"/>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>Chememan PCL (CMAN)  |  User Acceptance Testing (UAT)  |  Data &amp; Analytics  |  Round 1  |  FY2027</t>
         </is>
@@ -821,7 +866,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>Project Information</t>
         </is>
@@ -1012,7 +1057,7 @@
       </c>
     </row>
     <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="59" t="inlineStr">
         <is>
           <t>ข้อควรระวังก่อนเริ่มทดสอบ</t>
         </is>
@@ -1020,7 +1065,7 @@
       <c r="B21" s="50" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t>ข้อ 1 — UAT รอบนี้รันบน **ระบบจริง (production)** ใช้ฐานข้อมูลจริง และส่งอีเมลจริงถึงเพื่อนร่วมงานจริง ไม่มีระบบทดลองแยกต่างหาก ทุกอย่างที่กรอก ส่ง อนุมัติ หรือลบ คือข้อมูลจริงของปีงบประมาณ 2027</t>
         </is>
@@ -1028,7 +1073,7 @@
       <c r="B22" s="50" t="n"/>
     </row>
     <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>ข้อ 2 — สถานะ `Approved` **ย้อนกลับไม่ได้ในระบบ** ต้องแก้ที่ฐานข้อมูลเท่านั้น อย่ากด Approve ขั้นที่ 3 (เคส UAT-40) จนกว่าทุกเคสที่มีเลข `ลำดับการรัน` น้อยกว่า 52 จะเสร็จครบ — UAT-40 อยู่ที่ลำดับการรันที่ 52 และเป็นเคสสุดท้ายของสายอนุมัติฝ่ายนั้น ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ</t>
         </is>
@@ -1036,7 +1081,7 @@
       <c r="B23" s="50" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="60" t="inlineStr">
         <is>
           <t>ข้อ 3 — อายุ session ระหว่าง UAT ตั้งไว้ที่ **1 ชั่วโมง** (ค่าจริงคือ 14 ชั่วโมง และจะคืนค่าเดิมหลังจบรอบ) ถ้าระบบให้ล็อกอินใหม่ระหว่างทดสอบ ถือว่าเป็นเรื่องปกติของรอบนี้</t>
         </is>
@@ -1044,7 +1089,7 @@
       <c r="B24" s="50" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="60" t="inlineStr">
         <is>
           <t>ข้อ 4 — **KNOWN ISSUE ที่ไม่ต้องแจ้งเป็น defect:** กล่อง “หมดเวลาการเข้าใช้งาน” ยังเขียนว่า 14 ชั่วโมง ทั้งที่ตั้งไว้ 1 ชั่วโมง — ตัดสินแล้วว่ายอมรับได้ (jakkaritw 2026-09-06)</t>
         </is>
@@ -1052,7 +1097,7 @@
       <c r="B25" s="50" t="n"/>
     </row>
     <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="60" t="inlineStr">
         <is>
           <t>ข้อ 5 — **เตรียมไฟล์แนบให้ฝ่าย Solution Delivery ไว้ก่อนเริ่มรอบ อย่างน้อย 1 ไฟล์** ในโฟลเดอร์ `เอกสาร ฝ่าย/Solution Delivery/2027/` (ให้ Pornthip อัปโหลดด้วยขั้นตอนเดียวกับเคส UAT-27 ซึ่งอัปโหลดให้ฝ่าย Data &amp; Analytic เท่านั้น ไม่มีเคสใดในรอบนี้อัปโหลดให้ฝ่าย Solution Delivery) — เคส UAT-31 ต้องมีไฟล์อยู่แล้วในโฟลเดอร์นี้ก่อนจึงจะทดสอบได้ ถ้าไม่เตรียมไว้ล่วงหน้า เคสนี้จะทำไม่ได้เมื่อถึงลำดับการรัน</t>
         </is>
@@ -1060,7 +1105,7 @@
       <c r="B26" s="50" t="n"/>
     </row>
     <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="60" t="inlineStr">
         <is>
           <t>ข้อ 6 — **ฝ่าย Solution Delivery จะถูกล็อกชั่วคราวระหว่างรอบ (ตั้งแต่เคส UAT-36 ถึง UAT-43):** ทันทีที่ Pornthip กด Submit ฝ่ายนี้ (เคส UAT-36) คุณ Suchanya ผู้กรอกตัวจริงของฝ่าย Solution Delivery จะแก้ไขงบของฝ่ายตัวเองไม่ได้เลยจนกว่าจะถูกตีกลับ — **ต้องแจ้ง Suchanya ล่วงหน้าก่อนเริ่มรอบ** ว่าจะมีช่วงล็อกสั้น ๆ นี้ · เคส UAT-43 จะอนุมัติฝ่ายนี้ที่ขั้นที่ 1 แล้วตีกลับคืนทันทีในเคสเดียวกัน เพื่อให้เธอกลับมาแก้ไขได้ก่อนจบรอบ ไม่ต้องรอจนครบทั้ง 54 เคส</t>
         </is>
@@ -1068,7 +1113,7 @@
       <c r="B27" s="50" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="59" t="inlineStr">
         <is>
           <t>วิธีใช้ไฟล์นี้ / How to use this workbook</t>
         </is>
@@ -1076,7 +1121,7 @@
       <c r="B29" s="50" t="n"/>
     </row>
     <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>1.  ไปที่แท็บ “2. Test Cases” แล้วทดสอบ **เรียงตามคอลัมน์ `ลำดับการรัน` (Run Order) จาก 1 ถึง 54** — **ไม่ใช่เรียงตามคอลัมน์ Wave** · คอลัมน์ Wave ยังเป็นชื่อกลุ่มของเคสและใช้กรองดูได้เหมือนเดิม แต่ลำดับที่ต้องลงมือทำจริงคือคอลัมน์ `ลำดับการรัน` เพราะบางเคสต้องทำข้ามระลอก (เช่น UAT-53 และ UAT-54 อยู่ระลอก W8 แต่ต้องทำก่อนระลอก W5 · UAT-03 อยู่ระลอก W1 แต่ต้องทำหลัง UAT-32)</t>
         </is>
@@ -1084,7 +1129,7 @@
       <c r="B30" s="50" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>2.  วิธีเรียง: คลิกลูกศรกรองบนหัวคอลัมน์ `ลำดับการรัน` แล้วเลือก “Sort Smallest to Largest” จากนั้นไล่ทำจากบนลงล่าง</t>
         </is>
@@ -1092,7 +1137,7 @@
       <c r="B31" s="50" t="n"/>
     </row>
     <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="60" t="inlineStr">
         <is>
           <t>3.  ⚠ **อย่ากด `Approve` ขั้นที่ 3 ในเคส UAT-40 (ลำดับการรันที่ 52) จนกว่าทุกเคสที่มีลำดับการรันน้อยกว่า 52 จะเสร็จครบ** เพราะสถานะ `Approved` ย้อนกลับไม่ได้ ถ้ากดก่อน เคส UAT-41 · UAT-42 (ข้อ 5) · UAT-44 · UAT-47 · UAT-52 (ข้อ 1) จะทดสอบไม่ได้อีกเลยตลอดรอบ และต้องให้ทีม IT แก้ที่ฐานข้อมูลเท่านั้น</t>
         </is>
@@ -1100,7 +1145,7 @@
       <c r="B32" s="50" t="n"/>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="60" t="inlineStr">
         <is>
           <t>4.  ทดสอบทีละเคสตาม “Test Steps” แล้วเทียบผลกับ “Expected Result”</t>
         </is>
@@ -1108,7 +1153,7 @@
       <c r="B33" s="50" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>5.  **อ่าน “Expected Result” ให้จบทุกข้อก่อนตัดสินผล** — หลายเคสเป็นเคสรวม (merged) คือ 1 แถว แต่มีหลายข้อที่ต้องตรวจ ถ้าข้อใดข้อหนึ่งไม่ผ่าน ให้ทั้งแถวเป็น Fail แล้วระบุในช่อง Actual Result ว่าข้อไหนไม่ผ่าน</t>
         </is>
@@ -1116,7 +1161,7 @@
       <c r="B34" s="50" t="n"/>
     </row>
     <row r="35" ht="56" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>6.  **ผู้ทดสอบดูแลช่องพื้นหลังสีเหลือง 7 ช่องนี้:** Actual Result, Status, Severity, Defect ID, Tester, Test Date, Remarks · ช่อง `Tester` กรอกชื่อไว้ล่วงหน้าแล้วตามแผนคนจาก actor map ก่อนเริ่มรอบ (ตัวหนังสือสีม่วงเหมือนช่องเนื้อหาเคสอื่น ๆ) ถ้าคนที่ลงมือทดสอบจริงไม่ตรงกับชื่อที่กรอกไว้ ให้แก้ชื่อในช่องนี้ให้ตรงกับคนที่ทำจริง · อีก 6 ช่องที่เหลือยังว่างอยู่ ให้ผู้ทดสอบกรอกเองระหว่างทดสอบตามปกติ</t>
         </is>
@@ -1124,7 +1169,7 @@
       <c r="B35" s="50" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="60" t="inlineStr">
         <is>
           <t>7.  เลือก Status จาก dropdown: Pass / Fail / Blocked / N/A · **ช่องที่ยังว่าง = `Not Run` (ยังไม่ได้ทดสอบ) ซึ่งเป็นค่าเริ่มต้น** ไม่ต้องพิมพ์คำว่า Not Run เอง — แท็บ “3. Summary” นับช่องว่างเป็น Not Run ให้อัตโนมัติ</t>
         </is>
@@ -1132,7 +1177,7 @@
       <c r="B36" s="50" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="60" t="inlineStr">
         <is>
           <t>8.  ถ้า Fail ให้ระบุ Severity บันทึกรายละเอียดใน “Actual Result” แล้ว **เปิดแถวใหม่ในแท็บ “4. Defects”** จากนั้นนำเลข Defect ID (D-001, D-002, …) มาใส่ในคอลัมน์ Defect ID ของแถวนี้ · ช่อง Severity ของแถว defect ใช้ **ชุดค่าเดียวกัน** (Critical / High / Medium / Low) ยกค่าจากแถวเคสไปใส่ได้ตรง ๆ ไม่ต้องแปลงเป็นคำอื่น</t>
         </is>
@@ -1140,7 +1185,7 @@
       <c r="B37" s="50" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="60" t="inlineStr">
         <is>
           <t>9.  แท็บ “3. Summary” สรุปผลอัตโนมัติ (จำนวน / อัตราผ่าน / แยกตาม Module, Wave และฝ่าย) ไม่ต้องกรอกเอง</t>
         </is>
@@ -1148,7 +1193,7 @@
       <c r="B38" s="50" t="n"/>
     </row>
     <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="60" t="inlineStr">
         <is>
           <t>10. **ข้อยกเว้นเดียวของกติกา “กรอกเฉพาะช่องสีเหลือง” คือคอลัมน์ `PIC`** ซึ่งเป็นช่องสีขาว และคนที่กรอกไม่ใช่ผู้ทดสอบ แต่เป็น **Test Lead** ที่กรอกชื่อผู้รับผิดชอบรายเคสไว้ **ก่อน** เริ่มรอบทดสอบ (ใช้เมื่อ Test Lead ต้องการมอบหมายผู้รับผิดชอบเพิ่มเติม นอกเหนือจากชื่อที่กรอกไว้แล้วในช่อง `Tester`) · ระหว่างทดสอบ ผู้ทดสอบไม่ต้องแตะคอลัมน์นี้</t>
         </is>
@@ -1156,7 +1201,7 @@
       <c r="B39" s="50" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>11. ตัวหนังสือ **สีม่วง** คือข้อความที่ AI ร่างไว้ให้ ยังไม่ผ่านการตรวจจากผู้ทดสอบ ถ้าพบว่าไม่ตรงกับระบบจริง แก้ได้เลยแล้วบันทึกไว้ในช่อง Remarks · **ยกเว้นคอลัมน์ `Wave` และ `ลำดับการรัน` ซึ่งพิมพ์ด้วยตัวสีดำ** เพราะเป็นค่าที่โปรแกรมคำนวณมาให้ ไม่ใช่ข้อความที่ AI ร่าง — ห้ามแก้ ถ้าเห็นว่าลำดับผิดให้แจ้ง Test Lead แทน</t>
         </is>
@@ -1164,7 +1209,7 @@
       <c r="B40" s="50" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="60" t="inlineStr">
         <is>
           <t>12. อ่านเอกสารประกอบ `UAT_Test_Script.md` (ภาษาไทย) ก่อนเริ่ม — อธิบายลำดับการรัน บทบาทของแต่ละคน และสิ่งที่ตัดออกจากรอบนี้โดยตั้งใจ</t>
         </is>
@@ -1172,7 +1217,7 @@
       <c r="B41" s="50" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="59" t="inlineStr">
         <is>
           <t>ตัวอย่างการกรอก 1 แถว (worked example)</t>
         </is>
@@ -1180,7 +1225,7 @@
       <c r="B43" s="50" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="60" t="inlineStr">
         <is>
           <t>เคสตัวอย่าง UAT-09 (ระลอก W2) — “กรอกยอดแล้วคลิกออกจากช่อง = บันทึกอัตโนมัติ · refresh หน้าแล้วค่ายังอยู่”</t>
         </is>
@@ -1188,7 +1233,7 @@
       <c r="B44" s="50" t="n"/>
     </row>
     <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>ถ้าผ่าน → Actual Result = “กรอก 100 ที่เดือน ม.ค. คลิกออกจากช่อง แล้ว refresh หน้า ค่ายังเป็น 100” · Status = `Pass` · Severity = `-` · Defect ID = (เว้นว่าง) · Tester = `Pornthip` · Test Date = วันที่ทดสอบ · Remarks = (เว้นว่าง)</t>
         </is>
@@ -1196,7 +1241,7 @@
       <c r="B45" s="50" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>ถ้าไม่ผ่าน → Actual Result = “refresh แล้วค่าหาย กลับเป็นช่องว่าง” · Status = `Fail` · Severity = `High` · Defect ID = `D-001` แล้วไปเปิดแถว D-001 ในแท็บ “4. Defects” กรอกหัวข้อ ผู้แจ้ง วันที่ และสถานะ `Open`</t>
         </is>
@@ -1204,7 +1249,7 @@
       <c r="B46" s="50" t="n"/>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="60" t="inlineStr">
         <is>
           <t>ถ้าทดสอบไม่ได้เพราะติดเคสอื่นหรือข้อมูลยังไม่พร้อม → Status = `Blocked` และเขียนเหตุผลใน Remarks (อย่าปล่อยเป็น `Not Run` ถ้าพยายามทดสอบแล้ว)</t>
         </is>
@@ -1212,7 +1257,7 @@
       <c r="B47" s="50" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="59" t="inlineStr">
         <is>
           <t>Legend / คำอธิบายสี &amp; สถานะ</t>
         </is>
@@ -1284,7 +1329,7 @@
       </c>
     </row>
     <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="A58" s="61" t="inlineStr">
         <is>
           <t>Severity: Critical = ระบบใช้งานไม่ได้ / ข้อมูลผิดพลาดร้ายแรง  |  High = ฟังก์ชันหลักเสีย  |  Medium = มีทางเลี่ยง  |  Low = ปัญหาเล็กน้อย / UI  ·  ชุดค่านี้ใช้เหมือนกันทั้งแท็บ “2. Test Cases” และแท็บ “4. Defects” จึงยกค่าจากแถวเคสไปใส่แถว defect ได้ตรง ๆ ไม่ต้องแปลง (ค่า `-` มีเฉพาะแท็บ “2. Test Cases” ใช้เมื่อเคสนั้นไม่ Fail)</t>
         </is>
@@ -1360,7 +1405,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Budget Web App — UAT Test Cases (Round 1 · FY2027 · production)</t>
         </is>
@@ -1959,10 +2004,14 @@
       </c>
       <c r="N7" s="51" t="inlineStr">
         <is>
-          <t>AI ไม่ได้ทำ: ต้องทิ้งหน้าจอไว้ครบ 1 ชั่วโมงแล้วล็อกอินใหม่ด้วยบัญชีจริง · หลักฐานข้างเคียงจากรอบนี้: เวลา ~02:02 session ของ AI หมดอายุจริงหลังล็อกอิน ~1 ชั่วโมง (แอป redirect ไป login.microsoftonline.com) และกล่อง 'หมดเวลาการเข้าใช้งาน' ปรากฏใน UAT-04 พร้อมปุ่มทางออกเดียว 'เข้าสู่ระบบใหม่'</t>
-        </is>
-      </c>
-      <c r="O7" s="21" t="n"/>
+          <t>ข้อ 1-2: ทีมพัฒนายืนยันอายุ session = 1 ชั่วโมงในรอบ UAT · ล็อกอิน 16:22 (jakkaritw สวมสิทธิ์ Pornthip) เปิดฝ่าย Solution Delivery Year 2026 URL /?dept=Solution%20Delivery&amp;year=2026 · ข้อ 3-4: ช่อง 10IT012000 / GL 6210900060 / ก.พ. ค่าเดิม 0 (ยอดปี 10,000.00) พิมพ์ 200 เมื่อ 17:08 โดยไม่คลิกออก · ข้อ 5: เฝ้าทุก 1 นาที — /me ตอบ 200 จนถึง 17:22:06 และตอบ redirect (session ตาย) ที่ 17:23:06 = อายุจริง ~61 นาทีนับจาก 16:22 · ระหว่างที่ยังไม่บันทึก หน้าจอไม่เด้งกล่องเอง ค่า 200 ยังค้างในช่อง · ข้อ 6-7: คลิกออกจากช่อง 17:23:11 → ระบบไม่บันทึก ขึ้นกล่องทันที หัวข้อ 'หมดเวลาการเข้าใช้งาน' ข้อความ (คำต่อคำ) 'หมดเวลาการเข้าใช้งาน (ระบบให้ล็อกอินได้ครั้งละ 14 ชั่วโมง) กรุณา login ใหม่อีกครั้ง' ปุ่มเดียว 'เข้าสู่ระบบใหม่' · ตัวเลข 200 ที่พิมพ์ยังแสดงอยู่บนจอด้านหลังกล่อง · ข้อ 8: กด Esc → กล่องยังอยู่ · คลิกนอกกล่อง (พื้นหลังมืด) → กล่องยังอยู่ · ไม่มีปุ่มปิด/✕ · ข้อ 9: กด 'เข้าสู่ระบบใหม่' → ไปหน้า login.microsoftonline.com โดย state=redir ชี้กลับมาที่ URL เดิม (/?dept=Solution%20Delivery&amp;year=2026) · เบราว์เซอร์ทดสอบยังถือ cookie ของ Microsoft อยู่ จึงล็อกอินผ่านอัตโนมัติ (SSO) ไม่ต้องกรอกรหัส · ข้อ 10: กลับมาที่ฝ่าย Solution Delivery ปี Year 2026 URL เดิมทันที /me = 200 · ช่อง ก.พ. ของ 6210900060 = 0 (ค่า 200 ไม่ถูกบันทึก) ยอดปี 10,000.00 เท่าเดิม</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P7" s="22" t="n"/>
       <c r="Q7" s="22" t="n"/>
       <c r="R7" s="23" t="inlineStr">
@@ -1970,10 +2019,12 @@
           <t>ไม่ระบุชื่อในเคส (แนะนำ Pornthip เพราะฝ่ายเธอยังแก้ไขได้)</t>
         </is>
       </c>
-      <c r="S7" s="24" t="n"/>
+      <c r="S7" s="24" t="n">
+        <v>46274</v>
+      </c>
       <c r="T7" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Deferred to human · ข้อควรรู้ก่อนทำ: ข้อความในกล่องเขียนว่า '14 ชั่วโมง' ตายตัว (ดู UAT-04) ถ้าเห็นคำนี้ตอนหมดเวลาที่ 1 ชั่วโมง ไม่ใช่ความผิดของผู้ทดสอบ ให้จดเป็นข้อสังเกต · หลังจบรอบต้องคืนอายุ session เป็น 14 ชั่วโมง</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ (1-4 ตาม Expected) · ข้อสังเกตที่รับไว้แล้วใน UAT-04: ข้อความในกล่องบอก '14 ชั่วโมง' ตายตัว ทั้งที่รอบนี้หมดอายุจริงที่ ~1 ชั่วโมง · ข้อ 9 ในเครื่องผู้ทดสอบจริงอาจเห็นหน้ากรอกรหัสของ Microsoft แทน SSO อัตโนมัติ — ปลายทางเดียวกัน · ข้อ 11 (คืนอายุ session เป็น 14 ชั่วโมง) อยู่ใน tracker uat-post-run-reset</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4359,7 @@
       </c>
       <c r="N31" s="51" t="inlineStr">
         <is>
-          <t>กดปุ่ม 'เปิด/ดาวน์โหลด' ที่แถว UAT-27-budget-support.pdf → กล่องไฟล์แนบยังเปิดค้างอยู่ที่หน้าเดิม รายการไฟล์ครบ ไม่มีแถบแดง · กลไกจากโค้ด (AttachmentsModal.tsx:76): ระบบขอลิงก์ดาวน์โหลดจาก /attachments/download-url แล้วเรียก window.open(url, '_blank', 'noopener,noreferrer') = เปิดแท็บใหม่ · ในเบราว์เซอร์อัตโนมัติ (headless) ไม่พบแท็บใหม่และไม่พบไฟล์ที่ดาวน์โหลด จึงยืนยันเรื่องแท็บใหม่/ไฟล์ที่ได้ไม่ได้</t>
+          <t>อัปโหลด 2 ไฟล์เข้าโฟลเดอร์ 'เอกสาร ฝ่าย/Solution Delivery/2027/': UAT-27-budget-support.pdf (303 B ตรง md5 f2c55b95…) และ 'เอกสารประกอบงบ UAT.xlsx' (ชื่อไทย) แสดงในตารางครบ ชื่อไทยไม่เพี้ยน · กด 'เปิด/ดาวน์โหลด' ทั้ง 2 แถว → เบราว์เซอร์เปิดแท็บใหม่ (open_pages เพิ่มขึ้น 1 แท็บ) ตามโค้ด window.open(url,'_blank') · กล่องไฟล์แนบยังเปิดค้างที่หน้าเดิม ไม่มีแถบสีแดง · จากนั้นลบทั้ง 2 ไฟล์ → โฟลเดอร์กลับเป็น 'ยังไม่มีไฟล์ในโฟลเดอร์นี้' (0 ไฟล์) คืนสถานะตั้งต้นเรียบร้อย</t>
         </is>
       </c>
       <c r="O31" s="21" t="n"/>
@@ -4324,7 +4375,7 @@
       </c>
       <c r="T31" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only · ต้องให้คนกดในเบราว์เซอร์จริง: ดูว่าเปิดแท็บใหม่หรือไฟล์ลง Downloads, เปิดไฟล์ได้ครบ, ชื่อไทยไม่เพี้ยน · ส่วนที่ automation ยืนยันได้ (หน้าเดิมไม่หาย ไม่มี error) ผ่าน · หมายเหตุ: ระหว่างทดสอบ UAT-27 เกิดการกดปุ่มดาวน์โหลดโดยไม่ตั้งใจ 1 ครั้ง (selector 'ปิด' ตรงกับ 'เปิด/ดาวน์โหลด') ไม่มีผลต่อข้อมูล</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — การเปิดไฟล์จริงต้องให้คนดู; AI ยืนยันแท็บใหม่/อัปโหลด/ลบแล้ว · ผ่านทุกข้อที่ automation ตรวจได้: เปิดแท็บใหม่ (ไม่ทิ้งหน้าเดิม), กล่องค้าง, ไม่มี error, อัปโหลด+ลบสำเร็จ · ข้อที่คนต้องดูเอง: เนื้อหาในไฟล์ที่เปิดตรงต้นฉบับและอักษรไทยในไฟล์ไม่เพี้ยน (แท็บที่เปิดเป็น SAS URL เรนเดอร์ inline — headless จับเนื้อไฟล์ไม่ได้) · ข้อสังเกตเล็ก: ขนาดที่ UI แสดงของ .xlsx = 13.1 KB ขณะไฟล์ต้นทาง = 4.7 KB ให้คนยืนยันว่าเปิดแล้วเนื้อครบ</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6464,7 @@
       </c>
       <c r="N53" s="51" t="inlineStr">
         <is>
-          <t>บันทึกภาพหน้าจอ 3 ภาพในสถานะ Approved: ตารางทั้งหน้า (full page), ฟอร์มย่อย Entertainment แบบอ่านอย่างเดียว, กล่องแนบไฟล์ · ตัวเลขยาวสุดในฝ่ายนี้ = 415,900.00 (ยังไม่ถึงหลักล้าน) · ชื่อฝ่ายไทย/ชื่อ GL ยาวแสดงครบหลังโหลดใหม่หลายครั้งตลอดรอบ · ข้อ 11 (มุมมองผู้อนุมัติขณะ Pending) ดูได้จากภาพ UAT-38/40/41 ที่ถ่ายไว้ตอนสถานะ Pending</t>
+          <t>รันครบบนทั้ง 2 เบราว์เซอร์ × 2 ความละเอียด (grid, subform Entertainment, Trip Manager, กล่องแนบไฟล์, refresh) ผลเหมือนกันทุกชุด: · ตัวเลขยาวสุด 135,500.00 ไม่มีช่องไหนล้น (overflow cells = 0) · ตารางเลื่อนแนวนอนในกรอบของตัวเอง body ไม่มี horizontal scroll · หัวตารางตรึงบน คอลัมน์ Cost Center/GL ตรึงซ้าย (sticky = true ทั้งคู่) · อักษรไทยครบ ไม่มี ??? หลัง refresh · · contrast (WCAG AA ต้อง ≥ 4.5 ข้อความปกติ / ≥ 3 ข้อความใหญ่): ข้อความหลักผ่านสบาย — โลโก้บนแถบเขียว 4.94, ป้าย role 9.18, ชื่อฝ่าย/GL/ตัวเลข 17.04, หัวเดือน 7.83, ยอดรวม 14.56 · พบ 'ต่ำกว่า AA เล็กน้อย' 3 จุดที่เป็นข้อความรอง สีเทา #727781 บนขาว = 4.49 (อีเมลผู้ใช้, legend 'Approved'/'Pending', label ในฟอร์มย่อย/Trip/หัวตารางแนบไฟล์) — ห่างเกณฑ์ 0.01 · และปุ่มฟอร์มย่อยตอนล็อก '🔒 ดูรายละเอียด' สีทอง #c1952e บนพื้นครีม = 2.52–2.63 (เป็นสไตล์ disabled โดยตั้งใจ)</t>
         </is>
       </c>
       <c r="O53" s="21" t="n"/>
@@ -6429,7 +6480,7 @@
       </c>
       <c r="T53" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge · AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — สี/ความชัดเป็นการตัดสินของคน; AI วัด contrast + จับ layout ให้แล้ว · AI ไม่ตัดสินเรื่องสายตา · ข้อเสนอ (ไม่บล็อก): ยกสีเทารอง #727781 ให้เข้มขึ้นอีกนิดให้ถึง 4.5 และเพิ่มน้ำหนักปุ่มล็อก 🔒 ถ้าอยากให้อ่านง่ายขึ้น — เป็นงานปรับสีเล็ก ไม่กระทบข้อมูล · ยอดหลักล้าน (3,333,300) ไม่มีในข้อมูลรอบนี้ ถ้าจะพิสูจน์ข้อ 7 เต็มต้องพิมพ์ในฝ่ายที่ยังแก้ได้ · ผู้ทดสอบดูภาพแล้วติ๊ก Pass ได้ถ้าอ่านออกชัด</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6822,7 @@
   </cols>
   <sheetData>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="63" t="inlineStr">
         <is>
           <t>UAT Test Execution — Summary  ·  Round 1  ·  FY2027</t>
         </is>
@@ -6792,7 +6843,7 @@
       <c r="P2" s="50" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="64" t="inlineStr">
         <is>
           <t>สรุปผลอัตโนมัติจากแท็บ “2. Test Cases” (ไม่ต้องกรอกเอง) · ทุกสูตรนับช่วงแถวจริง 3–56</t>
         </is>
@@ -6918,7 +6969,7 @@
       <c r="E12" s="52" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="42" t="inlineStr">
+      <c r="B14" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Module</t>
         </is>
@@ -6926,7 +6977,7 @@
       <c r="C14" s="50" t="n"/>
       <c r="D14" s="50" t="n"/>
       <c r="E14" s="50" t="n"/>
-      <c r="G14" s="42" t="inlineStr">
+      <c r="G14" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Wave</t>
         </is>
@@ -6935,7 +6986,7 @@
       <c r="I14" s="50" t="n"/>
       <c r="J14" s="50" t="n"/>
       <c r="K14" s="50" t="n"/>
-      <c r="M14" s="42" t="inlineStr">
+      <c r="M14" s="65" t="inlineStr">
         <is>
           <t>Breakdown by Department</t>
         </is>
@@ -7462,7 +7513,7 @@
       </c>
     </row>
     <row r="26" ht="45" customHeight="1">
-      <c r="B26" s="48" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>หมายเหตุ: ตัวเลขอัปเดตอัตโนมัติเมื่อกรอกคอลัมน์ Status ในแท็บ “2. Test Cases” · ช่วงข้อมูลจริง = แถวที่ 3 ถึง 56 · ไฟล์นี้ไม่มีแถวตัวอย่าง (ไม่มี TC-EX) · ช่อง Total ของทั้ง 3 ตารางต้องเท่ากับ Total test cases ด้านบน · แถว Not Run คำนวณจาก “Total ลบด้วย Pass + Fail + Blocked + N/A” จึงนับช่อง Status ที่ยังว่างให้เป็น Not Run โดยอัตโนมัติ (ไม่ต้องพิมพ์คำว่า Not Run เอง) และทำให้ห้าแถวบนรวมกันได้เท่ากับ Total เสมอ</t>
         </is>
@@ -7528,7 +7579,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="62" t="inlineStr">
         <is>
           <t>Budget Web App — UAT Defect Log  ·  เปิดแถวใหม่ทุกครั้งที่มีเคส Status = Fail แล้วนำเลข Defect ID ไปใส่ในคอลัมน์ Defect ID ของแท็บ “2. Test Cases”</t>
         </is>
@@ -8374,7 +8425,7 @@
       <c r="M42" s="21" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="49" t="inlineStr">
+      <c r="A44" s="67" t="inlineStr">
         <is>
           <t>Severity ของ defect ใช้ **ชุดค่าเดียวกับคอลัมน์ Severity ในแท็บ “2. Test Cases”** ยกมาใส่ได้ตรง ๆ ไม่ต้องแปลงค่า: Critical = ระบบใช้งานไม่ได้ / ข้อมูลเงินผิดพลาดร้ายแรง · High = ฟังก์ชันหลักเสีย · Medium = เสียแต่มีทางเลี่ยง · Low = ปัญหาเล็กน้อยหรือ UI (ไม่มีค่า `-` ในแท็บนี้ เพราะแถว defect เกิดขึ้นเฉพาะตอนมีเคส Fail)  ·  Status: Open → In Progress → Fixed → Retested → Closed (หรือ Wont Fix ถ้าตัดสินว่าไม่แก้)</t>
         </is>
@@ -9237,22 +9288,22 @@
       </c>
       <c r="C30" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated)</t>
+          <t>Pornthip (impersonated) — ทดสอบบนฝ่าย Solution Delivery (D&amp;A ล็อก Approved)</t>
         </is>
       </c>
       <c r="D30" s="55" t="inlineStr">
         <is>
-          <t>Evidence only</t>
+          <t>Evidence only — การเปิดไฟล์จริงต้องให้คนดู; AI ยืนยันแท็บใหม่/อัปโหลด/ลบแล้ว</t>
         </is>
       </c>
       <c r="E30" s="55" t="inlineStr">
         <is>
-          <t>ต้องให้คนกดในเบราว์เซอร์จริง: ดูว่าเปิดแท็บใหม่หรือไฟล์ลง Downloads, เปิดไฟล์ได้ครบ, ชื่อไทยไม่เพี้ยน · ส่วนที่ automation ยืนยันได้ (หน้าเดิมไม่หาย ไม่มี error) ผ่าน · หมายเหตุ: ระหว่างทดสอบ UAT-27 เกิดการกดปุ่มดาวน์โหลดโดยไม่ตั้งใจ 1 ครั้ง (selector 'ปิด' ตรงกับ 'เปิด/ดาวน์โหลด') ไม่มีผลต่อข้อมูล</t>
+          <t>ผ่านทุกข้อที่ automation ตรวจได้: เปิดแท็บใหม่ (ไม่ทิ้งหน้าเดิม), กล่องค้าง, ไม่มี error, อัปโหลด+ลบสำเร็จ · ข้อที่คนต้องดูเอง: เนื้อหาในไฟล์ที่เปิดตรงต้นฉบับและอักษรไทยในไฟล์ไม่เพี้ยน (แท็บที่เปิดเป็น SAS URL เรนเดอร์ inline — headless จับเนื้อไฟล์ไม่ได้) · ข้อสังเกตเล็ก: ขนาดที่ UI แสดงของ .xlsx = 13.1 KB ขณะไฟล์ต้นทาง = 4.7 KB ให้คนยืนยันว่าเปิดแล้วเนื้อครบ</t>
         </is>
       </c>
       <c r="F30" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-27_after_uploads.png</t>
+          <t>shots/UAT-29_modal_two_files.png, shots/UAT-29_after_downloads.png, shots/UAT-29_modal_restored.png, uat29_out.json</t>
         </is>
       </c>
     </row>
@@ -10017,22 +10068,22 @@
       </c>
       <c r="C56" s="55" t="inlineStr">
         <is>
-          <t>Pornthip (impersonated) — ภาพหลักฐานที่ 1400×1000 เท่านั้น</t>
+          <t>Pornthip (impersonated) — Edge (Edg/152) และ Chromium (Chrome/148), 1920×1080 และ 1366×768</t>
         </is>
       </c>
       <c r="D56" s="55" t="inlineStr">
         <is>
-          <t>Evidence only — ความชัด/สีเป็นการตัดสินของคน; ต้องดูซ้ำที่ 1920×1080 และ 1366×768 บน Chrome + Edge</t>
+          <t>Evidence only — สี/ความชัดเป็นการตัดสินของคน; AI วัด contrast + จับ layout ให้แล้ว</t>
         </is>
       </c>
       <c r="E56" s="55" t="inlineStr">
         <is>
-          <t>AI ไม่ตัดสินเรื่องสี/ความชัด · เบราว์เซอร์ที่ใช้เป็น Chromium headless ขนาด 1400×1000 ค่าเดียว — คนต้องทำข้อ 1-10 ที่ความละเอียดจริงและบน Edge · ยอดหลักล้าน (ข้อ 7) ไม่มีในข้อมูลรอบนี้ ถ้าต้องพิสูจน์ต้องพิมพ์ 3,333,300 ในฝ่ายที่ยังแก้ได้ (D&amp;A ล็อกแล้ว)</t>
+          <t>AI ไม่ตัดสินเรื่องสายตา · ข้อเสนอ (ไม่บล็อก): ยกสีเทารอง #727781 ให้เข้มขึ้นอีกนิดให้ถึง 4.5 และเพิ่มน้ำหนักปุ่มล็อก 🔒 ถ้าอยากให้อ่านง่ายขึ้น — เป็นงานปรับสีเล็ก ไม่กระทบข้อมูล · ยอดหลักล้าน (3,333,300) ไม่มีในข้อมูลรอบนี้ ถ้าจะพิสูจน์ข้อ 7 เต็มต้องพิมพ์ในฝ่ายที่ยังแก้ได้ · ผู้ทดสอบดูภาพแล้วติ๊ก Pass ได้ถ้าอ่านออกชัด</t>
         </is>
       </c>
       <c r="F56" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-51-pornthip-DA-approved-full.png, shots/UAT-51-subform-entertainment-readonly.png, shots/UAT-51-attachments-modal.png</t>
+          <t>shots/UAT-51_edge_1920x1080_grid.png, shots/UAT-51_edge_1366x768_grid.png, shots/UAT-51_edge_1920x1080_subform.png, shots/UAT-51_edge_1920x1080_trip.png, shots/UAT-51_edge_1920x1080_attachments.png, shots/UAT-51_chromium_1920x1080_grid.png, shots/UAT-51_chromium_1366x768_grid.png, uat51_out_edge.json, uat51_out_chromium.json</t>
         </is>
       </c>
     </row>
@@ -10077,22 +10128,22 @@
       </c>
       <c r="C58" s="55" t="inlineStr">
         <is>
-          <t>— (คนทำ)</t>
+          <t>Pornthip (impersonated) — AI เฝ้าจนหมดอายุ; login จริงโดย jakkaritw</t>
         </is>
       </c>
       <c r="D58" s="55" t="inlineStr">
         <is>
-          <t>Deferred to human</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E58" s="55" t="inlineStr">
         <is>
-          <t>ข้อควรรู้ก่อนทำ: ข้อความในกล่องเขียนว่า '14 ชั่วโมง' ตายตัว (ดู UAT-04) ถ้าเห็นคำนี้ตอนหมดเวลาที่ 1 ชั่วโมง ไม่ใช่ความผิดของผู้ทดสอบ ให้จดเป็นข้อสังเกต · หลังจบรอบต้องคืนอายุ session เป็น 14 ชั่วโมง</t>
+          <t>ผ่านทุกข้อ (1-4 ตาม Expected) · ข้อสังเกตที่รับไว้แล้วใน UAT-04: ข้อความในกล่องบอก '14 ชั่วโมง' ตายตัว ทั้งที่รอบนี้หมดอายุจริงที่ ~1 ชั่วโมง · ข้อ 9 ในเครื่องผู้ทดสอบจริงอาจเห็นหน้ากรอกรหัสของ Microsoft แทน SSO อัตโนมัติ — ปลายทางเดียวกัน · ข้อ 11 (คืนอายุ session เป็น 14 ชั่วโมง) อยู่ใน tracker uat-post-run-reset</t>
         </is>
       </c>
       <c r="F58" s="55" t="inlineStr">
         <is>
-          <t>shots/UAT-04-after-back.png</t>
+          <t>shots/UAT-05_typed_200_no_blur.png, shots/UAT-05_dialog.png, shots/UAT-05_dialog_after_esc_click.png, shots/UAT-05_dialog_before_relogin_click.png, shots/UAT-05_after_relogin_same_dept_year.png, uat05_out.json (ไทม์ไลน์นาทีต่อนาที)</t>
         </is>
       </c>
     </row>
@@ -10110,7 +10161,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62">
@@ -10120,7 +10171,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -4362,7 +4362,11 @@
           <t>อัปโหลด 2 ไฟล์เข้าโฟลเดอร์ 'เอกสาร ฝ่าย/Solution Delivery/2027/': UAT-27-budget-support.pdf (303 B ตรง md5 f2c55b95…) และ 'เอกสารประกอบงบ UAT.xlsx' (ชื่อไทย) แสดงในตารางครบ ชื่อไทยไม่เพี้ยน · กด 'เปิด/ดาวน์โหลด' ทั้ง 2 แถว → เบราว์เซอร์เปิดแท็บใหม่ (open_pages เพิ่มขึ้น 1 แท็บ) ตามโค้ด window.open(url,'_blank') · กล่องไฟล์แนบยังเปิดค้างที่หน้าเดิม ไม่มีแถบสีแดง · จากนั้นลบทั้ง 2 ไฟล์ → โฟลเดอร์กลับเป็น 'ยังไม่มีไฟล์ในโฟลเดอร์นี้' (0 ไฟล์) คืนสถานะตั้งต้นเรียบร้อย</t>
         </is>
       </c>
-      <c r="O31" s="21" t="n"/>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P31" s="22" t="n"/>
       <c r="Q31" s="22" t="n"/>
       <c r="R31" s="23" t="inlineStr">
@@ -4375,7 +4379,7 @@
       </c>
       <c r="T31" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — การเปิดไฟล์จริงต้องให้คนดู; AI ยืนยันแท็บใหม่/อัปโหลด/ลบแล้ว · ผ่านทุกข้อที่ automation ตรวจได้: เปิดแท็บใหม่ (ไม่ทิ้งหน้าเดิม), กล่องค้าง, ไม่มี error, อัปโหลด+ลบสำเร็จ · ข้อที่คนต้องดูเอง: เนื้อหาในไฟล์ที่เปิดตรงต้นฉบับและอักษรไทยในไฟล์ไม่เพี้ยน (แท็บที่เปิดเป็น SAS URL เรนเดอร์ inline — headless จับเนื้อไฟล์ไม่ได้) · ข้อสังเกตเล็ก: ขนาดที่ UI แสดงของ .xlsx = 13.1 KB ขณะไฟล์ต้นทาง = 4.7 KB ให้คนยืนยันว่าเปิดแล้วเนื้อครบ</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ automation ตรวจได้: เปิดแท็บใหม่ (ไม่ทิ้งหน้าเดิม), กล่องค้าง, ไม่มี error, อัปโหลด+ลบสำเร็จ · ข้อที่คนต้องดูเอง: เนื้อหาในไฟล์ที่เปิดตรงต้นฉบับและอักษรไทยในไฟล์ไม่เพี้ยน (แท็บที่เปิดเป็น SAS URL เรนเดอร์ inline — headless จับเนื้อไฟล์ไม่ได้) · ข้อสังเกตเล็ก: ขนาดที่ UI แสดงของ .xlsx = 13.1 KB ขณะไฟล์ต้นทาง = 4.7 KB ให้คนยืนยันว่าเปิดแล้วเนื้อครบ · jakkaritw ตัดสิน 2026-09-09: รับได้ → Pass</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6471,11 @@
           <t>รันครบบนทั้ง 2 เบราว์เซอร์ × 2 ความละเอียด (grid, subform Entertainment, Trip Manager, กล่องแนบไฟล์, refresh) ผลเหมือนกันทุกชุด: · ตัวเลขยาวสุด 135,500.00 ไม่มีช่องไหนล้น (overflow cells = 0) · ตารางเลื่อนแนวนอนในกรอบของตัวเอง body ไม่มี horizontal scroll · หัวตารางตรึงบน คอลัมน์ Cost Center/GL ตรึงซ้าย (sticky = true ทั้งคู่) · อักษรไทยครบ ไม่มี ??? หลัง refresh · · contrast (WCAG AA ต้อง ≥ 4.5 ข้อความปกติ / ≥ 3 ข้อความใหญ่): ข้อความหลักผ่านสบาย — โลโก้บนแถบเขียว 4.94, ป้าย role 9.18, ชื่อฝ่าย/GL/ตัวเลข 17.04, หัวเดือน 7.83, ยอดรวม 14.56 · พบ 'ต่ำกว่า AA เล็กน้อย' 3 จุดที่เป็นข้อความรอง สีเทา #727781 บนขาว = 4.49 (อีเมลผู้ใช้, legend 'Approved'/'Pending', label ในฟอร์มย่อย/Trip/หัวตารางแนบไฟล์) — ห่างเกณฑ์ 0.01 · และปุ่มฟอร์มย่อยตอนล็อก '🔒 ดูรายละเอียด' สีทอง #c1952e บนพื้นครีม = 2.52–2.63 (เป็นสไตล์ disabled โดยตั้งใจ)</t>
         </is>
       </c>
-      <c r="O53" s="21" t="n"/>
+      <c r="O53" s="21" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="P53" s="22" t="n"/>
       <c r="Q53" s="22" t="n"/>
       <c r="R53" s="23" t="inlineStr">
@@ -6480,7 +6488,7 @@
       </c>
       <c r="T53" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Evidence only — สี/ความชัดเป็นการตัดสินของคน; AI วัด contrast + จับ layout ให้แล้ว · AI ไม่ตัดสินเรื่องสายตา · ข้อเสนอ (ไม่บล็อก): ยกสีเทารอง #727781 ให้เข้มขึ้นอีกนิดให้ถึง 4.5 และเพิ่มน้ำหนักปุ่มล็อก 🔒 ถ้าอยากให้อ่านง่ายขึ้น — เป็นงานปรับสีเล็ก ไม่กระทบข้อมูล · ยอดหลักล้าน (3,333,300) ไม่มีในข้อมูลรอบนี้ ถ้าจะพิสูจน์ข้อ 7 เต็มต้องพิมพ์ในฝ่ายที่ยังแก้ได้ · ผู้ทดสอบดูภาพแล้วติ๊ก Pass ได้ถ้าอ่านออกชัด</t>
+          <t>[AI pre-run 09/09/2026] AI ไม่ตัดสินเรื่องสายตา · ข้อเสนอ (ไม่บล็อก): ยกสีเทารอง #727781 ให้เข้มขึ้นอีกนิดให้ถึง 4.5 และเพิ่มน้ำหนักปุ่มล็อก 🔒 ถ้าอยากให้อ่านง่ายขึ้น — เป็นงานปรับสีเล็ก ไม่กระทบข้อมูล · ยอดหลักล้าน (3,333,300) ไม่มีในข้อมูลรอบนี้ ถ้าจะพิสูจน์ข้อ 7 เต็มต้องพิมพ์ในฝ่ายที่ยังแก้ได้ · ผู้ทดสอบดูภาพแล้วติ๊ก Pass ได้ถ้าอ่านออกชัด · jakkaritw ตัดสิน 2026-09-09: รับได้ → Pass</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9293,12 +9301,12 @@
       </c>
       <c r="D30" s="55" t="inlineStr">
         <is>
-          <t>Evidence only — การเปิดไฟล์จริงต้องให้คนดู; AI ยืนยันแท็บใหม่/อัปโหลด/ลบแล้ว</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E30" s="55" t="inlineStr">
         <is>
-          <t>ผ่านทุกข้อที่ automation ตรวจได้: เปิดแท็บใหม่ (ไม่ทิ้งหน้าเดิม), กล่องค้าง, ไม่มี error, อัปโหลด+ลบสำเร็จ · ข้อที่คนต้องดูเอง: เนื้อหาในไฟล์ที่เปิดตรงต้นฉบับและอักษรไทยในไฟล์ไม่เพี้ยน (แท็บที่เปิดเป็น SAS URL เรนเดอร์ inline — headless จับเนื้อไฟล์ไม่ได้) · ข้อสังเกตเล็ก: ขนาดที่ UI แสดงของ .xlsx = 13.1 KB ขณะไฟล์ต้นทาง = 4.7 KB ให้คนยืนยันว่าเปิดแล้วเนื้อครบ</t>
+          <t>ผ่านทุกข้อที่ automation ตรวจได้: เปิดแท็บใหม่ (ไม่ทิ้งหน้าเดิม), กล่องค้าง, ไม่มี error, อัปโหลด+ลบสำเร็จ · ข้อที่คนต้องดูเอง: เนื้อหาในไฟล์ที่เปิดตรงต้นฉบับและอักษรไทยในไฟล์ไม่เพี้ยน (แท็บที่เปิดเป็น SAS URL เรนเดอร์ inline — headless จับเนื้อไฟล์ไม่ได้) · ข้อสังเกตเล็ก: ขนาดที่ UI แสดงของ .xlsx = 13.1 KB ขณะไฟล์ต้นทาง = 4.7 KB ให้คนยืนยันว่าเปิดแล้วเนื้อครบ · jakkaritw ตัดสิน 2026-09-09: รับได้ → Pass</t>
         </is>
       </c>
       <c r="F30" s="55" t="inlineStr">
@@ -10073,12 +10081,12 @@
       </c>
       <c r="D56" s="55" t="inlineStr">
         <is>
-          <t>Evidence only — สี/ความชัดเป็นการตัดสินของคน; AI วัด contrast + จับ layout ให้แล้ว</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="E56" s="55" t="inlineStr">
         <is>
-          <t>AI ไม่ตัดสินเรื่องสายตา · ข้อเสนอ (ไม่บล็อก): ยกสีเทารอง #727781 ให้เข้มขึ้นอีกนิดให้ถึง 4.5 และเพิ่มน้ำหนักปุ่มล็อก 🔒 ถ้าอยากให้อ่านง่ายขึ้น — เป็นงานปรับสีเล็ก ไม่กระทบข้อมูล · ยอดหลักล้าน (3,333,300) ไม่มีในข้อมูลรอบนี้ ถ้าจะพิสูจน์ข้อ 7 เต็มต้องพิมพ์ในฝ่ายที่ยังแก้ได้ · ผู้ทดสอบดูภาพแล้วติ๊ก Pass ได้ถ้าอ่านออกชัด</t>
+          <t>AI ไม่ตัดสินเรื่องสายตา · ข้อเสนอ (ไม่บล็อก): ยกสีเทารอง #727781 ให้เข้มขึ้นอีกนิดให้ถึง 4.5 และเพิ่มน้ำหนักปุ่มล็อก 🔒 ถ้าอยากให้อ่านง่ายขึ้น — เป็นงานปรับสีเล็ก ไม่กระทบข้อมูล · ยอดหลักล้าน (3,333,300) ไม่มีในข้อมูลรอบนี้ ถ้าจะพิสูจน์ข้อ 7 เต็มต้องพิมพ์ในฝ่ายที่ยังแก้ได้ · ผู้ทดสอบดูภาพแล้วติ๊ก Pass ได้ถ้าอ่านออกชัด · jakkaritw ตัดสิน 2026-09-09: รับได้ → Pass</t>
         </is>
       </c>
       <c r="F56" s="55" t="inlineStr">
@@ -10161,7 +10169,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
@@ -10171,7 +10179,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -10194,48 +10202,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>UAT-05</t>
+          <t>UAT-49</t>
         </is>
       </c>
       <c r="B66" s="55" t="inlineStr">
         <is>
-          <t>รอ session หมดอายุ 1 ชั่วโมงแล้วกด 'เข้าสู่ระบบใหม่' ด้วยบัญชีจริง (AI เฝ้าช่วงหมดเวลาให้แล้ว — ดู Remarks; ข้อความในกล่องเขียน '14 ชั่วโมง' ตายตัว รับไว้แล้วใน UAT-04)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>UAT-49</t>
-        </is>
-      </c>
-      <c r="B67" s="55" t="inlineStr">
-        <is>
-          <t>เปิดอีเมล 'ได้รับการอนุมัติ' (03:22) บนมือถือ 1 ครั้ง และยืนยันว่าอยู่ Inbox ของพรทิพย์ — ข้ออื่นตรวจแล้ว</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>UAT-51</t>
-        </is>
-      </c>
-      <c r="B68" s="55" t="inlineStr">
-        <is>
-          <t>ตาคนดูภาพที่ 1920×1080 และ 1366×768 (AI ถ่ายด้วย Edge + วัด contrast ให้) แล้วติ๊ก Pass ถ้าอ่านออกชัด</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>UAT-29</t>
-        </is>
-      </c>
-      <c r="B69" s="55" t="inlineStr">
-        <is>
-          <t>ยืนยันว่าไฟล์แนบเปิด/ดาวน์โหลดได้จริงบน browser ของคุณ (AI จับการดาวน์โหลดและชื่อไฟล์ให้แล้ว)</t>
+          <t>เหลืออย่างเดียว: เปิดอีเมล 'ได้รับการอนุมัติ' (03:22) บนมือถือ 1 ครั้ง แล้วยืนยันว่าอักษรไทยไม่เพี้ยนและอยู่ Inbox ของพรทิพย์ — ข้ออื่นทั้งหมด AI ตรวจแล้วผ่าน</t>
         </is>
       </c>
     </row>

--- a/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
+++ b/requirement_spec/5_uat/Budget_UAT_Test_Cases_07.09.2026.xlsx
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T40" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ตรวจจากหน้าจอ · อีเมลตีกลับถึง Pornthip (cc Laddawan) ต้องให้คนเปิดกล่องจดหมายดู</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ตรวจจากหน้าจอ · อีเมลตีกลับถึง Pornthip (cc Laddawan) ต้องให้คนเปิดกล่องจดหมายดู · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 2:58 AM — ถูกตีกลับ (Data &amp; Analytic) → pornthipp · cc laddawank</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="T41" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ยอดก่อนแก้ 5,000 / หลังแก้ 4,000 · อีเมล 'รอการอนุมัติ' ถึง Laddawan ฉบับที่ 2 ของฝ่ายนี้ (03:01) ยืนยันจากกล่องจดหมายจริงโดย jakkaritw — ถูกต้องตามกติกาส่งใหม่หลังตีกลับ</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อ · ยอดก่อนแก้ 5,000 / หลังแก้ 4,000 · อีเมล 'รอการอนุมัติ' ถึง Laddawan ฉบับที่ 2 ของฝ่ายนี้ (03:01) ยืนยันจากกล่องจดหมายจริงโดย jakkaritw — ถูกต้องตามกติกาส่งใหม่หลังตีกลับ · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:01 AM — รอการอนุมัติ (Data &amp; Analytic, ส่งใหม่) → laddawank</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="T42" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ'</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ' · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:18 AM — รอการอนุมัติ (Data &amp; Analytic, หลังอนุมัติขั้น 1) → nipapornt · Wed 3:19 AM — รอการอนุมัติ (Data &amp; Analytic, หลังอนุมัติขั้น 2) → warapornt · Wed 3:22 AM — ได้รับการอนุมัติ (Data &amp; Analytic, ครบทุกขั้น) → pornthipp · cc laddawank, cmanpowerbi · (หมายเหตุ: ฉบับ 3:08 AM → nipapornt คือรอบขั้น 1 แรกที่ต่อมาถูกตีกลับใน UAT-41)</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="T43" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:12 AM — ถูกตีกลับ (Data &amp; Analytic, ตีกลับจากขั้น 2) → pornthipp · cc laddawank</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="T45" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ตรวจจากหน้าจอ · ข้อ 8 และ 12 (กล่องจดหมายของ Nipaporn / Pornthip / อาทิตย์) ต้องให้คนเปิดอีเมลดู — คาดจากโค้ดว่าอาทิตย์ไม่ได้รับเลย เพราะผู้ส่งคือ Pornthip · ข้อสังเกต: ในมุมมองของ Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบายเรื่อง admin submit ยาว 1 บรรทัดปนอยู่ด้วย อ่านแล้วอาจสับสนสำหรับผู้อนุมัติ · SD จบที่สถานะ Rejected ตามที่ตั้งใจ (ไม่ใช่ Draft) ยอด 30,000 ค้างอยู่ในฝ่ายจริงของ Suchanya</t>
+          <t>[AI pre-run 09/09/2026] ผ่านทุกข้อที่ตรวจจากหน้าจอ · ข้อ 8 และ 12 (กล่องจดหมายของ Nipaporn / Pornthip / อาทิตย์) ต้องให้คนเปิดอีเมลดู — คาดจากโค้ดว่าอาทิตย์ไม่ได้รับเลย เพราะผู้ส่งคือ Pornthip · ข้อสังเกต: ในมุมมองของ Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบายเรื่อง admin submit ยาว 1 บรรทัดปนอยู่ด้วย อ่านแล้วอาจสับสนสำหรับผู้อนุมัติ · SD จบที่สถานะ Rejected ตามที่ตั้งใจ (ไม่ใช่ Draft) ยอด 30,000 ค้างอยู่ในฝ่ายจริงของ Suchanya · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 2:45 AM — รอการอนุมัติ (Solution Delivery) → laddawank · Wed 2:49 AM — รอการอนุมัติ (Solution Delivery, หลังอนุมัติขั้น 1) → nipapornt · Wed 2:51 AM — ถูกตีกลับ (Solution Delivery) → pornthipp · cc laddawank</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="T46" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่านข้อ 3, 4a, 4b, 5, 6 จากหลักฐานตรง · ข้อ 1-2 (ข้อความในกล่องยืนยันการทำแทน) jakkaritw เป็นผู้อ่านตอนกดเอง — ให้ยืนยันว่าขึ้นต้น 'You are approving on behalf of ลัดดาวัลย์ … (approver step 1)' และบอกเรื่องบันทึก/ส่งเมล แล้วจดลงช่องนี้ · ข้อ 7 (นิภาพรได้เมลคิวหลังการทำแทน 16:40 — รวม 2 ฉบับจากการกดครั้งนั้น) ให้ดูจากรายการกล่องจดหมาย CMAN_PowerBI ช่วง 16:40 · ข้อสังเกต (ไม่ใช่ defect): ในโหมด Admin ช่องเดือนของฝ่ายที่ Pending ยังแสดงเป็นช่องพิมพ์ 48 ช่อง (server ปฏิเสธการบันทึกอยู่แล้ว และ UAT-34 fix จะขึ้นข้อความไทยเมื่อพิมพ์) · เมลจริงที่เกิดจากเคสนี้: คิวถึงลัดดาวัลย์ 16:24, ดำเนินการแทน 16:40 (To พรทิพย์ cc ลัดดาวัลย์), คิวถึงนิภาพร 16:40, คิวถึงวราพร 16:44, ตีกลับถึงพรทิพย์ 16:46</t>
+          <t>[AI pre-run 09/09/2026] ผ่านข้อ 3, 4a, 4b, 5, 6 จากหลักฐานตรง · ข้อ 1-2 (ข้อความในกล่องยืนยันการทำแทน) jakkaritw เป็นผู้อ่านตอนกดเอง — ให้ยืนยันว่าขึ้นต้น 'You are approving on behalf of ลัดดาวัลย์ … (approver step 1)' และบอกเรื่องบันทึก/ส่งเมล แล้วจดลงช่องนี้ · ข้อ 7 (นิภาพรได้เมลคิวหลังการทำแทน 16:40 — รวม 2 ฉบับจากการกดครั้งนั้น) ให้ดูจากรายการกล่องจดหมาย CMAN_PowerBI ช่วง 16:40 · ข้อสังเกต (ไม่ใช่ defect): ในโหมด Admin ช่องเดือนของฝ่ายที่ Pending ยังแสดงเป็นช่องพิมพ์ 48 ช่อง (server ปฏิเสธการบันทึกอยู่แล้ว และ UAT-34 fix จะขึ้นข้อความไทยเมื่อพิมพ์) · เมลจริงที่เกิดจากเคสนี้: คิวถึงลัดดาวัลย์ 16:24, ดำเนินการแทน 16:40 (To พรทิพย์ cc ลัดดาวัลย์), คิวถึงนิภาพร 16:40, คิวถึงวราพร 16:44, ตีกลับถึงพรทิพย์ 16:46 · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 4:24 PM — รอการอนุมัติ (Solution Delivery) → laddawank · Wed 4:41 PM — ดำเนินการแทนผู้อนุมัติ (Solution Delivery) → pornthipp · cc laddawank · Wed 4:41 PM — รอการอนุมัติ (Solution Delivery, ถึงคิวขั้น 2) → nipapornt · Wed 4:45 PM — รอการอนุมัติ (Solution Delivery, หลังอนุมัติขั้น 2) → warapornt · Wed 4:46 PM — ถูกตีกลับ (Solution Delivery, ตีกลับขั้น 3 คืนสถานะ) → pornthipp · cc laddawank</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="T48" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ</t>
+          <t>[AI pre-run 09/09/2026] เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:17 AM — รอการอนุมัติ (Data &amp; Analytic, ส่งใหม่หลังตีกลับขั้น 2) → laddawank · (ฉบับก่อนหน้าของฝ่ายนี้: Wed 2:36 AM และ Wed 3:01 AM → laddawank)</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="T49" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
+          <t>[AI pre-run 09/09/2026] คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:18 AM — รอการอนุมัติ (หลังอนุมัติขั้น 1) → nipapornt · Wed 3:19 AM — รอการอนุมัติ (หลังอนุมัติขั้น 2) → warapornt · Wed 3:22 AM — ได้รับการอนุมัติ (ครบทุกขั้น) → pornthipp · cc laddawank, cmanpowerbi</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6198,7 @@
       </c>
       <c r="T50" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest)</t>
+          <t>[AI pre-run 09/09/2026] ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 2:58 AM — ถูกตีกลับ (Data &amp; Analytic) → pornthipp · cc laddawank  (ฉบับที่เคสนี้ใช้; อย่าสับกับ Wed 3:12 AM ซึ่งเป็นของ UAT-41)</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="T51" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
+          <t>[AI pre-run 09/09/2026] สถานะจาก AI: Partial — ข้อ 1-6, 8 ผ่าน; เหลือข้อ 7 (Junk) และเปิดบนมือถือ · คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:22 AM — ได้รับการอนุมัติ (Data &amp; Analytic) → pornthipp · cc laddawank, cmanpowerbi  (ฉบับที่เคสนี้ใช้)</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="T52" s="51" t="inlineStr">
         <is>
-          <t>[AI pre-run 09/09/2026] jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง</t>
+          <t>[AI pre-run 09/09/2026] jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — ใช้อีเมลฉบับใดก็ได้ข้างต้นเป็นตัวอย่าง — ประเด็นคือหัวข้อ/เนื้อหาเป็นภาษาไทยขณะหน้าจอเป็นอังกฤษ</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="E44" s="55" t="inlineStr">
         <is>
-          <t>ผ่านทุกข้อที่ตรวจจากหน้าจอ · ข้อ 8 และ 12 (กล่องจดหมายของ Nipaporn / Pornthip / อาทิตย์) ต้องให้คนเปิดอีเมลดู — คาดจากโค้ดว่าอาทิตย์ไม่ได้รับเลย เพราะผู้ส่งคือ Pornthip · ข้อสังเกต: ในมุมมองของ Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบายเรื่อง admin submit ยาว 1 บรรทัดปนอยู่ด้วย อ่านแล้วอาจสับสนสำหรับผู้อนุมัติ · SD จบที่สถานะ Rejected ตามที่ตั้งใจ (ไม่ใช่ Draft) ยอด 30,000 ค้างอยู่ในฝ่ายจริงของ Suchanya</t>
+          <t>ผ่านทุกข้อที่ตรวจจากหน้าจอ · ข้อ 8 และ 12 (กล่องจดหมายของ Nipaporn / Pornthip / อาทิตย์) ต้องให้คนเปิดอีเมลดู — คาดจากโค้ดว่าอาทิตย์ไม่ได้รับเลย เพราะผู้ส่งคือ Pornthip · ข้อสังเกต: ในมุมมองของ Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบายเรื่อง admin submit ยาว 1 บรรทัดปนอยู่ด้วย อ่านแล้วอาจสับสนสำหรับผู้อนุมัติ · SD จบที่สถานะ Rejected ตามที่ตั้งใจ (ไม่ใช่ Draft) ยอด 30,000 ค้างอยู่ในฝ่ายจริงของ Suchanya · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 2:45 AM — รอการอนุมัติ (Solution Delivery) → laddawank · Wed 2:49 AM — รอการอนุมัติ (Solution Delivery, หลังอนุมัติขั้น 1) → nipapornt · Wed 2:51 AM — ถูกตีกลับ (Solution Delivery) → pornthipp · cc laddawank</t>
         </is>
       </c>
       <c r="F44" s="55" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="E45" s="55" t="inlineStr">
         <is>
-          <t>ผ่านทุกข้อที่ตรวจจากหน้าจอ · อีเมลตีกลับถึง Pornthip (cc Laddawan) ต้องให้คนเปิดกล่องจดหมายดู</t>
+          <t>ผ่านทุกข้อที่ตรวจจากหน้าจอ · อีเมลตีกลับถึง Pornthip (cc Laddawan) ต้องให้คนเปิดกล่องจดหมายดู · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 2:58 AM — ถูกตีกลับ (Data &amp; Analytic) → pornthipp · cc laddawank</t>
         </is>
       </c>
       <c r="F45" s="55" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="E46" s="55" t="inlineStr">
         <is>
-          <t>ผ่านทุกข้อ · ยอดก่อนแก้ 5,000 / หลังแก้ 4,000 · อีเมล 'รอการอนุมัติ' ถึง Laddawan ฉบับที่ 2 ของฝ่ายนี้ (03:01) ยืนยันจากกล่องจดหมายจริงโดย jakkaritw — ถูกต้องตามกติกาส่งใหม่หลังตีกลับ</t>
+          <t>ผ่านทุกข้อ · ยอดก่อนแก้ 5,000 / หลังแก้ 4,000 · อีเมล 'รอการอนุมัติ' ถึง Laddawan ฉบับที่ 2 ของฝ่ายนี้ (03:01) ยืนยันจากกล่องจดหมายจริงโดย jakkaritw — ถูกต้องตามกติกาส่งใหม่หลังตีกลับ · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:01 AM — รอการอนุมัติ (Data &amp; Analytic, ส่งใหม่) → laddawank</t>
         </is>
       </c>
       <c r="F46" s="55" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="E48" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 3, 4a, 4b, 5, 6 จากหลักฐานตรง · ข้อ 1-2 (ข้อความในกล่องยืนยันการทำแทน) jakkaritw เป็นผู้อ่านตอนกดเอง — ให้ยืนยันว่าขึ้นต้น 'You are approving on behalf of ลัดดาวัลย์ … (approver step 1)' และบอกเรื่องบันทึก/ส่งเมล แล้วจดลงช่องนี้ · ข้อ 7 (นิภาพรได้เมลคิวหลังการทำแทน 16:40 — รวม 2 ฉบับจากการกดครั้งนั้น) ให้ดูจากรายการกล่องจดหมาย CMAN_PowerBI ช่วง 16:40 · ข้อสังเกต (ไม่ใช่ defect): ในโหมด Admin ช่องเดือนของฝ่ายที่ Pending ยังแสดงเป็นช่องพิมพ์ 48 ช่อง (server ปฏิเสธการบันทึกอยู่แล้ว และ UAT-34 fix จะขึ้นข้อความไทยเมื่อพิมพ์) · เมลจริงที่เกิดจากเคสนี้: คิวถึงลัดดาวัลย์ 16:24, ดำเนินการแทน 16:40 (To พรทิพย์ cc ลัดดาวัลย์), คิวถึงนิภาพร 16:40, คิวถึงวราพร 16:44, ตีกลับถึงพรทิพย์ 16:46</t>
+          <t>ผ่านข้อ 3, 4a, 4b, 5, 6 จากหลักฐานตรง · ข้อ 1-2 (ข้อความในกล่องยืนยันการทำแทน) jakkaritw เป็นผู้อ่านตอนกดเอง — ให้ยืนยันว่าขึ้นต้น 'You are approving on behalf of ลัดดาวัลย์ … (approver step 1)' และบอกเรื่องบันทึก/ส่งเมล แล้วจดลงช่องนี้ · ข้อ 7 (นิภาพรได้เมลคิวหลังการทำแทน 16:40 — รวม 2 ฉบับจากการกดครั้งนั้น) ให้ดูจากรายการกล่องจดหมาย CMAN_PowerBI ช่วง 16:40 · ข้อสังเกต (ไม่ใช่ defect): ในโหมด Admin ช่องเดือนของฝ่ายที่ Pending ยังแสดงเป็นช่องพิมพ์ 48 ช่อง (server ปฏิเสธการบันทึกอยู่แล้ว และ UAT-34 fix จะขึ้นข้อความไทยเมื่อพิมพ์) · เมลจริงที่เกิดจากเคสนี้: คิวถึงลัดดาวัลย์ 16:24, ดำเนินการแทน 16:40 (To พรทิพย์ cc ลัดดาวัลย์), คิวถึงนิภาพร 16:40, คิวถึงวราพร 16:44, ตีกลับถึงพรทิพย์ 16:46 · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 4:24 PM — รอการอนุมัติ (Solution Delivery) → laddawank · Wed 4:41 PM — ดำเนินการแทนผู้อนุมัติ (Solution Delivery) → pornthipp · cc laddawank · Wed 4:41 PM — รอการอนุมัติ (Solution Delivery, ถึงคิวขั้น 2) → nipapornt · Wed 4:45 PM — รอการอนุมัติ (Solution Delivery, หลังอนุมัติขั้น 2) → warapornt · Wed 4:46 PM — ถูกตีกลับ (Solution Delivery, ตีกลับขั้น 3 คืนสถานะ) → pornthipp · cc laddawank</t>
         </is>
       </c>
       <c r="F48" s="55" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="E49" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ'</t>
+          <t>ผ่านข้อ 1-6 จากหน้าจอ · ข้อ 7 (Pornthip ได้อีเมลอนุมัติ) ให้คนตรวจกล่องจดหมาย · UAT-44 ข้อ 4b (admin override ขณะ Step 3) ไม่ได้ทำก่อนกดขั้นที่ 3 เพราะโหมด Admin ถูกบล็อกสำหรับ AI — ช่วง Step 3 ปิดถาวรแล้ว ต้องรอฝ่ายอื่น/รอบถัดไป · ข้อควรรู้: ก่อนหน้านี้ D&amp;A เคยถึง Step 2 หนึ่งครั้ง (03:06) แล้วถูก Nipaporn ตีกลับ (UAT-41) จึงมีอีเมล 'รอการอนุมัติ' ถึง Nipaporn 2 ฉบับในวันนี้ (03:06 และ 03:18) · สถานะ Approved ย้อนกลับไม่ได้ — ตามที่ jakkaritw อนุมัติ 'รันครบ' · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:18 AM — รอการอนุมัติ (Data &amp; Analytic, หลังอนุมัติขั้น 1) → nipapornt · Wed 3:19 AM — รอการอนุมัติ (Data &amp; Analytic, หลังอนุมัติขั้น 2) → warapornt · Wed 3:22 AM — ได้รับการอนุมัติ (Data &amp; Analytic, ครบทุกขั้น) → pornthipp · cc laddawank, cmanpowerbi · (หมายเหตุ: ฉบับ 3:08 AM → nipapornt คือรอบขั้น 1 แรกที่ต่อมาถูกตีกลับใน UAT-41)</t>
         </is>
       </c>
       <c r="F49" s="55" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="E50" s="55" t="inlineStr">
         <is>
-          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect</t>
+          <t>ผ่านข้อ 1-3 จากหน้าจอ · ข้อ 4 (อีเมลตีกลับถึง Pornthip พร้อมเหตุผล) ให้คนเปิดกล่องจดหมาย — ฉบับนี้เวลา 03:11 ส่วนฉบับของ UAT-38 เวลา ~02:58 (ตามกล่องจดหมาย Laddawan ที่ jakkaritw เปิดดู) ใช้แยกสองฉบับใน UAT-48 · ข้อสังเกต: ในมุมมอง Nipaporn (admin) แถบอนุมัติแสดงประโยคอธิบาย admin-submit ยาว 1 บรรทัดปนกับปุ่ม Reject/Approve (เหมือนที่พบใน UAT-43) — ควรพิจารณาซ่อนเมื่อโหมด Admin ปิด · เมล 'ถูกตีกลับ' 03:11 ถึงพรทิพย์ = หลักฐานเมลของเคสนี้ (แยกจากฉบับ 02:58 ของ UAT-38/48) · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เมล 'ถูกตีกลับ' 03:12 To Pornthip Cc Laddawan; CMAN_PowerBI เหตุผล 'ขอทบทวนตัวเลขใหม่ (UAT Round 1)' ตรงทุกตัวอักษร → Expected ข้อ 4 ผ่านแล้ว · ประโยคอธิบาย admin-submit ที่ปนบนแถบอนุมัติของนิภาพร/วราพร (admin) แม้ปิดโหมด Admin — jakkaritw ตัดสิน 2026-09-09 ว่ายอมรับได้ ไม่เปิด defect · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:12 AM — ถูกตีกลับ (Data &amp; Analytic, ตีกลับจากขั้น 2) → pornthipp · cc laddawank</t>
         </is>
       </c>
       <c r="F50" s="55" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="E51" s="55" t="inlineStr">
         <is>
-          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ</t>
+          <t>เวลากด Submit จริง = 03:16 — คนตรวจกล่องจดหมาย Laddawan เทียบเวลาอีเมล 'รอการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ฉบับล่าสุด (ฉบับก่อนหน้าของฝ่ายนี้: 02:36 และ 03:01 (ทั้งคู่ยืนยันแล้วจากภาพหน้าจอ)) · จากหลักฐานรอบก่อน อีเมลถึงภายใน ~1 นาที · ยืนยันจากภาพหน้าจอ: รอบ 02:36 และ 03:01 เมลถึงลัดดาวัลย์ในนาทีเดียวกับที่กด Submit · รอบ 03:16 ยังรอดู · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นฉบับ 'รอการอนุมัติ … Data &amp; Analytic … 2027' To Laddawan Kearnoi Cc CMAN_PowerBI: เนื้อหาครบ ฝ่าย / ปีงบประมาณ 2027 (หน้าจอ: Year 2026) / ผู้ส่ง pornthipp@chememan.com / สถานะ 'รอการอนุมัติจากท่าน' + ลิงก์ 'คลิกที่นี่เพื่อตรวจสอบและอนุมัติ' อักษรไทยครบ · เวลาในภาพถูกตัด — ยังเทียบ latency รอบ 03:16 ไม่ได้ (รอบ 02:36/03:01 ตรงนาทีจากภาพเมื่อเช้า) · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → 3 รอบ Submit ของ D&amp;A: กด 02:36→เมล 02:36, กด 03:01→เมล 03:01, กด 03:16→เมล 03:17 — latency ≤ 1 นาทีทุกรอบ · เนื้อหา/ลิงก์ตรวจแล้วจากภาพฉบับเต็ม → ผ่านทุกข้อ · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:17 AM — รอการอนุมัติ (Data &amp; Analytic, ส่งใหม่หลังตีกลับขั้น 2) → laddawank · (ฉบับก่อนหน้าของฝ่ายนี้: Wed 2:36 AM และ Wed 3:01 AM → laddawank)</t>
         </is>
       </c>
       <c r="F51" s="55" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest)</t>
+          <t>ผ่าน · ฉบับ 02:58 ของเคสนี้เองไม่ได้เปิดดูเนื้อหา แต่เป็น template เดียวกับ 03:12 ที่ตรวจแล้ว และเหตุผล 'UAT Round 1 — ขอทบทวนตัวเลขหมวดค่าเดินทางใหม่' ถูกพิมพ์โดย AI ตรงกับ UAT-38 · cc มีสำเนาเก็บ cmanpowerbi ครบ (ข้อกังวลเรื่องสำเนาหายตกไป) · ไทม์ไลน์เมลจริงจากรายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ): 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 2:58 AM — ถูกตีกลับ (Data &amp; Analytic) → pornthipp · cc laddawank  (ฉบับที่เคสนี้ใช้; อย่าสับกับ Wed 3:12 AM ซึ่งเป็นของ UAT-41)</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="E53" s="55" t="inlineStr">
         <is>
-          <t>jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง</t>
+          <t>jakkaritw ตัดสิน 2026-09-09: รับสภาพ 'หน้าจออังกฤษ / อีเมลไทย' ได้ → Pass ไม่เปิดคำขอเปลี่ยนแปลง · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — ใช้อีเมลฉบับใดก็ได้ข้างต้นเป็นตัวอย่าง — ประเด็นคือหัวข้อ/เนื้อหาเป็นภาษาไทยขณะหน้าจอเป็นอังกฤษ</t>
         </is>
       </c>
       <c r="F53" s="55" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="E54" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ</t>
+          <t>คนตรวจ: (1) Nipaporn ได้ 'รอการอนุมัติ … Data &amp; Analytic … 2027' ~03:18 (และอีกฉบับ ~03:06 จากรอบก่อนตีกลับ) (2) Waraporn ได้ฉบับเดียว ~03:18-03:19 ไม่มีฉบับก่อนหน้า (3) Pornthip ได้ 'ได้รับการอนุมัติ … 2027' ฉบับเดียว ~03:21 cc laddawank + cmanpowerbi · ฉบับที่ (3) ใช้ต่อใน UAT-49 · ยังไม่มีหลักฐานเมลจริงสำหรับ 03:06 / 03:18 / 03:18–19 / 03:21 · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] เห็นครบทั้ง 3 แบบ: (1) 'รอการอนุมัติ' To Nipaporn Tongking Cc CMAN_PowerBI (2) 'รอการอนุมัติ' To Waraporn Tirasit Cc CMAN_PowerBI (3) 'ได้รับการอนุมัติ … 2027' To Pornthip Phermsaphiran Cc Laddawan Kearnoi; CMAN_PowerBI เนื้อความ 'งบประมาณของท่านได้รับการอนุมัติครบทุกขั้นแล้ว' สถานะ 'อนุมัติครบทุกขั้นแล้ว' (สีเขียว) ลิงก์ 'คลิกที่นี่เพื่อดูรายละเอียด' · ยังขาด: เวลาถึงของแต่ละฉบับ (ถูกตัดในภาพ) และการยืนยันว่าวราพรได้ 'ฉบับเดียว ไม่มีก่อนหน้า' ต้องดูจากรายการกล่องจดหมาย · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ไทม์ไลน์เมลจริง: 02:36 รอ D&amp;A · 02:45 รอ SD · 02:49 รอ SD · 02:51 ตีกลับ SD · 02:58 ตีกลับ D&amp;A · 03:01 รอ D&amp;A · 03:08 รอ D&amp;A · 03:12 ตีกลับ D&amp;A · 03:17 รอ D&amp;A · 03:18 รอ D&amp;A · 03:19 รอ D&amp;A · 03:22 ได้รับการอนุมัติ D&amp;A · 14:26 รอ SD · 14:27 ตีกลับ SD (retest) → เมล 'รอการอนุมัติ D&amp;A' มี 6 ฉบับพอดี = ลัดดาวัลย์ 3 (02:36, 03:01, 03:17) + นิภาพร 2 (03:08 หลังขั้น 1 อนุมัติ 03:06, 03:18 หลังขั้น 1 อนุมัติ 03:18) + วราพร 1 (03:19 หลังขั้น 2 อนุมัติ) — วราพรได้ฉบับเดียว ไม่มีฉบับก่อนหน้า = ไม่ส่งล่วงหน้า ไม่ข้ามขั้น · 'ได้รับการอนุมัติ' 03:22 ฉบับเดียว (กด 03:21) To พรทิพย์ cc ลัดดาวัลย์ + cmanpowerbi → ผ่านทั้ง 3 ข้อ · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:18 AM — รอการอนุมัติ (หลังอนุมัติขั้น 1) → nipapornt · Wed 3:19 AM — รอการอนุมัติ (หลังอนุมัติขั้น 2) → warapornt · Wed 3:22 AM — ได้รับการอนุมัติ (ครบทุกขั้น) → pornthipp · cc laddawank, cmanpowerbi</t>
         </is>
       </c>
       <c r="F54" s="55" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="E55" s="55" t="inlineStr">
         <is>
-          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง</t>
+          <t>คนตรวจฉบับ 'ได้รับการอนุมัติ … 2027' ที่ Pornthip ได้ ~03:21: To pornthipp / Cc laddawank + cmanpowerbi, สถานะ 'อนุมัติครบทุกขั้นแล้ว', Inbox ไม่ใช่ Junk, และเปิดบนมือถือ 1 ครั้ง (ข้อค้างจาก SIT) · ยังไม่มีหลักฐานเมลฉบับ 'ได้รับการอนุมัติ' 03:21 จริง (To/CC/เนื้อหา/Junk/มือถือ) · [ตรวจอีเมล 09/09 บ่าย] หลักฐานจริงที่มี = ภาพหน้าจอ Outlook ของ jakkaritw เมื่อเช้า (เห็นเมล 02:36, 02:45, 02:49, 02:51, 02:58, 03:01) · เมลช่วง 03:06–03:21 ยังไม่มีใครเห็นจริง · การเข้า shared mailbox cmanpowerbi@chememan.com ผ่าน Claude ตอบ 404/FORBIDDEN = บัญชี jakkaritw ไม่มีสิทธิ์ Full Access ต้องขอจาก Exchange admin หรือให้เจ้าตัวเปิดกล่องเอง · รายงานจาก session อื่นที่สรุปว่า 'ผ่าน' เป็นการเทียบกับตารางคาดการณ์ ไม่ใช่หลักฐานจากกล่องจดหมาย จึงไม่เปลี่ยน Status · [ภาพอีเมลจริงจาก jakkaritw 09/09 ~16:00] จากฉบับ 'ได้รับการอนุมัติ': ข้อ 1 ผู้ส่ง CMAN_PowerBI ✓ · ข้อ 2 To pornthipp, CC laddawank + cmanpowerbi ✓ · ข้อ 3 หัวข้อ 'ได้รับการอนุมัติ งบประมาณของฝ่าย Data &amp; Analytic ปีงบประมาณ 2027' ✓ · ข้อ 4 ฝ่าย / 2027 / 'อนุมัติครบทุกขั้นแล้ว' ✓ · ข้อ 6 อักษรไทยครบบนคอมพิวเตอร์ ✓ · ข้อ 8 '2027 (หน้าจอ: Year 2026)' ✓ · ข้อ 5 ลิงก์ทดสอบแล้วโดย AI ✓ · เหลือข้อ 7 (Inbox ไม่ตก Junk — ภาพเปิดจากกล่องจดหมายปกติ น่าจะผ่าน ให้เจ้าตัวยืนยัน) และเปิดบนมือถือ 1 ครั้ง · [รายการกล่องจดหมาย CMAN_PowerBI (cc ทุกฉบับ) ภาพจาก jakkaritw 09/09 ~16:10] ฉบับ 'ได้รับการอนุมัติ' อยู่ในรายการกล่องจดหมายปกติ 03:22 (Inbox ไม่ตก Junk สำหรับกล่อง cmanpowerbi) · ยังเหลือเปิดบนมือถือ 1 ครั้ง และยืนยัน Inbox ของพรทิพย์เอง · 📧 อ้างอิงอีเมล (ทุกฉบับผู้ส่ง = CMAN_PowerBI cmanpowerbi@chememan.com · วันที่ = พุธ 9 ก.ย. 2026 · ชื่อ jakkaritw ไม่อยู่ทั้ง To/CC จึงต้องเปิดกล่อง cmanpowerbi หรือกล่องผู้รับ) — Wed 3:22 AM — ได้รับการอนุมัติ (Data &amp; Analytic) → pornthipp · cc laddawank, cmanpowerbi  (ฉบับที่เคสนี้ใช้)</t>
         </is>
       </c>
       <c r="F55" s="55" t="inlineStr">
